--- a/docs/rest-api.xlsx
+++ b/docs/rest-api.xlsx
@@ -109,7 +109,7 @@
     <t>Update user</t>
   </si>
   <si>
-    <t>PUT</t>
+    <t>PATCH</t>
   </si>
   <si>
     <t>UserUpdateDTO</t>
@@ -806,17 +806,6 @@
     <font>
       <b val="1"/>
       <sz val="12"/>
-      <color indexed="12"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color indexed="12"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <sz val="12"/>
       <color indexed="13"/>
       <name val="Aptos Narrow"/>
     </font>
@@ -826,18 +815,29 @@
       <name val="Aptos Narrow"/>
     </font>
     <font>
+      <b val="1"/>
       <sz val="12"/>
-      <color indexed="16"/>
+      <color indexed="14"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="14"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color indexed="17"/>
       <name val="Aptos Narrow"/>
     </font>
     <font>
       <b val="1"/>
       <sz val="12"/>
-      <color indexed="16"/>
+      <color indexed="17"/>
       <name val="Aptos Narrow"/>
     </font>
   </fonts>
-  <fills count="6">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -846,13 +846,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="10"/>
+        <fgColor indexed="9"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="14"/>
+        <fgColor indexed="11"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
@@ -864,12 +864,18 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor indexed="17"/>
+        <fgColor indexed="16"/>
+        <bgColor auto="1"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor indexed="18"/>
         <bgColor auto="1"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="17">
+  <borders count="27">
     <border>
       <left/>
       <right/>
@@ -879,10 +885,10 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
         <color indexed="8"/>
@@ -894,22 +900,22 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right/>
       <top style="thin">
@@ -930,22 +936,22 @@
     <border>
       <left/>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top/>
       <bottom/>
@@ -953,7 +959,7 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right/>
       <top/>
@@ -969,119 +975,227 @@
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top/>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right/>
+      <top/>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </left>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </left>
       <right style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </top>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
       <left style="thin">
-        <color indexed="9"/>
+        <color indexed="12"/>
       </left>
       <right style="thin">
-        <color indexed="11"/>
+        <color indexed="10"/>
       </right>
       <top style="thin">
-        <color indexed="9"/>
+        <color indexed="10"/>
       </top>
       <bottom style="thin">
-        <color indexed="11"/>
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
+      <right style="thin">
+        <color indexed="12"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="12"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1091,41 +1205,68 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="3" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="3" fillId="2" borderId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="3" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="6" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="7" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="2" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="3" borderId="8" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="49" fontId="0" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="0" fillId="2" borderId="9" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
@@ -1155,85 +1296,94 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="7" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="3" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" fillId="4" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="6" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="8" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="3" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="11" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="12" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="13" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="14" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="15" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" borderId="16" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="23" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="24" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="25" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="10" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="9" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" borderId="10" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -1253,6 +1403,7 @@
       <rgbColor rgb="ffff00ff"/>
       <rgbColor rgb="ff00ffff"/>
       <rgbColor rgb="ff000000"/>
+      <rgbColor rgb="ffffffff"/>
       <rgbColor rgb="ffaaaaaa"/>
       <rgbColor rgb="ffd8d8d8"/>
       <rgbColor rgb="ffa7a7a7"/>
@@ -1412,9 +1563,9 @@
         </a:effectStyle>
         <a:effectStyle>
           <a:effectLst>
-            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+            <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
               <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
+                <a:alpha val="35000"/>
               </a:srgbClr>
             </a:outerShdw>
           </a:effectLst>
@@ -1478,12 +1629,12 @@
         <a:solidFill>
           <a:srgbClr val="FFFFFF"/>
         </a:solidFill>
-        <a:ln w="19050" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst>
           <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
@@ -1494,7 +1645,7 @@
         </a:effectLst>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="ctr" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -1521,10 +1672,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow"/>
-            <a:ea typeface="Aptos Narrow"/>
-            <a:cs typeface="Aptos Narrow"/>
-            <a:sym typeface="Aptos Narrow"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -1763,17 +1914,17 @@
     <a:lnDef>
       <a:spPr>
         <a:noFill/>
-        <a:ln w="19050" cap="flat">
+        <a:ln w="25400" cap="flat">
           <a:solidFill>
             <a:schemeClr val="accent1"/>
           </a:solidFill>
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
+          <a:round/>
         </a:ln>
         <a:effectLst>
-          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="20000" dir="5400000">
+          <a:outerShdw sx="100000" sy="100000" kx="0" ky="0" algn="b" rotWithShape="0" blurRad="38100" dist="23000" dir="5400000">
             <a:srgbClr val="000000">
-              <a:alpha val="38000"/>
+              <a:alpha val="35000"/>
             </a:srgbClr>
           </a:outerShdw>
         </a:effectLst>
@@ -2051,7 +2202,7 @@
         <a:effectLst/>
         <a:sp3d/>
       </a:spPr>
-      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45719" tIns="45719" rIns="45719" bIns="45719" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
+      <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="overflow" horzOverflow="overflow" vert="horz" wrap="square" lIns="45718" tIns="45718" rIns="45718" bIns="45718" numCol="1" spcCol="38100" rtlCol="0" anchor="t" upright="0">
         <a:spAutoFit/>
       </a:bodyPr>
       <a:lstStyle>
@@ -2078,10 +2229,10 @@
             </a:solidFill>
             <a:effectLst/>
             <a:uFillTx/>
-            <a:latin typeface="Aptos Narrow"/>
-            <a:ea typeface="Aptos Narrow"/>
-            <a:cs typeface="Aptos Narrow"/>
-            <a:sym typeface="Aptos Narrow"/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+            <a:sym typeface="Helvetica Neue"/>
           </a:defRPr>
         </a:defPPr>
         <a:lvl1pPr marL="0" marR="0" indent="0" algn="l" defTabSz="914400" rtl="0" fontAlgn="auto" latinLnBrk="1" hangingPunct="0">
@@ -2323,13 +2474,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="30.6719" style="1" customWidth="1"/>
     <col min="2" max="2" width="35" style="1" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="1" customWidth="1"/>
-    <col min="4" max="4" width="49.75" style="1" customWidth="1"/>
+    <col min="4" max="4" width="49.8516" style="1" customWidth="1"/>
     <col min="5" max="5" width="25.8516" style="1" customWidth="1"/>
     <col min="6" max="6" width="34.1719" style="1" customWidth="1"/>
     <col min="7" max="7" width="24.1719" style="1" customWidth="1"/>
@@ -2527,6 +2678,39 @@
       </c>
       <c r="I7" s="3"/>
     </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
@@ -2538,3400 +2722,3424 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A2:W99"/>
+  <dimension ref="A1:W99"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23.0547" style="20" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="20" customWidth="1"/>
-    <col min="3" max="3" width="21.8516" style="20" customWidth="1"/>
-    <col min="4" max="4" width="11" style="20" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="20" customWidth="1"/>
-    <col min="6" max="6" width="15.3516" style="20" customWidth="1"/>
-    <col min="7" max="7" width="21.8516" style="20" customWidth="1"/>
-    <col min="8" max="8" width="11" style="20" customWidth="1"/>
-    <col min="9" max="9" width="24.3516" style="20" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="20" customWidth="1"/>
-    <col min="11" max="11" width="21.8516" style="20" customWidth="1"/>
-    <col min="12" max="12" width="11" style="20" customWidth="1"/>
-    <col min="13" max="13" width="27.5" style="20" customWidth="1"/>
-    <col min="14" max="14" width="16.5" style="20" customWidth="1"/>
-    <col min="15" max="15" width="22.1719" style="20" customWidth="1"/>
-    <col min="16" max="16" width="11" style="20" customWidth="1"/>
-    <col min="17" max="17" width="23.5" style="20" customWidth="1"/>
-    <col min="18" max="18" width="11" style="20" customWidth="1"/>
-    <col min="19" max="19" width="10" style="20" customWidth="1"/>
-    <col min="20" max="20" width="11" style="20" customWidth="1"/>
-    <col min="21" max="21" width="23.5" style="20" customWidth="1"/>
-    <col min="22" max="23" width="11" style="20" customWidth="1"/>
-    <col min="24" max="16384" width="11" style="20" customWidth="1"/>
+    <col min="1" max="1" width="23" style="29" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="29" customWidth="1"/>
+    <col min="3" max="3" width="21.8516" style="29" customWidth="1"/>
+    <col min="4" max="4" width="11" style="29" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="29" customWidth="1"/>
+    <col min="6" max="6" width="15.3516" style="29" customWidth="1"/>
+    <col min="7" max="7" width="21.8516" style="29" customWidth="1"/>
+    <col min="8" max="8" width="11" style="29" customWidth="1"/>
+    <col min="9" max="9" width="24.3516" style="29" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="29" customWidth="1"/>
+    <col min="11" max="11" width="21.8516" style="29" customWidth="1"/>
+    <col min="12" max="12" width="11" style="29" customWidth="1"/>
+    <col min="13" max="13" width="27.5" style="29" customWidth="1"/>
+    <col min="14" max="14" width="16.5" style="29" customWidth="1"/>
+    <col min="15" max="15" width="22.1719" style="29" customWidth="1"/>
+    <col min="16" max="16" width="11" style="29" customWidth="1"/>
+    <col min="17" max="17" width="23.5" style="29" customWidth="1"/>
+    <col min="18" max="18" width="11" style="29" customWidth="1"/>
+    <col min="19" max="19" width="10" style="29" customWidth="1"/>
+    <col min="20" max="20" width="11" style="29" customWidth="1"/>
+    <col min="21" max="21" width="23.5" style="29" customWidth="1"/>
+    <col min="22" max="23" width="11" style="29" customWidth="1"/>
+    <col min="24" max="16384" width="11" style="29" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="6.35" customHeight="1"/>
+    <row r="1" ht="8" customHeight="1">
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
+      <c r="W1" s="32"/>
+    </row>
     <row r="2" ht="29.55" customHeight="1">
-      <c r="A2" t="s" s="21">
+      <c r="A2" t="s" s="33">
         <v>104</v>
       </c>
-      <c r="B2" s="22"/>
-      <c r="C2" s="22"/>
-      <c r="D2" s="22"/>
-      <c r="E2" s="22"/>
-      <c r="F2" s="22"/>
-      <c r="G2" s="22"/>
-      <c r="H2" s="22"/>
-      <c r="I2" s="22"/>
-      <c r="J2" s="22"/>
-      <c r="K2" s="22"/>
-      <c r="L2" s="22"/>
-      <c r="M2" s="22"/>
-      <c r="N2" s="22"/>
-      <c r="O2" s="22"/>
-      <c r="P2" s="22"/>
-      <c r="Q2" s="22"/>
-      <c r="R2" s="22"/>
-      <c r="S2" s="22"/>
-      <c r="T2" s="22"/>
-      <c r="U2" s="22"/>
-      <c r="V2" s="22"/>
-      <c r="W2" s="22"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="34"/>
+      <c r="D2" s="34"/>
+      <c r="E2" s="34"/>
+      <c r="F2" s="34"/>
+      <c r="G2" s="34"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="34"/>
+      <c r="J2" s="34"/>
+      <c r="K2" s="34"/>
+      <c r="L2" s="34"/>
+      <c r="M2" s="34"/>
+      <c r="N2" s="34"/>
+      <c r="O2" s="34"/>
+      <c r="P2" s="34"/>
+      <c r="Q2" s="34"/>
+      <c r="R2" s="34"/>
+      <c r="S2" s="34"/>
+      <c r="T2" s="34"/>
+      <c r="U2" s="34"/>
+      <c r="V2" s="34"/>
+      <c r="W2" s="34"/>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" t="s" s="23">
+      <c r="A3" t="s" s="35">
         <v>36</v>
       </c>
-      <c r="B3" t="s" s="23">
+      <c r="B3" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="C3" t="s" s="23">
+      <c r="C3" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="D3" s="24"/>
-      <c r="E3" t="s" s="23">
+      <c r="D3" s="36"/>
+      <c r="E3" t="s" s="35">
         <v>37</v>
       </c>
-      <c r="F3" t="s" s="23">
+      <c r="F3" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="G3" t="s" s="23">
+      <c r="G3" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="H3" s="24"/>
-      <c r="I3" t="s" s="25">
+      <c r="H3" s="36"/>
+      <c r="I3" t="s" s="37">
         <v>107</v>
       </c>
-      <c r="J3" t="s" s="25">
+      <c r="J3" t="s" s="37">
         <v>105</v>
       </c>
-      <c r="K3" t="s" s="25">
+      <c r="K3" t="s" s="37">
         <v>106</v>
       </c>
-      <c r="L3" s="22"/>
-      <c r="M3" s="22"/>
-      <c r="N3" s="22"/>
-      <c r="O3" s="22"/>
-      <c r="P3" s="22"/>
-      <c r="Q3" s="22"/>
-      <c r="R3" s="22"/>
-      <c r="S3" s="22"/>
-      <c r="T3" s="22"/>
-      <c r="U3" s="22"/>
-      <c r="V3" s="22"/>
-      <c r="W3" s="22"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
+      <c r="N3" s="34"/>
+      <c r="O3" s="34"/>
+      <c r="P3" s="34"/>
+      <c r="Q3" s="34"/>
+      <c r="R3" s="34"/>
+      <c r="S3" s="34"/>
+      <c r="T3" s="34"/>
+      <c r="U3" s="34"/>
+      <c r="V3" s="34"/>
+      <c r="W3" s="34"/>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" t="s" s="26">
+      <c r="A4" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="B4" t="s" s="26">
+      <c r="B4" t="s" s="38">
         <v>109</v>
       </c>
-      <c r="C4" t="s" s="26">
+      <c r="C4" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="D4" s="24"/>
-      <c r="E4" t="s" s="26">
+      <c r="D4" s="36"/>
+      <c r="E4" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="F4" t="s" s="26">
+      <c r="F4" t="s" s="38">
         <v>111</v>
       </c>
-      <c r="G4" t="s" s="26">
+      <c r="G4" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="H4" s="24"/>
-      <c r="I4" t="s" s="27">
+      <c r="H4" s="36"/>
+      <c r="I4" t="s" s="39">
         <v>112</v>
       </c>
-      <c r="J4" t="s" s="27">
+      <c r="J4" t="s" s="39">
         <v>111</v>
       </c>
-      <c r="K4" t="s" s="27">
+      <c r="K4" t="s" s="39">
         <v>110</v>
       </c>
-      <c r="L4" s="22"/>
-      <c r="M4" s="22"/>
-      <c r="N4" s="22"/>
-      <c r="O4" s="22"/>
-      <c r="P4" s="22"/>
-      <c r="Q4" s="22"/>
-      <c r="R4" s="22"/>
-      <c r="S4" s="22"/>
-      <c r="T4" s="22"/>
-      <c r="U4" s="22"/>
-      <c r="V4" s="22"/>
-      <c r="W4" s="22"/>
+      <c r="L4" s="34"/>
+      <c r="M4" s="34"/>
+      <c r="N4" s="34"/>
+      <c r="O4" s="34"/>
+      <c r="P4" s="34"/>
+      <c r="Q4" s="34"/>
+      <c r="R4" s="34"/>
+      <c r="S4" s="34"/>
+      <c r="T4" s="34"/>
+      <c r="U4" s="34"/>
+      <c r="V4" s="34"/>
+      <c r="W4" s="34"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="24"/>
-      <c r="B5" t="s" s="28">
+      <c r="A5" s="36"/>
+      <c r="B5" t="s" s="40">
         <v>113</v>
       </c>
-      <c r="C5" t="s" s="28">
+      <c r="C5" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="D5" s="24"/>
-      <c r="E5" s="24"/>
-      <c r="F5" t="s" s="28">
+      <c r="D5" s="36"/>
+      <c r="E5" s="36"/>
+      <c r="F5" t="s" s="40">
         <v>114</v>
       </c>
-      <c r="G5" t="s" s="28">
+      <c r="G5" t="s" s="40">
         <v>115</v>
       </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="29"/>
-      <c r="J5" t="s" s="30">
+      <c r="H5" s="36"/>
+      <c r="I5" s="41"/>
+      <c r="J5" t="s" s="42">
         <v>114</v>
       </c>
-      <c r="K5" t="s" s="30">
+      <c r="K5" t="s" s="42">
         <v>115</v>
       </c>
-      <c r="L5" s="22"/>
-      <c r="M5" s="22"/>
-      <c r="N5" s="22"/>
-      <c r="O5" s="22"/>
-      <c r="P5" s="22"/>
-      <c r="Q5" s="22"/>
-      <c r="R5" s="22"/>
-      <c r="S5" s="22"/>
-      <c r="T5" s="22"/>
-      <c r="U5" s="22"/>
-      <c r="V5" s="22"/>
-      <c r="W5" s="22"/>
+      <c r="L5" s="34"/>
+      <c r="M5" s="34"/>
+      <c r="N5" s="34"/>
+      <c r="O5" s="34"/>
+      <c r="P5" s="34"/>
+      <c r="Q5" s="34"/>
+      <c r="R5" s="34"/>
+      <c r="S5" s="34"/>
+      <c r="T5" s="34"/>
+      <c r="U5" s="34"/>
+      <c r="V5" s="34"/>
+      <c r="W5" s="34"/>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="31"/>
-      <c r="B6" s="31"/>
-      <c r="C6" s="31"/>
-      <c r="D6" s="24"/>
-      <c r="E6" s="31"/>
-      <c r="F6" t="s" s="26">
+      <c r="A6" s="43"/>
+      <c r="B6" s="43"/>
+      <c r="C6" s="43"/>
+      <c r="D6" s="36"/>
+      <c r="E6" s="43"/>
+      <c r="F6" t="s" s="38">
         <v>116</v>
       </c>
-      <c r="G6" t="s" s="26">
+      <c r="G6" t="s" s="38">
         <v>40</v>
       </c>
-      <c r="H6" s="24"/>
-      <c r="I6" s="32"/>
-      <c r="J6" s="32"/>
-      <c r="K6" s="32"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
-      <c r="O6" s="22"/>
-      <c r="P6" s="22"/>
-      <c r="Q6" s="22"/>
-      <c r="R6" s="22"/>
-      <c r="S6" s="22"/>
-      <c r="T6" s="22"/>
-      <c r="U6" s="22"/>
-      <c r="V6" s="22"/>
-      <c r="W6" s="22"/>
+      <c r="H6" s="36"/>
+      <c r="I6" s="44"/>
+      <c r="J6" s="44"/>
+      <c r="K6" s="44"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
+      <c r="Q6" s="34"/>
+      <c r="R6" s="34"/>
+      <c r="S6" s="34"/>
+      <c r="T6" s="34"/>
+      <c r="U6" s="34"/>
+      <c r="V6" s="34"/>
+      <c r="W6" s="34"/>
     </row>
     <row r="7" ht="70.65" customHeight="1">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="22"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="22"/>
-      <c r="O7" s="22"/>
-      <c r="P7" s="22"/>
-      <c r="Q7" s="22"/>
-      <c r="R7" s="22"/>
-      <c r="S7" s="22"/>
-      <c r="T7" s="22"/>
-      <c r="U7" s="22"/>
-      <c r="V7" s="22"/>
-      <c r="W7" s="22"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="34"/>
+      <c r="E7" s="34"/>
+      <c r="F7" s="34"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="34"/>
+      <c r="I7" s="34"/>
+      <c r="J7" s="34"/>
+      <c r="K7" s="34"/>
+      <c r="L7" s="34"/>
+      <c r="M7" s="34"/>
+      <c r="N7" s="34"/>
+      <c r="O7" s="34"/>
+      <c r="P7" s="34"/>
+      <c r="Q7" s="34"/>
+      <c r="R7" s="34"/>
+      <c r="S7" s="34"/>
+      <c r="T7" s="34"/>
+      <c r="U7" s="34"/>
+      <c r="V7" s="34"/>
+      <c r="W7" s="34"/>
     </row>
     <row r="8" ht="34" customHeight="1">
-      <c r="A8" t="s" s="21">
+      <c r="A8" t="s" s="33">
         <v>117</v>
       </c>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="22"/>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="22"/>
-      <c r="O8" s="22"/>
-      <c r="P8" s="22"/>
-      <c r="Q8" s="22"/>
-      <c r="R8" s="22"/>
-      <c r="S8" s="22"/>
-      <c r="T8" s="22"/>
-      <c r="U8" s="22"/>
-      <c r="V8" s="22"/>
-      <c r="W8" s="22"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="34"/>
+      <c r="E8" s="34"/>
+      <c r="F8" s="34"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="34"/>
+      <c r="I8" s="34"/>
+      <c r="J8" s="34"/>
+      <c r="K8" s="34"/>
+      <c r="L8" s="34"/>
+      <c r="M8" s="34"/>
+      <c r="N8" s="34"/>
+      <c r="O8" s="34"/>
+      <c r="P8" s="34"/>
+      <c r="Q8" s="34"/>
+      <c r="R8" s="34"/>
+      <c r="S8" s="34"/>
+      <c r="T8" s="34"/>
+      <c r="U8" s="34"/>
+      <c r="V8" s="34"/>
+      <c r="W8" s="34"/>
     </row>
     <row r="9" ht="17" customHeight="1">
-      <c r="A9" t="s" s="23">
+      <c r="A9" t="s" s="35">
         <v>23</v>
       </c>
-      <c r="B9" t="s" s="23">
+      <c r="B9" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="C9" t="s" s="23">
+      <c r="C9" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="D9" s="24"/>
-      <c r="E9" t="s" s="23">
+      <c r="D9" s="36"/>
+      <c r="E9" t="s" s="35">
         <v>40</v>
       </c>
-      <c r="F9" t="s" s="23">
+      <c r="F9" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="G9" t="s" s="23">
+      <c r="G9" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="H9" s="24"/>
-      <c r="I9" t="s" s="23">
+      <c r="H9" s="36"/>
+      <c r="I9" t="s" s="35">
         <v>26</v>
       </c>
-      <c r="J9" t="s" s="23">
+      <c r="J9" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="K9" t="s" s="23">
+      <c r="K9" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="L9" s="24"/>
-      <c r="M9" t="s" s="23">
+      <c r="L9" s="36"/>
+      <c r="M9" t="s" s="35">
         <v>30</v>
       </c>
-      <c r="N9" t="s" s="23">
+      <c r="N9" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="O9" t="s" s="23">
+      <c r="O9" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="P9" s="24"/>
-      <c r="Q9" s="22"/>
-      <c r="R9" s="22"/>
-      <c r="S9" s="22"/>
-      <c r="T9" s="22"/>
-      <c r="U9" s="22"/>
-      <c r="V9" s="22"/>
-      <c r="W9" s="22"/>
+      <c r="P9" s="36"/>
+      <c r="Q9" s="34"/>
+      <c r="R9" s="34"/>
+      <c r="S9" s="34"/>
+      <c r="T9" s="34"/>
+      <c r="U9" s="34"/>
+      <c r="V9" s="34"/>
+      <c r="W9" s="34"/>
     </row>
     <row r="10" ht="17" customHeight="1">
-      <c r="A10" t="s" s="26">
+      <c r="A10" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="B10" t="s" s="26">
+      <c r="B10" t="s" s="38">
         <v>118</v>
       </c>
-      <c r="C10" t="s" s="26">
+      <c r="C10" t="s" s="38">
         <v>119</v>
       </c>
-      <c r="D10" s="24"/>
-      <c r="E10" t="s" s="26">
+      <c r="D10" s="36"/>
+      <c r="E10" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="F10" t="s" s="26">
+      <c r="F10" t="s" s="38">
         <v>109</v>
       </c>
-      <c r="G10" t="s" s="26">
+      <c r="G10" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="H10" s="24"/>
-      <c r="I10" t="s" s="26">
+      <c r="H10" s="36"/>
+      <c r="I10" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="J10" t="s" s="26">
+      <c r="J10" t="s" s="38">
         <v>109</v>
       </c>
-      <c r="K10" t="s" s="26">
+      <c r="K10" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="L10" s="24"/>
-      <c r="M10" t="s" s="26">
+      <c r="L10" s="36"/>
+      <c r="M10" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="N10" t="s" s="26">
+      <c r="N10" t="s" s="38">
         <v>120</v>
       </c>
-      <c r="O10" t="s" s="26">
+      <c r="O10" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="P10" s="24"/>
-      <c r="Q10" s="22"/>
-      <c r="R10" s="22"/>
-      <c r="S10" s="22"/>
-      <c r="T10" s="22"/>
-      <c r="U10" s="22"/>
-      <c r="V10" s="22"/>
-      <c r="W10" s="22"/>
+      <c r="P10" s="36"/>
+      <c r="Q10" s="34"/>
+      <c r="R10" s="34"/>
+      <c r="S10" s="34"/>
+      <c r="T10" s="34"/>
+      <c r="U10" s="34"/>
+      <c r="V10" s="34"/>
+      <c r="W10" s="34"/>
     </row>
     <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="24"/>
-      <c r="B11" t="s" s="28">
+      <c r="A11" s="36"/>
+      <c r="B11" t="s" s="40">
         <v>121</v>
       </c>
-      <c r="C11" t="s" s="28">
+      <c r="C11" t="s" s="40">
         <v>119</v>
       </c>
-      <c r="D11" s="24"/>
-      <c r="E11" s="24"/>
-      <c r="F11" t="s" s="28">
+      <c r="D11" s="36"/>
+      <c r="E11" s="36"/>
+      <c r="F11" t="s" s="40">
         <v>122</v>
       </c>
-      <c r="G11" t="s" s="28">
+      <c r="G11" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="H11" s="24"/>
-      <c r="I11" s="24"/>
-      <c r="J11" t="s" s="28">
+      <c r="H11" s="36"/>
+      <c r="I11" s="36"/>
+      <c r="J11" t="s" s="40">
         <v>122</v>
       </c>
-      <c r="K11" t="s" s="28">
+      <c r="K11" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="L11" s="24"/>
-      <c r="M11" s="24"/>
-      <c r="N11" t="s" s="28">
+      <c r="L11" s="36"/>
+      <c r="M11" s="36"/>
+      <c r="N11" t="s" s="40">
         <v>123</v>
       </c>
-      <c r="O11" t="s" s="28">
+      <c r="O11" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="P11" s="24"/>
-      <c r="Q11" s="22"/>
-      <c r="R11" s="22"/>
-      <c r="S11" s="22"/>
-      <c r="T11" s="22"/>
-      <c r="U11" s="22"/>
-      <c r="V11" s="22"/>
-      <c r="W11" s="22"/>
+      <c r="P11" s="36"/>
+      <c r="Q11" s="34"/>
+      <c r="R11" s="34"/>
+      <c r="S11" s="34"/>
+      <c r="T11" s="34"/>
+      <c r="U11" s="34"/>
+      <c r="V11" s="34"/>
+      <c r="W11" s="34"/>
     </row>
     <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="31"/>
-      <c r="B12" t="s" s="26">
+      <c r="A12" s="43"/>
+      <c r="B12" t="s" s="38">
         <v>124</v>
       </c>
-      <c r="C12" t="s" s="26">
+      <c r="C12" t="s" s="38">
         <v>115</v>
       </c>
-      <c r="D12" s="24"/>
-      <c r="E12" s="31"/>
-      <c r="F12" t="s" s="26">
+      <c r="D12" s="36"/>
+      <c r="E12" s="43"/>
+      <c r="F12" t="s" s="38">
         <v>125</v>
       </c>
-      <c r="G12" t="s" s="26">
+      <c r="G12" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="H12" s="24"/>
-      <c r="I12" s="31"/>
-      <c r="J12" t="s" s="26">
+      <c r="H12" s="36"/>
+      <c r="I12" s="43"/>
+      <c r="J12" t="s" s="38">
         <v>125</v>
       </c>
-      <c r="K12" t="s" s="26">
+      <c r="K12" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="L12" s="24"/>
-      <c r="M12" s="31"/>
-      <c r="N12" t="s" s="26">
+      <c r="L12" s="36"/>
+      <c r="M12" s="43"/>
+      <c r="N12" t="s" s="38">
         <v>126</v>
       </c>
-      <c r="O12" t="s" s="26">
+      <c r="O12" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="P12" s="24"/>
-      <c r="Q12" s="22"/>
-      <c r="R12" s="22"/>
-      <c r="S12" s="22"/>
-      <c r="T12" s="22"/>
-      <c r="U12" s="22"/>
-      <c r="V12" s="22"/>
-      <c r="W12" s="22"/>
+      <c r="P12" s="36"/>
+      <c r="Q12" s="34"/>
+      <c r="R12" s="34"/>
+      <c r="S12" s="34"/>
+      <c r="T12" s="34"/>
+      <c r="U12" s="34"/>
+      <c r="V12" s="34"/>
+      <c r="W12" s="34"/>
     </row>
     <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="24"/>
-      <c r="B13" t="s" s="28">
+      <c r="A13" s="36"/>
+      <c r="B13" t="s" s="40">
         <v>127</v>
       </c>
-      <c r="C13" t="s" s="28">
+      <c r="C13" t="s" s="40">
         <v>119</v>
       </c>
-      <c r="D13" s="24"/>
-      <c r="E13" s="24"/>
-      <c r="F13" t="s" s="28">
+      <c r="D13" s="36"/>
+      <c r="E13" s="36"/>
+      <c r="F13" t="s" s="40">
         <v>128</v>
       </c>
-      <c r="G13" t="s" s="28">
+      <c r="G13" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="H13" s="24"/>
-      <c r="I13" s="24"/>
-      <c r="J13" t="s" s="28">
+      <c r="H13" s="36"/>
+      <c r="I13" s="36"/>
+      <c r="J13" t="s" s="40">
         <v>128</v>
       </c>
-      <c r="K13" t="s" s="28">
+      <c r="K13" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="L13" s="24"/>
-      <c r="M13" s="24"/>
-      <c r="N13" t="s" s="28">
+      <c r="L13" s="36"/>
+      <c r="M13" s="36"/>
+      <c r="N13" t="s" s="40">
         <v>129</v>
       </c>
-      <c r="O13" t="s" s="28">
+      <c r="O13" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="P13" s="24"/>
-      <c r="Q13" s="22"/>
-      <c r="R13" s="22"/>
-      <c r="S13" s="22"/>
-      <c r="T13" s="22"/>
-      <c r="U13" s="22"/>
-      <c r="V13" s="22"/>
-      <c r="W13" s="22"/>
+      <c r="P13" s="36"/>
+      <c r="Q13" s="34"/>
+      <c r="R13" s="34"/>
+      <c r="S13" s="34"/>
+      <c r="T13" s="34"/>
+      <c r="U13" s="34"/>
+      <c r="V13" s="34"/>
+      <c r="W13" s="34"/>
     </row>
     <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="31"/>
-      <c r="B14" t="s" s="26">
+      <c r="A14" s="43"/>
+      <c r="B14" t="s" s="38">
         <v>130</v>
       </c>
-      <c r="C14" t="s" s="26">
+      <c r="C14" t="s" s="38">
         <v>115</v>
       </c>
-      <c r="D14" s="24"/>
-      <c r="E14" s="31"/>
-      <c r="F14" t="s" s="26">
+      <c r="D14" s="36"/>
+      <c r="E14" s="43"/>
+      <c r="F14" t="s" s="38">
         <v>113</v>
       </c>
-      <c r="G14" t="s" s="26">
+      <c r="G14" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="H14" s="24"/>
-      <c r="I14" s="31"/>
-      <c r="J14" t="s" s="26">
+      <c r="H14" s="36"/>
+      <c r="I14" s="43"/>
+      <c r="J14" t="s" s="38">
         <v>113</v>
       </c>
-      <c r="K14" t="s" s="26">
+      <c r="K14" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="L14" s="24"/>
-      <c r="M14" s="31"/>
-      <c r="N14" t="s" s="26">
+      <c r="L14" s="36"/>
+      <c r="M14" s="43"/>
+      <c r="N14" t="s" s="38">
         <v>131</v>
       </c>
-      <c r="O14" t="s" s="26">
+      <c r="O14" t="s" s="38">
         <v>132</v>
       </c>
-      <c r="P14" s="24"/>
-      <c r="Q14" s="22"/>
-      <c r="R14" s="22"/>
-      <c r="S14" s="22"/>
-      <c r="T14" s="22"/>
-      <c r="U14" s="22"/>
-      <c r="V14" s="22"/>
-      <c r="W14" s="22"/>
+      <c r="P14" s="36"/>
+      <c r="Q14" s="34"/>
+      <c r="R14" s="34"/>
+      <c r="S14" s="34"/>
+      <c r="T14" s="34"/>
+      <c r="U14" s="34"/>
+      <c r="V14" s="34"/>
+      <c r="W14" s="34"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="24"/>
-      <c r="B15" t="s" s="28">
+      <c r="A15" s="36"/>
+      <c r="B15" t="s" s="40">
         <v>109</v>
       </c>
-      <c r="C15" t="s" s="28">
+      <c r="C15" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="D15" s="24"/>
-      <c r="E15" s="24"/>
-      <c r="F15" t="s" s="28">
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" t="s" s="40">
         <v>133</v>
       </c>
-      <c r="G15" t="s" s="28">
+      <c r="G15" t="s" s="40">
         <v>132</v>
       </c>
-      <c r="H15" s="24"/>
-      <c r="I15" s="24"/>
-      <c r="J15" t="s" s="28">
+      <c r="H15" s="36"/>
+      <c r="I15" s="36"/>
+      <c r="J15" t="s" s="40">
         <v>133</v>
       </c>
-      <c r="K15" t="s" s="28">
+      <c r="K15" t="s" s="40">
         <v>132</v>
       </c>
-      <c r="L15" s="24"/>
-      <c r="M15" s="24"/>
-      <c r="N15" t="s" s="28">
+      <c r="L15" s="36"/>
+      <c r="M15" s="36"/>
+      <c r="N15" t="s" s="40">
         <v>134</v>
       </c>
-      <c r="O15" t="s" s="28">
+      <c r="O15" t="s" s="40">
         <v>135</v>
       </c>
-      <c r="P15" s="24"/>
-      <c r="Q15" s="22"/>
-      <c r="R15" s="22"/>
-      <c r="S15" s="22"/>
-      <c r="T15" s="22"/>
-      <c r="U15" s="22"/>
-      <c r="V15" s="22"/>
-      <c r="W15" s="22"/>
+      <c r="P15" s="36"/>
+      <c r="Q15" s="34"/>
+      <c r="R15" s="34"/>
+      <c r="S15" s="34"/>
+      <c r="T15" s="34"/>
+      <c r="U15" s="34"/>
+      <c r="V15" s="34"/>
+      <c r="W15" s="34"/>
     </row>
     <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="31"/>
-      <c r="B16" t="s" s="26">
+      <c r="A16" s="43"/>
+      <c r="B16" t="s" s="38">
         <v>122</v>
       </c>
-      <c r="C16" t="s" s="26">
+      <c r="C16" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="D16" s="24"/>
-      <c r="E16" s="31"/>
-      <c r="F16" s="31"/>
-      <c r="G16" s="31"/>
-      <c r="H16" s="24"/>
-      <c r="I16" s="31"/>
-      <c r="J16" s="31"/>
-      <c r="K16" s="31"/>
-      <c r="L16" s="24"/>
-      <c r="M16" s="31"/>
-      <c r="N16" s="31"/>
-      <c r="O16" s="31"/>
-      <c r="P16" s="24"/>
-      <c r="Q16" s="22"/>
-      <c r="R16" s="22"/>
-      <c r="S16" s="22"/>
-      <c r="T16" s="22"/>
-      <c r="U16" s="22"/>
-      <c r="V16" s="22"/>
-      <c r="W16" s="22"/>
+      <c r="D16" s="36"/>
+      <c r="E16" s="43"/>
+      <c r="F16" s="43"/>
+      <c r="G16" s="43"/>
+      <c r="H16" s="36"/>
+      <c r="I16" s="43"/>
+      <c r="J16" s="43"/>
+      <c r="K16" s="43"/>
+      <c r="L16" s="36"/>
+      <c r="M16" s="43"/>
+      <c r="N16" s="43"/>
+      <c r="O16" s="43"/>
+      <c r="P16" s="36"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="34"/>
+      <c r="S16" s="34"/>
+      <c r="T16" s="34"/>
+      <c r="U16" s="34"/>
+      <c r="V16" s="34"/>
+      <c r="W16" s="34"/>
     </row>
     <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="24"/>
-      <c r="B17" t="s" s="28">
+      <c r="A17" s="36"/>
+      <c r="B17" t="s" s="40">
         <v>125</v>
       </c>
-      <c r="C17" t="s" s="28">
+      <c r="C17" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="D17" s="24"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="22"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="22"/>
-      <c r="O17" s="22"/>
-      <c r="P17" s="24"/>
-      <c r="Q17" s="22"/>
-      <c r="R17" s="22"/>
-      <c r="S17" s="22"/>
-      <c r="T17" s="22"/>
-      <c r="U17" s="22"/>
-      <c r="V17" s="22"/>
-      <c r="W17" s="22"/>
+      <c r="D17" s="36"/>
+      <c r="E17" s="34"/>
+      <c r="F17" s="34"/>
+      <c r="G17" s="34"/>
+      <c r="H17" s="34"/>
+      <c r="I17" s="34"/>
+      <c r="J17" s="34"/>
+      <c r="K17" s="34"/>
+      <c r="L17" s="34"/>
+      <c r="M17" s="34"/>
+      <c r="N17" s="34"/>
+      <c r="O17" s="34"/>
+      <c r="P17" s="36"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="34"/>
+      <c r="S17" s="34"/>
+      <c r="T17" s="34"/>
+      <c r="U17" s="34"/>
+      <c r="V17" s="34"/>
+      <c r="W17" s="34"/>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="31"/>
-      <c r="B18" t="s" s="26">
+      <c r="A18" s="43"/>
+      <c r="B18" t="s" s="38">
         <v>128</v>
       </c>
-      <c r="C18" t="s" s="26">
+      <c r="C18" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="D18" s="24"/>
-      <c r="E18" s="22"/>
-      <c r="F18" s="22"/>
-      <c r="G18" s="22"/>
-      <c r="H18" s="22"/>
-      <c r="I18" s="22"/>
-      <c r="J18" s="22"/>
-      <c r="K18" s="22"/>
-      <c r="L18" s="22"/>
-      <c r="M18" s="22"/>
-      <c r="N18" s="22"/>
-      <c r="O18" s="22"/>
-      <c r="P18" s="24"/>
-      <c r="Q18" s="22"/>
-      <c r="R18" s="22"/>
-      <c r="S18" s="22"/>
-      <c r="T18" s="22"/>
-      <c r="U18" s="22"/>
-      <c r="V18" s="22"/>
-      <c r="W18" s="22"/>
+      <c r="D18" s="36"/>
+      <c r="E18" s="34"/>
+      <c r="F18" s="34"/>
+      <c r="G18" s="34"/>
+      <c r="H18" s="34"/>
+      <c r="I18" s="34"/>
+      <c r="J18" s="34"/>
+      <c r="K18" s="34"/>
+      <c r="L18" s="34"/>
+      <c r="M18" s="34"/>
+      <c r="N18" s="34"/>
+      <c r="O18" s="34"/>
+      <c r="P18" s="36"/>
+      <c r="Q18" s="34"/>
+      <c r="R18" s="34"/>
+      <c r="S18" s="34"/>
+      <c r="T18" s="34"/>
+      <c r="U18" s="34"/>
+      <c r="V18" s="34"/>
+      <c r="W18" s="34"/>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="24"/>
-      <c r="B19" t="s" s="28">
+      <c r="A19" s="36"/>
+      <c r="B19" t="s" s="40">
         <v>113</v>
       </c>
-      <c r="C19" t="s" s="28">
+      <c r="C19" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="D19" s="24"/>
-      <c r="E19" s="22"/>
-      <c r="F19" s="22"/>
-      <c r="G19" s="22"/>
-      <c r="H19" s="22"/>
-      <c r="I19" s="22"/>
-      <c r="J19" s="22"/>
-      <c r="K19" s="22"/>
-      <c r="L19" s="22"/>
-      <c r="M19" s="22"/>
-      <c r="N19" s="22"/>
-      <c r="O19" s="22"/>
-      <c r="P19" s="24"/>
-      <c r="Q19" s="22"/>
-      <c r="R19" s="22"/>
-      <c r="S19" s="22"/>
-      <c r="T19" s="22"/>
-      <c r="U19" s="22"/>
-      <c r="V19" s="22"/>
-      <c r="W19" s="22"/>
+      <c r="D19" s="36"/>
+      <c r="E19" s="34"/>
+      <c r="F19" s="34"/>
+      <c r="G19" s="34"/>
+      <c r="H19" s="34"/>
+      <c r="I19" s="34"/>
+      <c r="J19" s="34"/>
+      <c r="K19" s="34"/>
+      <c r="L19" s="34"/>
+      <c r="M19" s="34"/>
+      <c r="N19" s="34"/>
+      <c r="O19" s="34"/>
+      <c r="P19" s="36"/>
+      <c r="Q19" s="34"/>
+      <c r="R19" s="34"/>
+      <c r="S19" s="34"/>
+      <c r="T19" s="34"/>
+      <c r="U19" s="34"/>
+      <c r="V19" s="34"/>
+      <c r="W19" s="34"/>
     </row>
     <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="31"/>
-      <c r="B20" t="s" s="26">
+      <c r="A20" s="43"/>
+      <c r="B20" t="s" s="38">
         <v>136</v>
       </c>
-      <c r="C20" t="s" s="26">
+      <c r="C20" t="s" s="38">
         <v>137</v>
       </c>
-      <c r="D20" s="24"/>
-      <c r="E20" s="22"/>
-      <c r="F20" s="22"/>
-      <c r="G20" s="22"/>
-      <c r="H20" s="22"/>
-      <c r="I20" s="22"/>
-      <c r="J20" s="22"/>
-      <c r="K20" s="22"/>
-      <c r="L20" s="22"/>
-      <c r="M20" s="22"/>
-      <c r="N20" s="22"/>
-      <c r="O20" s="22"/>
-      <c r="P20" s="24"/>
-      <c r="Q20" s="22"/>
-      <c r="R20" s="22"/>
-      <c r="S20" s="22"/>
-      <c r="T20" s="22"/>
-      <c r="U20" s="22"/>
-      <c r="V20" s="22"/>
-      <c r="W20" s="22"/>
+      <c r="D20" s="36"/>
+      <c r="E20" s="34"/>
+      <c r="F20" s="34"/>
+      <c r="G20" s="34"/>
+      <c r="H20" s="34"/>
+      <c r="I20" s="34"/>
+      <c r="J20" s="34"/>
+      <c r="K20" s="34"/>
+      <c r="L20" s="34"/>
+      <c r="M20" s="34"/>
+      <c r="N20" s="34"/>
+      <c r="O20" s="34"/>
+      <c r="P20" s="36"/>
+      <c r="Q20" s="34"/>
+      <c r="R20" s="34"/>
+      <c r="S20" s="34"/>
+      <c r="T20" s="34"/>
+      <c r="U20" s="34"/>
+      <c r="V20" s="34"/>
+      <c r="W20" s="34"/>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="24"/>
-      <c r="B21" t="s" s="28">
+      <c r="A21" s="36"/>
+      <c r="B21" t="s" s="40">
         <v>133</v>
       </c>
-      <c r="C21" t="s" s="28">
+      <c r="C21" t="s" s="40">
         <v>132</v>
       </c>
-      <c r="D21" s="24"/>
-      <c r="E21" s="24"/>
-      <c r="F21" s="24"/>
-      <c r="G21" s="24"/>
-      <c r="H21" s="24"/>
-      <c r="I21" s="24"/>
-      <c r="J21" s="24"/>
-      <c r="K21" s="24"/>
-      <c r="L21" s="24"/>
-      <c r="M21" s="24"/>
-      <c r="N21" s="24"/>
-      <c r="O21" s="24"/>
-      <c r="P21" s="24"/>
-      <c r="Q21" s="22"/>
-      <c r="R21" s="22"/>
-      <c r="S21" s="22"/>
-      <c r="T21" s="22"/>
-      <c r="U21" s="22"/>
-      <c r="V21" s="22"/>
-      <c r="W21" s="22"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="36"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="36"/>
+      <c r="I21" s="36"/>
+      <c r="J21" s="36"/>
+      <c r="K21" s="36"/>
+      <c r="L21" s="36"/>
+      <c r="M21" s="36"/>
+      <c r="N21" s="36"/>
+      <c r="O21" s="36"/>
+      <c r="P21" s="36"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="34"/>
+      <c r="T21" s="34"/>
+      <c r="U21" s="34"/>
+      <c r="V21" s="34"/>
+      <c r="W21" s="34"/>
     </row>
     <row r="22" ht="70.75" customHeight="1">
-      <c r="A22" s="22"/>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
-      <c r="D22" s="22"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="22"/>
-      <c r="G22" s="22"/>
-      <c r="H22" s="22"/>
-      <c r="I22" s="22"/>
-      <c r="J22" s="22"/>
-      <c r="K22" s="22"/>
-      <c r="L22" s="22"/>
-      <c r="M22" s="22"/>
-      <c r="N22" s="22"/>
-      <c r="O22" s="22"/>
-      <c r="P22" s="22"/>
-      <c r="Q22" s="22"/>
-      <c r="R22" s="22"/>
-      <c r="S22" s="22"/>
-      <c r="T22" s="22"/>
-      <c r="U22" s="22"/>
-      <c r="V22" s="22"/>
-      <c r="W22" s="22"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="34"/>
+      <c r="C22" s="34"/>
+      <c r="D22" s="34"/>
+      <c r="E22" s="34"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="34"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="34"/>
+      <c r="J22" s="34"/>
+      <c r="K22" s="34"/>
+      <c r="L22" s="34"/>
+      <c r="M22" s="34"/>
+      <c r="N22" s="34"/>
+      <c r="O22" s="34"/>
+      <c r="P22" s="34"/>
+      <c r="Q22" s="34"/>
+      <c r="R22" s="34"/>
+      <c r="S22" s="34"/>
+      <c r="T22" s="34"/>
+      <c r="U22" s="34"/>
+      <c r="V22" s="34"/>
+      <c r="W22" s="34"/>
     </row>
     <row r="23" ht="34" customHeight="1">
-      <c r="A23" t="s" s="21">
+      <c r="A23" t="s" s="33">
         <v>138</v>
       </c>
-      <c r="B23" s="22"/>
-      <c r="C23" s="22"/>
-      <c r="D23" s="22"/>
-      <c r="E23" s="22"/>
-      <c r="F23" s="22"/>
-      <c r="G23" s="22"/>
-      <c r="H23" s="22"/>
-      <c r="I23" s="22"/>
-      <c r="J23" s="22"/>
-      <c r="K23" s="22"/>
-      <c r="L23" s="22"/>
-      <c r="M23" s="22"/>
-      <c r="N23" s="22"/>
-      <c r="O23" s="22"/>
-      <c r="P23" s="22"/>
-      <c r="Q23" s="22"/>
-      <c r="R23" s="22"/>
-      <c r="S23" s="22"/>
-      <c r="T23" s="22"/>
-      <c r="U23" s="22"/>
-      <c r="V23" s="22"/>
-      <c r="W23" s="22"/>
+      <c r="B23" s="34"/>
+      <c r="C23" s="34"/>
+      <c r="D23" s="34"/>
+      <c r="E23" s="34"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="34"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="34"/>
+      <c r="J23" s="34"/>
+      <c r="K23" s="34"/>
+      <c r="L23" s="34"/>
+      <c r="M23" s="34"/>
+      <c r="N23" s="34"/>
+      <c r="O23" s="34"/>
+      <c r="P23" s="34"/>
+      <c r="Q23" s="34"/>
+      <c r="R23" s="34"/>
+      <c r="S23" s="34"/>
+      <c r="T23" s="34"/>
+      <c r="U23" s="34"/>
+      <c r="V23" s="34"/>
+      <c r="W23" s="34"/>
     </row>
     <row r="24" ht="17" customHeight="1">
-      <c r="A24" t="s" s="23">
+      <c r="A24" t="s" s="35">
         <v>47</v>
       </c>
-      <c r="B24" t="s" s="23">
+      <c r="B24" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="C24" t="s" s="23">
+      <c r="C24" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="D24" s="22"/>
-      <c r="E24" t="s" s="23">
+      <c r="D24" s="34"/>
+      <c r="E24" t="s" s="35">
         <v>49</v>
       </c>
-      <c r="F24" t="s" s="23">
+      <c r="F24" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="G24" t="s" s="23">
+      <c r="G24" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="H24" s="24"/>
-      <c r="I24" t="s" s="23">
+      <c r="H24" s="36"/>
+      <c r="I24" t="s" s="35">
         <v>51</v>
       </c>
-      <c r="J24" t="s" s="23">
+      <c r="J24" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="K24" t="s" s="23">
+      <c r="K24" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="L24" s="22"/>
-      <c r="M24" t="s" s="25">
+      <c r="L24" s="34"/>
+      <c r="M24" t="s" s="37">
         <v>139</v>
       </c>
-      <c r="N24" t="s" s="25">
+      <c r="N24" t="s" s="37">
         <v>105</v>
       </c>
-      <c r="O24" t="s" s="25">
+      <c r="O24" t="s" s="37">
         <v>106</v>
       </c>
-      <c r="P24" s="22"/>
-      <c r="Q24" t="s" s="25">
+      <c r="P24" s="34"/>
+      <c r="Q24" t="s" s="37">
         <v>140</v>
       </c>
-      <c r="R24" t="s" s="25">
+      <c r="R24" t="s" s="37">
         <v>105</v>
       </c>
-      <c r="S24" t="s" s="25">
+      <c r="S24" t="s" s="37">
         <v>106</v>
       </c>
-      <c r="T24" s="22"/>
-      <c r="U24" s="22"/>
-      <c r="V24" s="22"/>
-      <c r="W24" s="22"/>
+      <c r="T24" s="34"/>
+      <c r="U24" s="34"/>
+      <c r="V24" s="34"/>
+      <c r="W24" s="34"/>
     </row>
     <row r="25" ht="17" customHeight="1">
-      <c r="A25" t="s" s="26">
+      <c r="A25" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="B25" t="s" s="26">
+      <c r="B25" t="s" s="38">
         <v>118</v>
       </c>
-      <c r="C25" t="s" s="26">
+      <c r="C25" t="s" s="38">
         <v>119</v>
       </c>
-      <c r="D25" s="22"/>
-      <c r="E25" t="s" s="26">
+      <c r="D25" s="34"/>
+      <c r="E25" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="F25" t="s" s="26">
+      <c r="F25" t="s" s="38">
         <v>141</v>
       </c>
-      <c r="G25" t="s" s="26">
+      <c r="G25" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="H25" s="24"/>
-      <c r="I25" t="s" s="26">
+      <c r="H25" s="36"/>
+      <c r="I25" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="J25" t="s" s="26">
+      <c r="J25" t="s" s="38">
         <v>142</v>
       </c>
-      <c r="K25" t="s" s="26">
+      <c r="K25" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="L25" s="22"/>
-      <c r="M25" t="s" s="27">
+      <c r="L25" s="34"/>
+      <c r="M25" t="s" s="39">
         <v>112</v>
       </c>
-      <c r="N25" t="s" s="27">
+      <c r="N25" t="s" s="39">
         <v>118</v>
       </c>
-      <c r="O25" t="s" s="27">
+      <c r="O25" t="s" s="39">
         <v>119</v>
       </c>
-      <c r="P25" s="22"/>
-      <c r="Q25" t="s" s="27">
+      <c r="P25" s="34"/>
+      <c r="Q25" t="s" s="39">
         <v>112</v>
       </c>
-      <c r="R25" t="s" s="27">
+      <c r="R25" t="s" s="39">
         <v>143</v>
       </c>
-      <c r="S25" t="s" s="27">
+      <c r="S25" t="s" s="39">
         <v>144</v>
       </c>
-      <c r="T25" s="22"/>
-      <c r="U25" s="22"/>
-      <c r="V25" s="22"/>
-      <c r="W25" s="22"/>
+      <c r="T25" s="34"/>
+      <c r="U25" s="34"/>
+      <c r="V25" s="34"/>
+      <c r="W25" s="34"/>
     </row>
     <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="24"/>
-      <c r="B26" t="s" s="28">
+      <c r="A26" s="36"/>
+      <c r="B26" t="s" s="40">
         <v>141</v>
       </c>
-      <c r="C26" t="s" s="28">
+      <c r="C26" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="D26" s="22"/>
-      <c r="E26" s="24"/>
-      <c r="F26" t="s" s="28">
+      <c r="D26" s="34"/>
+      <c r="E26" s="36"/>
+      <c r="F26" t="s" s="40">
         <v>145</v>
       </c>
-      <c r="G26" t="s" s="28">
+      <c r="G26" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="H26" s="24"/>
-      <c r="I26" s="24"/>
-      <c r="J26" t="s" s="28">
+      <c r="H26" s="36"/>
+      <c r="I26" s="36"/>
+      <c r="J26" t="s" s="40">
         <v>146</v>
       </c>
-      <c r="K26" t="s" s="28">
+      <c r="K26" t="s" s="40">
         <v>110</v>
       </c>
-      <c r="L26" s="22"/>
-      <c r="M26" s="29"/>
-      <c r="N26" t="s" s="30">
+      <c r="L26" s="34"/>
+      <c r="M26" s="41"/>
+      <c r="N26" t="s" s="42">
         <v>147</v>
       </c>
-      <c r="O26" t="s" s="30">
+      <c r="O26" t="s" s="42">
         <v>119</v>
       </c>
-      <c r="P26" s="22"/>
-      <c r="Q26" s="29"/>
-      <c r="R26" t="s" s="30">
+      <c r="P26" s="34"/>
+      <c r="Q26" s="41"/>
+      <c r="R26" t="s" s="42">
         <v>148</v>
       </c>
-      <c r="S26" t="s" s="30">
+      <c r="S26" t="s" s="42">
         <v>149</v>
       </c>
-      <c r="T26" s="22"/>
-      <c r="U26" s="22"/>
-      <c r="V26" s="22"/>
-      <c r="W26" s="22"/>
+      <c r="T26" s="34"/>
+      <c r="U26" s="34"/>
+      <c r="V26" s="34"/>
+      <c r="W26" s="34"/>
     </row>
     <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="31"/>
-      <c r="B27" t="s" s="26">
+      <c r="A27" s="43"/>
+      <c r="B27" t="s" s="38">
         <v>145</v>
       </c>
-      <c r="C27" t="s" s="26">
+      <c r="C27" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="D27" s="22"/>
-      <c r="E27" s="31"/>
-      <c r="F27" t="s" s="26">
+      <c r="D27" s="34"/>
+      <c r="E27" s="43"/>
+      <c r="F27" t="s" s="38">
         <v>143</v>
       </c>
-      <c r="G27" t="s" s="26">
+      <c r="G27" t="s" s="38">
         <v>144</v>
       </c>
-      <c r="H27" s="24"/>
-      <c r="I27" s="31"/>
-      <c r="J27" t="s" s="26">
+      <c r="H27" s="36"/>
+      <c r="I27" s="43"/>
+      <c r="J27" t="s" s="38">
         <v>150</v>
       </c>
-      <c r="K27" t="s" s="26">
+      <c r="K27" t="s" s="38">
         <v>144</v>
       </c>
-      <c r="L27" s="22"/>
-      <c r="M27" s="32"/>
-      <c r="N27" t="s" s="27">
+      <c r="L27" s="34"/>
+      <c r="M27" s="44"/>
+      <c r="N27" t="s" s="39">
         <v>151</v>
       </c>
-      <c r="O27" t="s" s="27">
+      <c r="O27" t="s" s="39">
         <v>152</v>
       </c>
-      <c r="P27" s="22"/>
-      <c r="Q27" s="32"/>
-      <c r="R27" t="s" s="27">
+      <c r="P27" s="34"/>
+      <c r="Q27" s="44"/>
+      <c r="R27" t="s" s="39">
         <v>153</v>
       </c>
-      <c r="S27" t="s" s="27">
+      <c r="S27" t="s" s="39">
         <v>144</v>
       </c>
-      <c r="T27" s="22"/>
-      <c r="U27" s="22"/>
-      <c r="V27" s="22"/>
-      <c r="W27" s="22"/>
+      <c r="T27" s="34"/>
+      <c r="U27" s="34"/>
+      <c r="V27" s="34"/>
+      <c r="W27" s="34"/>
     </row>
     <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="24"/>
-      <c r="B28" t="s" s="28">
+      <c r="A28" s="36"/>
+      <c r="B28" t="s" s="40">
         <v>143</v>
       </c>
-      <c r="C28" t="s" s="28">
+      <c r="C28" t="s" s="40">
         <v>144</v>
       </c>
-      <c r="D28" s="22"/>
-      <c r="E28" s="24"/>
-      <c r="F28" t="s" s="28">
+      <c r="D28" s="34"/>
+      <c r="E28" s="36"/>
+      <c r="F28" t="s" s="40">
         <v>148</v>
       </c>
-      <c r="G28" t="s" s="28">
+      <c r="G28" t="s" s="40">
         <v>149</v>
       </c>
-      <c r="H28" s="24"/>
-      <c r="I28" s="24"/>
-      <c r="J28" t="s" s="28">
+      <c r="H28" s="36"/>
+      <c r="I28" s="36"/>
+      <c r="J28" t="s" s="40">
         <v>154</v>
       </c>
-      <c r="K28" t="s" s="28">
+      <c r="K28" t="s" s="40">
         <v>149</v>
       </c>
-      <c r="L28" s="22"/>
-      <c r="M28" s="29"/>
-      <c r="N28" t="s" s="30">
+      <c r="L28" s="34"/>
+      <c r="M28" s="41"/>
+      <c r="N28" t="s" s="42">
         <v>155</v>
       </c>
-      <c r="O28" t="s" s="30">
+      <c r="O28" t="s" s="42">
         <v>140</v>
       </c>
-      <c r="P28" s="22"/>
-      <c r="Q28" s="29"/>
-      <c r="R28" t="s" s="30">
+      <c r="P28" s="34"/>
+      <c r="Q28" s="41"/>
+      <c r="R28" t="s" s="42">
         <v>156</v>
       </c>
-      <c r="S28" t="s" s="30">
+      <c r="S28" t="s" s="42">
         <v>137</v>
       </c>
-      <c r="T28" s="22"/>
-      <c r="U28" s="22"/>
-      <c r="V28" s="22"/>
-      <c r="W28" s="22"/>
+      <c r="T28" s="34"/>
+      <c r="U28" s="34"/>
+      <c r="V28" s="34"/>
+      <c r="W28" s="34"/>
     </row>
     <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="31"/>
-      <c r="B29" t="s" s="26">
+      <c r="A29" s="43"/>
+      <c r="B29" t="s" s="38">
         <v>148</v>
       </c>
-      <c r="C29" t="s" s="26">
+      <c r="C29" t="s" s="38">
         <v>149</v>
       </c>
-      <c r="D29" s="22"/>
-      <c r="E29" s="31"/>
-      <c r="F29" t="s" s="26">
+      <c r="D29" s="34"/>
+      <c r="E29" s="43"/>
+      <c r="F29" t="s" s="38">
         <v>153</v>
       </c>
-      <c r="G29" t="s" s="26">
+      <c r="G29" t="s" s="38">
         <v>144</v>
       </c>
-      <c r="H29" s="24"/>
-      <c r="I29" s="31"/>
-      <c r="J29" t="s" s="26">
+      <c r="H29" s="36"/>
+      <c r="I29" s="43"/>
+      <c r="J29" t="s" s="38">
         <v>157</v>
       </c>
-      <c r="K29" t="s" s="26">
+      <c r="K29" t="s" s="38">
         <v>144</v>
       </c>
-      <c r="L29" s="22"/>
-      <c r="M29" s="32"/>
-      <c r="N29" t="s" s="27">
+      <c r="L29" s="34"/>
+      <c r="M29" s="44"/>
+      <c r="N29" t="s" s="39">
         <v>158</v>
       </c>
-      <c r="O29" t="s" s="27">
+      <c r="O29" t="s" s="39">
         <v>140</v>
       </c>
-      <c r="P29" s="22"/>
-      <c r="Q29" s="32"/>
-      <c r="R29" s="32"/>
-      <c r="S29" s="32"/>
-      <c r="T29" s="22"/>
-      <c r="U29" s="22"/>
-      <c r="V29" s="22"/>
-      <c r="W29" s="22"/>
+      <c r="P29" s="34"/>
+      <c r="Q29" s="44"/>
+      <c r="R29" s="44"/>
+      <c r="S29" s="44"/>
+      <c r="T29" s="34"/>
+      <c r="U29" s="34"/>
+      <c r="V29" s="34"/>
+      <c r="W29" s="34"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="24"/>
-      <c r="B30" t="s" s="28">
+      <c r="A30" s="36"/>
+      <c r="B30" t="s" s="40">
         <v>153</v>
       </c>
-      <c r="C30" t="s" s="28">
+      <c r="C30" t="s" s="40">
         <v>144</v>
       </c>
-      <c r="D30" s="22"/>
-      <c r="E30" s="22"/>
-      <c r="F30" s="22"/>
-      <c r="G30" s="22"/>
-      <c r="H30" s="22"/>
-      <c r="I30" s="22"/>
-      <c r="J30" s="22"/>
-      <c r="K30" s="22"/>
-      <c r="L30" s="22"/>
-      <c r="M30" s="29"/>
-      <c r="N30" t="s" s="30">
+      <c r="D30" s="34"/>
+      <c r="E30" s="34"/>
+      <c r="F30" s="34"/>
+      <c r="G30" s="34"/>
+      <c r="H30" s="34"/>
+      <c r="I30" s="34"/>
+      <c r="J30" s="34"/>
+      <c r="K30" s="34"/>
+      <c r="L30" s="34"/>
+      <c r="M30" s="41"/>
+      <c r="N30" t="s" s="42">
         <v>159</v>
       </c>
-      <c r="O30" t="s" s="30">
+      <c r="O30" t="s" s="42">
         <v>115</v>
       </c>
-      <c r="P30" s="22"/>
-      <c r="Q30" s="33"/>
-      <c r="R30" s="34"/>
-      <c r="S30" s="35"/>
-      <c r="T30" s="22"/>
-      <c r="U30" s="22"/>
-      <c r="V30" s="22"/>
-      <c r="W30" s="22"/>
+      <c r="P30" s="34"/>
+      <c r="Q30" s="45"/>
+      <c r="R30" s="46"/>
+      <c r="S30" s="47"/>
+      <c r="T30" s="34"/>
+      <c r="U30" s="34"/>
+      <c r="V30" s="34"/>
+      <c r="W30" s="34"/>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="31"/>
-      <c r="B31" t="s" s="26">
+      <c r="A31" s="43"/>
+      <c r="B31" t="s" s="38">
         <v>160</v>
       </c>
-      <c r="C31" t="s" s="26">
+      <c r="C31" t="s" s="38">
         <v>144</v>
       </c>
-      <c r="D31" s="22"/>
-      <c r="E31" s="22"/>
-      <c r="F31" s="22"/>
-      <c r="G31" s="22"/>
-      <c r="H31" s="22"/>
-      <c r="I31" s="22"/>
-      <c r="J31" s="22"/>
-      <c r="K31" s="22"/>
-      <c r="L31" s="22"/>
-      <c r="M31" s="32"/>
-      <c r="N31" s="32"/>
-      <c r="O31" s="32"/>
-      <c r="P31" s="22"/>
-      <c r="Q31" s="36"/>
-      <c r="R31" s="37"/>
-      <c r="S31" s="38"/>
-      <c r="T31" s="22"/>
-      <c r="U31" s="22"/>
-      <c r="V31" s="22"/>
-      <c r="W31" s="22"/>
+      <c r="D31" s="34"/>
+      <c r="E31" s="34"/>
+      <c r="F31" s="34"/>
+      <c r="G31" s="34"/>
+      <c r="H31" s="34"/>
+      <c r="I31" s="34"/>
+      <c r="J31" s="34"/>
+      <c r="K31" s="34"/>
+      <c r="L31" s="34"/>
+      <c r="M31" s="44"/>
+      <c r="N31" s="44"/>
+      <c r="O31" s="44"/>
+      <c r="P31" s="34"/>
+      <c r="Q31" s="48"/>
+      <c r="R31" s="49"/>
+      <c r="S31" s="50"/>
+      <c r="T31" s="34"/>
+      <c r="U31" s="34"/>
+      <c r="V31" s="34"/>
+      <c r="W31" s="34"/>
     </row>
     <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="24"/>
-      <c r="B32" t="s" s="28">
+      <c r="A32" s="36"/>
+      <c r="B32" t="s" s="40">
         <v>161</v>
       </c>
-      <c r="C32" t="s" s="28">
+      <c r="C32" t="s" s="40">
         <v>162</v>
       </c>
-      <c r="D32" s="22"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="22"/>
-      <c r="G32" s="22"/>
-      <c r="H32" s="22"/>
-      <c r="I32" s="22"/>
-      <c r="J32" s="22"/>
-      <c r="K32" s="22"/>
-      <c r="L32" s="22"/>
-      <c r="M32" s="22"/>
-      <c r="N32" s="22"/>
-      <c r="O32" s="22"/>
-      <c r="P32" s="22"/>
-      <c r="Q32" s="22"/>
-      <c r="R32" s="22"/>
-      <c r="S32" s="22"/>
-      <c r="T32" s="22"/>
-      <c r="U32" s="22"/>
-      <c r="V32" s="22"/>
-      <c r="W32" s="22"/>
+      <c r="D32" s="34"/>
+      <c r="E32" s="34"/>
+      <c r="F32" s="34"/>
+      <c r="G32" s="34"/>
+      <c r="H32" s="34"/>
+      <c r="I32" s="34"/>
+      <c r="J32" s="34"/>
+      <c r="K32" s="34"/>
+      <c r="L32" s="34"/>
+      <c r="M32" s="34"/>
+      <c r="N32" s="34"/>
+      <c r="O32" s="34"/>
+      <c r="P32" s="34"/>
+      <c r="Q32" s="34"/>
+      <c r="R32" s="34"/>
+      <c r="S32" s="34"/>
+      <c r="T32" s="34"/>
+      <c r="U32" s="34"/>
+      <c r="V32" s="34"/>
+      <c r="W32" s="34"/>
     </row>
     <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="31"/>
-      <c r="B33" t="s" s="26">
+      <c r="A33" s="43"/>
+      <c r="B33" t="s" s="38">
         <v>163</v>
       </c>
-      <c r="C33" t="s" s="26">
+      <c r="C33" t="s" s="38">
         <v>137</v>
       </c>
-      <c r="D33" s="22"/>
-      <c r="E33" s="22"/>
-      <c r="F33" s="22"/>
-      <c r="G33" s="22"/>
-      <c r="H33" s="22"/>
-      <c r="I33" s="22"/>
-      <c r="J33" s="22"/>
-      <c r="K33" s="22"/>
-      <c r="L33" s="22"/>
-      <c r="M33" s="22"/>
-      <c r="N33" s="22"/>
-      <c r="O33" s="22"/>
-      <c r="P33" s="22"/>
-      <c r="Q33" s="22"/>
-      <c r="R33" s="22"/>
-      <c r="S33" s="22"/>
-      <c r="T33" s="22"/>
-      <c r="U33" s="22"/>
-      <c r="V33" s="22"/>
-      <c r="W33" s="22"/>
+      <c r="D33" s="34"/>
+      <c r="E33" s="34"/>
+      <c r="F33" s="34"/>
+      <c r="G33" s="34"/>
+      <c r="H33" s="34"/>
+      <c r="I33" s="34"/>
+      <c r="J33" s="34"/>
+      <c r="K33" s="34"/>
+      <c r="L33" s="34"/>
+      <c r="M33" s="34"/>
+      <c r="N33" s="34"/>
+      <c r="O33" s="34"/>
+      <c r="P33" s="34"/>
+      <c r="Q33" s="34"/>
+      <c r="R33" s="34"/>
+      <c r="S33" s="34"/>
+      <c r="T33" s="34"/>
+      <c r="U33" s="34"/>
+      <c r="V33" s="34"/>
+      <c r="W33" s="34"/>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" t="s" s="28">
+      <c r="A34" t="s" s="40">
         <v>164</v>
       </c>
-      <c r="B34" t="s" s="28">
+      <c r="B34" t="s" s="40">
         <v>165</v>
       </c>
-      <c r="C34" t="s" s="28">
+      <c r="C34" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="D34" s="34"/>
+      <c r="E34" s="34"/>
+      <c r="F34" s="34"/>
+      <c r="G34" s="34"/>
+      <c r="H34" s="34"/>
+      <c r="I34" s="34"/>
+      <c r="J34" s="34"/>
+      <c r="K34" s="34"/>
+      <c r="L34" s="34"/>
+      <c r="M34" s="34"/>
+      <c r="N34" s="34"/>
+      <c r="O34" s="34"/>
+      <c r="P34" s="34"/>
+      <c r="Q34" s="34"/>
+      <c r="R34" s="34"/>
+      <c r="S34" s="34"/>
+      <c r="T34" s="34"/>
+      <c r="U34" s="34"/>
+      <c r="V34" s="34"/>
+      <c r="W34" s="34"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="43"/>
+      <c r="B35" t="s" s="38">
+        <v>166</v>
+      </c>
+      <c r="C35" t="s" s="38">
+        <v>115</v>
+      </c>
+      <c r="D35" s="34"/>
+      <c r="E35" s="34"/>
+      <c r="F35" s="34"/>
+      <c r="G35" s="34"/>
+      <c r="H35" s="34"/>
+      <c r="I35" s="34"/>
+      <c r="J35" s="34"/>
+      <c r="K35" s="34"/>
+      <c r="L35" s="34"/>
+      <c r="M35" s="34"/>
+      <c r="N35" s="34"/>
+      <c r="O35" s="34"/>
+      <c r="P35" s="34"/>
+      <c r="Q35" s="34"/>
+      <c r="R35" s="34"/>
+      <c r="S35" s="34"/>
+      <c r="T35" s="34"/>
+      <c r="U35" s="34"/>
+      <c r="V35" s="34"/>
+      <c r="W35" s="34"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="36"/>
+      <c r="B36" t="s" s="40">
+        <v>167</v>
+      </c>
+      <c r="C36" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="D36" s="34"/>
+      <c r="E36" s="34"/>
+      <c r="F36" s="34"/>
+      <c r="G36" s="34"/>
+      <c r="H36" s="34"/>
+      <c r="I36" s="34"/>
+      <c r="J36" s="34"/>
+      <c r="K36" s="34"/>
+      <c r="L36" s="34"/>
+      <c r="M36" s="34"/>
+      <c r="N36" s="34"/>
+      <c r="O36" s="34"/>
+      <c r="P36" s="34"/>
+      <c r="Q36" s="34"/>
+      <c r="R36" s="34"/>
+      <c r="S36" s="34"/>
+      <c r="T36" s="34"/>
+      <c r="U36" s="34"/>
+      <c r="V36" s="34"/>
+      <c r="W36" s="34"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="43"/>
+      <c r="B37" t="s" s="38">
+        <v>168</v>
+      </c>
+      <c r="C37" t="s" s="38">
+        <v>115</v>
+      </c>
+      <c r="D37" s="34"/>
+      <c r="E37" s="34"/>
+      <c r="F37" s="34"/>
+      <c r="G37" s="34"/>
+      <c r="H37" s="34"/>
+      <c r="I37" s="34"/>
+      <c r="J37" s="34"/>
+      <c r="K37" s="34"/>
+      <c r="L37" s="34"/>
+      <c r="M37" s="34"/>
+      <c r="N37" s="34"/>
+      <c r="O37" s="34"/>
+      <c r="P37" s="34"/>
+      <c r="Q37" s="34"/>
+      <c r="R37" s="34"/>
+      <c r="S37" s="34"/>
+      <c r="T37" s="34"/>
+      <c r="U37" s="34"/>
+      <c r="V37" s="34"/>
+      <c r="W37" s="34"/>
+    </row>
+    <row r="38" ht="70.95" customHeight="1">
+      <c r="A38" s="36"/>
+      <c r="B38" s="36"/>
+      <c r="C38" s="36"/>
+      <c r="D38" s="34"/>
+      <c r="E38" s="41"/>
+      <c r="F38" s="41"/>
+      <c r="G38" s="41"/>
+      <c r="H38" s="34"/>
+      <c r="I38" s="41"/>
+      <c r="J38" s="41"/>
+      <c r="K38" s="41"/>
+      <c r="L38" s="34"/>
+      <c r="M38" s="41"/>
+      <c r="N38" s="41"/>
+      <c r="O38" s="41"/>
+      <c r="P38" s="34"/>
+      <c r="Q38" s="41"/>
+      <c r="R38" s="41"/>
+      <c r="S38" s="41"/>
+      <c r="T38" s="34"/>
+      <c r="U38" s="34"/>
+      <c r="V38" s="34"/>
+      <c r="W38" s="34"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" t="s" s="33">
+        <v>169</v>
+      </c>
+      <c r="B39" s="34"/>
+      <c r="C39" s="34"/>
+      <c r="D39" s="34"/>
+      <c r="E39" s="34"/>
+      <c r="F39" s="34"/>
+      <c r="G39" s="34"/>
+      <c r="H39" s="34"/>
+      <c r="I39" s="34"/>
+      <c r="J39" s="34"/>
+      <c r="K39" s="34"/>
+      <c r="L39" s="34"/>
+      <c r="M39" s="34"/>
+      <c r="N39" s="34"/>
+      <c r="O39" s="34"/>
+      <c r="P39" s="34"/>
+      <c r="Q39" s="34"/>
+      <c r="R39" s="34"/>
+      <c r="S39" s="34"/>
+      <c r="T39" s="34"/>
+      <c r="U39" s="34"/>
+      <c r="V39" s="34"/>
+      <c r="W39" s="34"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" t="s" s="35">
+        <v>55</v>
+      </c>
+      <c r="B40" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="C40" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="D40" s="34"/>
+      <c r="E40" t="s" s="35">
+        <v>170</v>
+      </c>
+      <c r="F40" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="G40" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="H40" s="36"/>
+      <c r="I40" t="s" s="35">
+        <v>58</v>
+      </c>
+      <c r="J40" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="K40" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="L40" s="34"/>
+      <c r="M40" t="s" s="35">
+        <v>61</v>
+      </c>
+      <c r="N40" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="O40" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="P40" s="34"/>
+      <c r="Q40" s="34"/>
+      <c r="R40" s="34"/>
+      <c r="S40" s="34"/>
+      <c r="T40" s="34"/>
+      <c r="U40" s="34"/>
+      <c r="V40" s="34"/>
+      <c r="W40" s="34"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="B41" t="s" s="38">
+        <v>171</v>
+      </c>
+      <c r="C41" t="s" s="38">
+        <v>172</v>
+      </c>
+      <c r="D41" s="34"/>
+      <c r="E41" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="F41" t="s" s="38">
+        <v>118</v>
+      </c>
+      <c r="G41" t="s" s="38">
         <v>119</v>
       </c>
-      <c r="D34" s="22"/>
-      <c r="E34" s="22"/>
-      <c r="F34" s="22"/>
-      <c r="G34" s="22"/>
-      <c r="H34" s="22"/>
-      <c r="I34" s="22"/>
-      <c r="J34" s="22"/>
-      <c r="K34" s="22"/>
-      <c r="L34" s="22"/>
-      <c r="M34" s="22"/>
-      <c r="N34" s="22"/>
-      <c r="O34" s="22"/>
-      <c r="P34" s="22"/>
-      <c r="Q34" s="22"/>
-      <c r="R34" s="22"/>
-      <c r="S34" s="22"/>
-      <c r="T34" s="22"/>
-      <c r="U34" s="22"/>
-      <c r="V34" s="22"/>
-      <c r="W34" s="22"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="31"/>
-      <c r="B35" t="s" s="26">
-        <v>166</v>
-      </c>
-      <c r="C35" t="s" s="26">
+      <c r="H41" s="36"/>
+      <c r="I41" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="J41" t="s" s="38">
+        <v>147</v>
+      </c>
+      <c r="K41" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="L41" s="34"/>
+      <c r="M41" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="N41" t="s" s="38">
+        <v>173</v>
+      </c>
+      <c r="O41" t="s" s="38">
+        <v>149</v>
+      </c>
+      <c r="P41" s="34"/>
+      <c r="Q41" s="34"/>
+      <c r="R41" s="34"/>
+      <c r="S41" s="34"/>
+      <c r="T41" s="34"/>
+      <c r="U41" s="34"/>
+      <c r="V41" s="34"/>
+      <c r="W41" s="34"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="34"/>
+      <c r="B42" s="34"/>
+      <c r="C42" s="34"/>
+      <c r="D42" s="34"/>
+      <c r="E42" s="36"/>
+      <c r="F42" t="s" s="40">
+        <v>147</v>
+      </c>
+      <c r="G42" t="s" s="40">
+        <v>119</v>
+      </c>
+      <c r="H42" s="36"/>
+      <c r="I42" s="36"/>
+      <c r="J42" t="s" s="40">
+        <v>174</v>
+      </c>
+      <c r="K42" t="s" s="40">
+        <v>149</v>
+      </c>
+      <c r="L42" s="34"/>
+      <c r="M42" s="36"/>
+      <c r="N42" t="s" s="40">
+        <v>175</v>
+      </c>
+      <c r="O42" t="s" s="40">
+        <v>144</v>
+      </c>
+      <c r="P42" s="34"/>
+      <c r="Q42" s="34"/>
+      <c r="R42" s="34"/>
+      <c r="S42" s="34"/>
+      <c r="T42" s="34"/>
+      <c r="U42" s="34"/>
+      <c r="V42" s="34"/>
+      <c r="W42" s="34"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="34"/>
+      <c r="B43" s="34"/>
+      <c r="C43" s="34"/>
+      <c r="D43" s="34"/>
+      <c r="E43" s="43"/>
+      <c r="F43" t="s" s="38">
+        <v>174</v>
+      </c>
+      <c r="G43" t="s" s="38">
+        <v>149</v>
+      </c>
+      <c r="H43" s="36"/>
+      <c r="I43" s="43"/>
+      <c r="J43" t="s" s="38">
+        <v>176</v>
+      </c>
+      <c r="K43" t="s" s="38">
+        <v>144</v>
+      </c>
+      <c r="L43" s="34"/>
+      <c r="M43" s="43"/>
+      <c r="N43" s="43"/>
+      <c r="O43" s="43"/>
+      <c r="P43" s="34"/>
+      <c r="Q43" s="34"/>
+      <c r="R43" s="34"/>
+      <c r="S43" s="34"/>
+      <c r="T43" s="34"/>
+      <c r="U43" s="34"/>
+      <c r="V43" s="34"/>
+      <c r="W43" s="34"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="34"/>
+      <c r="B44" s="34"/>
+      <c r="C44" s="34"/>
+      <c r="D44" s="34"/>
+      <c r="E44" s="36"/>
+      <c r="F44" t="s" s="40">
+        <v>177</v>
+      </c>
+      <c r="G44" t="s" s="40">
+        <v>144</v>
+      </c>
+      <c r="H44" s="36"/>
+      <c r="I44" s="34"/>
+      <c r="J44" s="34"/>
+      <c r="K44" s="34"/>
+      <c r="L44" s="34"/>
+      <c r="M44" s="34"/>
+      <c r="N44" s="34"/>
+      <c r="O44" s="34"/>
+      <c r="P44" s="34"/>
+      <c r="Q44" s="34"/>
+      <c r="R44" s="34"/>
+      <c r="S44" s="34"/>
+      <c r="T44" s="34"/>
+      <c r="U44" s="34"/>
+      <c r="V44" s="34"/>
+      <c r="W44" s="34"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="34"/>
+      <c r="B45" s="34"/>
+      <c r="C45" s="34"/>
+      <c r="D45" s="34"/>
+      <c r="E45" s="43"/>
+      <c r="F45" t="s" s="38">
+        <v>176</v>
+      </c>
+      <c r="G45" t="s" s="38">
+        <v>144</v>
+      </c>
+      <c r="H45" s="36"/>
+      <c r="I45" s="34"/>
+      <c r="J45" s="34"/>
+      <c r="K45" s="34"/>
+      <c r="L45" s="34"/>
+      <c r="M45" s="34"/>
+      <c r="N45" s="34"/>
+      <c r="O45" s="34"/>
+      <c r="P45" s="34"/>
+      <c r="Q45" s="34"/>
+      <c r="R45" s="34"/>
+      <c r="S45" s="34"/>
+      <c r="T45" s="34"/>
+      <c r="U45" s="34"/>
+      <c r="V45" s="34"/>
+      <c r="W45" s="34"/>
+    </row>
+    <row r="46" ht="70.1" customHeight="1">
+      <c r="A46" s="34"/>
+      <c r="B46" s="34"/>
+      <c r="C46" s="34"/>
+      <c r="D46" s="34"/>
+      <c r="E46" s="34"/>
+      <c r="F46" s="34"/>
+      <c r="G46" s="34"/>
+      <c r="H46" s="34"/>
+      <c r="I46" s="34"/>
+      <c r="J46" s="34"/>
+      <c r="K46" s="34"/>
+      <c r="L46" s="34"/>
+      <c r="M46" s="34"/>
+      <c r="N46" s="34"/>
+      <c r="O46" s="34"/>
+      <c r="P46" s="34"/>
+      <c r="Q46" s="34"/>
+      <c r="R46" s="34"/>
+      <c r="S46" s="34"/>
+      <c r="T46" s="34"/>
+      <c r="U46" s="34"/>
+      <c r="V46" s="34"/>
+      <c r="W46" s="34"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" t="s" s="33">
+        <v>178</v>
+      </c>
+      <c r="B47" s="34"/>
+      <c r="C47" s="34"/>
+      <c r="D47" s="34"/>
+      <c r="E47" s="34"/>
+      <c r="F47" s="34"/>
+      <c r="G47" s="34"/>
+      <c r="H47" s="34"/>
+      <c r="I47" s="34"/>
+      <c r="J47" s="34"/>
+      <c r="K47" s="34"/>
+      <c r="L47" s="34"/>
+      <c r="M47" s="34"/>
+      <c r="N47" s="34"/>
+      <c r="O47" s="34"/>
+      <c r="P47" s="34"/>
+      <c r="Q47" s="34"/>
+      <c r="R47" s="34"/>
+      <c r="S47" s="34"/>
+      <c r="T47" s="34"/>
+      <c r="U47" s="34"/>
+      <c r="V47" s="34"/>
+      <c r="W47" s="34"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" t="s" s="35">
+        <v>69</v>
+      </c>
+      <c r="B48" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="C48" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="D48" s="34"/>
+      <c r="E48" t="s" s="35">
+        <v>71</v>
+      </c>
+      <c r="F48" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="G48" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="H48" s="36"/>
+      <c r="I48" t="s" s="35">
+        <v>179</v>
+      </c>
+      <c r="J48" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="K48" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="L48" s="36"/>
+      <c r="M48" s="51"/>
+      <c r="N48" s="51"/>
+      <c r="O48" s="51"/>
+      <c r="P48" s="34"/>
+      <c r="Q48" s="52"/>
+      <c r="R48" s="52"/>
+      <c r="S48" s="52"/>
+      <c r="T48" s="34"/>
+      <c r="U48" s="52"/>
+      <c r="V48" s="52"/>
+      <c r="W48" s="52"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="B49" t="s" s="38">
+        <v>180</v>
+      </c>
+      <c r="C49" t="s" s="38">
+        <v>149</v>
+      </c>
+      <c r="D49" s="34"/>
+      <c r="E49" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="F49" t="s" s="38">
+        <v>181</v>
+      </c>
+      <c r="G49" t="s" s="38">
+        <v>85</v>
+      </c>
+      <c r="H49" s="36"/>
+      <c r="I49" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="J49" t="s" s="38">
+        <v>147</v>
+      </c>
+      <c r="K49" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="L49" s="36"/>
+      <c r="M49" s="34"/>
+      <c r="N49" s="34"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="34"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="34"/>
+      <c r="S49" s="34"/>
+      <c r="T49" s="34"/>
+      <c r="U49" s="34"/>
+      <c r="V49" s="34"/>
+      <c r="W49" s="34"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="36"/>
+      <c r="B50" t="s" s="40">
+        <v>182</v>
+      </c>
+      <c r="C50" t="s" s="40">
+        <v>183</v>
+      </c>
+      <c r="D50" s="34"/>
+      <c r="E50" s="36"/>
+      <c r="F50" t="s" s="40">
+        <v>184</v>
+      </c>
+      <c r="G50" t="s" s="40">
+        <v>85</v>
+      </c>
+      <c r="H50" s="36"/>
+      <c r="I50" s="36"/>
+      <c r="J50" t="s" s="40">
+        <v>174</v>
+      </c>
+      <c r="K50" t="s" s="40">
+        <v>149</v>
+      </c>
+      <c r="L50" s="36"/>
+      <c r="M50" s="34"/>
+      <c r="N50" s="34"/>
+      <c r="O50" s="34"/>
+      <c r="P50" s="34"/>
+      <c r="Q50" s="34"/>
+      <c r="R50" s="34"/>
+      <c r="S50" s="34"/>
+      <c r="T50" s="34"/>
+      <c r="U50" s="34"/>
+      <c r="V50" s="34"/>
+      <c r="W50" s="34"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="43"/>
+      <c r="B51" t="s" s="38">
+        <v>185</v>
+      </c>
+      <c r="C51" t="s" s="38">
+        <v>144</v>
+      </c>
+      <c r="D51" s="34"/>
+      <c r="E51" s="43"/>
+      <c r="F51" s="43"/>
+      <c r="G51" s="43"/>
+      <c r="H51" s="36"/>
+      <c r="I51" s="43"/>
+      <c r="J51" t="s" s="38">
+        <v>186</v>
+      </c>
+      <c r="K51" t="s" s="38">
+        <v>144</v>
+      </c>
+      <c r="L51" s="36"/>
+      <c r="M51" s="34"/>
+      <c r="N51" s="34"/>
+      <c r="O51" s="34"/>
+      <c r="P51" s="34"/>
+      <c r="Q51" s="34"/>
+      <c r="R51" s="34"/>
+      <c r="S51" s="34"/>
+      <c r="T51" s="34"/>
+      <c r="U51" s="34"/>
+      <c r="V51" s="34"/>
+      <c r="W51" s="34"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="36"/>
+      <c r="B52" t="s" s="40">
+        <v>159</v>
+      </c>
+      <c r="C52" t="s" s="40">
         <v>115</v>
       </c>
-      <c r="D35" s="22"/>
-      <c r="E35" s="22"/>
-      <c r="F35" s="22"/>
-      <c r="G35" s="22"/>
-      <c r="H35" s="22"/>
-      <c r="I35" s="22"/>
-      <c r="J35" s="22"/>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
-      <c r="N35" s="22"/>
-      <c r="O35" s="22"/>
-      <c r="P35" s="22"/>
-      <c r="Q35" s="22"/>
-      <c r="R35" s="22"/>
-      <c r="S35" s="22"/>
-      <c r="T35" s="22"/>
-      <c r="U35" s="22"/>
-      <c r="V35" s="22"/>
-      <c r="W35" s="22"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="24"/>
-      <c r="B36" t="s" s="28">
-        <v>167</v>
-      </c>
-      <c r="C36" t="s" s="28">
+      <c r="D52" s="34"/>
+      <c r="E52" s="34"/>
+      <c r="F52" s="34"/>
+      <c r="G52" s="34"/>
+      <c r="H52" s="36"/>
+      <c r="I52" s="36"/>
+      <c r="J52" t="s" s="40">
+        <v>176</v>
+      </c>
+      <c r="K52" t="s" s="40">
+        <v>144</v>
+      </c>
+      <c r="L52" s="36"/>
+      <c r="M52" s="34"/>
+      <c r="N52" s="34"/>
+      <c r="O52" s="34"/>
+      <c r="P52" s="34"/>
+      <c r="Q52" s="34"/>
+      <c r="R52" s="34"/>
+      <c r="S52" s="34"/>
+      <c r="T52" s="34"/>
+      <c r="U52" s="34"/>
+      <c r="V52" s="34"/>
+      <c r="W52" s="34"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="43"/>
+      <c r="B53" t="s" s="38">
+        <v>171</v>
+      </c>
+      <c r="C53" t="s" s="38">
+        <v>187</v>
+      </c>
+      <c r="D53" s="34"/>
+      <c r="E53" s="34"/>
+      <c r="F53" s="34"/>
+      <c r="G53" s="34"/>
+      <c r="H53" s="36"/>
+      <c r="I53" s="43"/>
+      <c r="J53" s="43"/>
+      <c r="K53" s="43"/>
+      <c r="L53" s="36"/>
+      <c r="M53" s="34"/>
+      <c r="N53" s="34"/>
+      <c r="O53" s="34"/>
+      <c r="P53" s="34"/>
+      <c r="Q53" s="34"/>
+      <c r="R53" s="34"/>
+      <c r="S53" s="34"/>
+      <c r="T53" s="34"/>
+      <c r="U53" s="34"/>
+      <c r="V53" s="34"/>
+      <c r="W53" s="34"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="36"/>
+      <c r="B54" t="s" s="40">
+        <v>188</v>
+      </c>
+      <c r="C54" t="s" s="40">
         <v>119</v>
       </c>
-      <c r="D36" s="22"/>
-      <c r="E36" s="22"/>
-      <c r="F36" s="22"/>
-      <c r="G36" s="22"/>
-      <c r="H36" s="22"/>
-      <c r="I36" s="22"/>
-      <c r="J36" s="22"/>
-      <c r="K36" s="22"/>
-      <c r="L36" s="22"/>
-      <c r="M36" s="22"/>
-      <c r="N36" s="22"/>
-      <c r="O36" s="22"/>
-      <c r="P36" s="22"/>
-      <c r="Q36" s="22"/>
-      <c r="R36" s="22"/>
-      <c r="S36" s="22"/>
-      <c r="T36" s="22"/>
-      <c r="U36" s="22"/>
-      <c r="V36" s="22"/>
-      <c r="W36" s="22"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="31"/>
-      <c r="B37" t="s" s="26">
-        <v>168</v>
-      </c>
-      <c r="C37" t="s" s="26">
+      <c r="D54" s="34"/>
+      <c r="E54" s="34"/>
+      <c r="F54" s="34"/>
+      <c r="G54" s="34"/>
+      <c r="H54" s="34"/>
+      <c r="I54" s="34"/>
+      <c r="J54" s="34"/>
+      <c r="K54" s="34"/>
+      <c r="L54" s="36"/>
+      <c r="M54" s="34"/>
+      <c r="N54" s="34"/>
+      <c r="O54" s="34"/>
+      <c r="P54" s="34"/>
+      <c r="Q54" s="34"/>
+      <c r="R54" s="34"/>
+      <c r="S54" s="34"/>
+      <c r="T54" s="34"/>
+      <c r="U54" s="34"/>
+      <c r="V54" s="34"/>
+      <c r="W54" s="34"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="43"/>
+      <c r="B55" t="s" s="38">
+        <v>189</v>
+      </c>
+      <c r="C55" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="D55" s="34"/>
+      <c r="E55" s="34"/>
+      <c r="F55" s="34"/>
+      <c r="G55" s="34"/>
+      <c r="H55" s="34"/>
+      <c r="I55" s="34"/>
+      <c r="J55" s="34"/>
+      <c r="K55" s="34"/>
+      <c r="L55" s="36"/>
+      <c r="M55" s="34"/>
+      <c r="N55" s="34"/>
+      <c r="O55" s="34"/>
+      <c r="P55" s="34"/>
+      <c r="Q55" s="34"/>
+      <c r="R55" s="34"/>
+      <c r="S55" s="34"/>
+      <c r="T55" s="34"/>
+      <c r="U55" s="34"/>
+      <c r="V55" s="34"/>
+      <c r="W55" s="34"/>
+    </row>
+    <row r="56" ht="70.3" customHeight="1">
+      <c r="A56" s="34"/>
+      <c r="B56" s="34"/>
+      <c r="C56" s="34"/>
+      <c r="D56" s="34"/>
+      <c r="E56" s="34"/>
+      <c r="F56" s="34"/>
+      <c r="G56" s="34"/>
+      <c r="H56" s="34"/>
+      <c r="I56" s="34"/>
+      <c r="J56" s="34"/>
+      <c r="K56" s="34"/>
+      <c r="L56" s="36"/>
+      <c r="M56" s="34"/>
+      <c r="N56" s="34"/>
+      <c r="O56" s="34"/>
+      <c r="P56" s="34"/>
+      <c r="Q56" s="34"/>
+      <c r="R56" s="34"/>
+      <c r="S56" s="34"/>
+      <c r="T56" s="34"/>
+      <c r="U56" s="34"/>
+      <c r="V56" s="34"/>
+      <c r="W56" s="34"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" t="s" s="33">
+        <v>190</v>
+      </c>
+      <c r="B57" s="34"/>
+      <c r="C57" s="34"/>
+      <c r="D57" s="34"/>
+      <c r="E57" s="34"/>
+      <c r="F57" s="34"/>
+      <c r="G57" s="34"/>
+      <c r="H57" s="34"/>
+      <c r="I57" s="34"/>
+      <c r="J57" s="34"/>
+      <c r="K57" s="34"/>
+      <c r="L57" s="34"/>
+      <c r="M57" s="34"/>
+      <c r="N57" s="34"/>
+      <c r="O57" s="34"/>
+      <c r="P57" s="34"/>
+      <c r="Q57" s="34"/>
+      <c r="R57" s="34"/>
+      <c r="S57" s="34"/>
+      <c r="T57" s="34"/>
+      <c r="U57" s="34"/>
+      <c r="V57" s="34"/>
+      <c r="W57" s="34"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" t="s" s="35">
+        <v>79</v>
+      </c>
+      <c r="B58" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="C58" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="D58" s="34"/>
+      <c r="E58" t="s" s="35">
+        <v>78</v>
+      </c>
+      <c r="F58" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="G58" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="H58" s="36"/>
+      <c r="I58" s="51"/>
+      <c r="J58" s="51"/>
+      <c r="K58" s="51"/>
+      <c r="L58" s="36"/>
+      <c r="M58" s="51"/>
+      <c r="N58" s="51"/>
+      <c r="O58" s="51"/>
+      <c r="P58" s="34"/>
+      <c r="Q58" s="52"/>
+      <c r="R58" s="52"/>
+      <c r="S58" s="52"/>
+      <c r="T58" s="34"/>
+      <c r="U58" s="52"/>
+      <c r="V58" s="52"/>
+      <c r="W58" s="52"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="B59" t="s" s="38">
+        <v>147</v>
+      </c>
+      <c r="C59" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="D59" s="34"/>
+      <c r="E59" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="F59" t="s" s="38">
+        <v>147</v>
+      </c>
+      <c r="G59" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="H59" s="36"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="34"/>
+      <c r="M59" s="34"/>
+      <c r="N59" s="34"/>
+      <c r="O59" s="34"/>
+      <c r="P59" s="34"/>
+      <c r="Q59" s="34"/>
+      <c r="R59" s="34"/>
+      <c r="S59" s="34"/>
+      <c r="T59" s="34"/>
+      <c r="U59" s="34"/>
+      <c r="V59" s="34"/>
+      <c r="W59" s="34"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="36"/>
+      <c r="B60" t="s" s="40">
+        <v>191</v>
+      </c>
+      <c r="C60" t="s" s="40">
+        <v>192</v>
+      </c>
+      <c r="D60" s="34"/>
+      <c r="E60" s="36"/>
+      <c r="F60" t="s" s="40">
+        <v>193</v>
+      </c>
+      <c r="G60" t="s" s="40">
+        <v>149</v>
+      </c>
+      <c r="H60" s="36"/>
+      <c r="I60" s="34"/>
+      <c r="J60" s="34"/>
+      <c r="K60" s="34"/>
+      <c r="L60" s="34"/>
+      <c r="M60" s="34"/>
+      <c r="N60" s="34"/>
+      <c r="O60" s="34"/>
+      <c r="P60" s="34"/>
+      <c r="Q60" s="34"/>
+      <c r="R60" s="34"/>
+      <c r="S60" s="34"/>
+      <c r="T60" s="34"/>
+      <c r="U60" s="34"/>
+      <c r="V60" s="34"/>
+      <c r="W60" s="34"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="43"/>
+      <c r="B61" t="s" s="38">
+        <v>193</v>
+      </c>
+      <c r="C61" t="s" s="38">
+        <v>149</v>
+      </c>
+      <c r="D61" s="34"/>
+      <c r="E61" s="43"/>
+      <c r="F61" t="s" s="38">
+        <v>194</v>
+      </c>
+      <c r="G61" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="H61" s="36"/>
+      <c r="I61" s="34"/>
+      <c r="J61" s="34"/>
+      <c r="K61" s="34"/>
+      <c r="L61" s="34"/>
+      <c r="M61" s="34"/>
+      <c r="N61" s="34"/>
+      <c r="O61" s="34"/>
+      <c r="P61" s="34"/>
+      <c r="Q61" s="34"/>
+      <c r="R61" s="34"/>
+      <c r="S61" s="34"/>
+      <c r="T61" s="34"/>
+      <c r="U61" s="34"/>
+      <c r="V61" s="34"/>
+      <c r="W61" s="34"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="36"/>
+      <c r="B62" t="s" s="40">
+        <v>194</v>
+      </c>
+      <c r="C62" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="D62" s="34"/>
+      <c r="E62" s="34"/>
+      <c r="F62" s="34"/>
+      <c r="G62" s="34"/>
+      <c r="H62" s="36"/>
+      <c r="I62" s="34"/>
+      <c r="J62" s="34"/>
+      <c r="K62" s="34"/>
+      <c r="L62" s="34"/>
+      <c r="M62" s="34"/>
+      <c r="N62" s="34"/>
+      <c r="O62" s="34"/>
+      <c r="P62" s="34"/>
+      <c r="Q62" s="34"/>
+      <c r="R62" s="34"/>
+      <c r="S62" s="34"/>
+      <c r="T62" s="34"/>
+      <c r="U62" s="34"/>
+      <c r="V62" s="34"/>
+      <c r="W62" s="34"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="43"/>
+      <c r="B63" t="s" s="38">
+        <v>159</v>
+      </c>
+      <c r="C63" t="s" s="38">
         <v>115</v>
       </c>
-      <c r="D37" s="22"/>
-      <c r="E37" s="22"/>
-      <c r="F37" s="22"/>
-      <c r="G37" s="22"/>
-      <c r="H37" s="22"/>
-      <c r="I37" s="22"/>
-      <c r="J37" s="22"/>
-      <c r="K37" s="22"/>
-      <c r="L37" s="22"/>
-      <c r="M37" s="22"/>
-      <c r="N37" s="22"/>
-      <c r="O37" s="22"/>
-      <c r="P37" s="22"/>
-      <c r="Q37" s="22"/>
-      <c r="R37" s="22"/>
-      <c r="S37" s="22"/>
-      <c r="T37" s="22"/>
-      <c r="U37" s="22"/>
-      <c r="V37" s="22"/>
-      <c r="W37" s="22"/>
-    </row>
-    <row r="38" ht="70.95" customHeight="1">
-      <c r="A38" s="24"/>
-      <c r="B38" s="24"/>
-      <c r="C38" s="24"/>
-      <c r="D38" s="22"/>
-      <c r="E38" s="29"/>
-      <c r="F38" s="29"/>
-      <c r="G38" s="29"/>
-      <c r="H38" s="22"/>
-      <c r="I38" s="29"/>
-      <c r="J38" s="29"/>
-      <c r="K38" s="29"/>
-      <c r="L38" s="22"/>
-      <c r="M38" s="29"/>
-      <c r="N38" s="29"/>
-      <c r="O38" s="29"/>
-      <c r="P38" s="22"/>
-      <c r="Q38" s="29"/>
-      <c r="R38" s="29"/>
-      <c r="S38" s="29"/>
-      <c r="T38" s="22"/>
-      <c r="U38" s="22"/>
-      <c r="V38" s="22"/>
-      <c r="W38" s="22"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" t="s" s="21">
-        <v>169</v>
-      </c>
-      <c r="B39" s="22"/>
-      <c r="C39" s="22"/>
-      <c r="D39" s="22"/>
-      <c r="E39" s="22"/>
-      <c r="F39" s="22"/>
-      <c r="G39" s="22"/>
-      <c r="H39" s="22"/>
-      <c r="I39" s="22"/>
-      <c r="J39" s="22"/>
-      <c r="K39" s="22"/>
-      <c r="L39" s="22"/>
-      <c r="M39" s="22"/>
-      <c r="N39" s="22"/>
-      <c r="O39" s="22"/>
-      <c r="P39" s="22"/>
-      <c r="Q39" s="22"/>
-      <c r="R39" s="22"/>
-      <c r="S39" s="22"/>
-      <c r="T39" s="22"/>
-      <c r="U39" s="22"/>
-      <c r="V39" s="22"/>
-      <c r="W39" s="22"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" t="s" s="23">
-        <v>55</v>
-      </c>
-      <c r="B40" t="s" s="23">
+      <c r="D63" s="34"/>
+      <c r="E63" s="34"/>
+      <c r="F63" s="34"/>
+      <c r="G63" s="34"/>
+      <c r="H63" s="36"/>
+      <c r="I63" s="34"/>
+      <c r="J63" s="34"/>
+      <c r="K63" s="34"/>
+      <c r="L63" s="34"/>
+      <c r="M63" s="34"/>
+      <c r="N63" s="34"/>
+      <c r="O63" s="34"/>
+      <c r="P63" s="34"/>
+      <c r="Q63" s="34"/>
+      <c r="R63" s="34"/>
+      <c r="S63" s="34"/>
+      <c r="T63" s="34"/>
+      <c r="U63" s="34"/>
+      <c r="V63" s="34"/>
+      <c r="W63" s="34"/>
+    </row>
+    <row r="64" ht="70.7" customHeight="1">
+      <c r="A64" s="36"/>
+      <c r="B64" s="36"/>
+      <c r="C64" s="36"/>
+      <c r="D64" s="34"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="53"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="36"/>
+      <c r="I64" s="36"/>
+      <c r="J64" s="36"/>
+      <c r="K64" s="36"/>
+      <c r="L64" s="36"/>
+      <c r="M64" s="36"/>
+      <c r="N64" s="36"/>
+      <c r="O64" s="36"/>
+      <c r="P64" s="34"/>
+      <c r="Q64" s="41"/>
+      <c r="R64" s="41"/>
+      <c r="S64" s="41"/>
+      <c r="T64" s="34"/>
+      <c r="U64" s="41"/>
+      <c r="V64" s="41"/>
+      <c r="W64" s="41"/>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" t="s" s="33">
+        <v>195</v>
+      </c>
+      <c r="B65" s="34"/>
+      <c r="C65" s="34"/>
+      <c r="D65" s="34"/>
+      <c r="E65" s="34"/>
+      <c r="F65" s="34"/>
+      <c r="G65" s="34"/>
+      <c r="H65" s="34"/>
+      <c r="I65" s="34"/>
+      <c r="J65" s="34"/>
+      <c r="K65" s="34"/>
+      <c r="L65" s="34"/>
+      <c r="M65" s="34"/>
+      <c r="N65" s="34"/>
+      <c r="O65" s="34"/>
+      <c r="P65" s="34"/>
+      <c r="Q65" s="34"/>
+      <c r="R65" s="34"/>
+      <c r="S65" s="34"/>
+      <c r="T65" s="34"/>
+      <c r="U65" s="34"/>
+      <c r="V65" s="34"/>
+      <c r="W65" s="34"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" t="s" s="35">
+        <v>85</v>
+      </c>
+      <c r="B66" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="C40" t="s" s="23">
+      <c r="C66" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="D40" s="22"/>
-      <c r="E40" t="s" s="23">
-        <v>170</v>
-      </c>
-      <c r="F40" t="s" s="23">
+      <c r="D66" s="34"/>
+      <c r="E66" t="s" s="35">
+        <v>84</v>
+      </c>
+      <c r="F66" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="G40" t="s" s="23">
+      <c r="G66" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="H40" s="24"/>
-      <c r="I40" t="s" s="23">
-        <v>58</v>
-      </c>
-      <c r="J40" t="s" s="23">
+      <c r="H66" s="36"/>
+      <c r="I66" t="s" s="35">
+        <v>88</v>
+      </c>
+      <c r="J66" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="K40" t="s" s="23">
+      <c r="K66" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="L40" s="22"/>
-      <c r="M40" t="s" s="23">
-        <v>61</v>
-      </c>
-      <c r="N40" t="s" s="23">
+      <c r="L66" s="36"/>
+      <c r="M66" s="51"/>
+      <c r="N66" s="51"/>
+      <c r="O66" s="51"/>
+      <c r="P66" s="34"/>
+      <c r="Q66" s="52"/>
+      <c r="R66" s="52"/>
+      <c r="S66" s="52"/>
+      <c r="T66" s="34"/>
+      <c r="U66" s="52"/>
+      <c r="V66" s="52"/>
+      <c r="W66" s="52"/>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="B67" t="s" s="38">
+        <v>118</v>
+      </c>
+      <c r="C67" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="D67" s="34"/>
+      <c r="E67" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="F67" t="s" s="38">
+        <v>196</v>
+      </c>
+      <c r="G67" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="H67" s="36"/>
+      <c r="I67" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="J67" t="s" s="38">
+        <v>197</v>
+      </c>
+      <c r="K67" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="L67" s="36"/>
+      <c r="M67" s="34"/>
+      <c r="N67" s="34"/>
+      <c r="O67" s="34"/>
+      <c r="P67" s="34"/>
+      <c r="Q67" s="34"/>
+      <c r="R67" s="34"/>
+      <c r="S67" s="34"/>
+      <c r="T67" s="34"/>
+      <c r="U67" s="34"/>
+      <c r="V67" s="34"/>
+      <c r="W67" s="34"/>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="36"/>
+      <c r="B68" t="s" s="40">
+        <v>196</v>
+      </c>
+      <c r="C68" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="D68" s="34"/>
+      <c r="E68" s="36"/>
+      <c r="F68" t="s" s="40">
+        <v>198</v>
+      </c>
+      <c r="G68" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="H68" s="36"/>
+      <c r="I68" s="36"/>
+      <c r="J68" t="s" s="40">
+        <v>199</v>
+      </c>
+      <c r="K68" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="L68" s="36"/>
+      <c r="M68" s="34"/>
+      <c r="N68" s="34"/>
+      <c r="O68" s="34"/>
+      <c r="P68" s="34"/>
+      <c r="Q68" s="34"/>
+      <c r="R68" s="34"/>
+      <c r="S68" s="34"/>
+      <c r="T68" s="34"/>
+      <c r="U68" s="34"/>
+      <c r="V68" s="34"/>
+      <c r="W68" s="34"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="43"/>
+      <c r="B69" t="s" s="38">
+        <v>198</v>
+      </c>
+      <c r="C69" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="D69" s="34"/>
+      <c r="E69" s="43"/>
+      <c r="F69" t="s" s="38">
+        <v>200</v>
+      </c>
+      <c r="G69" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="H69" s="36"/>
+      <c r="I69" s="43"/>
+      <c r="J69" t="s" s="38">
+        <v>201</v>
+      </c>
+      <c r="K69" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="L69" s="36"/>
+      <c r="M69" s="34"/>
+      <c r="N69" s="34"/>
+      <c r="O69" s="34"/>
+      <c r="P69" s="34"/>
+      <c r="Q69" s="34"/>
+      <c r="R69" s="34"/>
+      <c r="S69" s="34"/>
+      <c r="T69" s="34"/>
+      <c r="U69" s="34"/>
+      <c r="V69" s="34"/>
+      <c r="W69" s="34"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="36"/>
+      <c r="B70" t="s" s="40">
+        <v>200</v>
+      </c>
+      <c r="C70" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="D70" s="34"/>
+      <c r="E70" s="36"/>
+      <c r="F70" t="s" s="40">
+        <v>202</v>
+      </c>
+      <c r="G70" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="H70" s="36"/>
+      <c r="I70" s="36"/>
+      <c r="J70" t="s" s="40">
+        <v>203</v>
+      </c>
+      <c r="K70" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="L70" s="36"/>
+      <c r="M70" s="34"/>
+      <c r="N70" s="34"/>
+      <c r="O70" s="34"/>
+      <c r="P70" s="34"/>
+      <c r="Q70" s="34"/>
+      <c r="R70" s="34"/>
+      <c r="S70" s="34"/>
+      <c r="T70" s="34"/>
+      <c r="U70" s="34"/>
+      <c r="V70" s="34"/>
+      <c r="W70" s="34"/>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="43"/>
+      <c r="B71" t="s" s="38">
+        <v>202</v>
+      </c>
+      <c r="C71" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="D71" s="34"/>
+      <c r="E71" s="43"/>
+      <c r="F71" t="s" s="38">
+        <v>204</v>
+      </c>
+      <c r="G71" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="H71" s="36"/>
+      <c r="I71" s="43"/>
+      <c r="J71" t="s" s="38">
+        <v>205</v>
+      </c>
+      <c r="K71" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="L71" s="36"/>
+      <c r="M71" s="34"/>
+      <c r="N71" s="34"/>
+      <c r="O71" s="34"/>
+      <c r="P71" s="34"/>
+      <c r="Q71" s="34"/>
+      <c r="R71" s="34"/>
+      <c r="S71" s="34"/>
+      <c r="T71" s="34"/>
+      <c r="U71" s="34"/>
+      <c r="V71" s="34"/>
+      <c r="W71" s="34"/>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="36"/>
+      <c r="B72" t="s" s="40">
+        <v>204</v>
+      </c>
+      <c r="C72" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="D72" s="34"/>
+      <c r="E72" s="36"/>
+      <c r="F72" t="s" s="40">
+        <v>206</v>
+      </c>
+      <c r="G72" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="H72" s="36"/>
+      <c r="I72" s="36"/>
+      <c r="J72" t="s" s="40">
+        <v>207</v>
+      </c>
+      <c r="K72" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="L72" s="36"/>
+      <c r="M72" s="34"/>
+      <c r="N72" s="34"/>
+      <c r="O72" s="34"/>
+      <c r="P72" s="34"/>
+      <c r="Q72" s="34"/>
+      <c r="R72" s="34"/>
+      <c r="S72" s="34"/>
+      <c r="T72" s="34"/>
+      <c r="U72" s="34"/>
+      <c r="V72" s="34"/>
+      <c r="W72" s="34"/>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="43"/>
+      <c r="B73" t="s" s="38">
+        <v>206</v>
+      </c>
+      <c r="C73" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="D73" s="34"/>
+      <c r="E73" s="43"/>
+      <c r="F73" s="43"/>
+      <c r="G73" s="43"/>
+      <c r="H73" s="36"/>
+      <c r="I73" s="43"/>
+      <c r="J73" s="43"/>
+      <c r="K73" s="43"/>
+      <c r="L73" s="36"/>
+      <c r="M73" s="34"/>
+      <c r="N73" s="34"/>
+      <c r="O73" s="34"/>
+      <c r="P73" s="34"/>
+      <c r="Q73" s="34"/>
+      <c r="R73" s="34"/>
+      <c r="S73" s="34"/>
+      <c r="T73" s="34"/>
+      <c r="U73" s="34"/>
+      <c r="V73" s="34"/>
+      <c r="W73" s="34"/>
+    </row>
+    <row r="74" ht="70.2" customHeight="1">
+      <c r="A74" s="36"/>
+      <c r="B74" s="36"/>
+      <c r="C74" s="36"/>
+      <c r="D74" s="34"/>
+      <c r="E74" s="36"/>
+      <c r="F74" s="36"/>
+      <c r="G74" s="36"/>
+      <c r="H74" s="36"/>
+      <c r="I74" s="36"/>
+      <c r="J74" s="36"/>
+      <c r="K74" s="36"/>
+      <c r="L74" s="36"/>
+      <c r="M74" s="36"/>
+      <c r="N74" s="36"/>
+      <c r="O74" s="36"/>
+      <c r="P74" s="34"/>
+      <c r="Q74" s="41"/>
+      <c r="R74" s="41"/>
+      <c r="S74" s="41"/>
+      <c r="T74" s="34"/>
+      <c r="U74" s="41"/>
+      <c r="V74" s="41"/>
+      <c r="W74" s="41"/>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" t="s" s="33">
+        <v>208</v>
+      </c>
+      <c r="B75" s="34"/>
+      <c r="C75" s="34"/>
+      <c r="D75" s="34"/>
+      <c r="E75" s="34"/>
+      <c r="F75" s="34"/>
+      <c r="G75" s="34"/>
+      <c r="H75" s="34"/>
+      <c r="I75" s="34"/>
+      <c r="J75" s="34"/>
+      <c r="K75" s="34"/>
+      <c r="L75" s="34"/>
+      <c r="M75" s="34"/>
+      <c r="N75" s="34"/>
+      <c r="O75" s="34"/>
+      <c r="P75" s="34"/>
+      <c r="Q75" s="34"/>
+      <c r="R75" s="34"/>
+      <c r="S75" s="34"/>
+      <c r="T75" s="34"/>
+      <c r="U75" s="34"/>
+      <c r="V75" s="34"/>
+      <c r="W75" s="34"/>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" t="s" s="35">
+        <v>95</v>
+      </c>
+      <c r="B76" t="s" s="35">
         <v>105</v>
       </c>
-      <c r="O40" t="s" s="23">
+      <c r="C76" t="s" s="35">
         <v>106</v>
       </c>
-      <c r="P40" s="22"/>
-      <c r="Q40" s="22"/>
-      <c r="R40" s="22"/>
-      <c r="S40" s="22"/>
-      <c r="T40" s="22"/>
-      <c r="U40" s="22"/>
-      <c r="V40" s="22"/>
-      <c r="W40" s="22"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" t="s" s="26">
+      <c r="D76" s="34"/>
+      <c r="E76" t="s" s="35">
+        <v>94</v>
+      </c>
+      <c r="F76" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="G76" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="H76" s="36"/>
+      <c r="I76" t="s" s="35">
+        <v>98</v>
+      </c>
+      <c r="J76" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="K76" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="L76" s="36"/>
+      <c r="M76" s="51"/>
+      <c r="N76" s="51"/>
+      <c r="O76" s="51"/>
+      <c r="P76" s="34"/>
+      <c r="Q76" s="52"/>
+      <c r="R76" s="52"/>
+      <c r="S76" s="52"/>
+      <c r="T76" s="34"/>
+      <c r="U76" s="52"/>
+      <c r="V76" s="52"/>
+      <c r="W76" s="52"/>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="B41" t="s" s="26">
-        <v>171</v>
-      </c>
-      <c r="C41" t="s" s="26">
-        <v>172</v>
-      </c>
-      <c r="D41" s="22"/>
-      <c r="E41" t="s" s="26">
+      <c r="B77" t="s" s="38">
+        <v>118</v>
+      </c>
+      <c r="C77" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="D77" s="34"/>
+      <c r="E77" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="F41" t="s" s="26">
+      <c r="F77" t="s" s="38">
+        <v>147</v>
+      </c>
+      <c r="G77" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="H77" s="36"/>
+      <c r="I77" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="J77" t="s" s="38">
+        <v>209</v>
+      </c>
+      <c r="K77" t="s" s="38">
+        <v>210</v>
+      </c>
+      <c r="L77" s="36"/>
+      <c r="M77" s="34"/>
+      <c r="N77" s="34"/>
+      <c r="O77" s="34"/>
+      <c r="P77" s="34"/>
+      <c r="Q77" s="34"/>
+      <c r="R77" s="34"/>
+      <c r="S77" s="34"/>
+      <c r="T77" s="34"/>
+      <c r="U77" s="34"/>
+      <c r="V77" s="34"/>
+      <c r="W77" s="34"/>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="36"/>
+      <c r="B78" t="s" s="40">
+        <v>211</v>
+      </c>
+      <c r="C78" t="s" s="40">
+        <v>119</v>
+      </c>
+      <c r="D78" s="34"/>
+      <c r="E78" s="36"/>
+      <c r="F78" t="s" s="40">
+        <v>209</v>
+      </c>
+      <c r="G78" t="s" s="40">
+        <v>210</v>
+      </c>
+      <c r="H78" s="36"/>
+      <c r="I78" s="34"/>
+      <c r="J78" s="34"/>
+      <c r="K78" s="34"/>
+      <c r="L78" s="36"/>
+      <c r="M78" s="34"/>
+      <c r="N78" s="34"/>
+      <c r="O78" s="34"/>
+      <c r="P78" s="34"/>
+      <c r="Q78" s="34"/>
+      <c r="R78" s="34"/>
+      <c r="S78" s="34"/>
+      <c r="T78" s="34"/>
+      <c r="U78" s="34"/>
+      <c r="V78" s="34"/>
+      <c r="W78" s="34"/>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="43"/>
+      <c r="B79" t="s" s="38">
+        <v>147</v>
+      </c>
+      <c r="C79" t="s" s="38">
+        <v>119</v>
+      </c>
+      <c r="D79" s="34"/>
+      <c r="E79" s="43"/>
+      <c r="F79" s="43"/>
+      <c r="G79" s="43"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="34"/>
+      <c r="J79" s="34"/>
+      <c r="K79" s="34"/>
+      <c r="L79" s="36"/>
+      <c r="M79" s="34"/>
+      <c r="N79" s="34"/>
+      <c r="O79" s="34"/>
+      <c r="P79" s="34"/>
+      <c r="Q79" s="34"/>
+      <c r="R79" s="34"/>
+      <c r="S79" s="34"/>
+      <c r="T79" s="34"/>
+      <c r="U79" s="34"/>
+      <c r="V79" s="34"/>
+      <c r="W79" s="34"/>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="36"/>
+      <c r="B80" t="s" s="40">
+        <v>209</v>
+      </c>
+      <c r="C80" t="s" s="40">
+        <v>210</v>
+      </c>
+      <c r="D80" s="34"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36"/>
+      <c r="K80" s="36"/>
+      <c r="L80" s="36"/>
+      <c r="M80" s="36"/>
+      <c r="N80" s="36"/>
+      <c r="O80" s="36"/>
+      <c r="P80" s="34"/>
+      <c r="Q80" s="41"/>
+      <c r="R80" s="41"/>
+      <c r="S80" s="41"/>
+      <c r="T80" s="34"/>
+      <c r="U80" s="41"/>
+      <c r="V80" s="41"/>
+      <c r="W80" s="41"/>
+    </row>
+    <row r="81" ht="70.5" customHeight="1">
+      <c r="A81" s="36"/>
+      <c r="B81" s="36"/>
+      <c r="C81" s="36"/>
+      <c r="D81" s="34"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="53"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36"/>
+      <c r="J81" s="36"/>
+      <c r="K81" s="36"/>
+      <c r="L81" s="36"/>
+      <c r="M81" s="36"/>
+      <c r="N81" s="36"/>
+      <c r="O81" s="36"/>
+      <c r="P81" s="34"/>
+      <c r="Q81" s="41"/>
+      <c r="R81" s="41"/>
+      <c r="S81" s="41"/>
+      <c r="T81" s="34"/>
+      <c r="U81" s="41"/>
+      <c r="V81" s="41"/>
+      <c r="W81" s="41"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" t="s" s="33">
+        <v>212</v>
+      </c>
+      <c r="B82" s="34"/>
+      <c r="C82" s="34"/>
+      <c r="D82" s="34"/>
+      <c r="E82" s="34"/>
+      <c r="F82" s="34"/>
+      <c r="G82" s="34"/>
+      <c r="H82" s="34"/>
+      <c r="I82" s="34"/>
+      <c r="J82" s="34"/>
+      <c r="K82" s="34"/>
+      <c r="L82" s="34"/>
+      <c r="M82" s="34"/>
+      <c r="N82" s="34"/>
+      <c r="O82" s="34"/>
+      <c r="P82" s="34"/>
+      <c r="Q82" s="34"/>
+      <c r="R82" s="34"/>
+      <c r="S82" s="34"/>
+      <c r="T82" s="34"/>
+      <c r="U82" s="34"/>
+      <c r="V82" s="34"/>
+      <c r="W82" s="34"/>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" t="s" s="37">
+        <v>213</v>
+      </c>
+      <c r="B83" t="s" s="37">
+        <v>105</v>
+      </c>
+      <c r="C83" t="s" s="37">
+        <v>106</v>
+      </c>
+      <c r="D83" s="34"/>
+      <c r="E83" t="s" s="54">
+        <v>214</v>
+      </c>
+      <c r="F83" t="s" s="54">
+        <v>105</v>
+      </c>
+      <c r="G83" t="s" s="54">
+        <v>106</v>
+      </c>
+      <c r="H83" s="36"/>
+      <c r="I83" s="51"/>
+      <c r="J83" s="51"/>
+      <c r="K83" s="51"/>
+      <c r="L83" s="36"/>
+      <c r="M83" s="51"/>
+      <c r="N83" s="51"/>
+      <c r="O83" s="51"/>
+      <c r="P83" s="34"/>
+      <c r="Q83" s="52"/>
+      <c r="R83" s="52"/>
+      <c r="S83" s="52"/>
+      <c r="T83" s="34"/>
+      <c r="U83" s="52"/>
+      <c r="V83" s="52"/>
+      <c r="W83" s="52"/>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" t="s" s="39">
+        <v>112</v>
+      </c>
+      <c r="B84" t="s" s="39">
         <v>118</v>
       </c>
-      <c r="G41" t="s" s="26">
+      <c r="C84" t="s" s="39">
         <v>119</v>
       </c>
-      <c r="H41" s="24"/>
-      <c r="I41" t="s" s="26">
+      <c r="D84" s="34"/>
+      <c r="E84" t="s" s="55">
+        <v>215</v>
+      </c>
+      <c r="F84" t="s" s="55">
+        <v>216</v>
+      </c>
+      <c r="G84" t="s" s="55">
+        <v>110</v>
+      </c>
+      <c r="H84" s="34"/>
+      <c r="I84" s="34"/>
+      <c r="J84" s="34"/>
+      <c r="K84" s="34"/>
+      <c r="L84" s="34"/>
+      <c r="M84" s="34"/>
+      <c r="N84" s="34"/>
+      <c r="O84" s="34"/>
+      <c r="P84" s="34"/>
+      <c r="Q84" s="34"/>
+      <c r="R84" s="34"/>
+      <c r="S84" s="34"/>
+      <c r="T84" s="34"/>
+      <c r="U84" s="34"/>
+      <c r="V84" s="34"/>
+      <c r="W84" s="34"/>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="41"/>
+      <c r="B85" t="s" s="42">
+        <v>211</v>
+      </c>
+      <c r="C85" t="s" s="42">
+        <v>119</v>
+      </c>
+      <c r="D85" s="34"/>
+      <c r="E85" s="53"/>
+      <c r="F85" t="s" s="56">
+        <v>217</v>
+      </c>
+      <c r="G85" t="s" s="56">
+        <v>218</v>
+      </c>
+      <c r="H85" s="34"/>
+      <c r="I85" s="34"/>
+      <c r="J85" s="34"/>
+      <c r="K85" s="34"/>
+      <c r="L85" s="34"/>
+      <c r="M85" s="34"/>
+      <c r="N85" s="34"/>
+      <c r="O85" s="34"/>
+      <c r="P85" s="34"/>
+      <c r="Q85" s="34"/>
+      <c r="R85" s="34"/>
+      <c r="S85" s="34"/>
+      <c r="T85" s="34"/>
+      <c r="U85" s="34"/>
+      <c r="V85" s="34"/>
+      <c r="W85" s="34"/>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="44"/>
+      <c r="B86" t="s" s="39">
+        <v>216</v>
+      </c>
+      <c r="C86" t="s" s="39">
+        <v>110</v>
+      </c>
+      <c r="D86" s="34"/>
+      <c r="E86" s="57"/>
+      <c r="F86" t="s" s="55">
+        <v>182</v>
+      </c>
+      <c r="G86" t="s" s="55">
+        <v>219</v>
+      </c>
+      <c r="H86" s="34"/>
+      <c r="I86" s="34"/>
+      <c r="J86" s="34"/>
+      <c r="K86" s="34"/>
+      <c r="L86" s="34"/>
+      <c r="M86" s="34"/>
+      <c r="N86" s="34"/>
+      <c r="O86" s="34"/>
+      <c r="P86" s="34"/>
+      <c r="Q86" s="34"/>
+      <c r="R86" s="34"/>
+      <c r="S86" s="34"/>
+      <c r="T86" s="34"/>
+      <c r="U86" s="34"/>
+      <c r="V86" s="34"/>
+      <c r="W86" s="34"/>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="41"/>
+      <c r="B87" t="s" s="42">
+        <v>217</v>
+      </c>
+      <c r="C87" t="s" s="42">
+        <v>218</v>
+      </c>
+      <c r="D87" s="34"/>
+      <c r="E87" s="53"/>
+      <c r="F87" t="s" s="56">
+        <v>159</v>
+      </c>
+      <c r="G87" t="s" s="56">
+        <v>115</v>
+      </c>
+      <c r="H87" s="34"/>
+      <c r="I87" s="34"/>
+      <c r="J87" s="34"/>
+      <c r="K87" s="34"/>
+      <c r="L87" s="34"/>
+      <c r="M87" s="34"/>
+      <c r="N87" s="34"/>
+      <c r="O87" s="34"/>
+      <c r="P87" s="34"/>
+      <c r="Q87" s="34"/>
+      <c r="R87" s="34"/>
+      <c r="S87" s="34"/>
+      <c r="T87" s="34"/>
+      <c r="U87" s="34"/>
+      <c r="V87" s="34"/>
+      <c r="W87" s="34"/>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="44"/>
+      <c r="B88" t="s" s="39">
+        <v>182</v>
+      </c>
+      <c r="C88" t="s" s="39">
+        <v>219</v>
+      </c>
+      <c r="D88" s="34"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="57"/>
+      <c r="H88" s="34"/>
+      <c r="I88" s="34"/>
+      <c r="J88" s="34"/>
+      <c r="K88" s="34"/>
+      <c r="L88" s="34"/>
+      <c r="M88" s="34"/>
+      <c r="N88" s="34"/>
+      <c r="O88" s="34"/>
+      <c r="P88" s="34"/>
+      <c r="Q88" s="34"/>
+      <c r="R88" s="34"/>
+      <c r="S88" s="34"/>
+      <c r="T88" s="34"/>
+      <c r="U88" s="34"/>
+      <c r="V88" s="34"/>
+      <c r="W88" s="34"/>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="41"/>
+      <c r="B89" t="s" s="42">
+        <v>159</v>
+      </c>
+      <c r="C89" t="s" s="42">
+        <v>115</v>
+      </c>
+      <c r="D89" s="34"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="53"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="36"/>
+      <c r="I89" s="36"/>
+      <c r="J89" s="36"/>
+      <c r="K89" s="36"/>
+      <c r="L89" s="36"/>
+      <c r="M89" s="36"/>
+      <c r="N89" s="36"/>
+      <c r="O89" s="36"/>
+      <c r="P89" s="34"/>
+      <c r="Q89" s="41"/>
+      <c r="R89" s="41"/>
+      <c r="S89" s="41"/>
+      <c r="T89" s="34"/>
+      <c r="U89" s="41"/>
+      <c r="V89" s="41"/>
+      <c r="W89" s="41"/>
+    </row>
+    <row r="90" ht="70.45" customHeight="1">
+      <c r="A90" s="34"/>
+      <c r="B90" s="34"/>
+      <c r="C90" s="34"/>
+      <c r="D90" s="34"/>
+      <c r="E90" s="34"/>
+      <c r="F90" s="34"/>
+      <c r="G90" s="34"/>
+      <c r="H90" s="34"/>
+      <c r="I90" s="34"/>
+      <c r="J90" s="34"/>
+      <c r="K90" s="34"/>
+      <c r="L90" s="34"/>
+      <c r="M90" s="34"/>
+      <c r="N90" s="34"/>
+      <c r="O90" s="34"/>
+      <c r="P90" s="34"/>
+      <c r="Q90" s="34"/>
+      <c r="R90" s="34"/>
+      <c r="S90" s="34"/>
+      <c r="T90" s="34"/>
+      <c r="U90" s="34"/>
+      <c r="V90" s="34"/>
+      <c r="W90" s="34"/>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" t="s" s="33">
+        <v>220</v>
+      </c>
+      <c r="B91" s="34"/>
+      <c r="C91" s="34"/>
+      <c r="D91" s="34"/>
+      <c r="E91" s="34"/>
+      <c r="F91" s="34"/>
+      <c r="G91" s="34"/>
+      <c r="H91" s="34"/>
+      <c r="I91" s="34"/>
+      <c r="J91" s="34"/>
+      <c r="K91" s="34"/>
+      <c r="L91" s="34"/>
+      <c r="M91" s="34"/>
+      <c r="N91" s="34"/>
+      <c r="O91" s="34"/>
+      <c r="P91" s="34"/>
+      <c r="Q91" s="34"/>
+      <c r="R91" s="34"/>
+      <c r="S91" s="34"/>
+      <c r="T91" s="34"/>
+      <c r="U91" s="34"/>
+      <c r="V91" s="34"/>
+      <c r="W91" s="34"/>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" t="s" s="35">
+        <v>221</v>
+      </c>
+      <c r="B92" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="C92" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="D92" s="34"/>
+      <c r="E92" t="s" s="35">
+        <v>222</v>
+      </c>
+      <c r="F92" t="s" s="35">
+        <v>105</v>
+      </c>
+      <c r="G92" t="s" s="35">
+        <v>106</v>
+      </c>
+      <c r="H92" s="36"/>
+      <c r="I92" t="s" s="54">
+        <v>223</v>
+      </c>
+      <c r="J92" t="s" s="54">
+        <v>224</v>
+      </c>
+      <c r="K92" t="s" s="54">
+        <v>106</v>
+      </c>
+      <c r="L92" t="s" s="54">
+        <v>225</v>
+      </c>
+      <c r="M92" t="s" s="54">
+        <v>1</v>
+      </c>
+      <c r="N92" s="51"/>
+      <c r="O92" s="51"/>
+      <c r="P92" s="34"/>
+      <c r="Q92" s="52"/>
+      <c r="R92" s="52"/>
+      <c r="S92" s="52"/>
+      <c r="T92" s="34"/>
+      <c r="U92" s="52"/>
+      <c r="V92" s="52"/>
+      <c r="W92" s="52"/>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="J41" t="s" s="26">
-        <v>147</v>
-      </c>
-      <c r="K41" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="L41" s="22"/>
-      <c r="M41" t="s" s="26">
+      <c r="B93" t="s" s="38">
+        <v>226</v>
+      </c>
+      <c r="C93" t="s" s="38">
+        <v>227</v>
+      </c>
+      <c r="D93" s="34"/>
+      <c r="E93" t="s" s="38">
         <v>108</v>
       </c>
-      <c r="N41" t="s" s="26">
-        <v>173</v>
-      </c>
-      <c r="O41" t="s" s="26">
+      <c r="F93" t="s" s="38">
+        <v>159</v>
+      </c>
+      <c r="G93" t="s" s="38">
+        <v>115</v>
+      </c>
+      <c r="H93" s="36"/>
+      <c r="I93" t="s" s="55">
+        <v>228</v>
+      </c>
+      <c r="J93" t="s" s="55">
+        <v>229</v>
+      </c>
+      <c r="K93" t="s" s="55">
         <v>149</v>
       </c>
-      <c r="P41" s="22"/>
-      <c r="Q41" s="22"/>
-      <c r="R41" s="22"/>
-      <c r="S41" s="22"/>
-      <c r="T41" s="22"/>
-      <c r="U41" s="22"/>
-      <c r="V41" s="22"/>
-      <c r="W41" s="22"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="22"/>
-      <c r="B42" s="22"/>
-      <c r="C42" s="22"/>
-      <c r="D42" s="22"/>
-      <c r="E42" s="24"/>
-      <c r="F42" t="s" s="28">
-        <v>147</v>
-      </c>
-      <c r="G42" t="s" s="28">
-        <v>119</v>
-      </c>
-      <c r="H42" s="24"/>
-      <c r="I42" s="24"/>
-      <c r="J42" t="s" s="28">
-        <v>174</v>
-      </c>
-      <c r="K42" t="s" s="28">
+      <c r="L93" s="58">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s" s="55">
+        <v>230</v>
+      </c>
+      <c r="N93" s="34"/>
+      <c r="O93" s="34"/>
+      <c r="P93" s="34"/>
+      <c r="Q93" s="34"/>
+      <c r="R93" s="34"/>
+      <c r="S93" s="34"/>
+      <c r="T93" s="34"/>
+      <c r="U93" s="34"/>
+      <c r="V93" s="34"/>
+      <c r="W93" s="34"/>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="36"/>
+      <c r="B94" t="s" s="40">
+        <v>229</v>
+      </c>
+      <c r="C94" t="s" s="40">
         <v>149</v>
       </c>
-      <c r="L42" s="22"/>
-      <c r="M42" s="24"/>
-      <c r="N42" t="s" s="28">
-        <v>175</v>
-      </c>
-      <c r="O42" t="s" s="28">
-        <v>144</v>
-      </c>
-      <c r="P42" s="22"/>
-      <c r="Q42" s="22"/>
-      <c r="R42" s="22"/>
-      <c r="S42" s="22"/>
-      <c r="T42" s="22"/>
-      <c r="U42" s="22"/>
-      <c r="V42" s="22"/>
-      <c r="W42" s="22"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="22"/>
-      <c r="B43" s="22"/>
-      <c r="C43" s="22"/>
-      <c r="D43" s="22"/>
-      <c r="E43" s="31"/>
-      <c r="F43" t="s" s="26">
-        <v>174</v>
-      </c>
-      <c r="G43" t="s" s="26">
+      <c r="D94" s="34"/>
+      <c r="E94" s="36"/>
+      <c r="F94" t="s" s="40">
+        <v>182</v>
+      </c>
+      <c r="G94" t="s" s="40">
         <v>149</v>
       </c>
-      <c r="H43" s="24"/>
-      <c r="I43" s="31"/>
-      <c r="J43" t="s" s="26">
-        <v>176</v>
-      </c>
-      <c r="K43" t="s" s="26">
-        <v>144</v>
-      </c>
-      <c r="L43" s="22"/>
-      <c r="M43" s="31"/>
-      <c r="N43" s="31"/>
-      <c r="O43" s="31"/>
-      <c r="P43" s="22"/>
-      <c r="Q43" s="22"/>
-      <c r="R43" s="22"/>
-      <c r="S43" s="22"/>
-      <c r="T43" s="22"/>
-      <c r="U43" s="22"/>
-      <c r="V43" s="22"/>
-      <c r="W43" s="22"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="22"/>
-      <c r="B44" s="22"/>
-      <c r="C44" s="22"/>
-      <c r="D44" s="22"/>
-      <c r="E44" s="24"/>
-      <c r="F44" t="s" s="28">
-        <v>177</v>
-      </c>
-      <c r="G44" t="s" s="28">
-        <v>144</v>
-      </c>
-      <c r="H44" s="24"/>
-      <c r="I44" s="22"/>
-      <c r="J44" s="22"/>
-      <c r="K44" s="22"/>
-      <c r="L44" s="22"/>
-      <c r="M44" s="22"/>
-      <c r="N44" s="22"/>
-      <c r="O44" s="22"/>
-      <c r="P44" s="22"/>
-      <c r="Q44" s="22"/>
-      <c r="R44" s="22"/>
-      <c r="S44" s="22"/>
-      <c r="T44" s="22"/>
-      <c r="U44" s="22"/>
-      <c r="V44" s="22"/>
-      <c r="W44" s="22"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="22"/>
-      <c r="B45" s="22"/>
-      <c r="C45" s="22"/>
-      <c r="D45" s="22"/>
-      <c r="E45" s="31"/>
-      <c r="F45" t="s" s="26">
-        <v>176</v>
-      </c>
-      <c r="G45" t="s" s="26">
-        <v>144</v>
-      </c>
-      <c r="H45" s="24"/>
-      <c r="I45" s="22"/>
-      <c r="J45" s="22"/>
-      <c r="K45" s="22"/>
-      <c r="L45" s="22"/>
-      <c r="M45" s="22"/>
-      <c r="N45" s="22"/>
-      <c r="O45" s="22"/>
-      <c r="P45" s="22"/>
-      <c r="Q45" s="22"/>
-      <c r="R45" s="22"/>
-      <c r="S45" s="22"/>
-      <c r="T45" s="22"/>
-      <c r="U45" s="22"/>
-      <c r="V45" s="22"/>
-      <c r="W45" s="22"/>
-    </row>
-    <row r="46" ht="70.1" customHeight="1">
-      <c r="A46" s="22"/>
-      <c r="B46" s="22"/>
-      <c r="C46" s="22"/>
-      <c r="D46" s="22"/>
-      <c r="E46" s="22"/>
-      <c r="F46" s="22"/>
-      <c r="G46" s="22"/>
-      <c r="H46" s="22"/>
-      <c r="I46" s="22"/>
-      <c r="J46" s="22"/>
-      <c r="K46" s="22"/>
-      <c r="L46" s="22"/>
-      <c r="M46" s="22"/>
-      <c r="N46" s="22"/>
-      <c r="O46" s="22"/>
-      <c r="P46" s="22"/>
-      <c r="Q46" s="22"/>
-      <c r="R46" s="22"/>
-      <c r="S46" s="22"/>
-      <c r="T46" s="22"/>
-      <c r="U46" s="22"/>
-      <c r="V46" s="22"/>
-      <c r="W46" s="22"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" t="s" s="21">
-        <v>178</v>
-      </c>
-      <c r="B47" s="22"/>
-      <c r="C47" s="22"/>
-      <c r="D47" s="22"/>
-      <c r="E47" s="22"/>
-      <c r="F47" s="22"/>
-      <c r="G47" s="22"/>
-      <c r="H47" s="22"/>
-      <c r="I47" s="22"/>
-      <c r="J47" s="22"/>
-      <c r="K47" s="22"/>
-      <c r="L47" s="22"/>
-      <c r="M47" s="22"/>
-      <c r="N47" s="22"/>
-      <c r="O47" s="22"/>
-      <c r="P47" s="22"/>
-      <c r="Q47" s="22"/>
-      <c r="R47" s="22"/>
-      <c r="S47" s="22"/>
-      <c r="T47" s="22"/>
-      <c r="U47" s="22"/>
-      <c r="V47" s="22"/>
-      <c r="W47" s="22"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" t="s" s="23">
-        <v>69</v>
-      </c>
-      <c r="B48" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="C48" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="D48" s="22"/>
-      <c r="E48" t="s" s="23">
-        <v>71</v>
-      </c>
-      <c r="F48" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="G48" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="H48" s="24"/>
-      <c r="I48" t="s" s="23">
-        <v>179</v>
-      </c>
-      <c r="J48" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="K48" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="L48" s="24"/>
-      <c r="M48" s="39"/>
-      <c r="N48" s="39"/>
-      <c r="O48" s="39"/>
-      <c r="P48" s="22"/>
-      <c r="Q48" s="40"/>
-      <c r="R48" s="40"/>
-      <c r="S48" s="40"/>
-      <c r="T48" s="22"/>
-      <c r="U48" s="40"/>
-      <c r="V48" s="40"/>
-      <c r="W48" s="40"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="B49" t="s" s="26">
-        <v>180</v>
-      </c>
-      <c r="C49" t="s" s="26">
+      <c r="H94" s="36"/>
+      <c r="I94" t="s" s="56">
+        <v>231</v>
+      </c>
+      <c r="J94" t="s" s="56">
+        <v>232</v>
+      </c>
+      <c r="K94" t="s" s="56">
         <v>149</v>
       </c>
-      <c r="D49" s="22"/>
-      <c r="E49" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="F49" t="s" s="26">
-        <v>181</v>
-      </c>
-      <c r="G49" t="s" s="26">
-        <v>85</v>
-      </c>
-      <c r="H49" s="24"/>
-      <c r="I49" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="J49" t="s" s="26">
-        <v>147</v>
-      </c>
-      <c r="K49" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="L49" s="24"/>
-      <c r="M49" s="22"/>
-      <c r="N49" s="22"/>
-      <c r="O49" s="22"/>
-      <c r="P49" s="22"/>
-      <c r="Q49" s="22"/>
-      <c r="R49" s="22"/>
-      <c r="S49" s="22"/>
-      <c r="T49" s="22"/>
-      <c r="U49" s="22"/>
-      <c r="V49" s="22"/>
-      <c r="W49" s="22"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="24"/>
-      <c r="B50" t="s" s="28">
-        <v>182</v>
-      </c>
-      <c r="C50" t="s" s="28">
-        <v>183</v>
-      </c>
-      <c r="D50" s="22"/>
-      <c r="E50" s="24"/>
-      <c r="F50" t="s" s="28">
-        <v>184</v>
-      </c>
-      <c r="G50" t="s" s="28">
-        <v>85</v>
-      </c>
-      <c r="H50" s="24"/>
-      <c r="I50" s="24"/>
-      <c r="J50" t="s" s="28">
-        <v>174</v>
-      </c>
-      <c r="K50" t="s" s="28">
+      <c r="L94" s="59">
+        <v>20</v>
+      </c>
+      <c r="M94" t="s" s="56">
+        <v>233</v>
+      </c>
+      <c r="N94" s="34"/>
+      <c r="O94" s="34"/>
+      <c r="P94" s="34"/>
+      <c r="Q94" s="34"/>
+      <c r="R94" s="34"/>
+      <c r="S94" s="34"/>
+      <c r="T94" s="34"/>
+      <c r="U94" s="34"/>
+      <c r="V94" s="34"/>
+      <c r="W94" s="34"/>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="43"/>
+      <c r="B95" t="s" s="38">
+        <v>232</v>
+      </c>
+      <c r="C95" t="s" s="38">
         <v>149</v>
       </c>
-      <c r="L50" s="24"/>
-      <c r="M50" s="22"/>
-      <c r="N50" s="22"/>
-      <c r="O50" s="22"/>
-      <c r="P50" s="22"/>
-      <c r="Q50" s="22"/>
-      <c r="R50" s="22"/>
-      <c r="S50" s="22"/>
-      <c r="T50" s="22"/>
-      <c r="U50" s="22"/>
-      <c r="V50" s="22"/>
-      <c r="W50" s="22"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="31"/>
-      <c r="B51" t="s" s="26">
-        <v>185</v>
-      </c>
-      <c r="C51" t="s" s="26">
-        <v>144</v>
-      </c>
-      <c r="D51" s="22"/>
-      <c r="E51" s="31"/>
-      <c r="F51" s="31"/>
-      <c r="G51" s="31"/>
-      <c r="H51" s="24"/>
-      <c r="I51" s="31"/>
-      <c r="J51" t="s" s="26">
-        <v>186</v>
-      </c>
-      <c r="K51" t="s" s="26">
-        <v>144</v>
-      </c>
-      <c r="L51" s="24"/>
-      <c r="M51" s="22"/>
-      <c r="N51" s="22"/>
-      <c r="O51" s="22"/>
-      <c r="P51" s="22"/>
-      <c r="Q51" s="22"/>
-      <c r="R51" s="22"/>
-      <c r="S51" s="22"/>
-      <c r="T51" s="22"/>
-      <c r="U51" s="22"/>
-      <c r="V51" s="22"/>
-      <c r="W51" s="22"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="24"/>
-      <c r="B52" t="s" s="28">
-        <v>159</v>
-      </c>
-      <c r="C52" t="s" s="28">
-        <v>115</v>
-      </c>
-      <c r="D52" s="22"/>
-      <c r="E52" s="22"/>
-      <c r="F52" s="22"/>
-      <c r="G52" s="22"/>
-      <c r="H52" s="24"/>
-      <c r="I52" s="24"/>
-      <c r="J52" t="s" s="28">
-        <v>176</v>
-      </c>
-      <c r="K52" t="s" s="28">
-        <v>144</v>
-      </c>
-      <c r="L52" s="24"/>
-      <c r="M52" s="22"/>
-      <c r="N52" s="22"/>
-      <c r="O52" s="22"/>
-      <c r="P52" s="22"/>
-      <c r="Q52" s="22"/>
-      <c r="R52" s="22"/>
-      <c r="S52" s="22"/>
-      <c r="T52" s="22"/>
-      <c r="U52" s="22"/>
-      <c r="V52" s="22"/>
-      <c r="W52" s="22"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="31"/>
-      <c r="B53" t="s" s="26">
-        <v>171</v>
-      </c>
-      <c r="C53" t="s" s="26">
-        <v>187</v>
-      </c>
-      <c r="D53" s="22"/>
-      <c r="E53" s="22"/>
-      <c r="F53" s="22"/>
-      <c r="G53" s="22"/>
-      <c r="H53" s="24"/>
-      <c r="I53" s="31"/>
-      <c r="J53" s="31"/>
-      <c r="K53" s="31"/>
-      <c r="L53" s="24"/>
-      <c r="M53" s="22"/>
-      <c r="N53" s="22"/>
-      <c r="O53" s="22"/>
-      <c r="P53" s="22"/>
-      <c r="Q53" s="22"/>
-      <c r="R53" s="22"/>
-      <c r="S53" s="22"/>
-      <c r="T53" s="22"/>
-      <c r="U53" s="22"/>
-      <c r="V53" s="22"/>
-      <c r="W53" s="22"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="24"/>
-      <c r="B54" t="s" s="28">
-        <v>188</v>
-      </c>
-      <c r="C54" t="s" s="28">
-        <v>119</v>
-      </c>
-      <c r="D54" s="22"/>
-      <c r="E54" s="22"/>
-      <c r="F54" s="22"/>
-      <c r="G54" s="22"/>
-      <c r="H54" s="22"/>
-      <c r="I54" s="22"/>
-      <c r="J54" s="22"/>
-      <c r="K54" s="22"/>
-      <c r="L54" s="24"/>
-      <c r="M54" s="22"/>
-      <c r="N54" s="22"/>
-      <c r="O54" s="22"/>
-      <c r="P54" s="22"/>
-      <c r="Q54" s="22"/>
-      <c r="R54" s="22"/>
-      <c r="S54" s="22"/>
-      <c r="T54" s="22"/>
-      <c r="U54" s="22"/>
-      <c r="V54" s="22"/>
-      <c r="W54" s="22"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="31"/>
-      <c r="B55" t="s" s="26">
-        <v>189</v>
-      </c>
-      <c r="C55" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="D55" s="22"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="22"/>
-      <c r="G55" s="22"/>
-      <c r="H55" s="22"/>
-      <c r="I55" s="22"/>
-      <c r="J55" s="22"/>
-      <c r="K55" s="22"/>
-      <c r="L55" s="24"/>
-      <c r="M55" s="22"/>
-      <c r="N55" s="22"/>
-      <c r="O55" s="22"/>
-      <c r="P55" s="22"/>
-      <c r="Q55" s="22"/>
-      <c r="R55" s="22"/>
-      <c r="S55" s="22"/>
-      <c r="T55" s="22"/>
-      <c r="U55" s="22"/>
-      <c r="V55" s="22"/>
-      <c r="W55" s="22"/>
-    </row>
-    <row r="56" ht="70.3" customHeight="1">
-      <c r="A56" s="22"/>
-      <c r="B56" s="22"/>
-      <c r="C56" s="22"/>
-      <c r="D56" s="22"/>
-      <c r="E56" s="22"/>
-      <c r="F56" s="22"/>
-      <c r="G56" s="22"/>
-      <c r="H56" s="22"/>
-      <c r="I56" s="22"/>
-      <c r="J56" s="22"/>
-      <c r="K56" s="22"/>
-      <c r="L56" s="24"/>
-      <c r="M56" s="22"/>
-      <c r="N56" s="22"/>
-      <c r="O56" s="22"/>
-      <c r="P56" s="22"/>
-      <c r="Q56" s="22"/>
-      <c r="R56" s="22"/>
-      <c r="S56" s="22"/>
-      <c r="T56" s="22"/>
-      <c r="U56" s="22"/>
-      <c r="V56" s="22"/>
-      <c r="W56" s="22"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" t="s" s="21">
-        <v>190</v>
-      </c>
-      <c r="B57" s="22"/>
-      <c r="C57" s="22"/>
-      <c r="D57" s="22"/>
-      <c r="E57" s="22"/>
-      <c r="F57" s="22"/>
-      <c r="G57" s="22"/>
-      <c r="H57" s="22"/>
-      <c r="I57" s="22"/>
-      <c r="J57" s="22"/>
-      <c r="K57" s="22"/>
-      <c r="L57" s="22"/>
-      <c r="M57" s="22"/>
-      <c r="N57" s="22"/>
-      <c r="O57" s="22"/>
-      <c r="P57" s="22"/>
-      <c r="Q57" s="22"/>
-      <c r="R57" s="22"/>
-      <c r="S57" s="22"/>
-      <c r="T57" s="22"/>
-      <c r="U57" s="22"/>
-      <c r="V57" s="22"/>
-      <c r="W57" s="22"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" t="s" s="23">
-        <v>79</v>
-      </c>
-      <c r="B58" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="C58" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="D58" s="22"/>
-      <c r="E58" t="s" s="23">
-        <v>78</v>
-      </c>
-      <c r="F58" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="G58" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="H58" s="24"/>
-      <c r="I58" s="39"/>
-      <c r="J58" s="39"/>
-      <c r="K58" s="39"/>
-      <c r="L58" s="24"/>
-      <c r="M58" s="39"/>
-      <c r="N58" s="39"/>
-      <c r="O58" s="39"/>
-      <c r="P58" s="22"/>
-      <c r="Q58" s="40"/>
-      <c r="R58" s="40"/>
-      <c r="S58" s="40"/>
-      <c r="T58" s="22"/>
-      <c r="U58" s="40"/>
-      <c r="V58" s="40"/>
-      <c r="W58" s="40"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="B59" t="s" s="26">
-        <v>147</v>
-      </c>
-      <c r="C59" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="D59" s="22"/>
-      <c r="E59" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="F59" t="s" s="26">
-        <v>147</v>
-      </c>
-      <c r="G59" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="H59" s="24"/>
-      <c r="I59" s="22"/>
-      <c r="J59" s="22"/>
-      <c r="K59" s="22"/>
-      <c r="L59" s="22"/>
-      <c r="M59" s="22"/>
-      <c r="N59" s="22"/>
-      <c r="O59" s="22"/>
-      <c r="P59" s="22"/>
-      <c r="Q59" s="22"/>
-      <c r="R59" s="22"/>
-      <c r="S59" s="22"/>
-      <c r="T59" s="22"/>
-      <c r="U59" s="22"/>
-      <c r="V59" s="22"/>
-      <c r="W59" s="22"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="24"/>
-      <c r="B60" t="s" s="28">
-        <v>191</v>
-      </c>
-      <c r="C60" t="s" s="28">
-        <v>192</v>
-      </c>
-      <c r="D60" s="22"/>
-      <c r="E60" s="24"/>
-      <c r="F60" t="s" s="28">
-        <v>193</v>
-      </c>
-      <c r="G60" t="s" s="28">
+      <c r="D95" s="34"/>
+      <c r="E95" s="43"/>
+      <c r="F95" t="s" s="38">
+        <v>234</v>
+      </c>
+      <c r="G95" t="s" s="38">
+        <v>110</v>
+      </c>
+      <c r="H95" s="36"/>
+      <c r="I95" s="57"/>
+      <c r="J95" t="s" s="55">
+        <v>235</v>
+      </c>
+      <c r="K95" t="s" s="55">
+        <v>110</v>
+      </c>
+      <c r="L95" t="s" s="55">
+        <v>236</v>
+      </c>
+      <c r="M95" t="s" s="55">
+        <v>237</v>
+      </c>
+      <c r="N95" s="34"/>
+      <c r="O95" s="34"/>
+      <c r="P95" s="34"/>
+      <c r="Q95" s="34"/>
+      <c r="R95" s="34"/>
+      <c r="S95" s="34"/>
+      <c r="T95" s="34"/>
+      <c r="U95" s="34"/>
+      <c r="V95" s="34"/>
+      <c r="W95" s="34"/>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="36"/>
+      <c r="B96" t="s" s="40">
+        <v>238</v>
+      </c>
+      <c r="C96" t="s" s="40">
+        <v>239</v>
+      </c>
+      <c r="D96" s="34"/>
+      <c r="E96" s="36"/>
+      <c r="F96" t="s" s="40">
+        <v>216</v>
+      </c>
+      <c r="G96" t="s" s="40">
+        <v>110</v>
+      </c>
+      <c r="H96" s="36"/>
+      <c r="I96" s="53"/>
+      <c r="J96" t="s" s="56">
+        <v>240</v>
+      </c>
+      <c r="K96" t="s" s="56">
+        <v>241</v>
+      </c>
+      <c r="L96" t="s" s="56">
+        <v>242</v>
+      </c>
+      <c r="M96" t="s" s="56">
+        <v>243</v>
+      </c>
+      <c r="N96" s="34"/>
+      <c r="O96" s="34"/>
+      <c r="P96" s="34"/>
+      <c r="Q96" s="34"/>
+      <c r="R96" s="34"/>
+      <c r="S96" s="34"/>
+      <c r="T96" s="34"/>
+      <c r="U96" s="34"/>
+      <c r="V96" s="34"/>
+      <c r="W96" s="34"/>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="43"/>
+      <c r="B97" t="s" s="38">
+        <v>244</v>
+      </c>
+      <c r="C97" t="s" s="38">
         <v>149</v>
       </c>
-      <c r="H60" s="24"/>
-      <c r="I60" s="22"/>
-      <c r="J60" s="22"/>
-      <c r="K60" s="22"/>
-      <c r="L60" s="22"/>
-      <c r="M60" s="22"/>
-      <c r="N60" s="22"/>
-      <c r="O60" s="22"/>
-      <c r="P60" s="22"/>
-      <c r="Q60" s="22"/>
-      <c r="R60" s="22"/>
-      <c r="S60" s="22"/>
-      <c r="T60" s="22"/>
-      <c r="U60" s="22"/>
-      <c r="V60" s="22"/>
-      <c r="W60" s="22"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="31"/>
-      <c r="B61" t="s" s="26">
-        <v>193</v>
-      </c>
-      <c r="C61" t="s" s="26">
-        <v>149</v>
-      </c>
-      <c r="D61" s="22"/>
-      <c r="E61" s="31"/>
-      <c r="F61" t="s" s="26">
-        <v>194</v>
-      </c>
-      <c r="G61" t="s" s="26">
+      <c r="D97" s="34"/>
+      <c r="E97" s="43"/>
+      <c r="F97" t="s" s="38">
+        <v>245</v>
+      </c>
+      <c r="G97" t="s" s="38">
         <v>110</v>
       </c>
-      <c r="H61" s="24"/>
-      <c r="I61" s="22"/>
-      <c r="J61" s="22"/>
-      <c r="K61" s="22"/>
-      <c r="L61" s="22"/>
-      <c r="M61" s="22"/>
-      <c r="N61" s="22"/>
-      <c r="O61" s="22"/>
-      <c r="P61" s="22"/>
-      <c r="Q61" s="22"/>
-      <c r="R61" s="22"/>
-      <c r="S61" s="22"/>
-      <c r="T61" s="22"/>
-      <c r="U61" s="22"/>
-      <c r="V61" s="22"/>
-      <c r="W61" s="22"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="24"/>
-      <c r="B62" t="s" s="28">
-        <v>194</v>
-      </c>
-      <c r="C62" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="D62" s="22"/>
-      <c r="E62" s="22"/>
-      <c r="F62" s="22"/>
-      <c r="G62" s="22"/>
-      <c r="H62" s="24"/>
-      <c r="I62" s="22"/>
-      <c r="J62" s="22"/>
-      <c r="K62" s="22"/>
-      <c r="L62" s="22"/>
-      <c r="M62" s="22"/>
-      <c r="N62" s="22"/>
-      <c r="O62" s="22"/>
-      <c r="P62" s="22"/>
-      <c r="Q62" s="22"/>
-      <c r="R62" s="22"/>
-      <c r="S62" s="22"/>
-      <c r="T62" s="22"/>
-      <c r="U62" s="22"/>
-      <c r="V62" s="22"/>
-      <c r="W62" s="22"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="31"/>
-      <c r="B63" t="s" s="26">
-        <v>159</v>
-      </c>
-      <c r="C63" t="s" s="26">
-        <v>115</v>
-      </c>
-      <c r="D63" s="22"/>
-      <c r="E63" s="22"/>
-      <c r="F63" s="22"/>
-      <c r="G63" s="22"/>
-      <c r="H63" s="24"/>
-      <c r="I63" s="22"/>
-      <c r="J63" s="22"/>
-      <c r="K63" s="22"/>
-      <c r="L63" s="22"/>
-      <c r="M63" s="22"/>
-      <c r="N63" s="22"/>
-      <c r="O63" s="22"/>
-      <c r="P63" s="22"/>
-      <c r="Q63" s="22"/>
-      <c r="R63" s="22"/>
-      <c r="S63" s="22"/>
-      <c r="T63" s="22"/>
-      <c r="U63" s="22"/>
-      <c r="V63" s="22"/>
-      <c r="W63" s="22"/>
-    </row>
-    <row r="64" ht="70.7" customHeight="1">
-      <c r="A64" s="24"/>
-      <c r="B64" s="24"/>
-      <c r="C64" s="24"/>
-      <c r="D64" s="22"/>
-      <c r="E64" s="41"/>
-      <c r="F64" s="41"/>
-      <c r="G64" s="41"/>
-      <c r="H64" s="24"/>
-      <c r="I64" s="24"/>
-      <c r="J64" s="24"/>
-      <c r="K64" s="24"/>
-      <c r="L64" s="24"/>
-      <c r="M64" s="24"/>
-      <c r="N64" s="24"/>
-      <c r="O64" s="24"/>
-      <c r="P64" s="22"/>
-      <c r="Q64" s="29"/>
-      <c r="R64" s="29"/>
-      <c r="S64" s="29"/>
-      <c r="T64" s="22"/>
-      <c r="U64" s="29"/>
-      <c r="V64" s="29"/>
-      <c r="W64" s="29"/>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" t="s" s="21">
-        <v>195</v>
-      </c>
-      <c r="B65" s="22"/>
-      <c r="C65" s="22"/>
-      <c r="D65" s="22"/>
-      <c r="E65" s="22"/>
-      <c r="F65" s="22"/>
-      <c r="G65" s="22"/>
-      <c r="H65" s="22"/>
-      <c r="I65" s="22"/>
-      <c r="J65" s="22"/>
-      <c r="K65" s="22"/>
-      <c r="L65" s="22"/>
-      <c r="M65" s="22"/>
-      <c r="N65" s="22"/>
-      <c r="O65" s="22"/>
-      <c r="P65" s="22"/>
-      <c r="Q65" s="22"/>
-      <c r="R65" s="22"/>
-      <c r="S65" s="22"/>
-      <c r="T65" s="22"/>
-      <c r="U65" s="22"/>
-      <c r="V65" s="22"/>
-      <c r="W65" s="22"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" t="s" s="23">
-        <v>85</v>
-      </c>
-      <c r="B66" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="C66" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="D66" s="22"/>
-      <c r="E66" t="s" s="23">
-        <v>84</v>
-      </c>
-      <c r="F66" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="G66" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="H66" s="24"/>
-      <c r="I66" t="s" s="23">
-        <v>88</v>
-      </c>
-      <c r="J66" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="K66" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="L66" s="24"/>
-      <c r="M66" s="39"/>
-      <c r="N66" s="39"/>
-      <c r="O66" s="39"/>
-      <c r="P66" s="22"/>
-      <c r="Q66" s="40"/>
-      <c r="R66" s="40"/>
-      <c r="S66" s="40"/>
-      <c r="T66" s="22"/>
-      <c r="U66" s="40"/>
-      <c r="V66" s="40"/>
-      <c r="W66" s="40"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="B67" t="s" s="26">
-        <v>118</v>
-      </c>
-      <c r="C67" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="D67" s="22"/>
-      <c r="E67" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="F67" t="s" s="26">
-        <v>196</v>
-      </c>
-      <c r="G67" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="H67" s="24"/>
-      <c r="I67" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="J67" t="s" s="26">
-        <v>197</v>
-      </c>
-      <c r="K67" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="L67" s="24"/>
-      <c r="M67" s="22"/>
-      <c r="N67" s="22"/>
-      <c r="O67" s="22"/>
-      <c r="P67" s="22"/>
-      <c r="Q67" s="22"/>
-      <c r="R67" s="22"/>
-      <c r="S67" s="22"/>
-      <c r="T67" s="22"/>
-      <c r="U67" s="22"/>
-      <c r="V67" s="22"/>
-      <c r="W67" s="22"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="24"/>
-      <c r="B68" t="s" s="28">
-        <v>196</v>
-      </c>
-      <c r="C68" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="D68" s="22"/>
-      <c r="E68" s="24"/>
-      <c r="F68" t="s" s="28">
-        <v>198</v>
-      </c>
-      <c r="G68" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="H68" s="24"/>
-      <c r="I68" s="24"/>
-      <c r="J68" t="s" s="28">
-        <v>199</v>
-      </c>
-      <c r="K68" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="L68" s="24"/>
-      <c r="M68" s="22"/>
-      <c r="N68" s="22"/>
-      <c r="O68" s="22"/>
-      <c r="P68" s="22"/>
-      <c r="Q68" s="22"/>
-      <c r="R68" s="22"/>
-      <c r="S68" s="22"/>
-      <c r="T68" s="22"/>
-      <c r="U68" s="22"/>
-      <c r="V68" s="22"/>
-      <c r="W68" s="22"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="31"/>
-      <c r="B69" t="s" s="26">
-        <v>198</v>
-      </c>
-      <c r="C69" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="D69" s="22"/>
-      <c r="E69" s="31"/>
-      <c r="F69" t="s" s="26">
-        <v>200</v>
-      </c>
-      <c r="G69" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="H69" s="24"/>
-      <c r="I69" s="31"/>
-      <c r="J69" t="s" s="26">
-        <v>201</v>
-      </c>
-      <c r="K69" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="L69" s="24"/>
-      <c r="M69" s="22"/>
-      <c r="N69" s="22"/>
-      <c r="O69" s="22"/>
-      <c r="P69" s="22"/>
-      <c r="Q69" s="22"/>
-      <c r="R69" s="22"/>
-      <c r="S69" s="22"/>
-      <c r="T69" s="22"/>
-      <c r="U69" s="22"/>
-      <c r="V69" s="22"/>
-      <c r="W69" s="22"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="24"/>
-      <c r="B70" t="s" s="28">
-        <v>200</v>
-      </c>
-      <c r="C70" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="D70" s="22"/>
-      <c r="E70" s="24"/>
-      <c r="F70" t="s" s="28">
-        <v>202</v>
-      </c>
-      <c r="G70" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="H70" s="24"/>
-      <c r="I70" s="24"/>
-      <c r="J70" t="s" s="28">
-        <v>203</v>
-      </c>
-      <c r="K70" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="L70" s="24"/>
-      <c r="M70" s="22"/>
-      <c r="N70" s="22"/>
-      <c r="O70" s="22"/>
-      <c r="P70" s="22"/>
-      <c r="Q70" s="22"/>
-      <c r="R70" s="22"/>
-      <c r="S70" s="22"/>
-      <c r="T70" s="22"/>
-      <c r="U70" s="22"/>
-      <c r="V70" s="22"/>
-      <c r="W70" s="22"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="31"/>
-      <c r="B71" t="s" s="26">
-        <v>202</v>
-      </c>
-      <c r="C71" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="D71" s="22"/>
-      <c r="E71" s="31"/>
-      <c r="F71" t="s" s="26">
-        <v>204</v>
-      </c>
-      <c r="G71" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="H71" s="24"/>
-      <c r="I71" s="31"/>
-      <c r="J71" t="s" s="26">
-        <v>205</v>
-      </c>
-      <c r="K71" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="L71" s="24"/>
-      <c r="M71" s="22"/>
-      <c r="N71" s="22"/>
-      <c r="O71" s="22"/>
-      <c r="P71" s="22"/>
-      <c r="Q71" s="22"/>
-      <c r="R71" s="22"/>
-      <c r="S71" s="22"/>
-      <c r="T71" s="22"/>
-      <c r="U71" s="22"/>
-      <c r="V71" s="22"/>
-      <c r="W71" s="22"/>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="24"/>
-      <c r="B72" t="s" s="28">
-        <v>204</v>
-      </c>
-      <c r="C72" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="D72" s="22"/>
-      <c r="E72" s="24"/>
-      <c r="F72" t="s" s="28">
-        <v>206</v>
-      </c>
-      <c r="G72" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="H72" s="24"/>
-      <c r="I72" s="24"/>
-      <c r="J72" t="s" s="28">
-        <v>207</v>
-      </c>
-      <c r="K72" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="L72" s="24"/>
-      <c r="M72" s="22"/>
-      <c r="N72" s="22"/>
-      <c r="O72" s="22"/>
-      <c r="P72" s="22"/>
-      <c r="Q72" s="22"/>
-      <c r="R72" s="22"/>
-      <c r="S72" s="22"/>
-      <c r="T72" s="22"/>
-      <c r="U72" s="22"/>
-      <c r="V72" s="22"/>
-      <c r="W72" s="22"/>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="31"/>
-      <c r="B73" t="s" s="26">
-        <v>206</v>
-      </c>
-      <c r="C73" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="D73" s="22"/>
-      <c r="E73" s="31"/>
-      <c r="F73" s="31"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="24"/>
-      <c r="I73" s="31"/>
-      <c r="J73" s="31"/>
-      <c r="K73" s="31"/>
-      <c r="L73" s="24"/>
-      <c r="M73" s="22"/>
-      <c r="N73" s="22"/>
-      <c r="O73" s="22"/>
-      <c r="P73" s="22"/>
-      <c r="Q73" s="22"/>
-      <c r="R73" s="22"/>
-      <c r="S73" s="22"/>
-      <c r="T73" s="22"/>
-      <c r="U73" s="22"/>
-      <c r="V73" s="22"/>
-      <c r="W73" s="22"/>
-    </row>
-    <row r="74" ht="70.2" customHeight="1">
-      <c r="A74" s="24"/>
-      <c r="B74" s="24"/>
-      <c r="C74" s="24"/>
-      <c r="D74" s="22"/>
-      <c r="E74" s="24"/>
-      <c r="F74" s="24"/>
-      <c r="G74" s="24"/>
-      <c r="H74" s="24"/>
-      <c r="I74" s="24"/>
-      <c r="J74" s="24"/>
-      <c r="K74" s="24"/>
-      <c r="L74" s="24"/>
-      <c r="M74" s="24"/>
-      <c r="N74" s="24"/>
-      <c r="O74" s="24"/>
-      <c r="P74" s="22"/>
-      <c r="Q74" s="29"/>
-      <c r="R74" s="29"/>
-      <c r="S74" s="29"/>
-      <c r="T74" s="22"/>
-      <c r="U74" s="29"/>
-      <c r="V74" s="29"/>
-      <c r="W74" s="29"/>
-    </row>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" t="s" s="21">
-        <v>208</v>
-      </c>
-      <c r="B75" s="22"/>
-      <c r="C75" s="22"/>
-      <c r="D75" s="22"/>
-      <c r="E75" s="22"/>
-      <c r="F75" s="22"/>
-      <c r="G75" s="22"/>
-      <c r="H75" s="22"/>
-      <c r="I75" s="22"/>
-      <c r="J75" s="22"/>
-      <c r="K75" s="22"/>
-      <c r="L75" s="22"/>
-      <c r="M75" s="22"/>
-      <c r="N75" s="22"/>
-      <c r="O75" s="22"/>
-      <c r="P75" s="22"/>
-      <c r="Q75" s="22"/>
-      <c r="R75" s="22"/>
-      <c r="S75" s="22"/>
-      <c r="T75" s="22"/>
-      <c r="U75" s="22"/>
-      <c r="V75" s="22"/>
-      <c r="W75" s="22"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" t="s" s="23">
-        <v>95</v>
-      </c>
-      <c r="B76" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="C76" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="D76" s="22"/>
-      <c r="E76" t="s" s="23">
-        <v>94</v>
-      </c>
-      <c r="F76" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="G76" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="H76" s="24"/>
-      <c r="I76" t="s" s="23">
-        <v>98</v>
-      </c>
-      <c r="J76" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="K76" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="L76" s="24"/>
-      <c r="M76" s="39"/>
-      <c r="N76" s="39"/>
-      <c r="O76" s="39"/>
-      <c r="P76" s="22"/>
-      <c r="Q76" s="40"/>
-      <c r="R76" s="40"/>
-      <c r="S76" s="40"/>
-      <c r="T76" s="22"/>
-      <c r="U76" s="40"/>
-      <c r="V76" s="40"/>
-      <c r="W76" s="40"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="B77" t="s" s="26">
-        <v>118</v>
-      </c>
-      <c r="C77" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="D77" s="22"/>
-      <c r="E77" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="F77" t="s" s="26">
-        <v>147</v>
-      </c>
-      <c r="G77" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="H77" s="24"/>
-      <c r="I77" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="J77" t="s" s="26">
-        <v>209</v>
-      </c>
-      <c r="K77" t="s" s="26">
-        <v>210</v>
-      </c>
-      <c r="L77" s="24"/>
-      <c r="M77" s="22"/>
-      <c r="N77" s="22"/>
-      <c r="O77" s="22"/>
-      <c r="P77" s="22"/>
-      <c r="Q77" s="22"/>
-      <c r="R77" s="22"/>
-      <c r="S77" s="22"/>
-      <c r="T77" s="22"/>
-      <c r="U77" s="22"/>
-      <c r="V77" s="22"/>
-      <c r="W77" s="22"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="24"/>
-      <c r="B78" t="s" s="28">
-        <v>211</v>
-      </c>
-      <c r="C78" t="s" s="28">
-        <v>119</v>
-      </c>
-      <c r="D78" s="22"/>
-      <c r="E78" s="24"/>
-      <c r="F78" t="s" s="28">
-        <v>209</v>
-      </c>
-      <c r="G78" t="s" s="28">
-        <v>210</v>
-      </c>
-      <c r="H78" s="24"/>
-      <c r="I78" s="22"/>
-      <c r="J78" s="22"/>
-      <c r="K78" s="22"/>
-      <c r="L78" s="24"/>
-      <c r="M78" s="22"/>
-      <c r="N78" s="22"/>
-      <c r="O78" s="22"/>
-      <c r="P78" s="22"/>
-      <c r="Q78" s="22"/>
-      <c r="R78" s="22"/>
-      <c r="S78" s="22"/>
-      <c r="T78" s="22"/>
-      <c r="U78" s="22"/>
-      <c r="V78" s="22"/>
-      <c r="W78" s="22"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="31"/>
-      <c r="B79" t="s" s="26">
-        <v>147</v>
-      </c>
-      <c r="C79" t="s" s="26">
-        <v>119</v>
-      </c>
-      <c r="D79" s="22"/>
-      <c r="E79" s="31"/>
-      <c r="F79" s="31"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="24"/>
-      <c r="I79" s="22"/>
-      <c r="J79" s="22"/>
-      <c r="K79" s="22"/>
-      <c r="L79" s="24"/>
-      <c r="M79" s="22"/>
-      <c r="N79" s="22"/>
-      <c r="O79" s="22"/>
-      <c r="P79" s="22"/>
-      <c r="Q79" s="22"/>
-      <c r="R79" s="22"/>
-      <c r="S79" s="22"/>
-      <c r="T79" s="22"/>
-      <c r="U79" s="22"/>
-      <c r="V79" s="22"/>
-      <c r="W79" s="22"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="24"/>
-      <c r="B80" t="s" s="28">
-        <v>209</v>
-      </c>
-      <c r="C80" t="s" s="28">
-        <v>210</v>
-      </c>
-      <c r="D80" s="22"/>
-      <c r="E80" s="24"/>
-      <c r="F80" s="24"/>
-      <c r="G80" s="24"/>
-      <c r="H80" s="24"/>
-      <c r="I80" s="24"/>
-      <c r="J80" s="24"/>
-      <c r="K80" s="24"/>
-      <c r="L80" s="24"/>
-      <c r="M80" s="24"/>
-      <c r="N80" s="24"/>
-      <c r="O80" s="24"/>
-      <c r="P80" s="22"/>
-      <c r="Q80" s="29"/>
-      <c r="R80" s="29"/>
-      <c r="S80" s="29"/>
-      <c r="T80" s="22"/>
-      <c r="U80" s="29"/>
-      <c r="V80" s="29"/>
-      <c r="W80" s="29"/>
-    </row>
-    <row r="81" ht="70.5" customHeight="1">
-      <c r="A81" s="24"/>
-      <c r="B81" s="24"/>
-      <c r="C81" s="24"/>
-      <c r="D81" s="22"/>
-      <c r="E81" s="41"/>
-      <c r="F81" s="41"/>
-      <c r="G81" s="41"/>
-      <c r="H81" s="24"/>
-      <c r="I81" s="24"/>
-      <c r="J81" s="24"/>
-      <c r="K81" s="24"/>
-      <c r="L81" s="24"/>
-      <c r="M81" s="24"/>
-      <c r="N81" s="24"/>
-      <c r="O81" s="24"/>
-      <c r="P81" s="22"/>
-      <c r="Q81" s="29"/>
-      <c r="R81" s="29"/>
-      <c r="S81" s="29"/>
-      <c r="T81" s="22"/>
-      <c r="U81" s="29"/>
-      <c r="V81" s="29"/>
-      <c r="W81" s="29"/>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" t="s" s="21">
-        <v>212</v>
-      </c>
-      <c r="B82" s="22"/>
-      <c r="C82" s="22"/>
-      <c r="D82" s="22"/>
-      <c r="E82" s="22"/>
-      <c r="F82" s="22"/>
-      <c r="G82" s="22"/>
-      <c r="H82" s="22"/>
-      <c r="I82" s="22"/>
-      <c r="J82" s="22"/>
-      <c r="K82" s="22"/>
-      <c r="L82" s="22"/>
-      <c r="M82" s="22"/>
-      <c r="N82" s="22"/>
-      <c r="O82" s="22"/>
-      <c r="P82" s="22"/>
-      <c r="Q82" s="22"/>
-      <c r="R82" s="22"/>
-      <c r="S82" s="22"/>
-      <c r="T82" s="22"/>
-      <c r="U82" s="22"/>
-      <c r="V82" s="22"/>
-      <c r="W82" s="22"/>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" t="s" s="25">
-        <v>213</v>
-      </c>
-      <c r="B83" t="s" s="25">
-        <v>105</v>
-      </c>
-      <c r="C83" t="s" s="25">
-        <v>106</v>
-      </c>
-      <c r="D83" s="22"/>
-      <c r="E83" t="s" s="42">
-        <v>214</v>
-      </c>
-      <c r="F83" t="s" s="42">
-        <v>105</v>
-      </c>
-      <c r="G83" t="s" s="42">
-        <v>106</v>
-      </c>
-      <c r="H83" s="24"/>
-      <c r="I83" s="39"/>
-      <c r="J83" s="39"/>
-      <c r="K83" s="39"/>
-      <c r="L83" s="24"/>
-      <c r="M83" s="39"/>
-      <c r="N83" s="39"/>
-      <c r="O83" s="39"/>
-      <c r="P83" s="22"/>
-      <c r="Q83" s="40"/>
-      <c r="R83" s="40"/>
-      <c r="S83" s="40"/>
-      <c r="T83" s="22"/>
-      <c r="U83" s="40"/>
-      <c r="V83" s="40"/>
-      <c r="W83" s="40"/>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" t="s" s="27">
-        <v>112</v>
-      </c>
-      <c r="B84" t="s" s="27">
-        <v>118</v>
-      </c>
-      <c r="C84" t="s" s="27">
-        <v>119</v>
-      </c>
-      <c r="D84" s="22"/>
-      <c r="E84" t="s" s="43">
-        <v>215</v>
-      </c>
-      <c r="F84" t="s" s="43">
-        <v>216</v>
-      </c>
-      <c r="G84" t="s" s="43">
-        <v>110</v>
-      </c>
-      <c r="H84" s="22"/>
-      <c r="I84" s="22"/>
-      <c r="J84" s="22"/>
-      <c r="K84" s="22"/>
-      <c r="L84" s="22"/>
-      <c r="M84" s="22"/>
-      <c r="N84" s="22"/>
-      <c r="O84" s="22"/>
-      <c r="P84" s="22"/>
-      <c r="Q84" s="22"/>
-      <c r="R84" s="22"/>
-      <c r="S84" s="22"/>
-      <c r="T84" s="22"/>
-      <c r="U84" s="22"/>
-      <c r="V84" s="22"/>
-      <c r="W84" s="22"/>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="29"/>
-      <c r="B85" t="s" s="30">
-        <v>211</v>
-      </c>
-      <c r="C85" t="s" s="30">
-        <v>119</v>
-      </c>
-      <c r="D85" s="22"/>
-      <c r="E85" s="41"/>
-      <c r="F85" t="s" s="44">
-        <v>217</v>
-      </c>
-      <c r="G85" t="s" s="44">
-        <v>218</v>
-      </c>
-      <c r="H85" s="22"/>
-      <c r="I85" s="22"/>
-      <c r="J85" s="22"/>
-      <c r="K85" s="22"/>
-      <c r="L85" s="22"/>
-      <c r="M85" s="22"/>
-      <c r="N85" s="22"/>
-      <c r="O85" s="22"/>
-      <c r="P85" s="22"/>
-      <c r="Q85" s="22"/>
-      <c r="R85" s="22"/>
-      <c r="S85" s="22"/>
-      <c r="T85" s="22"/>
-      <c r="U85" s="22"/>
-      <c r="V85" s="22"/>
-      <c r="W85" s="22"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="32"/>
-      <c r="B86" t="s" s="27">
-        <v>216</v>
-      </c>
-      <c r="C86" t="s" s="27">
-        <v>110</v>
-      </c>
-      <c r="D86" s="22"/>
-      <c r="E86" s="45"/>
-      <c r="F86" t="s" s="43">
-        <v>182</v>
-      </c>
-      <c r="G86" t="s" s="43">
-        <v>219</v>
-      </c>
-      <c r="H86" s="22"/>
-      <c r="I86" s="22"/>
-      <c r="J86" s="22"/>
-      <c r="K86" s="22"/>
-      <c r="L86" s="22"/>
-      <c r="M86" s="22"/>
-      <c r="N86" s="22"/>
-      <c r="O86" s="22"/>
-      <c r="P86" s="22"/>
-      <c r="Q86" s="22"/>
-      <c r="R86" s="22"/>
-      <c r="S86" s="22"/>
-      <c r="T86" s="22"/>
-      <c r="U86" s="22"/>
-      <c r="V86" s="22"/>
-      <c r="W86" s="22"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="29"/>
-      <c r="B87" t="s" s="30">
-        <v>217</v>
-      </c>
-      <c r="C87" t="s" s="30">
-        <v>218</v>
-      </c>
-      <c r="D87" s="22"/>
-      <c r="E87" s="41"/>
-      <c r="F87" t="s" s="44">
-        <v>159</v>
-      </c>
-      <c r="G87" t="s" s="44">
-        <v>115</v>
-      </c>
-      <c r="H87" s="22"/>
-      <c r="I87" s="22"/>
-      <c r="J87" s="22"/>
-      <c r="K87" s="22"/>
-      <c r="L87" s="22"/>
-      <c r="M87" s="22"/>
-      <c r="N87" s="22"/>
-      <c r="O87" s="22"/>
-      <c r="P87" s="22"/>
-      <c r="Q87" s="22"/>
-      <c r="R87" s="22"/>
-      <c r="S87" s="22"/>
-      <c r="T87" s="22"/>
-      <c r="U87" s="22"/>
-      <c r="V87" s="22"/>
-      <c r="W87" s="22"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="32"/>
-      <c r="B88" t="s" s="27">
-        <v>182</v>
-      </c>
-      <c r="C88" t="s" s="27">
-        <v>219</v>
-      </c>
-      <c r="D88" s="22"/>
-      <c r="E88" s="45"/>
-      <c r="F88" s="45"/>
-      <c r="G88" s="45"/>
-      <c r="H88" s="22"/>
-      <c r="I88" s="22"/>
-      <c r="J88" s="22"/>
-      <c r="K88" s="22"/>
-      <c r="L88" s="22"/>
-      <c r="M88" s="22"/>
-      <c r="N88" s="22"/>
-      <c r="O88" s="22"/>
-      <c r="P88" s="22"/>
-      <c r="Q88" s="22"/>
-      <c r="R88" s="22"/>
-      <c r="S88" s="22"/>
-      <c r="T88" s="22"/>
-      <c r="U88" s="22"/>
-      <c r="V88" s="22"/>
-      <c r="W88" s="22"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="29"/>
-      <c r="B89" t="s" s="30">
-        <v>159</v>
-      </c>
-      <c r="C89" t="s" s="30">
-        <v>115</v>
-      </c>
-      <c r="D89" s="22"/>
-      <c r="E89" s="41"/>
-      <c r="F89" s="41"/>
-      <c r="G89" s="41"/>
-      <c r="H89" s="24"/>
-      <c r="I89" s="24"/>
-      <c r="J89" s="24"/>
-      <c r="K89" s="24"/>
-      <c r="L89" s="24"/>
-      <c r="M89" s="24"/>
-      <c r="N89" s="24"/>
-      <c r="O89" s="24"/>
-      <c r="P89" s="22"/>
-      <c r="Q89" s="29"/>
-      <c r="R89" s="29"/>
-      <c r="S89" s="29"/>
-      <c r="T89" s="22"/>
-      <c r="U89" s="29"/>
-      <c r="V89" s="29"/>
-      <c r="W89" s="29"/>
-    </row>
-    <row r="90" ht="70.45" customHeight="1">
-      <c r="A90" s="22"/>
-      <c r="B90" s="22"/>
-      <c r="C90" s="22"/>
-      <c r="D90" s="22"/>
-      <c r="E90" s="22"/>
-      <c r="F90" s="22"/>
-      <c r="G90" s="22"/>
-      <c r="H90" s="22"/>
-      <c r="I90" s="22"/>
-      <c r="J90" s="22"/>
-      <c r="K90" s="22"/>
-      <c r="L90" s="22"/>
-      <c r="M90" s="22"/>
-      <c r="N90" s="22"/>
-      <c r="O90" s="22"/>
-      <c r="P90" s="22"/>
-      <c r="Q90" s="22"/>
-      <c r="R90" s="22"/>
-      <c r="S90" s="22"/>
-      <c r="T90" s="22"/>
-      <c r="U90" s="22"/>
-      <c r="V90" s="22"/>
-      <c r="W90" s="22"/>
-    </row>
-    <row r="91" ht="34" customHeight="1">
-      <c r="A91" t="s" s="21">
-        <v>220</v>
-      </c>
-      <c r="B91" s="22"/>
-      <c r="C91" s="22"/>
-      <c r="D91" s="22"/>
-      <c r="E91" s="22"/>
-      <c r="F91" s="22"/>
-      <c r="G91" s="22"/>
-      <c r="H91" s="22"/>
-      <c r="I91" s="22"/>
-      <c r="J91" s="22"/>
-      <c r="K91" s="22"/>
-      <c r="L91" s="22"/>
-      <c r="M91" s="22"/>
-      <c r="N91" s="22"/>
-      <c r="O91" s="22"/>
-      <c r="P91" s="22"/>
-      <c r="Q91" s="22"/>
-      <c r="R91" s="22"/>
-      <c r="S91" s="22"/>
-      <c r="T91" s="22"/>
-      <c r="U91" s="22"/>
-      <c r="V91" s="22"/>
-      <c r="W91" s="22"/>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" t="s" s="23">
-        <v>221</v>
-      </c>
-      <c r="B92" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="C92" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="D92" s="22"/>
-      <c r="E92" t="s" s="23">
-        <v>222</v>
-      </c>
-      <c r="F92" t="s" s="23">
-        <v>105</v>
-      </c>
-      <c r="G92" t="s" s="23">
-        <v>106</v>
-      </c>
-      <c r="H92" s="24"/>
-      <c r="I92" t="s" s="42">
-        <v>223</v>
-      </c>
-      <c r="J92" t="s" s="42">
-        <v>224</v>
-      </c>
-      <c r="K92" t="s" s="42">
-        <v>106</v>
-      </c>
-      <c r="L92" t="s" s="42">
-        <v>225</v>
-      </c>
-      <c r="M92" t="s" s="42">
-        <v>1</v>
-      </c>
-      <c r="N92" s="39"/>
-      <c r="O92" s="39"/>
-      <c r="P92" s="22"/>
-      <c r="Q92" s="40"/>
-      <c r="R92" s="40"/>
-      <c r="S92" s="40"/>
-      <c r="T92" s="22"/>
-      <c r="U92" s="40"/>
-      <c r="V92" s="40"/>
-      <c r="W92" s="40"/>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="B93" t="s" s="26">
-        <v>226</v>
-      </c>
-      <c r="C93" t="s" s="26">
-        <v>227</v>
-      </c>
-      <c r="D93" s="22"/>
-      <c r="E93" t="s" s="26">
-        <v>108</v>
-      </c>
-      <c r="F93" t="s" s="26">
-        <v>159</v>
-      </c>
-      <c r="G93" t="s" s="26">
-        <v>115</v>
-      </c>
-      <c r="H93" s="24"/>
-      <c r="I93" t="s" s="43">
-        <v>228</v>
-      </c>
-      <c r="J93" t="s" s="43">
-        <v>229</v>
-      </c>
-      <c r="K93" t="s" s="43">
-        <v>149</v>
-      </c>
-      <c r="L93" s="46">
-        <v>0</v>
-      </c>
-      <c r="M93" t="s" s="43">
-        <v>230</v>
-      </c>
-      <c r="N93" s="22"/>
-      <c r="O93" s="22"/>
-      <c r="P93" s="22"/>
-      <c r="Q93" s="22"/>
-      <c r="R93" s="22"/>
-      <c r="S93" s="22"/>
-      <c r="T93" s="22"/>
-      <c r="U93" s="22"/>
-      <c r="V93" s="22"/>
-      <c r="W93" s="22"/>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="24"/>
-      <c r="B94" t="s" s="28">
-        <v>229</v>
-      </c>
-      <c r="C94" t="s" s="28">
-        <v>149</v>
-      </c>
-      <c r="D94" s="22"/>
-      <c r="E94" s="24"/>
-      <c r="F94" t="s" s="28">
-        <v>182</v>
-      </c>
-      <c r="G94" t="s" s="28">
-        <v>149</v>
-      </c>
-      <c r="H94" s="24"/>
-      <c r="I94" t="s" s="44">
-        <v>231</v>
-      </c>
-      <c r="J94" t="s" s="44">
-        <v>232</v>
-      </c>
-      <c r="K94" t="s" s="44">
-        <v>149</v>
-      </c>
-      <c r="L94" s="47">
-        <v>20</v>
-      </c>
-      <c r="M94" t="s" s="44">
-        <v>233</v>
-      </c>
-      <c r="N94" s="22"/>
-      <c r="O94" s="22"/>
-      <c r="P94" s="22"/>
-      <c r="Q94" s="22"/>
-      <c r="R94" s="22"/>
-      <c r="S94" s="22"/>
-      <c r="T94" s="22"/>
-      <c r="U94" s="22"/>
-      <c r="V94" s="22"/>
-      <c r="W94" s="22"/>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="31"/>
-      <c r="B95" t="s" s="26">
-        <v>232</v>
-      </c>
-      <c r="C95" t="s" s="26">
-        <v>149</v>
-      </c>
-      <c r="D95" s="22"/>
-      <c r="E95" s="31"/>
-      <c r="F95" t="s" s="26">
-        <v>234</v>
-      </c>
-      <c r="G95" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="H95" s="24"/>
-      <c r="I95" s="45"/>
-      <c r="J95" t="s" s="43">
+      <c r="H97" s="36"/>
+      <c r="I97" s="57"/>
+      <c r="J97" s="57"/>
+      <c r="K97" s="57"/>
+      <c r="L97" s="57"/>
+      <c r="M97" s="57"/>
+      <c r="N97" s="34"/>
+      <c r="O97" s="34"/>
+      <c r="P97" s="34"/>
+      <c r="Q97" s="34"/>
+      <c r="R97" s="34"/>
+      <c r="S97" s="34"/>
+      <c r="T97" s="34"/>
+      <c r="U97" s="34"/>
+      <c r="V97" s="34"/>
+      <c r="W97" s="34"/>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="36"/>
+      <c r="B98" t="s" s="40">
         <v>235</v>
       </c>
-      <c r="K95" t="s" s="43">
-        <v>110</v>
-      </c>
-      <c r="L95" t="s" s="43">
-        <v>236</v>
-      </c>
-      <c r="M95" t="s" s="43">
-        <v>237</v>
-      </c>
-      <c r="N95" s="22"/>
-      <c r="O95" s="22"/>
-      <c r="P95" s="22"/>
-      <c r="Q95" s="22"/>
-      <c r="R95" s="22"/>
-      <c r="S95" s="22"/>
-      <c r="T95" s="22"/>
-      <c r="U95" s="22"/>
-      <c r="V95" s="22"/>
-      <c r="W95" s="22"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="24"/>
-      <c r="B96" t="s" s="28">
-        <v>238</v>
-      </c>
-      <c r="C96" t="s" s="28">
-        <v>239</v>
-      </c>
-      <c r="D96" s="22"/>
-      <c r="E96" s="24"/>
-      <c r="F96" t="s" s="28">
-        <v>216</v>
-      </c>
-      <c r="G96" t="s" s="28">
-        <v>110</v>
-      </c>
-      <c r="H96" s="24"/>
-      <c r="I96" s="41"/>
-      <c r="J96" t="s" s="44">
-        <v>240</v>
-      </c>
-      <c r="K96" t="s" s="44">
-        <v>241</v>
-      </c>
-      <c r="L96" t="s" s="44">
-        <v>242</v>
-      </c>
-      <c r="M96" t="s" s="44">
-        <v>243</v>
-      </c>
-      <c r="N96" s="22"/>
-      <c r="O96" s="22"/>
-      <c r="P96" s="22"/>
-      <c r="Q96" s="22"/>
-      <c r="R96" s="22"/>
-      <c r="S96" s="22"/>
-      <c r="T96" s="22"/>
-      <c r="U96" s="22"/>
-      <c r="V96" s="22"/>
-      <c r="W96" s="22"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="31"/>
-      <c r="B97" t="s" s="26">
-        <v>244</v>
-      </c>
-      <c r="C97" t="s" s="26">
-        <v>149</v>
-      </c>
-      <c r="D97" s="22"/>
-      <c r="E97" s="31"/>
-      <c r="F97" t="s" s="26">
-        <v>245</v>
-      </c>
-      <c r="G97" t="s" s="26">
-        <v>110</v>
-      </c>
-      <c r="H97" s="24"/>
-      <c r="I97" s="45"/>
-      <c r="J97" s="45"/>
-      <c r="K97" s="45"/>
-      <c r="L97" s="45"/>
-      <c r="M97" s="45"/>
-      <c r="N97" s="22"/>
-      <c r="O97" s="22"/>
-      <c r="P97" s="22"/>
-      <c r="Q97" s="22"/>
-      <c r="R97" s="22"/>
-      <c r="S97" s="22"/>
-      <c r="T97" s="22"/>
-      <c r="U97" s="22"/>
-      <c r="V97" s="22"/>
-      <c r="W97" s="22"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="24"/>
-      <c r="B98" t="s" s="28">
-        <v>235</v>
-      </c>
-      <c r="C98" t="s" s="28">
+      <c r="C98" t="s" s="40">
         <v>246</v>
       </c>
-      <c r="D98" s="22"/>
-      <c r="E98" s="24"/>
-      <c r="F98" s="24"/>
-      <c r="G98" s="24"/>
-      <c r="H98" s="24"/>
-      <c r="I98" s="24"/>
-      <c r="J98" s="24"/>
-      <c r="K98" s="24"/>
-      <c r="L98" s="22"/>
-      <c r="M98" s="22"/>
-      <c r="N98" s="22"/>
-      <c r="O98" s="22"/>
-      <c r="P98" s="22"/>
-      <c r="Q98" s="22"/>
-      <c r="R98" s="22"/>
-      <c r="S98" s="22"/>
-      <c r="T98" s="22"/>
-      <c r="U98" s="22"/>
-      <c r="V98" s="22"/>
-      <c r="W98" s="22"/>
+      <c r="D98" s="34"/>
+      <c r="E98" s="36"/>
+      <c r="F98" s="36"/>
+      <c r="G98" s="36"/>
+      <c r="H98" s="36"/>
+      <c r="I98" s="36"/>
+      <c r="J98" s="36"/>
+      <c r="K98" s="36"/>
+      <c r="L98" s="34"/>
+      <c r="M98" s="34"/>
+      <c r="N98" s="34"/>
+      <c r="O98" s="34"/>
+      <c r="P98" s="34"/>
+      <c r="Q98" s="34"/>
+      <c r="R98" s="34"/>
+      <c r="S98" s="34"/>
+      <c r="T98" s="34"/>
+      <c r="U98" s="34"/>
+      <c r="V98" s="34"/>
+      <c r="W98" s="34"/>
     </row>
     <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="31"/>
-      <c r="B99" t="s" s="26">
+      <c r="A99" s="43"/>
+      <c r="B99" t="s" s="38">
         <v>247</v>
       </c>
-      <c r="C99" t="s" s="26">
+      <c r="C99" t="s" s="38">
         <v>248</v>
       </c>
-      <c r="D99" s="22"/>
-      <c r="E99" s="33"/>
-      <c r="F99" s="34"/>
-      <c r="G99" s="34"/>
-      <c r="H99" s="34"/>
-      <c r="I99" s="34"/>
-      <c r="J99" s="34"/>
-      <c r="K99" s="35"/>
-      <c r="L99" s="22"/>
-      <c r="M99" s="22"/>
-      <c r="N99" s="22"/>
-      <c r="O99" s="22"/>
-      <c r="P99" s="22"/>
-      <c r="Q99" s="22"/>
-      <c r="R99" s="22"/>
-      <c r="S99" s="22"/>
-      <c r="T99" s="22"/>
-      <c r="U99" s="22"/>
-      <c r="V99" s="22"/>
-      <c r="W99" s="22"/>
+      <c r="D99" s="34"/>
+      <c r="E99" s="45"/>
+      <c r="F99" s="46"/>
+      <c r="G99" s="46"/>
+      <c r="H99" s="46"/>
+      <c r="I99" s="46"/>
+      <c r="J99" s="46"/>
+      <c r="K99" s="47"/>
+      <c r="L99" s="34"/>
+      <c r="M99" s="34"/>
+      <c r="N99" s="34"/>
+      <c r="O99" s="34"/>
+      <c r="P99" s="34"/>
+      <c r="Q99" s="34"/>
+      <c r="R99" s="34"/>
+      <c r="S99" s="34"/>
+      <c r="T99" s="34"/>
+      <c r="U99" s="34"/>
+      <c r="V99" s="34"/>
+      <c r="W99" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5944,19 +6152,19 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="12" customWidth="1"/>
-    <col min="2" max="2" width="35" style="12" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="12" customWidth="1"/>
-    <col min="4" max="4" width="28.1719" style="12" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="12" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="12" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="12" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="12" customWidth="1"/>
-    <col min="9" max="9" width="11" style="12" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="12" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="21" customWidth="1"/>
+    <col min="2" max="2" width="35" style="21" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="21" customWidth="1"/>
+    <col min="4" max="4" width="28.1719" style="21" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="21" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="21" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="21" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="21" customWidth="1"/>
+    <col min="9" max="9" width="11" style="21" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="21" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6066,6 +6274,72 @@
         <v>40</v>
       </c>
       <c r="I4" s="7"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6078,19 +6352,19 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I7"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="13" customWidth="1"/>
-    <col min="2" max="2" width="35" style="13" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="13" customWidth="1"/>
-    <col min="4" max="4" width="84.3828" style="13" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="13" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="13" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="13" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="13" customWidth="1"/>
-    <col min="9" max="9" width="11" style="13" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="13" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="22" customWidth="1"/>
+    <col min="2" max="2" width="35" style="22" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="22" customWidth="1"/>
+    <col min="4" max="4" width="84.3516" style="22" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="22" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="22" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="22" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="22" customWidth="1"/>
+    <col min="9" max="9" width="11" style="22" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="22" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6281,6 +6555,39 @@
         <v>17</v>
       </c>
       <c r="I7" s="3"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13"/>
+      <c r="C8" s="13"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="13"/>
+      <c r="F8" s="13"/>
+      <c r="G8" s="13"/>
+      <c r="H8" s="13"/>
+      <c r="I8" s="14"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6293,19 +6600,19 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="14" customWidth="1"/>
-    <col min="2" max="2" width="35" style="14" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="14" customWidth="1"/>
-    <col min="4" max="4" width="28.1719" style="14" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="14" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="14" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="14" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="14" customWidth="1"/>
-    <col min="9" max="9" width="11" style="14" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="14" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="23" customWidth="1"/>
+    <col min="2" max="2" width="35" style="23" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="23" customWidth="1"/>
+    <col min="4" max="4" width="28.1719" style="23" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="23" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="23" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="23" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="23" customWidth="1"/>
+    <col min="9" max="9" width="11" style="23" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="23" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6469,6 +6776,50 @@
         <v>17</v>
       </c>
       <c r="I6" s="7"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6481,19 +6832,19 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I5"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="15" customWidth="1"/>
-    <col min="2" max="2" width="35" style="15" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="15" customWidth="1"/>
-    <col min="4" max="4" width="36.8438" style="15" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="15" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="15" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="15" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="15" customWidth="1"/>
-    <col min="9" max="9" width="11" style="15" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="15" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="24" customWidth="1"/>
+    <col min="2" max="2" width="35" style="24" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="24" customWidth="1"/>
+    <col min="4" max="4" width="36.8516" style="24" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="24" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="24" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="24" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="24" customWidth="1"/>
+    <col min="9" max="9" width="11" style="24" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="24" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6630,6 +6981,61 @@
         <v>69</v>
       </c>
       <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13"/>
+      <c r="C6" s="13"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="13"/>
+      <c r="F6" s="13"/>
+      <c r="G6" s="13"/>
+      <c r="H6" s="13"/>
+      <c r="I6" s="14"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6642,19 +7048,19 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I4"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="16" customWidth="1"/>
-    <col min="2" max="2" width="35" style="16" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="16" customWidth="1"/>
-    <col min="4" max="4" width="44.5" style="16" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="16" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="16" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="16" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="16" customWidth="1"/>
-    <col min="9" max="9" width="11" style="16" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="16" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="25" customWidth="1"/>
+    <col min="2" max="2" width="35" style="25" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="25" customWidth="1"/>
+    <col min="4" max="4" width="44.5" style="25" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="25" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="25" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="25" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="25" customWidth="1"/>
+    <col min="9" max="9" width="11" style="25" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6764,6 +7170,72 @@
         <v>79</v>
       </c>
       <c r="I4" s="7"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="14"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6776,19 +7248,19 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="17" customWidth="1"/>
-    <col min="2" max="2" width="35" style="17" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="17" customWidth="1"/>
-    <col min="4" max="4" width="42.0312" style="17" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="17" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="17" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="17" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="17" customWidth="1"/>
-    <col min="9" max="9" width="11" style="17" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="17" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="26" customWidth="1"/>
+    <col min="2" max="2" width="35" style="26" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="26" customWidth="1"/>
+    <col min="4" max="4" width="42" style="26" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="26" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="26" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="26" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="26" customWidth="1"/>
+    <col min="9" max="9" width="11" style="26" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="26" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6952,6 +7424,50 @@
         <v>17</v>
       </c>
       <c r="I6" s="7"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6964,19 +7480,19 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="18" customWidth="1"/>
-    <col min="2" max="2" width="35" style="18" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="18" customWidth="1"/>
-    <col min="4" max="4" width="42.0312" style="18" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="18" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="18" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="18" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="18" customWidth="1"/>
-    <col min="9" max="9" width="11" style="18" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="18" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="27" customWidth="1"/>
+    <col min="2" max="2" width="35" style="27" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="27" customWidth="1"/>
+    <col min="4" max="4" width="42" style="27" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="27" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="27" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="27" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="27" customWidth="1"/>
+    <col min="9" max="9" width="11" style="27" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="27" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -7140,6 +7656,50 @@
         <v>17</v>
       </c>
       <c r="I6" s="7"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7152,19 +7712,19 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="19" customWidth="1"/>
-    <col min="2" max="2" width="35" style="19" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="19" customWidth="1"/>
-    <col min="4" max="4" width="67.3281" style="19" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="19" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="19" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="19" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="19" customWidth="1"/>
-    <col min="9" max="9" width="11" style="19" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="19" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="28" customWidth="1"/>
+    <col min="2" max="2" width="35" style="28" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="28" customWidth="1"/>
+    <col min="4" max="4" width="67.3516" style="28" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="28" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="28" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="28" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="28" customWidth="1"/>
+    <col min="9" max="9" width="11" style="28" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="28" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -7247,6 +7807,83 @@
         <v>103</v>
       </c>
       <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" s="12"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="14"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="17"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="17"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/docs/rest-api.xlsx
+++ b/docs/rest-api.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="249">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="250">
   <si>
     <t>URI-Template</t>
   </si>
@@ -209,6 +209,9 @@
   </si>
   <si>
     <t>Remove item from cart</t>
+  </si>
+  <si>
+    <t>Clear cart</t>
   </si>
   <si>
     <t>/orders</t>
@@ -875,7 +878,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="27">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1061,6 +1064,19 @@
       <left style="thin">
         <color indexed="10"/>
       </left>
+      <right style="thin">
+        <color indexed="10"/>
+      </right>
+      <top style="thin">
+        <color indexed="10"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="10"/>
+      </left>
       <right/>
       <top style="thin">
         <color indexed="10"/>
@@ -1205,7 +1221,7 @@
       <alignment vertical="bottom"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" applyNumberFormat="0" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1278,6 +1294,9 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
@@ -1296,52 +1315,49 @@
     <xf numFmtId="0" fontId="0" applyNumberFormat="1" applyFont="1" applyFill="0" applyBorder="0" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="18" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="19" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="4" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="7" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="4" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="5" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="49" fontId="8" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
-      <alignment vertical="bottom"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="4" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="7" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="4" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="5" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="22" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
@@ -1359,31 +1375,34 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="26" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="27" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="10" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="6" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="10" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="49" fontId="9" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="6" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="49" fontId="9" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" applyNumberFormat="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+      <alignment vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="20" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="21" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="0">
       <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
@@ -2725,3421 +2744,3421 @@
   <dimension ref="A1:W99"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="23" style="29" customWidth="1"/>
-    <col min="2" max="2" width="17.5" style="29" customWidth="1"/>
-    <col min="3" max="3" width="21.8516" style="29" customWidth="1"/>
-    <col min="4" max="4" width="11" style="29" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="29" customWidth="1"/>
-    <col min="6" max="6" width="15.3516" style="29" customWidth="1"/>
-    <col min="7" max="7" width="21.8516" style="29" customWidth="1"/>
-    <col min="8" max="8" width="11" style="29" customWidth="1"/>
-    <col min="9" max="9" width="24.3516" style="29" customWidth="1"/>
-    <col min="10" max="10" width="16.5" style="29" customWidth="1"/>
-    <col min="11" max="11" width="21.8516" style="29" customWidth="1"/>
-    <col min="12" max="12" width="11" style="29" customWidth="1"/>
-    <col min="13" max="13" width="27.5" style="29" customWidth="1"/>
-    <col min="14" max="14" width="16.5" style="29" customWidth="1"/>
-    <col min="15" max="15" width="22.1719" style="29" customWidth="1"/>
-    <col min="16" max="16" width="11" style="29" customWidth="1"/>
-    <col min="17" max="17" width="23.5" style="29" customWidth="1"/>
-    <col min="18" max="18" width="11" style="29" customWidth="1"/>
-    <col min="19" max="19" width="10" style="29" customWidth="1"/>
-    <col min="20" max="20" width="11" style="29" customWidth="1"/>
-    <col min="21" max="21" width="23.5" style="29" customWidth="1"/>
-    <col min="22" max="23" width="11" style="29" customWidth="1"/>
-    <col min="24" max="16384" width="11" style="29" customWidth="1"/>
+    <col min="1" max="1" width="23" style="30" customWidth="1"/>
+    <col min="2" max="2" width="17.5" style="30" customWidth="1"/>
+    <col min="3" max="3" width="21.8516" style="30" customWidth="1"/>
+    <col min="4" max="4" width="11" style="30" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="30" customWidth="1"/>
+    <col min="6" max="6" width="15.3516" style="30" customWidth="1"/>
+    <col min="7" max="7" width="21.8516" style="30" customWidth="1"/>
+    <col min="8" max="8" width="11" style="30" customWidth="1"/>
+    <col min="9" max="9" width="24.3516" style="30" customWidth="1"/>
+    <col min="10" max="10" width="16.5" style="30" customWidth="1"/>
+    <col min="11" max="11" width="21.8516" style="30" customWidth="1"/>
+    <col min="12" max="12" width="11" style="30" customWidth="1"/>
+    <col min="13" max="13" width="27.5" style="30" customWidth="1"/>
+    <col min="14" max="14" width="16.5" style="30" customWidth="1"/>
+    <col min="15" max="15" width="22.1719" style="30" customWidth="1"/>
+    <col min="16" max="16" width="11" style="30" customWidth="1"/>
+    <col min="17" max="17" width="23.5" style="30" customWidth="1"/>
+    <col min="18" max="18" width="11" style="30" customWidth="1"/>
+    <col min="19" max="19" width="10" style="30" customWidth="1"/>
+    <col min="20" max="20" width="11" style="30" customWidth="1"/>
+    <col min="21" max="21" width="23.5" style="30" customWidth="1"/>
+    <col min="22" max="23" width="11" style="30" customWidth="1"/>
+    <col min="24" max="16384" width="11" style="30" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="8" customHeight="1">
-      <c r="A1" s="30"/>
-      <c r="B1" s="31"/>
-      <c r="C1" s="31"/>
-      <c r="D1" s="31"/>
-      <c r="E1" s="31"/>
-      <c r="F1" s="31"/>
-      <c r="G1" s="31"/>
-      <c r="H1" s="31"/>
-      <c r="I1" s="31"/>
-      <c r="J1" s="31"/>
-      <c r="K1" s="31"/>
-      <c r="L1" s="31"/>
-      <c r="M1" s="31"/>
-      <c r="N1" s="31"/>
-      <c r="O1" s="31"/>
-      <c r="P1" s="31"/>
-      <c r="Q1" s="31"/>
-      <c r="R1" s="31"/>
-      <c r="S1" s="31"/>
-      <c r="T1" s="31"/>
-      <c r="U1" s="31"/>
-      <c r="V1" s="31"/>
-      <c r="W1" s="32"/>
+      <c r="A1" s="31"/>
+      <c r="B1" s="32"/>
+      <c r="C1" s="32"/>
+      <c r="D1" s="32"/>
+      <c r="E1" s="32"/>
+      <c r="F1" s="32"/>
+      <c r="G1" s="32"/>
+      <c r="H1" s="32"/>
+      <c r="I1" s="32"/>
+      <c r="J1" s="32"/>
+      <c r="K1" s="32"/>
+      <c r="L1" s="32"/>
+      <c r="M1" s="32"/>
+      <c r="N1" s="32"/>
+      <c r="O1" s="32"/>
+      <c r="P1" s="32"/>
+      <c r="Q1" s="32"/>
+      <c r="R1" s="32"/>
+      <c r="S1" s="32"/>
+      <c r="T1" s="32"/>
+      <c r="U1" s="32"/>
+      <c r="V1" s="32"/>
+      <c r="W1" s="33"/>
     </row>
     <row r="2" ht="29.55" customHeight="1">
-      <c r="A2" t="s" s="33">
-        <v>104</v>
-      </c>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="34"/>
-      <c r="K2" s="34"/>
-      <c r="L2" s="34"/>
-      <c r="M2" s="34"/>
-      <c r="N2" s="34"/>
-      <c r="O2" s="34"/>
-      <c r="P2" s="34"/>
-      <c r="Q2" s="34"/>
-      <c r="R2" s="34"/>
-      <c r="S2" s="34"/>
-      <c r="T2" s="34"/>
-      <c r="U2" s="34"/>
-      <c r="V2" s="34"/>
-      <c r="W2" s="34"/>
+      <c r="A2" t="s" s="34">
+        <v>105</v>
+      </c>
+      <c r="B2" s="35"/>
+      <c r="C2" s="35"/>
+      <c r="D2" s="35"/>
+      <c r="E2" s="35"/>
+      <c r="F2" s="35"/>
+      <c r="G2" s="35"/>
+      <c r="H2" s="35"/>
+      <c r="I2" s="35"/>
+      <c r="J2" s="35"/>
+      <c r="K2" s="35"/>
+      <c r="L2" s="35"/>
+      <c r="M2" s="35"/>
+      <c r="N2" s="35"/>
+      <c r="O2" s="35"/>
+      <c r="P2" s="35"/>
+      <c r="Q2" s="35"/>
+      <c r="R2" s="35"/>
+      <c r="S2" s="35"/>
+      <c r="T2" s="35"/>
+      <c r="U2" s="35"/>
+      <c r="V2" s="35"/>
+      <c r="W2" s="35"/>
     </row>
     <row r="3" ht="17" customHeight="1">
-      <c r="A3" t="s" s="35">
+      <c r="A3" t="s" s="36">
         <v>36</v>
       </c>
-      <c r="B3" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C3" t="s" s="35">
+      <c r="B3" t="s" s="36">
         <v>106</v>
       </c>
-      <c r="D3" s="36"/>
-      <c r="E3" t="s" s="35">
+      <c r="C3" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D3" s="37"/>
+      <c r="E3" t="s" s="36">
         <v>37</v>
       </c>
-      <c r="F3" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G3" t="s" s="35">
+      <c r="F3" t="s" s="36">
         <v>106</v>
       </c>
-      <c r="H3" s="36"/>
-      <c r="I3" t="s" s="37">
+      <c r="G3" t="s" s="36">
         <v>107</v>
       </c>
-      <c r="J3" t="s" s="37">
-        <v>105</v>
-      </c>
-      <c r="K3" t="s" s="37">
+      <c r="H3" s="37"/>
+      <c r="I3" t="s" s="38">
+        <v>108</v>
+      </c>
+      <c r="J3" t="s" s="38">
         <v>106</v>
       </c>
-      <c r="L3" s="34"/>
-      <c r="M3" s="34"/>
-      <c r="N3" s="34"/>
-      <c r="O3" s="34"/>
-      <c r="P3" s="34"/>
-      <c r="Q3" s="34"/>
-      <c r="R3" s="34"/>
-      <c r="S3" s="34"/>
-      <c r="T3" s="34"/>
-      <c r="U3" s="34"/>
-      <c r="V3" s="34"/>
-      <c r="W3" s="34"/>
+      <c r="K3" t="s" s="38">
+        <v>107</v>
+      </c>
+      <c r="L3" s="35"/>
+      <c r="M3" s="35"/>
+      <c r="N3" s="35"/>
+      <c r="O3" s="35"/>
+      <c r="P3" s="35"/>
+      <c r="Q3" s="35"/>
+      <c r="R3" s="35"/>
+      <c r="S3" s="35"/>
+      <c r="T3" s="35"/>
+      <c r="U3" s="35"/>
+      <c r="V3" s="35"/>
+      <c r="W3" s="35"/>
     </row>
     <row r="4" ht="17" customHeight="1">
-      <c r="A4" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B4" t="s" s="38">
+      <c r="A4" t="s" s="39">
         <v>109</v>
       </c>
-      <c r="C4" t="s" s="38">
+      <c r="B4" t="s" s="39">
         <v>110</v>
       </c>
-      <c r="D4" s="36"/>
-      <c r="E4" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F4" t="s" s="38">
+      <c r="C4" t="s" s="39">
         <v>111</v>
       </c>
-      <c r="G4" t="s" s="38">
+      <c r="D4" s="37"/>
+      <c r="E4" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F4" t="s" s="39">
+        <v>112</v>
+      </c>
+      <c r="G4" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H4" s="37"/>
+      <c r="I4" t="s" s="40">
+        <v>113</v>
+      </c>
+      <c r="J4" t="s" s="40">
+        <v>112</v>
+      </c>
+      <c r="K4" t="s" s="40">
+        <v>111</v>
+      </c>
+      <c r="L4" s="35"/>
+      <c r="M4" s="35"/>
+      <c r="N4" s="35"/>
+      <c r="O4" s="35"/>
+      <c r="P4" s="35"/>
+      <c r="Q4" s="35"/>
+      <c r="R4" s="35"/>
+      <c r="S4" s="35"/>
+      <c r="T4" s="35"/>
+      <c r="U4" s="35"/>
+      <c r="V4" s="35"/>
+      <c r="W4" s="35"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" s="37"/>
+      <c r="B5" t="s" s="41">
+        <v>114</v>
+      </c>
+      <c r="C5" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
+      <c r="F5" t="s" s="41">
+        <v>115</v>
+      </c>
+      <c r="G5" t="s" s="41">
+        <v>116</v>
+      </c>
+      <c r="H5" s="37"/>
+      <c r="I5" s="42"/>
+      <c r="J5" t="s" s="43">
+        <v>115</v>
+      </c>
+      <c r="K5" t="s" s="43">
+        <v>116</v>
+      </c>
+      <c r="L5" s="35"/>
+      <c r="M5" s="35"/>
+      <c r="N5" s="35"/>
+      <c r="O5" s="35"/>
+      <c r="P5" s="35"/>
+      <c r="Q5" s="35"/>
+      <c r="R5" s="35"/>
+      <c r="S5" s="35"/>
+      <c r="T5" s="35"/>
+      <c r="U5" s="35"/>
+      <c r="V5" s="35"/>
+      <c r="W5" s="35"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" s="44"/>
+      <c r="B6" s="44"/>
+      <c r="C6" s="44"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="44"/>
+      <c r="F6" t="s" s="39">
+        <v>117</v>
+      </c>
+      <c r="G6" t="s" s="39">
+        <v>40</v>
+      </c>
+      <c r="H6" s="37"/>
+      <c r="I6" s="45"/>
+      <c r="J6" s="45"/>
+      <c r="K6" s="45"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
+      <c r="N6" s="35"/>
+      <c r="O6" s="35"/>
+      <c r="P6" s="35"/>
+      <c r="Q6" s="35"/>
+      <c r="R6" s="35"/>
+      <c r="S6" s="35"/>
+      <c r="T6" s="35"/>
+      <c r="U6" s="35"/>
+      <c r="V6" s="35"/>
+      <c r="W6" s="35"/>
+    </row>
+    <row r="7" ht="70.65" customHeight="1">
+      <c r="A7" s="35"/>
+      <c r="B7" s="35"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="35"/>
+      <c r="E7" s="35"/>
+      <c r="F7" s="35"/>
+      <c r="G7" s="35"/>
+      <c r="H7" s="35"/>
+      <c r="I7" s="35"/>
+      <c r="J7" s="35"/>
+      <c r="K7" s="35"/>
+      <c r="L7" s="35"/>
+      <c r="M7" s="35"/>
+      <c r="N7" s="35"/>
+      <c r="O7" s="35"/>
+      <c r="P7" s="35"/>
+      <c r="Q7" s="35"/>
+      <c r="R7" s="35"/>
+      <c r="S7" s="35"/>
+      <c r="T7" s="35"/>
+      <c r="U7" s="35"/>
+      <c r="V7" s="35"/>
+      <c r="W7" s="35"/>
+    </row>
+    <row r="8" ht="34" customHeight="1">
+      <c r="A8" t="s" s="34">
+        <v>118</v>
+      </c>
+      <c r="B8" s="35"/>
+      <c r="C8" s="35"/>
+      <c r="D8" s="35"/>
+      <c r="E8" s="35"/>
+      <c r="F8" s="35"/>
+      <c r="G8" s="35"/>
+      <c r="H8" s="35"/>
+      <c r="I8" s="35"/>
+      <c r="J8" s="35"/>
+      <c r="K8" s="35"/>
+      <c r="L8" s="35"/>
+      <c r="M8" s="35"/>
+      <c r="N8" s="35"/>
+      <c r="O8" s="35"/>
+      <c r="P8" s="35"/>
+      <c r="Q8" s="35"/>
+      <c r="R8" s="35"/>
+      <c r="S8" s="35"/>
+      <c r="T8" s="35"/>
+      <c r="U8" s="35"/>
+      <c r="V8" s="35"/>
+      <c r="W8" s="35"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" t="s" s="36">
+        <v>23</v>
+      </c>
+      <c r="B9" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C9" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D9" s="37"/>
+      <c r="E9" t="s" s="36">
+        <v>40</v>
+      </c>
+      <c r="F9" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G9" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H9" s="37"/>
+      <c r="I9" t="s" s="36">
+        <v>26</v>
+      </c>
+      <c r="J9" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="K9" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="L9" s="37"/>
+      <c r="M9" t="s" s="36">
+        <v>30</v>
+      </c>
+      <c r="N9" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="O9" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="P9" s="37"/>
+      <c r="Q9" s="35"/>
+      <c r="R9" s="35"/>
+      <c r="S9" s="35"/>
+      <c r="T9" s="35"/>
+      <c r="U9" s="35"/>
+      <c r="V9" s="35"/>
+      <c r="W9" s="35"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B10" t="s" s="39">
+        <v>119</v>
+      </c>
+      <c r="C10" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D10" s="37"/>
+      <c r="E10" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F10" t="s" s="39">
         <v>110</v>
       </c>
-      <c r="H4" s="36"/>
-      <c r="I4" t="s" s="39">
-        <v>112</v>
-      </c>
-      <c r="J4" t="s" s="39">
+      <c r="G10" t="s" s="39">
         <v>111</v>
       </c>
-      <c r="K4" t="s" s="39">
+      <c r="H10" s="37"/>
+      <c r="I10" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="J10" t="s" s="39">
         <v>110</v>
       </c>
-      <c r="L4" s="34"/>
-      <c r="M4" s="34"/>
-      <c r="N4" s="34"/>
-      <c r="O4" s="34"/>
-      <c r="P4" s="34"/>
-      <c r="Q4" s="34"/>
-      <c r="R4" s="34"/>
-      <c r="S4" s="34"/>
-      <c r="T4" s="34"/>
-      <c r="U4" s="34"/>
-      <c r="V4" s="34"/>
-      <c r="W4" s="34"/>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="36"/>
-      <c r="B5" t="s" s="40">
+      <c r="K10" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L10" s="37"/>
+      <c r="M10" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="N10" t="s" s="39">
+        <v>121</v>
+      </c>
+      <c r="O10" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="P10" s="37"/>
+      <c r="Q10" s="35"/>
+      <c r="R10" s="35"/>
+      <c r="S10" s="35"/>
+      <c r="T10" s="35"/>
+      <c r="U10" s="35"/>
+      <c r="V10" s="35"/>
+      <c r="W10" s="35"/>
+    </row>
+    <row r="11" ht="17" customHeight="1">
+      <c r="A11" s="37"/>
+      <c r="B11" t="s" s="41">
+        <v>122</v>
+      </c>
+      <c r="C11" t="s" s="41">
+        <v>120</v>
+      </c>
+      <c r="D11" s="37"/>
+      <c r="E11" s="37"/>
+      <c r="F11" t="s" s="41">
+        <v>123</v>
+      </c>
+      <c r="G11" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H11" s="37"/>
+      <c r="I11" s="37"/>
+      <c r="J11" t="s" s="41">
+        <v>123</v>
+      </c>
+      <c r="K11" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="L11" s="37"/>
+      <c r="M11" s="37"/>
+      <c r="N11" t="s" s="41">
+        <v>124</v>
+      </c>
+      <c r="O11" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="P11" s="37"/>
+      <c r="Q11" s="35"/>
+      <c r="R11" s="35"/>
+      <c r="S11" s="35"/>
+      <c r="T11" s="35"/>
+      <c r="U11" s="35"/>
+      <c r="V11" s="35"/>
+      <c r="W11" s="35"/>
+    </row>
+    <row r="12" ht="17" customHeight="1">
+      <c r="A12" s="44"/>
+      <c r="B12" t="s" s="39">
+        <v>125</v>
+      </c>
+      <c r="C12" t="s" s="39">
+        <v>116</v>
+      </c>
+      <c r="D12" s="37"/>
+      <c r="E12" s="44"/>
+      <c r="F12" t="s" s="39">
+        <v>126</v>
+      </c>
+      <c r="G12" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H12" s="37"/>
+      <c r="I12" s="44"/>
+      <c r="J12" t="s" s="39">
+        <v>126</v>
+      </c>
+      <c r="K12" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L12" s="37"/>
+      <c r="M12" s="44"/>
+      <c r="N12" t="s" s="39">
+        <v>127</v>
+      </c>
+      <c r="O12" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="P12" s="37"/>
+      <c r="Q12" s="35"/>
+      <c r="R12" s="35"/>
+      <c r="S12" s="35"/>
+      <c r="T12" s="35"/>
+      <c r="U12" s="35"/>
+      <c r="V12" s="35"/>
+      <c r="W12" s="35"/>
+    </row>
+    <row r="13" ht="17" customHeight="1">
+      <c r="A13" s="37"/>
+      <c r="B13" t="s" s="41">
+        <v>128</v>
+      </c>
+      <c r="C13" t="s" s="41">
+        <v>120</v>
+      </c>
+      <c r="D13" s="37"/>
+      <c r="E13" s="37"/>
+      <c r="F13" t="s" s="41">
+        <v>129</v>
+      </c>
+      <c r="G13" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H13" s="37"/>
+      <c r="I13" s="37"/>
+      <c r="J13" t="s" s="41">
+        <v>129</v>
+      </c>
+      <c r="K13" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="L13" s="37"/>
+      <c r="M13" s="37"/>
+      <c r="N13" t="s" s="41">
+        <v>130</v>
+      </c>
+      <c r="O13" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="P13" s="37"/>
+      <c r="Q13" s="35"/>
+      <c r="R13" s="35"/>
+      <c r="S13" s="35"/>
+      <c r="T13" s="35"/>
+      <c r="U13" s="35"/>
+      <c r="V13" s="35"/>
+      <c r="W13" s="35"/>
+    </row>
+    <row r="14" ht="17" customHeight="1">
+      <c r="A14" s="44"/>
+      <c r="B14" t="s" s="39">
+        <v>131</v>
+      </c>
+      <c r="C14" t="s" s="39">
+        <v>116</v>
+      </c>
+      <c r="D14" s="37"/>
+      <c r="E14" s="44"/>
+      <c r="F14" t="s" s="39">
+        <v>114</v>
+      </c>
+      <c r="G14" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H14" s="37"/>
+      <c r="I14" s="44"/>
+      <c r="J14" t="s" s="39">
+        <v>114</v>
+      </c>
+      <c r="K14" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L14" s="37"/>
+      <c r="M14" s="44"/>
+      <c r="N14" t="s" s="39">
+        <v>132</v>
+      </c>
+      <c r="O14" t="s" s="39">
+        <v>133</v>
+      </c>
+      <c r="P14" s="37"/>
+      <c r="Q14" s="35"/>
+      <c r="R14" s="35"/>
+      <c r="S14" s="35"/>
+      <c r="T14" s="35"/>
+      <c r="U14" s="35"/>
+      <c r="V14" s="35"/>
+      <c r="W14" s="35"/>
+    </row>
+    <row r="15" ht="17" customHeight="1">
+      <c r="A15" s="37"/>
+      <c r="B15" t="s" s="41">
+        <v>110</v>
+      </c>
+      <c r="C15" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D15" s="37"/>
+      <c r="E15" s="37"/>
+      <c r="F15" t="s" s="41">
+        <v>134</v>
+      </c>
+      <c r="G15" t="s" s="41">
+        <v>133</v>
+      </c>
+      <c r="H15" s="37"/>
+      <c r="I15" s="37"/>
+      <c r="J15" t="s" s="41">
+        <v>134</v>
+      </c>
+      <c r="K15" t="s" s="41">
+        <v>133</v>
+      </c>
+      <c r="L15" s="37"/>
+      <c r="M15" s="37"/>
+      <c r="N15" t="s" s="41">
+        <v>135</v>
+      </c>
+      <c r="O15" t="s" s="41">
+        <v>136</v>
+      </c>
+      <c r="P15" s="37"/>
+      <c r="Q15" s="35"/>
+      <c r="R15" s="35"/>
+      <c r="S15" s="35"/>
+      <c r="T15" s="35"/>
+      <c r="U15" s="35"/>
+      <c r="V15" s="35"/>
+      <c r="W15" s="35"/>
+    </row>
+    <row r="16" ht="17" customHeight="1">
+      <c r="A16" s="44"/>
+      <c r="B16" t="s" s="39">
+        <v>123</v>
+      </c>
+      <c r="C16" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="D16" s="37"/>
+      <c r="E16" s="44"/>
+      <c r="F16" s="44"/>
+      <c r="G16" s="44"/>
+      <c r="H16" s="37"/>
+      <c r="I16" s="44"/>
+      <c r="J16" s="44"/>
+      <c r="K16" s="44"/>
+      <c r="L16" s="37"/>
+      <c r="M16" s="44"/>
+      <c r="N16" s="44"/>
+      <c r="O16" s="44"/>
+      <c r="P16" s="37"/>
+      <c r="Q16" s="35"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="35"/>
+      <c r="T16" s="35"/>
+      <c r="U16" s="35"/>
+      <c r="V16" s="35"/>
+      <c r="W16" s="35"/>
+    </row>
+    <row r="17" ht="17" customHeight="1">
+      <c r="A17" s="37"/>
+      <c r="B17" t="s" s="41">
+        <v>126</v>
+      </c>
+      <c r="C17" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D17" s="37"/>
+      <c r="E17" s="35"/>
+      <c r="F17" s="35"/>
+      <c r="G17" s="35"/>
+      <c r="H17" s="35"/>
+      <c r="I17" s="35"/>
+      <c r="J17" s="35"/>
+      <c r="K17" s="35"/>
+      <c r="L17" s="35"/>
+      <c r="M17" s="35"/>
+      <c r="N17" s="35"/>
+      <c r="O17" s="35"/>
+      <c r="P17" s="37"/>
+      <c r="Q17" s="35"/>
+      <c r="R17" s="35"/>
+      <c r="S17" s="35"/>
+      <c r="T17" s="35"/>
+      <c r="U17" s="35"/>
+      <c r="V17" s="35"/>
+      <c r="W17" s="35"/>
+    </row>
+    <row r="18" ht="17" customHeight="1">
+      <c r="A18" s="44"/>
+      <c r="B18" t="s" s="39">
+        <v>129</v>
+      </c>
+      <c r="C18" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="D18" s="37"/>
+      <c r="E18" s="35"/>
+      <c r="F18" s="35"/>
+      <c r="G18" s="35"/>
+      <c r="H18" s="35"/>
+      <c r="I18" s="35"/>
+      <c r="J18" s="35"/>
+      <c r="K18" s="35"/>
+      <c r="L18" s="35"/>
+      <c r="M18" s="35"/>
+      <c r="N18" s="35"/>
+      <c r="O18" s="35"/>
+      <c r="P18" s="37"/>
+      <c r="Q18" s="35"/>
+      <c r="R18" s="35"/>
+      <c r="S18" s="35"/>
+      <c r="T18" s="35"/>
+      <c r="U18" s="35"/>
+      <c r="V18" s="35"/>
+      <c r="W18" s="35"/>
+    </row>
+    <row r="19" ht="17" customHeight="1">
+      <c r="A19" s="37"/>
+      <c r="B19" t="s" s="41">
+        <v>114</v>
+      </c>
+      <c r="C19" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D19" s="37"/>
+      <c r="E19" s="35"/>
+      <c r="F19" s="35"/>
+      <c r="G19" s="35"/>
+      <c r="H19" s="35"/>
+      <c r="I19" s="35"/>
+      <c r="J19" s="35"/>
+      <c r="K19" s="35"/>
+      <c r="L19" s="35"/>
+      <c r="M19" s="35"/>
+      <c r="N19" s="35"/>
+      <c r="O19" s="35"/>
+      <c r="P19" s="37"/>
+      <c r="Q19" s="35"/>
+      <c r="R19" s="35"/>
+      <c r="S19" s="35"/>
+      <c r="T19" s="35"/>
+      <c r="U19" s="35"/>
+      <c r="V19" s="35"/>
+      <c r="W19" s="35"/>
+    </row>
+    <row r="20" ht="17" customHeight="1">
+      <c r="A20" s="44"/>
+      <c r="B20" t="s" s="39">
+        <v>137</v>
+      </c>
+      <c r="C20" t="s" s="39">
+        <v>138</v>
+      </c>
+      <c r="D20" s="37"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
+      <c r="H20" s="35"/>
+      <c r="I20" s="35"/>
+      <c r="J20" s="35"/>
+      <c r="K20" s="35"/>
+      <c r="L20" s="35"/>
+      <c r="M20" s="35"/>
+      <c r="N20" s="35"/>
+      <c r="O20" s="35"/>
+      <c r="P20" s="37"/>
+      <c r="Q20" s="35"/>
+      <c r="R20" s="35"/>
+      <c r="S20" s="35"/>
+      <c r="T20" s="35"/>
+      <c r="U20" s="35"/>
+      <c r="V20" s="35"/>
+      <c r="W20" s="35"/>
+    </row>
+    <row r="21" ht="17" customHeight="1">
+      <c r="A21" s="37"/>
+      <c r="B21" t="s" s="41">
+        <v>134</v>
+      </c>
+      <c r="C21" t="s" s="41">
+        <v>133</v>
+      </c>
+      <c r="D21" s="37"/>
+      <c r="E21" s="37"/>
+      <c r="F21" s="37"/>
+      <c r="G21" s="37"/>
+      <c r="H21" s="37"/>
+      <c r="I21" s="37"/>
+      <c r="J21" s="37"/>
+      <c r="K21" s="37"/>
+      <c r="L21" s="37"/>
+      <c r="M21" s="37"/>
+      <c r="N21" s="37"/>
+      <c r="O21" s="37"/>
+      <c r="P21" s="37"/>
+      <c r="Q21" s="35"/>
+      <c r="R21" s="35"/>
+      <c r="S21" s="35"/>
+      <c r="T21" s="35"/>
+      <c r="U21" s="35"/>
+      <c r="V21" s="35"/>
+      <c r="W21" s="35"/>
+    </row>
+    <row r="22" ht="70.75" customHeight="1">
+      <c r="A22" s="35"/>
+      <c r="B22" s="35"/>
+      <c r="C22" s="35"/>
+      <c r="D22" s="35"/>
+      <c r="E22" s="35"/>
+      <c r="F22" s="35"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="35"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="35"/>
+      <c r="M22" s="35"/>
+      <c r="N22" s="35"/>
+      <c r="O22" s="35"/>
+      <c r="P22" s="35"/>
+      <c r="Q22" s="35"/>
+      <c r="R22" s="35"/>
+      <c r="S22" s="35"/>
+      <c r="T22" s="35"/>
+      <c r="U22" s="35"/>
+      <c r="V22" s="35"/>
+      <c r="W22" s="35"/>
+    </row>
+    <row r="23" ht="34" customHeight="1">
+      <c r="A23" t="s" s="34">
+        <v>139</v>
+      </c>
+      <c r="B23" s="35"/>
+      <c r="C23" s="35"/>
+      <c r="D23" s="35"/>
+      <c r="E23" s="35"/>
+      <c r="F23" s="35"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="35"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="35"/>
+      <c r="N23" s="35"/>
+      <c r="O23" s="35"/>
+      <c r="P23" s="35"/>
+      <c r="Q23" s="35"/>
+      <c r="R23" s="35"/>
+      <c r="S23" s="35"/>
+      <c r="T23" s="35"/>
+      <c r="U23" s="35"/>
+      <c r="V23" s="35"/>
+      <c r="W23" s="35"/>
+    </row>
+    <row r="24" ht="17" customHeight="1">
+      <c r="A24" t="s" s="36">
+        <v>47</v>
+      </c>
+      <c r="B24" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C24" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D24" s="35"/>
+      <c r="E24" t="s" s="36">
+        <v>49</v>
+      </c>
+      <c r="F24" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G24" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H24" s="37"/>
+      <c r="I24" t="s" s="36">
+        <v>51</v>
+      </c>
+      <c r="J24" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="K24" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="L24" s="35"/>
+      <c r="M24" t="s" s="38">
+        <v>140</v>
+      </c>
+      <c r="N24" t="s" s="38">
+        <v>106</v>
+      </c>
+      <c r="O24" t="s" s="38">
+        <v>107</v>
+      </c>
+      <c r="P24" s="35"/>
+      <c r="Q24" t="s" s="38">
+        <v>141</v>
+      </c>
+      <c r="R24" t="s" s="38">
+        <v>106</v>
+      </c>
+      <c r="S24" t="s" s="38">
+        <v>107</v>
+      </c>
+      <c r="T24" s="35"/>
+      <c r="U24" s="35"/>
+      <c r="V24" s="35"/>
+      <c r="W24" s="35"/>
+    </row>
+    <row r="25" ht="17" customHeight="1">
+      <c r="A25" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B25" t="s" s="39">
+        <v>119</v>
+      </c>
+      <c r="C25" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D25" s="35"/>
+      <c r="E25" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F25" t="s" s="39">
+        <v>142</v>
+      </c>
+      <c r="G25" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H25" s="37"/>
+      <c r="I25" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="J25" t="s" s="39">
+        <v>143</v>
+      </c>
+      <c r="K25" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L25" s="35"/>
+      <c r="M25" t="s" s="40">
         <v>113</v>
       </c>
-      <c r="C5" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D5" s="36"/>
-      <c r="E5" s="36"/>
-      <c r="F5" t="s" s="40">
-        <v>114</v>
-      </c>
-      <c r="G5" t="s" s="40">
-        <v>115</v>
-      </c>
-      <c r="H5" s="36"/>
-      <c r="I5" s="41"/>
-      <c r="J5" t="s" s="42">
-        <v>114</v>
-      </c>
-      <c r="K5" t="s" s="42">
-        <v>115</v>
-      </c>
-      <c r="L5" s="34"/>
-      <c r="M5" s="34"/>
-      <c r="N5" s="34"/>
-      <c r="O5" s="34"/>
-      <c r="P5" s="34"/>
-      <c r="Q5" s="34"/>
-      <c r="R5" s="34"/>
-      <c r="S5" s="34"/>
-      <c r="T5" s="34"/>
-      <c r="U5" s="34"/>
-      <c r="V5" s="34"/>
-      <c r="W5" s="34"/>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="43"/>
-      <c r="B6" s="43"/>
-      <c r="C6" s="43"/>
-      <c r="D6" s="36"/>
-      <c r="E6" s="43"/>
-      <c r="F6" t="s" s="38">
+      <c r="N25" t="s" s="40">
+        <v>119</v>
+      </c>
+      <c r="O25" t="s" s="40">
+        <v>120</v>
+      </c>
+      <c r="P25" s="35"/>
+      <c r="Q25" t="s" s="40">
+        <v>113</v>
+      </c>
+      <c r="R25" t="s" s="40">
+        <v>144</v>
+      </c>
+      <c r="S25" t="s" s="40">
+        <v>145</v>
+      </c>
+      <c r="T25" s="35"/>
+      <c r="U25" s="35"/>
+      <c r="V25" s="35"/>
+      <c r="W25" s="35"/>
+    </row>
+    <row r="26" ht="17" customHeight="1">
+      <c r="A26" s="37"/>
+      <c r="B26" t="s" s="41">
+        <v>142</v>
+      </c>
+      <c r="C26" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D26" s="35"/>
+      <c r="E26" s="37"/>
+      <c r="F26" t="s" s="41">
+        <v>146</v>
+      </c>
+      <c r="G26" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H26" s="37"/>
+      <c r="I26" s="37"/>
+      <c r="J26" t="s" s="41">
+        <v>147</v>
+      </c>
+      <c r="K26" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="L26" s="35"/>
+      <c r="M26" s="42"/>
+      <c r="N26" t="s" s="43">
+        <v>148</v>
+      </c>
+      <c r="O26" t="s" s="43">
+        <v>120</v>
+      </c>
+      <c r="P26" s="35"/>
+      <c r="Q26" s="42"/>
+      <c r="R26" t="s" s="43">
+        <v>149</v>
+      </c>
+      <c r="S26" t="s" s="43">
+        <v>150</v>
+      </c>
+      <c r="T26" s="35"/>
+      <c r="U26" s="35"/>
+      <c r="V26" s="35"/>
+      <c r="W26" s="35"/>
+    </row>
+    <row r="27" ht="17" customHeight="1">
+      <c r="A27" s="44"/>
+      <c r="B27" t="s" s="39">
+        <v>146</v>
+      </c>
+      <c r="C27" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="D27" s="35"/>
+      <c r="E27" s="44"/>
+      <c r="F27" t="s" s="39">
+        <v>144</v>
+      </c>
+      <c r="G27" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="H27" s="37"/>
+      <c r="I27" s="44"/>
+      <c r="J27" t="s" s="39">
+        <v>151</v>
+      </c>
+      <c r="K27" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="L27" s="35"/>
+      <c r="M27" s="45"/>
+      <c r="N27" t="s" s="40">
+        <v>152</v>
+      </c>
+      <c r="O27" t="s" s="40">
+        <v>153</v>
+      </c>
+      <c r="P27" s="35"/>
+      <c r="Q27" s="45"/>
+      <c r="R27" t="s" s="40">
+        <v>154</v>
+      </c>
+      <c r="S27" t="s" s="40">
+        <v>145</v>
+      </c>
+      <c r="T27" s="35"/>
+      <c r="U27" s="35"/>
+      <c r="V27" s="35"/>
+      <c r="W27" s="35"/>
+    </row>
+    <row r="28" ht="17" customHeight="1">
+      <c r="A28" s="37"/>
+      <c r="B28" t="s" s="41">
+        <v>144</v>
+      </c>
+      <c r="C28" t="s" s="41">
+        <v>145</v>
+      </c>
+      <c r="D28" s="35"/>
+      <c r="E28" s="37"/>
+      <c r="F28" t="s" s="41">
+        <v>149</v>
+      </c>
+      <c r="G28" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="H28" s="37"/>
+      <c r="I28" s="37"/>
+      <c r="J28" t="s" s="41">
+        <v>155</v>
+      </c>
+      <c r="K28" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="L28" s="35"/>
+      <c r="M28" s="42"/>
+      <c r="N28" t="s" s="43">
+        <v>156</v>
+      </c>
+      <c r="O28" t="s" s="43">
+        <v>141</v>
+      </c>
+      <c r="P28" s="35"/>
+      <c r="Q28" s="42"/>
+      <c r="R28" t="s" s="43">
+        <v>157</v>
+      </c>
+      <c r="S28" t="s" s="43">
+        <v>138</v>
+      </c>
+      <c r="T28" s="35"/>
+      <c r="U28" s="35"/>
+      <c r="V28" s="35"/>
+      <c r="W28" s="35"/>
+    </row>
+    <row r="29" ht="17" customHeight="1">
+      <c r="A29" s="44"/>
+      <c r="B29" t="s" s="39">
+        <v>149</v>
+      </c>
+      <c r="C29" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="D29" s="35"/>
+      <c r="E29" s="44"/>
+      <c r="F29" t="s" s="39">
+        <v>154</v>
+      </c>
+      <c r="G29" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="H29" s="37"/>
+      <c r="I29" s="44"/>
+      <c r="J29" t="s" s="39">
+        <v>158</v>
+      </c>
+      <c r="K29" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="L29" s="35"/>
+      <c r="M29" s="45"/>
+      <c r="N29" t="s" s="40">
+        <v>159</v>
+      </c>
+      <c r="O29" t="s" s="40">
+        <v>141</v>
+      </c>
+      <c r="P29" s="35"/>
+      <c r="Q29" s="45"/>
+      <c r="R29" s="45"/>
+      <c r="S29" s="45"/>
+      <c r="T29" s="35"/>
+      <c r="U29" s="35"/>
+      <c r="V29" s="35"/>
+      <c r="W29" s="35"/>
+    </row>
+    <row r="30" ht="17" customHeight="1">
+      <c r="A30" s="37"/>
+      <c r="B30" t="s" s="41">
+        <v>154</v>
+      </c>
+      <c r="C30" t="s" s="41">
+        <v>145</v>
+      </c>
+      <c r="D30" s="35"/>
+      <c r="E30" s="35"/>
+      <c r="F30" s="35"/>
+      <c r="G30" s="35"/>
+      <c r="H30" s="35"/>
+      <c r="I30" s="35"/>
+      <c r="J30" s="35"/>
+      <c r="K30" s="35"/>
+      <c r="L30" s="35"/>
+      <c r="M30" s="42"/>
+      <c r="N30" t="s" s="43">
+        <v>160</v>
+      </c>
+      <c r="O30" t="s" s="43">
         <v>116</v>
       </c>
-      <c r="G6" t="s" s="38">
-        <v>40</v>
-      </c>
-      <c r="H6" s="36"/>
-      <c r="I6" s="44"/>
-      <c r="J6" s="44"/>
-      <c r="K6" s="44"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="34"/>
-      <c r="R6" s="34"/>
-      <c r="S6" s="34"/>
-      <c r="T6" s="34"/>
-      <c r="U6" s="34"/>
-      <c r="V6" s="34"/>
-      <c r="W6" s="34"/>
-    </row>
-    <row r="7" ht="70.65" customHeight="1">
-      <c r="A7" s="34"/>
-      <c r="B7" s="34"/>
-      <c r="C7" s="34"/>
-      <c r="D7" s="34"/>
-      <c r="E7" s="34"/>
-      <c r="F7" s="34"/>
-      <c r="G7" s="34"/>
-      <c r="H7" s="34"/>
-      <c r="I7" s="34"/>
-      <c r="J7" s="34"/>
-      <c r="K7" s="34"/>
-      <c r="L7" s="34"/>
-      <c r="M7" s="34"/>
-      <c r="N7" s="34"/>
-      <c r="O7" s="34"/>
-      <c r="P7" s="34"/>
-      <c r="Q7" s="34"/>
-      <c r="R7" s="34"/>
-      <c r="S7" s="34"/>
-      <c r="T7" s="34"/>
-      <c r="U7" s="34"/>
-      <c r="V7" s="34"/>
-      <c r="W7" s="34"/>
-    </row>
-    <row r="8" ht="34" customHeight="1">
-      <c r="A8" t="s" s="33">
-        <v>117</v>
-      </c>
-      <c r="B8" s="34"/>
-      <c r="C8" s="34"/>
-      <c r="D8" s="34"/>
-      <c r="E8" s="34"/>
-      <c r="F8" s="34"/>
-      <c r="G8" s="34"/>
-      <c r="H8" s="34"/>
-      <c r="I8" s="34"/>
-      <c r="J8" s="34"/>
-      <c r="K8" s="34"/>
-      <c r="L8" s="34"/>
-      <c r="M8" s="34"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="34"/>
-      <c r="P8" s="34"/>
-      <c r="Q8" s="34"/>
-      <c r="R8" s="34"/>
-      <c r="S8" s="34"/>
-      <c r="T8" s="34"/>
-      <c r="U8" s="34"/>
-      <c r="V8" s="34"/>
-      <c r="W8" s="34"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" t="s" s="35">
-        <v>23</v>
-      </c>
-      <c r="B9" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C9" t="s" s="35">
+      <c r="P30" s="35"/>
+      <c r="Q30" s="46"/>
+      <c r="R30" s="47"/>
+      <c r="S30" s="48"/>
+      <c r="T30" s="35"/>
+      <c r="U30" s="35"/>
+      <c r="V30" s="35"/>
+      <c r="W30" s="35"/>
+    </row>
+    <row r="31" ht="17" customHeight="1">
+      <c r="A31" s="44"/>
+      <c r="B31" t="s" s="39">
+        <v>161</v>
+      </c>
+      <c r="C31" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="D31" s="35"/>
+      <c r="E31" s="35"/>
+      <c r="F31" s="35"/>
+      <c r="G31" s="35"/>
+      <c r="H31" s="35"/>
+      <c r="I31" s="35"/>
+      <c r="J31" s="35"/>
+      <c r="K31" s="35"/>
+      <c r="L31" s="35"/>
+      <c r="M31" s="45"/>
+      <c r="N31" s="45"/>
+      <c r="O31" s="45"/>
+      <c r="P31" s="35"/>
+      <c r="Q31" s="49"/>
+      <c r="R31" s="50"/>
+      <c r="S31" s="51"/>
+      <c r="T31" s="35"/>
+      <c r="U31" s="35"/>
+      <c r="V31" s="35"/>
+      <c r="W31" s="35"/>
+    </row>
+    <row r="32" ht="17" customHeight="1">
+      <c r="A32" s="37"/>
+      <c r="B32" t="s" s="41">
+        <v>162</v>
+      </c>
+      <c r="C32" t="s" s="41">
+        <v>163</v>
+      </c>
+      <c r="D32" s="35"/>
+      <c r="E32" s="35"/>
+      <c r="F32" s="35"/>
+      <c r="G32" s="35"/>
+      <c r="H32" s="35"/>
+      <c r="I32" s="35"/>
+      <c r="J32" s="35"/>
+      <c r="K32" s="35"/>
+      <c r="L32" s="35"/>
+      <c r="M32" s="35"/>
+      <c r="N32" s="35"/>
+      <c r="O32" s="35"/>
+      <c r="P32" s="35"/>
+      <c r="Q32" s="35"/>
+      <c r="R32" s="35"/>
+      <c r="S32" s="35"/>
+      <c r="T32" s="35"/>
+      <c r="U32" s="35"/>
+      <c r="V32" s="35"/>
+      <c r="W32" s="35"/>
+    </row>
+    <row r="33" ht="17" customHeight="1">
+      <c r="A33" s="44"/>
+      <c r="B33" t="s" s="39">
+        <v>164</v>
+      </c>
+      <c r="C33" t="s" s="39">
+        <v>138</v>
+      </c>
+      <c r="D33" s="35"/>
+      <c r="E33" s="35"/>
+      <c r="F33" s="35"/>
+      <c r="G33" s="35"/>
+      <c r="H33" s="35"/>
+      <c r="I33" s="35"/>
+      <c r="J33" s="35"/>
+      <c r="K33" s="35"/>
+      <c r="L33" s="35"/>
+      <c r="M33" s="35"/>
+      <c r="N33" s="35"/>
+      <c r="O33" s="35"/>
+      <c r="P33" s="35"/>
+      <c r="Q33" s="35"/>
+      <c r="R33" s="35"/>
+      <c r="S33" s="35"/>
+      <c r="T33" s="35"/>
+      <c r="U33" s="35"/>
+      <c r="V33" s="35"/>
+      <c r="W33" s="35"/>
+    </row>
+    <row r="34" ht="17" customHeight="1">
+      <c r="A34" t="s" s="41">
+        <v>165</v>
+      </c>
+      <c r="B34" t="s" s="41">
+        <v>166</v>
+      </c>
+      <c r="C34" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D34" s="35"/>
+      <c r="E34" s="35"/>
+      <c r="F34" s="35"/>
+      <c r="G34" s="35"/>
+      <c r="H34" s="35"/>
+      <c r="I34" s="35"/>
+      <c r="J34" s="35"/>
+      <c r="K34" s="35"/>
+      <c r="L34" s="35"/>
+      <c r="M34" s="35"/>
+      <c r="N34" s="35"/>
+      <c r="O34" s="35"/>
+      <c r="P34" s="35"/>
+      <c r="Q34" s="35"/>
+      <c r="R34" s="35"/>
+      <c r="S34" s="35"/>
+      <c r="T34" s="35"/>
+      <c r="U34" s="35"/>
+      <c r="V34" s="35"/>
+      <c r="W34" s="35"/>
+    </row>
+    <row r="35" ht="17" customHeight="1">
+      <c r="A35" s="44"/>
+      <c r="B35" t="s" s="39">
+        <v>167</v>
+      </c>
+      <c r="C35" t="s" s="39">
+        <v>116</v>
+      </c>
+      <c r="D35" s="35"/>
+      <c r="E35" s="35"/>
+      <c r="F35" s="35"/>
+      <c r="G35" s="35"/>
+      <c r="H35" s="35"/>
+      <c r="I35" s="35"/>
+      <c r="J35" s="35"/>
+      <c r="K35" s="35"/>
+      <c r="L35" s="35"/>
+      <c r="M35" s="35"/>
+      <c r="N35" s="35"/>
+      <c r="O35" s="35"/>
+      <c r="P35" s="35"/>
+      <c r="Q35" s="35"/>
+      <c r="R35" s="35"/>
+      <c r="S35" s="35"/>
+      <c r="T35" s="35"/>
+      <c r="U35" s="35"/>
+      <c r="V35" s="35"/>
+      <c r="W35" s="35"/>
+    </row>
+    <row r="36" ht="17" customHeight="1">
+      <c r="A36" s="37"/>
+      <c r="B36" t="s" s="41">
+        <v>168</v>
+      </c>
+      <c r="C36" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D36" s="35"/>
+      <c r="E36" s="35"/>
+      <c r="F36" s="35"/>
+      <c r="G36" s="35"/>
+      <c r="H36" s="35"/>
+      <c r="I36" s="35"/>
+      <c r="J36" s="35"/>
+      <c r="K36" s="35"/>
+      <c r="L36" s="35"/>
+      <c r="M36" s="35"/>
+      <c r="N36" s="35"/>
+      <c r="O36" s="35"/>
+      <c r="P36" s="35"/>
+      <c r="Q36" s="35"/>
+      <c r="R36" s="35"/>
+      <c r="S36" s="35"/>
+      <c r="T36" s="35"/>
+      <c r="U36" s="35"/>
+      <c r="V36" s="35"/>
+      <c r="W36" s="35"/>
+    </row>
+    <row r="37" ht="17" customHeight="1">
+      <c r="A37" s="44"/>
+      <c r="B37" t="s" s="39">
+        <v>169</v>
+      </c>
+      <c r="C37" t="s" s="39">
+        <v>116</v>
+      </c>
+      <c r="D37" s="35"/>
+      <c r="E37" s="35"/>
+      <c r="F37" s="35"/>
+      <c r="G37" s="35"/>
+      <c r="H37" s="35"/>
+      <c r="I37" s="35"/>
+      <c r="J37" s="35"/>
+      <c r="K37" s="35"/>
+      <c r="L37" s="35"/>
+      <c r="M37" s="35"/>
+      <c r="N37" s="35"/>
+      <c r="O37" s="35"/>
+      <c r="P37" s="35"/>
+      <c r="Q37" s="35"/>
+      <c r="R37" s="35"/>
+      <c r="S37" s="35"/>
+      <c r="T37" s="35"/>
+      <c r="U37" s="35"/>
+      <c r="V37" s="35"/>
+      <c r="W37" s="35"/>
+    </row>
+    <row r="38" ht="70.95" customHeight="1">
+      <c r="A38" s="37"/>
+      <c r="B38" s="37"/>
+      <c r="C38" s="37"/>
+      <c r="D38" s="35"/>
+      <c r="E38" s="42"/>
+      <c r="F38" s="42"/>
+      <c r="G38" s="42"/>
+      <c r="H38" s="35"/>
+      <c r="I38" s="42"/>
+      <c r="J38" s="42"/>
+      <c r="K38" s="42"/>
+      <c r="L38" s="35"/>
+      <c r="M38" s="42"/>
+      <c r="N38" s="42"/>
+      <c r="O38" s="42"/>
+      <c r="P38" s="35"/>
+      <c r="Q38" s="42"/>
+      <c r="R38" s="42"/>
+      <c r="S38" s="42"/>
+      <c r="T38" s="35"/>
+      <c r="U38" s="35"/>
+      <c r="V38" s="35"/>
+      <c r="W38" s="35"/>
+    </row>
+    <row r="39" ht="34" customHeight="1">
+      <c r="A39" t="s" s="34">
+        <v>170</v>
+      </c>
+      <c r="B39" s="35"/>
+      <c r="C39" s="35"/>
+      <c r="D39" s="35"/>
+      <c r="E39" s="35"/>
+      <c r="F39" s="35"/>
+      <c r="G39" s="35"/>
+      <c r="H39" s="35"/>
+      <c r="I39" s="35"/>
+      <c r="J39" s="35"/>
+      <c r="K39" s="35"/>
+      <c r="L39" s="35"/>
+      <c r="M39" s="35"/>
+      <c r="N39" s="35"/>
+      <c r="O39" s="35"/>
+      <c r="P39" s="35"/>
+      <c r="Q39" s="35"/>
+      <c r="R39" s="35"/>
+      <c r="S39" s="35"/>
+      <c r="T39" s="35"/>
+      <c r="U39" s="35"/>
+      <c r="V39" s="35"/>
+      <c r="W39" s="35"/>
+    </row>
+    <row r="40" ht="17" customHeight="1">
+      <c r="A40" t="s" s="36">
+        <v>55</v>
+      </c>
+      <c r="B40" t="s" s="36">
         <v>106</v>
       </c>
-      <c r="D9" s="36"/>
-      <c r="E9" t="s" s="35">
-        <v>40</v>
-      </c>
-      <c r="F9" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G9" t="s" s="35">
+      <c r="C40" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D40" s="35"/>
+      <c r="E40" t="s" s="36">
+        <v>171</v>
+      </c>
+      <c r="F40" t="s" s="36">
         <v>106</v>
       </c>
-      <c r="H9" s="36"/>
-      <c r="I9" t="s" s="35">
-        <v>26</v>
-      </c>
-      <c r="J9" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="K9" t="s" s="35">
+      <c r="G40" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H40" s="37"/>
+      <c r="I40" t="s" s="36">
+        <v>58</v>
+      </c>
+      <c r="J40" t="s" s="36">
         <v>106</v>
       </c>
-      <c r="L9" s="36"/>
-      <c r="M9" t="s" s="35">
-        <v>30</v>
-      </c>
-      <c r="N9" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="O9" t="s" s="35">
+      <c r="K40" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="L40" s="35"/>
+      <c r="M40" t="s" s="36">
+        <v>61</v>
+      </c>
+      <c r="N40" t="s" s="36">
         <v>106</v>
       </c>
-      <c r="P9" s="36"/>
-      <c r="Q9" s="34"/>
-      <c r="R9" s="34"/>
-      <c r="S9" s="34"/>
-      <c r="T9" s="34"/>
-      <c r="U9" s="34"/>
-      <c r="V9" s="34"/>
-      <c r="W9" s="34"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B10" t="s" s="38">
-        <v>118</v>
-      </c>
-      <c r="C10" t="s" s="38">
+      <c r="O40" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="P40" s="35"/>
+      <c r="Q40" s="35"/>
+      <c r="R40" s="35"/>
+      <c r="S40" s="35"/>
+      <c r="T40" s="35"/>
+      <c r="U40" s="35"/>
+      <c r="V40" s="35"/>
+      <c r="W40" s="35"/>
+    </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B41" t="s" s="39">
+        <v>172</v>
+      </c>
+      <c r="C41" t="s" s="39">
+        <v>173</v>
+      </c>
+      <c r="D41" s="35"/>
+      <c r="E41" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F41" t="s" s="39">
         <v>119</v>
       </c>
-      <c r="D10" s="36"/>
-      <c r="E10" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F10" t="s" s="38">
+      <c r="G41" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="H41" s="37"/>
+      <c r="I41" t="s" s="39">
         <v>109</v>
       </c>
-      <c r="G10" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H10" s="36"/>
-      <c r="I10" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="J10" t="s" s="38">
+      <c r="J41" t="s" s="39">
+        <v>148</v>
+      </c>
+      <c r="K41" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="L41" s="35"/>
+      <c r="M41" t="s" s="39">
         <v>109</v>
       </c>
-      <c r="K10" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L10" s="36"/>
-      <c r="M10" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="N10" t="s" s="38">
+      <c r="N41" t="s" s="39">
+        <v>174</v>
+      </c>
+      <c r="O41" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="P41" s="35"/>
+      <c r="Q41" s="35"/>
+      <c r="R41" s="35"/>
+      <c r="S41" s="35"/>
+      <c r="T41" s="35"/>
+      <c r="U41" s="35"/>
+      <c r="V41" s="35"/>
+      <c r="W41" s="35"/>
+    </row>
+    <row r="42" ht="17" customHeight="1">
+      <c r="A42" s="35"/>
+      <c r="B42" s="35"/>
+      <c r="C42" s="35"/>
+      <c r="D42" s="35"/>
+      <c r="E42" s="37"/>
+      <c r="F42" t="s" s="41">
+        <v>148</v>
+      </c>
+      <c r="G42" t="s" s="41">
         <v>120</v>
       </c>
-      <c r="O10" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="34"/>
-      <c r="R10" s="34"/>
-      <c r="S10" s="34"/>
-      <c r="T10" s="34"/>
-      <c r="U10" s="34"/>
-      <c r="V10" s="34"/>
-      <c r="W10" s="34"/>
-    </row>
-    <row r="11" ht="17" customHeight="1">
-      <c r="A11" s="36"/>
-      <c r="B11" t="s" s="40">
-        <v>121</v>
-      </c>
-      <c r="C11" t="s" s="40">
+      <c r="H42" s="37"/>
+      <c r="I42" s="37"/>
+      <c r="J42" t="s" s="41">
+        <v>175</v>
+      </c>
+      <c r="K42" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="L42" s="35"/>
+      <c r="M42" s="37"/>
+      <c r="N42" t="s" s="41">
+        <v>176</v>
+      </c>
+      <c r="O42" t="s" s="41">
+        <v>145</v>
+      </c>
+      <c r="P42" s="35"/>
+      <c r="Q42" s="35"/>
+      <c r="R42" s="35"/>
+      <c r="S42" s="35"/>
+      <c r="T42" s="35"/>
+      <c r="U42" s="35"/>
+      <c r="V42" s="35"/>
+      <c r="W42" s="35"/>
+    </row>
+    <row r="43" ht="17" customHeight="1">
+      <c r="A43" s="35"/>
+      <c r="B43" s="35"/>
+      <c r="C43" s="35"/>
+      <c r="D43" s="35"/>
+      <c r="E43" s="44"/>
+      <c r="F43" t="s" s="39">
+        <v>175</v>
+      </c>
+      <c r="G43" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="H43" s="37"/>
+      <c r="I43" s="44"/>
+      <c r="J43" t="s" s="39">
+        <v>177</v>
+      </c>
+      <c r="K43" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="L43" s="35"/>
+      <c r="M43" s="44"/>
+      <c r="N43" s="44"/>
+      <c r="O43" s="44"/>
+      <c r="P43" s="35"/>
+      <c r="Q43" s="35"/>
+      <c r="R43" s="35"/>
+      <c r="S43" s="35"/>
+      <c r="T43" s="35"/>
+      <c r="U43" s="35"/>
+      <c r="V43" s="35"/>
+      <c r="W43" s="35"/>
+    </row>
+    <row r="44" ht="17" customHeight="1">
+      <c r="A44" s="35"/>
+      <c r="B44" s="35"/>
+      <c r="C44" s="35"/>
+      <c r="D44" s="35"/>
+      <c r="E44" s="37"/>
+      <c r="F44" t="s" s="41">
+        <v>178</v>
+      </c>
+      <c r="G44" t="s" s="41">
+        <v>145</v>
+      </c>
+      <c r="H44" s="37"/>
+      <c r="I44" s="35"/>
+      <c r="J44" s="35"/>
+      <c r="K44" s="35"/>
+      <c r="L44" s="35"/>
+      <c r="M44" s="35"/>
+      <c r="N44" s="35"/>
+      <c r="O44" s="35"/>
+      <c r="P44" s="35"/>
+      <c r="Q44" s="35"/>
+      <c r="R44" s="35"/>
+      <c r="S44" s="35"/>
+      <c r="T44" s="35"/>
+      <c r="U44" s="35"/>
+      <c r="V44" s="35"/>
+      <c r="W44" s="35"/>
+    </row>
+    <row r="45" ht="17" customHeight="1">
+      <c r="A45" s="35"/>
+      <c r="B45" s="35"/>
+      <c r="C45" s="35"/>
+      <c r="D45" s="35"/>
+      <c r="E45" s="44"/>
+      <c r="F45" t="s" s="39">
+        <v>177</v>
+      </c>
+      <c r="G45" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="H45" s="37"/>
+      <c r="I45" s="35"/>
+      <c r="J45" s="35"/>
+      <c r="K45" s="35"/>
+      <c r="L45" s="35"/>
+      <c r="M45" s="35"/>
+      <c r="N45" s="35"/>
+      <c r="O45" s="35"/>
+      <c r="P45" s="35"/>
+      <c r="Q45" s="35"/>
+      <c r="R45" s="35"/>
+      <c r="S45" s="35"/>
+      <c r="T45" s="35"/>
+      <c r="U45" s="35"/>
+      <c r="V45" s="35"/>
+      <c r="W45" s="35"/>
+    </row>
+    <row r="46" ht="70.1" customHeight="1">
+      <c r="A46" s="35"/>
+      <c r="B46" s="35"/>
+      <c r="C46" s="35"/>
+      <c r="D46" s="35"/>
+      <c r="E46" s="35"/>
+      <c r="F46" s="35"/>
+      <c r="G46" s="35"/>
+      <c r="H46" s="35"/>
+      <c r="I46" s="35"/>
+      <c r="J46" s="35"/>
+      <c r="K46" s="35"/>
+      <c r="L46" s="35"/>
+      <c r="M46" s="35"/>
+      <c r="N46" s="35"/>
+      <c r="O46" s="35"/>
+      <c r="P46" s="35"/>
+      <c r="Q46" s="35"/>
+      <c r="R46" s="35"/>
+      <c r="S46" s="35"/>
+      <c r="T46" s="35"/>
+      <c r="U46" s="35"/>
+      <c r="V46" s="35"/>
+      <c r="W46" s="35"/>
+    </row>
+    <row r="47" ht="34" customHeight="1">
+      <c r="A47" t="s" s="34">
+        <v>179</v>
+      </c>
+      <c r="B47" s="35"/>
+      <c r="C47" s="35"/>
+      <c r="D47" s="35"/>
+      <c r="E47" s="35"/>
+      <c r="F47" s="35"/>
+      <c r="G47" s="35"/>
+      <c r="H47" s="35"/>
+      <c r="I47" s="35"/>
+      <c r="J47" s="35"/>
+      <c r="K47" s="35"/>
+      <c r="L47" s="35"/>
+      <c r="M47" s="35"/>
+      <c r="N47" s="35"/>
+      <c r="O47" s="35"/>
+      <c r="P47" s="35"/>
+      <c r="Q47" s="35"/>
+      <c r="R47" s="35"/>
+      <c r="S47" s="35"/>
+      <c r="T47" s="35"/>
+      <c r="U47" s="35"/>
+      <c r="V47" s="35"/>
+      <c r="W47" s="35"/>
+    </row>
+    <row r="48" ht="17" customHeight="1">
+      <c r="A48" t="s" s="36">
+        <v>70</v>
+      </c>
+      <c r="B48" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C48" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D48" s="35"/>
+      <c r="E48" t="s" s="36">
+        <v>72</v>
+      </c>
+      <c r="F48" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G48" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H48" s="37"/>
+      <c r="I48" t="s" s="36">
+        <v>180</v>
+      </c>
+      <c r="J48" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="K48" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="L48" s="37"/>
+      <c r="M48" s="52"/>
+      <c r="N48" s="52"/>
+      <c r="O48" s="52"/>
+      <c r="P48" s="35"/>
+      <c r="Q48" s="53"/>
+      <c r="R48" s="53"/>
+      <c r="S48" s="53"/>
+      <c r="T48" s="35"/>
+      <c r="U48" s="53"/>
+      <c r="V48" s="53"/>
+      <c r="W48" s="53"/>
+    </row>
+    <row r="49" ht="17" customHeight="1">
+      <c r="A49" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B49" t="s" s="39">
+        <v>181</v>
+      </c>
+      <c r="C49" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="D49" s="35"/>
+      <c r="E49" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F49" t="s" s="39">
+        <v>182</v>
+      </c>
+      <c r="G49" t="s" s="39">
+        <v>86</v>
+      </c>
+      <c r="H49" s="37"/>
+      <c r="I49" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="J49" t="s" s="39">
+        <v>148</v>
+      </c>
+      <c r="K49" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="L49" s="37"/>
+      <c r="M49" s="35"/>
+      <c r="N49" s="35"/>
+      <c r="O49" s="35"/>
+      <c r="P49" s="35"/>
+      <c r="Q49" s="35"/>
+      <c r="R49" s="35"/>
+      <c r="S49" s="35"/>
+      <c r="T49" s="35"/>
+      <c r="U49" s="35"/>
+      <c r="V49" s="35"/>
+      <c r="W49" s="35"/>
+    </row>
+    <row r="50" ht="17" customHeight="1">
+      <c r="A50" s="37"/>
+      <c r="B50" t="s" s="41">
+        <v>183</v>
+      </c>
+      <c r="C50" t="s" s="41">
+        <v>184</v>
+      </c>
+      <c r="D50" s="35"/>
+      <c r="E50" s="37"/>
+      <c r="F50" t="s" s="41">
+        <v>185</v>
+      </c>
+      <c r="G50" t="s" s="41">
+        <v>86</v>
+      </c>
+      <c r="H50" s="37"/>
+      <c r="I50" s="37"/>
+      <c r="J50" t="s" s="41">
+        <v>175</v>
+      </c>
+      <c r="K50" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="L50" s="37"/>
+      <c r="M50" s="35"/>
+      <c r="N50" s="35"/>
+      <c r="O50" s="35"/>
+      <c r="P50" s="35"/>
+      <c r="Q50" s="35"/>
+      <c r="R50" s="35"/>
+      <c r="S50" s="35"/>
+      <c r="T50" s="35"/>
+      <c r="U50" s="35"/>
+      <c r="V50" s="35"/>
+      <c r="W50" s="35"/>
+    </row>
+    <row r="51" ht="17" customHeight="1">
+      <c r="A51" s="44"/>
+      <c r="B51" t="s" s="39">
+        <v>186</v>
+      </c>
+      <c r="C51" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="D51" s="35"/>
+      <c r="E51" s="44"/>
+      <c r="F51" s="44"/>
+      <c r="G51" s="44"/>
+      <c r="H51" s="37"/>
+      <c r="I51" s="44"/>
+      <c r="J51" t="s" s="39">
+        <v>187</v>
+      </c>
+      <c r="K51" t="s" s="39">
+        <v>145</v>
+      </c>
+      <c r="L51" s="37"/>
+      <c r="M51" s="35"/>
+      <c r="N51" s="35"/>
+      <c r="O51" s="35"/>
+      <c r="P51" s="35"/>
+      <c r="Q51" s="35"/>
+      <c r="R51" s="35"/>
+      <c r="S51" s="35"/>
+      <c r="T51" s="35"/>
+      <c r="U51" s="35"/>
+      <c r="V51" s="35"/>
+      <c r="W51" s="35"/>
+    </row>
+    <row r="52" ht="17" customHeight="1">
+      <c r="A52" s="37"/>
+      <c r="B52" t="s" s="41">
+        <v>160</v>
+      </c>
+      <c r="C52" t="s" s="41">
+        <v>116</v>
+      </c>
+      <c r="D52" s="35"/>
+      <c r="E52" s="35"/>
+      <c r="F52" s="35"/>
+      <c r="G52" s="35"/>
+      <c r="H52" s="37"/>
+      <c r="I52" s="37"/>
+      <c r="J52" t="s" s="41">
+        <v>177</v>
+      </c>
+      <c r="K52" t="s" s="41">
+        <v>145</v>
+      </c>
+      <c r="L52" s="37"/>
+      <c r="M52" s="35"/>
+      <c r="N52" s="35"/>
+      <c r="O52" s="35"/>
+      <c r="P52" s="35"/>
+      <c r="Q52" s="35"/>
+      <c r="R52" s="35"/>
+      <c r="S52" s="35"/>
+      <c r="T52" s="35"/>
+      <c r="U52" s="35"/>
+      <c r="V52" s="35"/>
+      <c r="W52" s="35"/>
+    </row>
+    <row r="53" ht="17" customHeight="1">
+      <c r="A53" s="44"/>
+      <c r="B53" t="s" s="39">
+        <v>172</v>
+      </c>
+      <c r="C53" t="s" s="39">
+        <v>188</v>
+      </c>
+      <c r="D53" s="35"/>
+      <c r="E53" s="35"/>
+      <c r="F53" s="35"/>
+      <c r="G53" s="35"/>
+      <c r="H53" s="37"/>
+      <c r="I53" s="44"/>
+      <c r="J53" s="44"/>
+      <c r="K53" s="44"/>
+      <c r="L53" s="37"/>
+      <c r="M53" s="35"/>
+      <c r="N53" s="35"/>
+      <c r="O53" s="35"/>
+      <c r="P53" s="35"/>
+      <c r="Q53" s="35"/>
+      <c r="R53" s="35"/>
+      <c r="S53" s="35"/>
+      <c r="T53" s="35"/>
+      <c r="U53" s="35"/>
+      <c r="V53" s="35"/>
+      <c r="W53" s="35"/>
+    </row>
+    <row r="54" ht="17" customHeight="1">
+      <c r="A54" s="37"/>
+      <c r="B54" t="s" s="41">
+        <v>189</v>
+      </c>
+      <c r="C54" t="s" s="41">
+        <v>120</v>
+      </c>
+      <c r="D54" s="35"/>
+      <c r="E54" s="35"/>
+      <c r="F54" s="35"/>
+      <c r="G54" s="35"/>
+      <c r="H54" s="35"/>
+      <c r="I54" s="35"/>
+      <c r="J54" s="35"/>
+      <c r="K54" s="35"/>
+      <c r="L54" s="37"/>
+      <c r="M54" s="35"/>
+      <c r="N54" s="35"/>
+      <c r="O54" s="35"/>
+      <c r="P54" s="35"/>
+      <c r="Q54" s="35"/>
+      <c r="R54" s="35"/>
+      <c r="S54" s="35"/>
+      <c r="T54" s="35"/>
+      <c r="U54" s="35"/>
+      <c r="V54" s="35"/>
+      <c r="W54" s="35"/>
+    </row>
+    <row r="55" ht="17" customHeight="1">
+      <c r="A55" s="44"/>
+      <c r="B55" t="s" s="39">
+        <v>190</v>
+      </c>
+      <c r="C55" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D55" s="35"/>
+      <c r="E55" s="35"/>
+      <c r="F55" s="35"/>
+      <c r="G55" s="35"/>
+      <c r="H55" s="35"/>
+      <c r="I55" s="35"/>
+      <c r="J55" s="35"/>
+      <c r="K55" s="35"/>
+      <c r="L55" s="37"/>
+      <c r="M55" s="35"/>
+      <c r="N55" s="35"/>
+      <c r="O55" s="35"/>
+      <c r="P55" s="35"/>
+      <c r="Q55" s="35"/>
+      <c r="R55" s="35"/>
+      <c r="S55" s="35"/>
+      <c r="T55" s="35"/>
+      <c r="U55" s="35"/>
+      <c r="V55" s="35"/>
+      <c r="W55" s="35"/>
+    </row>
+    <row r="56" ht="70.3" customHeight="1">
+      <c r="A56" s="35"/>
+      <c r="B56" s="35"/>
+      <c r="C56" s="35"/>
+      <c r="D56" s="35"/>
+      <c r="E56" s="35"/>
+      <c r="F56" s="35"/>
+      <c r="G56" s="35"/>
+      <c r="H56" s="35"/>
+      <c r="I56" s="35"/>
+      <c r="J56" s="35"/>
+      <c r="K56" s="35"/>
+      <c r="L56" s="37"/>
+      <c r="M56" s="35"/>
+      <c r="N56" s="35"/>
+      <c r="O56" s="35"/>
+      <c r="P56" s="35"/>
+      <c r="Q56" s="35"/>
+      <c r="R56" s="35"/>
+      <c r="S56" s="35"/>
+      <c r="T56" s="35"/>
+      <c r="U56" s="35"/>
+      <c r="V56" s="35"/>
+      <c r="W56" s="35"/>
+    </row>
+    <row r="57" ht="34" customHeight="1">
+      <c r="A57" t="s" s="34">
+        <v>191</v>
+      </c>
+      <c r="B57" s="35"/>
+      <c r="C57" s="35"/>
+      <c r="D57" s="35"/>
+      <c r="E57" s="35"/>
+      <c r="F57" s="35"/>
+      <c r="G57" s="35"/>
+      <c r="H57" s="35"/>
+      <c r="I57" s="35"/>
+      <c r="J57" s="35"/>
+      <c r="K57" s="35"/>
+      <c r="L57" s="35"/>
+      <c r="M57" s="35"/>
+      <c r="N57" s="35"/>
+      <c r="O57" s="35"/>
+      <c r="P57" s="35"/>
+      <c r="Q57" s="35"/>
+      <c r="R57" s="35"/>
+      <c r="S57" s="35"/>
+      <c r="T57" s="35"/>
+      <c r="U57" s="35"/>
+      <c r="V57" s="35"/>
+      <c r="W57" s="35"/>
+    </row>
+    <row r="58" ht="17" customHeight="1">
+      <c r="A58" t="s" s="36">
+        <v>80</v>
+      </c>
+      <c r="B58" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C58" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D58" s="35"/>
+      <c r="E58" t="s" s="36">
+        <v>79</v>
+      </c>
+      <c r="F58" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G58" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H58" s="37"/>
+      <c r="I58" s="52"/>
+      <c r="J58" s="52"/>
+      <c r="K58" s="52"/>
+      <c r="L58" s="37"/>
+      <c r="M58" s="52"/>
+      <c r="N58" s="52"/>
+      <c r="O58" s="52"/>
+      <c r="P58" s="35"/>
+      <c r="Q58" s="53"/>
+      <c r="R58" s="53"/>
+      <c r="S58" s="53"/>
+      <c r="T58" s="35"/>
+      <c r="U58" s="53"/>
+      <c r="V58" s="53"/>
+      <c r="W58" s="53"/>
+    </row>
+    <row r="59" ht="17" customHeight="1">
+      <c r="A59" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B59" t="s" s="39">
+        <v>148</v>
+      </c>
+      <c r="C59" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D59" s="35"/>
+      <c r="E59" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F59" t="s" s="39">
+        <v>148</v>
+      </c>
+      <c r="G59" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="H59" s="37"/>
+      <c r="I59" s="35"/>
+      <c r="J59" s="35"/>
+      <c r="K59" s="35"/>
+      <c r="L59" s="35"/>
+      <c r="M59" s="35"/>
+      <c r="N59" s="35"/>
+      <c r="O59" s="35"/>
+      <c r="P59" s="35"/>
+      <c r="Q59" s="35"/>
+      <c r="R59" s="35"/>
+      <c r="S59" s="35"/>
+      <c r="T59" s="35"/>
+      <c r="U59" s="35"/>
+      <c r="V59" s="35"/>
+      <c r="W59" s="35"/>
+    </row>
+    <row r="60" ht="17" customHeight="1">
+      <c r="A60" s="37"/>
+      <c r="B60" t="s" s="41">
+        <v>192</v>
+      </c>
+      <c r="C60" t="s" s="41">
+        <v>193</v>
+      </c>
+      <c r="D60" s="35"/>
+      <c r="E60" s="37"/>
+      <c r="F60" t="s" s="41">
+        <v>194</v>
+      </c>
+      <c r="G60" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="H60" s="37"/>
+      <c r="I60" s="35"/>
+      <c r="J60" s="35"/>
+      <c r="K60" s="35"/>
+      <c r="L60" s="35"/>
+      <c r="M60" s="35"/>
+      <c r="N60" s="35"/>
+      <c r="O60" s="35"/>
+      <c r="P60" s="35"/>
+      <c r="Q60" s="35"/>
+      <c r="R60" s="35"/>
+      <c r="S60" s="35"/>
+      <c r="T60" s="35"/>
+      <c r="U60" s="35"/>
+      <c r="V60" s="35"/>
+      <c r="W60" s="35"/>
+    </row>
+    <row r="61" ht="17" customHeight="1">
+      <c r="A61" s="44"/>
+      <c r="B61" t="s" s="39">
+        <v>194</v>
+      </c>
+      <c r="C61" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="D61" s="35"/>
+      <c r="E61" s="44"/>
+      <c r="F61" t="s" s="39">
+        <v>195</v>
+      </c>
+      <c r="G61" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H61" s="37"/>
+      <c r="I61" s="35"/>
+      <c r="J61" s="35"/>
+      <c r="K61" s="35"/>
+      <c r="L61" s="35"/>
+      <c r="M61" s="35"/>
+      <c r="N61" s="35"/>
+      <c r="O61" s="35"/>
+      <c r="P61" s="35"/>
+      <c r="Q61" s="35"/>
+      <c r="R61" s="35"/>
+      <c r="S61" s="35"/>
+      <c r="T61" s="35"/>
+      <c r="U61" s="35"/>
+      <c r="V61" s="35"/>
+      <c r="W61" s="35"/>
+    </row>
+    <row r="62" ht="17" customHeight="1">
+      <c r="A62" s="37"/>
+      <c r="B62" t="s" s="41">
+        <v>195</v>
+      </c>
+      <c r="C62" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D62" s="35"/>
+      <c r="E62" s="35"/>
+      <c r="F62" s="35"/>
+      <c r="G62" s="35"/>
+      <c r="H62" s="37"/>
+      <c r="I62" s="35"/>
+      <c r="J62" s="35"/>
+      <c r="K62" s="35"/>
+      <c r="L62" s="35"/>
+      <c r="M62" s="35"/>
+      <c r="N62" s="35"/>
+      <c r="O62" s="35"/>
+      <c r="P62" s="35"/>
+      <c r="Q62" s="35"/>
+      <c r="R62" s="35"/>
+      <c r="S62" s="35"/>
+      <c r="T62" s="35"/>
+      <c r="U62" s="35"/>
+      <c r="V62" s="35"/>
+      <c r="W62" s="35"/>
+    </row>
+    <row r="63" ht="17" customHeight="1">
+      <c r="A63" s="44"/>
+      <c r="B63" t="s" s="39">
+        <v>160</v>
+      </c>
+      <c r="C63" t="s" s="39">
+        <v>116</v>
+      </c>
+      <c r="D63" s="35"/>
+      <c r="E63" s="35"/>
+      <c r="F63" s="35"/>
+      <c r="G63" s="35"/>
+      <c r="H63" s="37"/>
+      <c r="I63" s="35"/>
+      <c r="J63" s="35"/>
+      <c r="K63" s="35"/>
+      <c r="L63" s="35"/>
+      <c r="M63" s="35"/>
+      <c r="N63" s="35"/>
+      <c r="O63" s="35"/>
+      <c r="P63" s="35"/>
+      <c r="Q63" s="35"/>
+      <c r="R63" s="35"/>
+      <c r="S63" s="35"/>
+      <c r="T63" s="35"/>
+      <c r="U63" s="35"/>
+      <c r="V63" s="35"/>
+      <c r="W63" s="35"/>
+    </row>
+    <row r="64" ht="70.7" customHeight="1">
+      <c r="A64" s="37"/>
+      <c r="B64" s="37"/>
+      <c r="C64" s="37"/>
+      <c r="D64" s="35"/>
+      <c r="E64" s="54"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="54"/>
+      <c r="H64" s="37"/>
+      <c r="I64" s="37"/>
+      <c r="J64" s="37"/>
+      <c r="K64" s="37"/>
+      <c r="L64" s="37"/>
+      <c r="M64" s="37"/>
+      <c r="N64" s="37"/>
+      <c r="O64" s="37"/>
+      <c r="P64" s="35"/>
+      <c r="Q64" s="42"/>
+      <c r="R64" s="42"/>
+      <c r="S64" s="42"/>
+      <c r="T64" s="35"/>
+      <c r="U64" s="42"/>
+      <c r="V64" s="42"/>
+      <c r="W64" s="42"/>
+    </row>
+    <row r="65" ht="34" customHeight="1">
+      <c r="A65" t="s" s="34">
+        <v>196</v>
+      </c>
+      <c r="B65" s="35"/>
+      <c r="C65" s="35"/>
+      <c r="D65" s="35"/>
+      <c r="E65" s="35"/>
+      <c r="F65" s="35"/>
+      <c r="G65" s="35"/>
+      <c r="H65" s="35"/>
+      <c r="I65" s="35"/>
+      <c r="J65" s="35"/>
+      <c r="K65" s="35"/>
+      <c r="L65" s="35"/>
+      <c r="M65" s="35"/>
+      <c r="N65" s="35"/>
+      <c r="O65" s="35"/>
+      <c r="P65" s="35"/>
+      <c r="Q65" s="35"/>
+      <c r="R65" s="35"/>
+      <c r="S65" s="35"/>
+      <c r="T65" s="35"/>
+      <c r="U65" s="35"/>
+      <c r="V65" s="35"/>
+      <c r="W65" s="35"/>
+    </row>
+    <row r="66" ht="17" customHeight="1">
+      <c r="A66" t="s" s="36">
+        <v>86</v>
+      </c>
+      <c r="B66" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C66" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D66" s="35"/>
+      <c r="E66" t="s" s="36">
+        <v>85</v>
+      </c>
+      <c r="F66" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G66" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H66" s="37"/>
+      <c r="I66" t="s" s="36">
+        <v>89</v>
+      </c>
+      <c r="J66" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="K66" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="L66" s="37"/>
+      <c r="M66" s="52"/>
+      <c r="N66" s="52"/>
+      <c r="O66" s="52"/>
+      <c r="P66" s="35"/>
+      <c r="Q66" s="53"/>
+      <c r="R66" s="53"/>
+      <c r="S66" s="53"/>
+      <c r="T66" s="35"/>
+      <c r="U66" s="53"/>
+      <c r="V66" s="53"/>
+      <c r="W66" s="53"/>
+    </row>
+    <row r="67" ht="17" customHeight="1">
+      <c r="A67" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B67" t="s" s="39">
         <v>119</v>
       </c>
-      <c r="D11" s="36"/>
-      <c r="E11" s="36"/>
-      <c r="F11" t="s" s="40">
-        <v>122</v>
-      </c>
-      <c r="G11" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H11" s="36"/>
-      <c r="I11" s="36"/>
-      <c r="J11" t="s" s="40">
-        <v>122</v>
-      </c>
-      <c r="K11" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" t="s" s="40">
-        <v>123</v>
-      </c>
-      <c r="O11" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="34"/>
-      <c r="R11" s="34"/>
-      <c r="S11" s="34"/>
-      <c r="T11" s="34"/>
-      <c r="U11" s="34"/>
-      <c r="V11" s="34"/>
-      <c r="W11" s="34"/>
-    </row>
-    <row r="12" ht="17" customHeight="1">
-      <c r="A12" s="43"/>
-      <c r="B12" t="s" s="38">
-        <v>124</v>
-      </c>
-      <c r="C12" t="s" s="38">
-        <v>115</v>
-      </c>
-      <c r="D12" s="36"/>
-      <c r="E12" s="43"/>
-      <c r="F12" t="s" s="38">
-        <v>125</v>
-      </c>
-      <c r="G12" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H12" s="36"/>
-      <c r="I12" s="43"/>
-      <c r="J12" t="s" s="38">
-        <v>125</v>
-      </c>
-      <c r="K12" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L12" s="36"/>
-      <c r="M12" s="43"/>
-      <c r="N12" t="s" s="38">
-        <v>126</v>
-      </c>
-      <c r="O12" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="34"/>
-      <c r="R12" s="34"/>
-      <c r="S12" s="34"/>
-      <c r="T12" s="34"/>
-      <c r="U12" s="34"/>
-      <c r="V12" s="34"/>
-      <c r="W12" s="34"/>
-    </row>
-    <row r="13" ht="17" customHeight="1">
-      <c r="A13" s="36"/>
-      <c r="B13" t="s" s="40">
-        <v>127</v>
-      </c>
-      <c r="C13" t="s" s="40">
+      <c r="C67" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D67" s="35"/>
+      <c r="E67" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F67" t="s" s="39">
+        <v>197</v>
+      </c>
+      <c r="G67" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H67" s="37"/>
+      <c r="I67" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="J67" t="s" s="39">
+        <v>198</v>
+      </c>
+      <c r="K67" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L67" s="37"/>
+      <c r="M67" s="35"/>
+      <c r="N67" s="35"/>
+      <c r="O67" s="35"/>
+      <c r="P67" s="35"/>
+      <c r="Q67" s="35"/>
+      <c r="R67" s="35"/>
+      <c r="S67" s="35"/>
+      <c r="T67" s="35"/>
+      <c r="U67" s="35"/>
+      <c r="V67" s="35"/>
+      <c r="W67" s="35"/>
+    </row>
+    <row r="68" ht="17" customHeight="1">
+      <c r="A68" s="37"/>
+      <c r="B68" t="s" s="41">
+        <v>197</v>
+      </c>
+      <c r="C68" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D68" s="35"/>
+      <c r="E68" s="37"/>
+      <c r="F68" t="s" s="41">
+        <v>199</v>
+      </c>
+      <c r="G68" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H68" s="37"/>
+      <c r="I68" s="37"/>
+      <c r="J68" t="s" s="41">
+        <v>200</v>
+      </c>
+      <c r="K68" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="L68" s="37"/>
+      <c r="M68" s="35"/>
+      <c r="N68" s="35"/>
+      <c r="O68" s="35"/>
+      <c r="P68" s="35"/>
+      <c r="Q68" s="35"/>
+      <c r="R68" s="35"/>
+      <c r="S68" s="35"/>
+      <c r="T68" s="35"/>
+      <c r="U68" s="35"/>
+      <c r="V68" s="35"/>
+      <c r="W68" s="35"/>
+    </row>
+    <row r="69" ht="17" customHeight="1">
+      <c r="A69" s="44"/>
+      <c r="B69" t="s" s="39">
+        <v>199</v>
+      </c>
+      <c r="C69" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="D69" s="35"/>
+      <c r="E69" s="44"/>
+      <c r="F69" t="s" s="39">
+        <v>201</v>
+      </c>
+      <c r="G69" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H69" s="37"/>
+      <c r="I69" s="44"/>
+      <c r="J69" t="s" s="39">
+        <v>202</v>
+      </c>
+      <c r="K69" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L69" s="37"/>
+      <c r="M69" s="35"/>
+      <c r="N69" s="35"/>
+      <c r="O69" s="35"/>
+      <c r="P69" s="35"/>
+      <c r="Q69" s="35"/>
+      <c r="R69" s="35"/>
+      <c r="S69" s="35"/>
+      <c r="T69" s="35"/>
+      <c r="U69" s="35"/>
+      <c r="V69" s="35"/>
+      <c r="W69" s="35"/>
+    </row>
+    <row r="70" ht="17" customHeight="1">
+      <c r="A70" s="37"/>
+      <c r="B70" t="s" s="41">
+        <v>201</v>
+      </c>
+      <c r="C70" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D70" s="35"/>
+      <c r="E70" s="37"/>
+      <c r="F70" t="s" s="41">
+        <v>203</v>
+      </c>
+      <c r="G70" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H70" s="37"/>
+      <c r="I70" s="37"/>
+      <c r="J70" t="s" s="41">
+        <v>204</v>
+      </c>
+      <c r="K70" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="L70" s="37"/>
+      <c r="M70" s="35"/>
+      <c r="N70" s="35"/>
+      <c r="O70" s="35"/>
+      <c r="P70" s="35"/>
+      <c r="Q70" s="35"/>
+      <c r="R70" s="35"/>
+      <c r="S70" s="35"/>
+      <c r="T70" s="35"/>
+      <c r="U70" s="35"/>
+      <c r="V70" s="35"/>
+      <c r="W70" s="35"/>
+    </row>
+    <row r="71" ht="17" customHeight="1">
+      <c r="A71" s="44"/>
+      <c r="B71" t="s" s="39">
+        <v>203</v>
+      </c>
+      <c r="C71" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="D71" s="35"/>
+      <c r="E71" s="44"/>
+      <c r="F71" t="s" s="39">
+        <v>205</v>
+      </c>
+      <c r="G71" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H71" s="37"/>
+      <c r="I71" s="44"/>
+      <c r="J71" t="s" s="39">
+        <v>206</v>
+      </c>
+      <c r="K71" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="L71" s="37"/>
+      <c r="M71" s="35"/>
+      <c r="N71" s="35"/>
+      <c r="O71" s="35"/>
+      <c r="P71" s="35"/>
+      <c r="Q71" s="35"/>
+      <c r="R71" s="35"/>
+      <c r="S71" s="35"/>
+      <c r="T71" s="35"/>
+      <c r="U71" s="35"/>
+      <c r="V71" s="35"/>
+      <c r="W71" s="35"/>
+    </row>
+    <row r="72" ht="17" customHeight="1">
+      <c r="A72" s="37"/>
+      <c r="B72" t="s" s="41">
+        <v>205</v>
+      </c>
+      <c r="C72" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="D72" s="35"/>
+      <c r="E72" s="37"/>
+      <c r="F72" t="s" s="41">
+        <v>207</v>
+      </c>
+      <c r="G72" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H72" s="37"/>
+      <c r="I72" s="37"/>
+      <c r="J72" t="s" s="41">
+        <v>208</v>
+      </c>
+      <c r="K72" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="L72" s="37"/>
+      <c r="M72" s="35"/>
+      <c r="N72" s="35"/>
+      <c r="O72" s="35"/>
+      <c r="P72" s="35"/>
+      <c r="Q72" s="35"/>
+      <c r="R72" s="35"/>
+      <c r="S72" s="35"/>
+      <c r="T72" s="35"/>
+      <c r="U72" s="35"/>
+      <c r="V72" s="35"/>
+      <c r="W72" s="35"/>
+    </row>
+    <row r="73" ht="17" customHeight="1">
+      <c r="A73" s="44"/>
+      <c r="B73" t="s" s="39">
+        <v>207</v>
+      </c>
+      <c r="C73" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="D73" s="35"/>
+      <c r="E73" s="44"/>
+      <c r="F73" s="44"/>
+      <c r="G73" s="44"/>
+      <c r="H73" s="37"/>
+      <c r="I73" s="44"/>
+      <c r="J73" s="44"/>
+      <c r="K73" s="44"/>
+      <c r="L73" s="37"/>
+      <c r="M73" s="35"/>
+      <c r="N73" s="35"/>
+      <c r="O73" s="35"/>
+      <c r="P73" s="35"/>
+      <c r="Q73" s="35"/>
+      <c r="R73" s="35"/>
+      <c r="S73" s="35"/>
+      <c r="T73" s="35"/>
+      <c r="U73" s="35"/>
+      <c r="V73" s="35"/>
+      <c r="W73" s="35"/>
+    </row>
+    <row r="74" ht="70.2" customHeight="1">
+      <c r="A74" s="37"/>
+      <c r="B74" s="37"/>
+      <c r="C74" s="37"/>
+      <c r="D74" s="35"/>
+      <c r="E74" s="37"/>
+      <c r="F74" s="37"/>
+      <c r="G74" s="37"/>
+      <c r="H74" s="37"/>
+      <c r="I74" s="37"/>
+      <c r="J74" s="37"/>
+      <c r="K74" s="37"/>
+      <c r="L74" s="37"/>
+      <c r="M74" s="37"/>
+      <c r="N74" s="37"/>
+      <c r="O74" s="37"/>
+      <c r="P74" s="35"/>
+      <c r="Q74" s="42"/>
+      <c r="R74" s="42"/>
+      <c r="S74" s="42"/>
+      <c r="T74" s="35"/>
+      <c r="U74" s="42"/>
+      <c r="V74" s="42"/>
+      <c r="W74" s="42"/>
+    </row>
+    <row r="75" ht="34" customHeight="1">
+      <c r="A75" t="s" s="34">
+        <v>209</v>
+      </c>
+      <c r="B75" s="35"/>
+      <c r="C75" s="35"/>
+      <c r="D75" s="35"/>
+      <c r="E75" s="35"/>
+      <c r="F75" s="35"/>
+      <c r="G75" s="35"/>
+      <c r="H75" s="35"/>
+      <c r="I75" s="35"/>
+      <c r="J75" s="35"/>
+      <c r="K75" s="35"/>
+      <c r="L75" s="35"/>
+      <c r="M75" s="35"/>
+      <c r="N75" s="35"/>
+      <c r="O75" s="35"/>
+      <c r="P75" s="35"/>
+      <c r="Q75" s="35"/>
+      <c r="R75" s="35"/>
+      <c r="S75" s="35"/>
+      <c r="T75" s="35"/>
+      <c r="U75" s="35"/>
+      <c r="V75" s="35"/>
+      <c r="W75" s="35"/>
+    </row>
+    <row r="76" ht="17" customHeight="1">
+      <c r="A76" t="s" s="36">
+        <v>96</v>
+      </c>
+      <c r="B76" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C76" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D76" s="35"/>
+      <c r="E76" t="s" s="36">
+        <v>95</v>
+      </c>
+      <c r="F76" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G76" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H76" s="37"/>
+      <c r="I76" t="s" s="36">
+        <v>99</v>
+      </c>
+      <c r="J76" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="K76" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="L76" s="37"/>
+      <c r="M76" s="52"/>
+      <c r="N76" s="52"/>
+      <c r="O76" s="52"/>
+      <c r="P76" s="35"/>
+      <c r="Q76" s="53"/>
+      <c r="R76" s="53"/>
+      <c r="S76" s="53"/>
+      <c r="T76" s="35"/>
+      <c r="U76" s="53"/>
+      <c r="V76" s="53"/>
+      <c r="W76" s="53"/>
+    </row>
+    <row r="77" ht="17" customHeight="1">
+      <c r="A77" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="B77" t="s" s="39">
         <v>119</v>
       </c>
-      <c r="D13" s="36"/>
-      <c r="E13" s="36"/>
-      <c r="F13" t="s" s="40">
-        <v>128</v>
-      </c>
-      <c r="G13" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H13" s="36"/>
-      <c r="I13" s="36"/>
-      <c r="J13" t="s" s="40">
-        <v>128</v>
-      </c>
-      <c r="K13" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36"/>
-      <c r="N13" t="s" s="40">
-        <v>129</v>
-      </c>
-      <c r="O13" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="P13" s="36"/>
-      <c r="Q13" s="34"/>
-      <c r="R13" s="34"/>
-      <c r="S13" s="34"/>
-      <c r="T13" s="34"/>
-      <c r="U13" s="34"/>
-      <c r="V13" s="34"/>
-      <c r="W13" s="34"/>
-    </row>
-    <row r="14" ht="17" customHeight="1">
-      <c r="A14" s="43"/>
-      <c r="B14" t="s" s="38">
-        <v>130</v>
-      </c>
-      <c r="C14" t="s" s="38">
-        <v>115</v>
-      </c>
-      <c r="D14" s="36"/>
-      <c r="E14" s="43"/>
-      <c r="F14" t="s" s="38">
+      <c r="C77" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D77" s="35"/>
+      <c r="E77" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F77" t="s" s="39">
+        <v>148</v>
+      </c>
+      <c r="G77" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="H77" s="37"/>
+      <c r="I77" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="J77" t="s" s="39">
+        <v>210</v>
+      </c>
+      <c r="K77" t="s" s="39">
+        <v>211</v>
+      </c>
+      <c r="L77" s="37"/>
+      <c r="M77" s="35"/>
+      <c r="N77" s="35"/>
+      <c r="O77" s="35"/>
+      <c r="P77" s="35"/>
+      <c r="Q77" s="35"/>
+      <c r="R77" s="35"/>
+      <c r="S77" s="35"/>
+      <c r="T77" s="35"/>
+      <c r="U77" s="35"/>
+      <c r="V77" s="35"/>
+      <c r="W77" s="35"/>
+    </row>
+    <row r="78" ht="17" customHeight="1">
+      <c r="A78" s="37"/>
+      <c r="B78" t="s" s="41">
+        <v>212</v>
+      </c>
+      <c r="C78" t="s" s="41">
+        <v>120</v>
+      </c>
+      <c r="D78" s="35"/>
+      <c r="E78" s="37"/>
+      <c r="F78" t="s" s="41">
+        <v>210</v>
+      </c>
+      <c r="G78" t="s" s="41">
+        <v>211</v>
+      </c>
+      <c r="H78" s="37"/>
+      <c r="I78" s="35"/>
+      <c r="J78" s="35"/>
+      <c r="K78" s="35"/>
+      <c r="L78" s="37"/>
+      <c r="M78" s="35"/>
+      <c r="N78" s="35"/>
+      <c r="O78" s="35"/>
+      <c r="P78" s="35"/>
+      <c r="Q78" s="35"/>
+      <c r="R78" s="35"/>
+      <c r="S78" s="35"/>
+      <c r="T78" s="35"/>
+      <c r="U78" s="35"/>
+      <c r="V78" s="35"/>
+      <c r="W78" s="35"/>
+    </row>
+    <row r="79" ht="17" customHeight="1">
+      <c r="A79" s="44"/>
+      <c r="B79" t="s" s="39">
+        <v>148</v>
+      </c>
+      <c r="C79" t="s" s="39">
+        <v>120</v>
+      </c>
+      <c r="D79" s="35"/>
+      <c r="E79" s="44"/>
+      <c r="F79" s="44"/>
+      <c r="G79" s="44"/>
+      <c r="H79" s="37"/>
+      <c r="I79" s="35"/>
+      <c r="J79" s="35"/>
+      <c r="K79" s="35"/>
+      <c r="L79" s="37"/>
+      <c r="M79" s="35"/>
+      <c r="N79" s="35"/>
+      <c r="O79" s="35"/>
+      <c r="P79" s="35"/>
+      <c r="Q79" s="35"/>
+      <c r="R79" s="35"/>
+      <c r="S79" s="35"/>
+      <c r="T79" s="35"/>
+      <c r="U79" s="35"/>
+      <c r="V79" s="35"/>
+      <c r="W79" s="35"/>
+    </row>
+    <row r="80" ht="17" customHeight="1">
+      <c r="A80" s="37"/>
+      <c r="B80" t="s" s="41">
+        <v>210</v>
+      </c>
+      <c r="C80" t="s" s="41">
+        <v>211</v>
+      </c>
+      <c r="D80" s="35"/>
+      <c r="E80" s="37"/>
+      <c r="F80" s="37"/>
+      <c r="G80" s="37"/>
+      <c r="H80" s="37"/>
+      <c r="I80" s="37"/>
+      <c r="J80" s="37"/>
+      <c r="K80" s="37"/>
+      <c r="L80" s="37"/>
+      <c r="M80" s="37"/>
+      <c r="N80" s="37"/>
+      <c r="O80" s="37"/>
+      <c r="P80" s="35"/>
+      <c r="Q80" s="42"/>
+      <c r="R80" s="42"/>
+      <c r="S80" s="42"/>
+      <c r="T80" s="35"/>
+      <c r="U80" s="42"/>
+      <c r="V80" s="42"/>
+      <c r="W80" s="42"/>
+    </row>
+    <row r="81" ht="70.5" customHeight="1">
+      <c r="A81" s="37"/>
+      <c r="B81" s="37"/>
+      <c r="C81" s="37"/>
+      <c r="D81" s="35"/>
+      <c r="E81" s="54"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="54"/>
+      <c r="H81" s="37"/>
+      <c r="I81" s="37"/>
+      <c r="J81" s="37"/>
+      <c r="K81" s="37"/>
+      <c r="L81" s="37"/>
+      <c r="M81" s="37"/>
+      <c r="N81" s="37"/>
+      <c r="O81" s="37"/>
+      <c r="P81" s="35"/>
+      <c r="Q81" s="42"/>
+      <c r="R81" s="42"/>
+      <c r="S81" s="42"/>
+      <c r="T81" s="35"/>
+      <c r="U81" s="42"/>
+      <c r="V81" s="42"/>
+      <c r="W81" s="42"/>
+    </row>
+    <row r="82" ht="34" customHeight="1">
+      <c r="A82" t="s" s="34">
+        <v>213</v>
+      </c>
+      <c r="B82" s="35"/>
+      <c r="C82" s="35"/>
+      <c r="D82" s="35"/>
+      <c r="E82" s="35"/>
+      <c r="F82" s="35"/>
+      <c r="G82" s="35"/>
+      <c r="H82" s="35"/>
+      <c r="I82" s="35"/>
+      <c r="J82" s="35"/>
+      <c r="K82" s="35"/>
+      <c r="L82" s="35"/>
+      <c r="M82" s="35"/>
+      <c r="N82" s="35"/>
+      <c r="O82" s="35"/>
+      <c r="P82" s="35"/>
+      <c r="Q82" s="35"/>
+      <c r="R82" s="35"/>
+      <c r="S82" s="35"/>
+      <c r="T82" s="35"/>
+      <c r="U82" s="35"/>
+      <c r="V82" s="35"/>
+      <c r="W82" s="35"/>
+    </row>
+    <row r="83" ht="17" customHeight="1">
+      <c r="A83" t="s" s="38">
+        <v>214</v>
+      </c>
+      <c r="B83" t="s" s="38">
+        <v>106</v>
+      </c>
+      <c r="C83" t="s" s="38">
+        <v>107</v>
+      </c>
+      <c r="D83" s="35"/>
+      <c r="E83" t="s" s="55">
+        <v>215</v>
+      </c>
+      <c r="F83" t="s" s="55">
+        <v>106</v>
+      </c>
+      <c r="G83" t="s" s="55">
+        <v>107</v>
+      </c>
+      <c r="H83" s="37"/>
+      <c r="I83" s="52"/>
+      <c r="J83" s="52"/>
+      <c r="K83" s="52"/>
+      <c r="L83" s="37"/>
+      <c r="M83" s="52"/>
+      <c r="N83" s="52"/>
+      <c r="O83" s="52"/>
+      <c r="P83" s="35"/>
+      <c r="Q83" s="53"/>
+      <c r="R83" s="53"/>
+      <c r="S83" s="53"/>
+      <c r="T83" s="35"/>
+      <c r="U83" s="53"/>
+      <c r="V83" s="53"/>
+      <c r="W83" s="53"/>
+    </row>
+    <row r="84" ht="17" customHeight="1">
+      <c r="A84" t="s" s="40">
         <v>113</v>
       </c>
-      <c r="G14" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H14" s="36"/>
-      <c r="I14" s="43"/>
-      <c r="J14" t="s" s="38">
-        <v>113</v>
-      </c>
-      <c r="K14" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="43"/>
-      <c r="N14" t="s" s="38">
-        <v>131</v>
-      </c>
-      <c r="O14" t="s" s="38">
-        <v>132</v>
-      </c>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="34"/>
-      <c r="R14" s="34"/>
-      <c r="S14" s="34"/>
-      <c r="T14" s="34"/>
-      <c r="U14" s="34"/>
-      <c r="V14" s="34"/>
-      <c r="W14" s="34"/>
-    </row>
-    <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="36"/>
-      <c r="B15" t="s" s="40">
+      <c r="B84" t="s" s="40">
+        <v>119</v>
+      </c>
+      <c r="C84" t="s" s="40">
+        <v>120</v>
+      </c>
+      <c r="D84" s="35"/>
+      <c r="E84" t="s" s="56">
+        <v>216</v>
+      </c>
+      <c r="F84" t="s" s="56">
+        <v>217</v>
+      </c>
+      <c r="G84" t="s" s="56">
+        <v>111</v>
+      </c>
+      <c r="H84" s="35"/>
+      <c r="I84" s="35"/>
+      <c r="J84" s="35"/>
+      <c r="K84" s="35"/>
+      <c r="L84" s="35"/>
+      <c r="M84" s="35"/>
+      <c r="N84" s="35"/>
+      <c r="O84" s="35"/>
+      <c r="P84" s="35"/>
+      <c r="Q84" s="35"/>
+      <c r="R84" s="35"/>
+      <c r="S84" s="35"/>
+      <c r="T84" s="35"/>
+      <c r="U84" s="35"/>
+      <c r="V84" s="35"/>
+      <c r="W84" s="35"/>
+    </row>
+    <row r="85" ht="17" customHeight="1">
+      <c r="A85" s="42"/>
+      <c r="B85" t="s" s="43">
+        <v>212</v>
+      </c>
+      <c r="C85" t="s" s="43">
+        <v>120</v>
+      </c>
+      <c r="D85" s="35"/>
+      <c r="E85" s="54"/>
+      <c r="F85" t="s" s="57">
+        <v>218</v>
+      </c>
+      <c r="G85" t="s" s="57">
+        <v>219</v>
+      </c>
+      <c r="H85" s="35"/>
+      <c r="I85" s="35"/>
+      <c r="J85" s="35"/>
+      <c r="K85" s="35"/>
+      <c r="L85" s="35"/>
+      <c r="M85" s="35"/>
+      <c r="N85" s="35"/>
+      <c r="O85" s="35"/>
+      <c r="P85" s="35"/>
+      <c r="Q85" s="35"/>
+      <c r="R85" s="35"/>
+      <c r="S85" s="35"/>
+      <c r="T85" s="35"/>
+      <c r="U85" s="35"/>
+      <c r="V85" s="35"/>
+      <c r="W85" s="35"/>
+    </row>
+    <row r="86" ht="17" customHeight="1">
+      <c r="A86" s="45"/>
+      <c r="B86" t="s" s="40">
+        <v>217</v>
+      </c>
+      <c r="C86" t="s" s="40">
+        <v>111</v>
+      </c>
+      <c r="D86" s="35"/>
+      <c r="E86" s="58"/>
+      <c r="F86" t="s" s="56">
+        <v>183</v>
+      </c>
+      <c r="G86" t="s" s="56">
+        <v>220</v>
+      </c>
+      <c r="H86" s="35"/>
+      <c r="I86" s="35"/>
+      <c r="J86" s="35"/>
+      <c r="K86" s="35"/>
+      <c r="L86" s="35"/>
+      <c r="M86" s="35"/>
+      <c r="N86" s="35"/>
+      <c r="O86" s="35"/>
+      <c r="P86" s="35"/>
+      <c r="Q86" s="35"/>
+      <c r="R86" s="35"/>
+      <c r="S86" s="35"/>
+      <c r="T86" s="35"/>
+      <c r="U86" s="35"/>
+      <c r="V86" s="35"/>
+      <c r="W86" s="35"/>
+    </row>
+    <row r="87" ht="17" customHeight="1">
+      <c r="A87" s="42"/>
+      <c r="B87" t="s" s="43">
+        <v>218</v>
+      </c>
+      <c r="C87" t="s" s="43">
+        <v>219</v>
+      </c>
+      <c r="D87" s="35"/>
+      <c r="E87" s="54"/>
+      <c r="F87" t="s" s="57">
+        <v>160</v>
+      </c>
+      <c r="G87" t="s" s="57">
+        <v>116</v>
+      </c>
+      <c r="H87" s="35"/>
+      <c r="I87" s="35"/>
+      <c r="J87" s="35"/>
+      <c r="K87" s="35"/>
+      <c r="L87" s="35"/>
+      <c r="M87" s="35"/>
+      <c r="N87" s="35"/>
+      <c r="O87" s="35"/>
+      <c r="P87" s="35"/>
+      <c r="Q87" s="35"/>
+      <c r="R87" s="35"/>
+      <c r="S87" s="35"/>
+      <c r="T87" s="35"/>
+      <c r="U87" s="35"/>
+      <c r="V87" s="35"/>
+      <c r="W87" s="35"/>
+    </row>
+    <row r="88" ht="17" customHeight="1">
+      <c r="A88" s="45"/>
+      <c r="B88" t="s" s="40">
+        <v>183</v>
+      </c>
+      <c r="C88" t="s" s="40">
+        <v>220</v>
+      </c>
+      <c r="D88" s="35"/>
+      <c r="E88" s="58"/>
+      <c r="F88" s="58"/>
+      <c r="G88" s="58"/>
+      <c r="H88" s="35"/>
+      <c r="I88" s="35"/>
+      <c r="J88" s="35"/>
+      <c r="K88" s="35"/>
+      <c r="L88" s="35"/>
+      <c r="M88" s="35"/>
+      <c r="N88" s="35"/>
+      <c r="O88" s="35"/>
+      <c r="P88" s="35"/>
+      <c r="Q88" s="35"/>
+      <c r="R88" s="35"/>
+      <c r="S88" s="35"/>
+      <c r="T88" s="35"/>
+      <c r="U88" s="35"/>
+      <c r="V88" s="35"/>
+      <c r="W88" s="35"/>
+    </row>
+    <row r="89" ht="17" customHeight="1">
+      <c r="A89" s="42"/>
+      <c r="B89" t="s" s="43">
+        <v>160</v>
+      </c>
+      <c r="C89" t="s" s="43">
+        <v>116</v>
+      </c>
+      <c r="D89" s="35"/>
+      <c r="E89" s="54"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="54"/>
+      <c r="H89" s="37"/>
+      <c r="I89" s="37"/>
+      <c r="J89" s="37"/>
+      <c r="K89" s="37"/>
+      <c r="L89" s="37"/>
+      <c r="M89" s="37"/>
+      <c r="N89" s="37"/>
+      <c r="O89" s="37"/>
+      <c r="P89" s="35"/>
+      <c r="Q89" s="42"/>
+      <c r="R89" s="42"/>
+      <c r="S89" s="42"/>
+      <c r="T89" s="35"/>
+      <c r="U89" s="42"/>
+      <c r="V89" s="42"/>
+      <c r="W89" s="42"/>
+    </row>
+    <row r="90" ht="70.45" customHeight="1">
+      <c r="A90" s="35"/>
+      <c r="B90" s="35"/>
+      <c r="C90" s="35"/>
+      <c r="D90" s="35"/>
+      <c r="E90" s="35"/>
+      <c r="F90" s="35"/>
+      <c r="G90" s="35"/>
+      <c r="H90" s="35"/>
+      <c r="I90" s="35"/>
+      <c r="J90" s="35"/>
+      <c r="K90" s="35"/>
+      <c r="L90" s="35"/>
+      <c r="M90" s="35"/>
+      <c r="N90" s="35"/>
+      <c r="O90" s="35"/>
+      <c r="P90" s="35"/>
+      <c r="Q90" s="35"/>
+      <c r="R90" s="35"/>
+      <c r="S90" s="35"/>
+      <c r="T90" s="35"/>
+      <c r="U90" s="35"/>
+      <c r="V90" s="35"/>
+      <c r="W90" s="35"/>
+    </row>
+    <row r="91" ht="34" customHeight="1">
+      <c r="A91" t="s" s="34">
+        <v>221</v>
+      </c>
+      <c r="B91" s="35"/>
+      <c r="C91" s="35"/>
+      <c r="D91" s="35"/>
+      <c r="E91" s="35"/>
+      <c r="F91" s="35"/>
+      <c r="G91" s="35"/>
+      <c r="H91" s="35"/>
+      <c r="I91" s="35"/>
+      <c r="J91" s="35"/>
+      <c r="K91" s="35"/>
+      <c r="L91" s="35"/>
+      <c r="M91" s="35"/>
+      <c r="N91" s="35"/>
+      <c r="O91" s="35"/>
+      <c r="P91" s="35"/>
+      <c r="Q91" s="35"/>
+      <c r="R91" s="35"/>
+      <c r="S91" s="35"/>
+      <c r="T91" s="35"/>
+      <c r="U91" s="35"/>
+      <c r="V91" s="35"/>
+      <c r="W91" s="35"/>
+    </row>
+    <row r="92" ht="17" customHeight="1">
+      <c r="A92" t="s" s="36">
+        <v>222</v>
+      </c>
+      <c r="B92" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="C92" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="D92" s="35"/>
+      <c r="E92" t="s" s="36">
+        <v>223</v>
+      </c>
+      <c r="F92" t="s" s="36">
+        <v>106</v>
+      </c>
+      <c r="G92" t="s" s="36">
+        <v>107</v>
+      </c>
+      <c r="H92" s="37"/>
+      <c r="I92" t="s" s="55">
+        <v>224</v>
+      </c>
+      <c r="J92" t="s" s="55">
+        <v>225</v>
+      </c>
+      <c r="K92" t="s" s="55">
+        <v>107</v>
+      </c>
+      <c r="L92" t="s" s="55">
+        <v>226</v>
+      </c>
+      <c r="M92" t="s" s="55">
+        <v>1</v>
+      </c>
+      <c r="N92" s="52"/>
+      <c r="O92" s="52"/>
+      <c r="P92" s="35"/>
+      <c r="Q92" s="53"/>
+      <c r="R92" s="53"/>
+      <c r="S92" s="53"/>
+      <c r="T92" s="35"/>
+      <c r="U92" s="53"/>
+      <c r="V92" s="53"/>
+      <c r="W92" s="53"/>
+    </row>
+    <row r="93" ht="17" customHeight="1">
+      <c r="A93" t="s" s="39">
         <v>109</v>
       </c>
-      <c r="C15" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D15" s="36"/>
-      <c r="E15" s="36"/>
-      <c r="F15" t="s" s="40">
-        <v>133</v>
-      </c>
-      <c r="G15" t="s" s="40">
-        <v>132</v>
-      </c>
-      <c r="H15" s="36"/>
-      <c r="I15" s="36"/>
-      <c r="J15" t="s" s="40">
-        <v>133</v>
-      </c>
-      <c r="K15" t="s" s="40">
-        <v>132</v>
-      </c>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36"/>
-      <c r="N15" t="s" s="40">
-        <v>134</v>
-      </c>
-      <c r="O15" t="s" s="40">
-        <v>135</v>
-      </c>
-      <c r="P15" s="36"/>
-      <c r="Q15" s="34"/>
-      <c r="R15" s="34"/>
-      <c r="S15" s="34"/>
-      <c r="T15" s="34"/>
-      <c r="U15" s="34"/>
-      <c r="V15" s="34"/>
-      <c r="W15" s="34"/>
-    </row>
-    <row r="16" ht="17" customHeight="1">
-      <c r="A16" s="43"/>
-      <c r="B16" t="s" s="38">
-        <v>122</v>
-      </c>
-      <c r="C16" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="D16" s="36"/>
-      <c r="E16" s="43"/>
-      <c r="F16" s="43"/>
-      <c r="G16" s="43"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="43"/>
-      <c r="J16" s="43"/>
-      <c r="K16" s="43"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="43"/>
-      <c r="N16" s="43"/>
-      <c r="O16" s="43"/>
-      <c r="P16" s="36"/>
-      <c r="Q16" s="34"/>
-      <c r="R16" s="34"/>
-      <c r="S16" s="34"/>
-      <c r="T16" s="34"/>
-      <c r="U16" s="34"/>
-      <c r="V16" s="34"/>
-      <c r="W16" s="34"/>
-    </row>
-    <row r="17" ht="17" customHeight="1">
-      <c r="A17" s="36"/>
-      <c r="B17" t="s" s="40">
-        <v>125</v>
-      </c>
-      <c r="C17" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D17" s="36"/>
-      <c r="E17" s="34"/>
-      <c r="F17" s="34"/>
-      <c r="G17" s="34"/>
-      <c r="H17" s="34"/>
-      <c r="I17" s="34"/>
-      <c r="J17" s="34"/>
-      <c r="K17" s="34"/>
-      <c r="L17" s="34"/>
-      <c r="M17" s="34"/>
-      <c r="N17" s="34"/>
-      <c r="O17" s="34"/>
-      <c r="P17" s="36"/>
-      <c r="Q17" s="34"/>
-      <c r="R17" s="34"/>
-      <c r="S17" s="34"/>
-      <c r="T17" s="34"/>
-      <c r="U17" s="34"/>
-      <c r="V17" s="34"/>
-      <c r="W17" s="34"/>
-    </row>
-    <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="43"/>
-      <c r="B18" t="s" s="38">
-        <v>128</v>
-      </c>
-      <c r="C18" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="D18" s="36"/>
-      <c r="E18" s="34"/>
-      <c r="F18" s="34"/>
-      <c r="G18" s="34"/>
-      <c r="H18" s="34"/>
-      <c r="I18" s="34"/>
-      <c r="J18" s="34"/>
-      <c r="K18" s="34"/>
-      <c r="L18" s="34"/>
-      <c r="M18" s="34"/>
-      <c r="N18" s="34"/>
-      <c r="O18" s="34"/>
-      <c r="P18" s="36"/>
-      <c r="Q18" s="34"/>
-      <c r="R18" s="34"/>
-      <c r="S18" s="34"/>
-      <c r="T18" s="34"/>
-      <c r="U18" s="34"/>
-      <c r="V18" s="34"/>
-      <c r="W18" s="34"/>
-    </row>
-    <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="36"/>
-      <c r="B19" t="s" s="40">
-        <v>113</v>
-      </c>
-      <c r="C19" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D19" s="36"/>
-      <c r="E19" s="34"/>
-      <c r="F19" s="34"/>
-      <c r="G19" s="34"/>
-      <c r="H19" s="34"/>
-      <c r="I19" s="34"/>
-      <c r="J19" s="34"/>
-      <c r="K19" s="34"/>
-      <c r="L19" s="34"/>
-      <c r="M19" s="34"/>
-      <c r="N19" s="34"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="36"/>
-      <c r="Q19" s="34"/>
-      <c r="R19" s="34"/>
-      <c r="S19" s="34"/>
-      <c r="T19" s="34"/>
-      <c r="U19" s="34"/>
-      <c r="V19" s="34"/>
-      <c r="W19" s="34"/>
-    </row>
-    <row r="20" ht="17" customHeight="1">
-      <c r="A20" s="43"/>
-      <c r="B20" t="s" s="38">
-        <v>136</v>
-      </c>
-      <c r="C20" t="s" s="38">
-        <v>137</v>
-      </c>
-      <c r="D20" s="36"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="34"/>
-      <c r="J20" s="34"/>
-      <c r="K20" s="34"/>
-      <c r="L20" s="34"/>
-      <c r="M20" s="34"/>
-      <c r="N20" s="34"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="36"/>
-      <c r="Q20" s="34"/>
-      <c r="R20" s="34"/>
-      <c r="S20" s="34"/>
-      <c r="T20" s="34"/>
-      <c r="U20" s="34"/>
-      <c r="V20" s="34"/>
-      <c r="W20" s="34"/>
-    </row>
-    <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="36"/>
-      <c r="B21" t="s" s="40">
-        <v>133</v>
-      </c>
-      <c r="C21" t="s" s="40">
-        <v>132</v>
-      </c>
-      <c r="D21" s="36"/>
-      <c r="E21" s="36"/>
-      <c r="F21" s="36"/>
-      <c r="G21" s="36"/>
-      <c r="H21" s="36"/>
-      <c r="I21" s="36"/>
-      <c r="J21" s="36"/>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36"/>
-      <c r="N21" s="36"/>
-      <c r="O21" s="36"/>
-      <c r="P21" s="36"/>
-      <c r="Q21" s="34"/>
-      <c r="R21" s="34"/>
-      <c r="S21" s="34"/>
-      <c r="T21" s="34"/>
-      <c r="U21" s="34"/>
-      <c r="V21" s="34"/>
-      <c r="W21" s="34"/>
-    </row>
-    <row r="22" ht="70.75" customHeight="1">
-      <c r="A22" s="34"/>
-      <c r="B22" s="34"/>
-      <c r="C22" s="34"/>
-      <c r="D22" s="34"/>
-      <c r="E22" s="34"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="34"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="34"/>
-      <c r="J22" s="34"/>
-      <c r="K22" s="34"/>
-      <c r="L22" s="34"/>
-      <c r="M22" s="34"/>
-      <c r="N22" s="34"/>
-      <c r="O22" s="34"/>
-      <c r="P22" s="34"/>
-      <c r="Q22" s="34"/>
-      <c r="R22" s="34"/>
-      <c r="S22" s="34"/>
-      <c r="T22" s="34"/>
-      <c r="U22" s="34"/>
-      <c r="V22" s="34"/>
-      <c r="W22" s="34"/>
-    </row>
-    <row r="23" ht="34" customHeight="1">
-      <c r="A23" t="s" s="33">
-        <v>138</v>
-      </c>
-      <c r="B23" s="34"/>
-      <c r="C23" s="34"/>
-      <c r="D23" s="34"/>
-      <c r="E23" s="34"/>
-      <c r="F23" s="34"/>
-      <c r="G23" s="34"/>
-      <c r="H23" s="34"/>
-      <c r="I23" s="34"/>
-      <c r="J23" s="34"/>
-      <c r="K23" s="34"/>
-      <c r="L23" s="34"/>
-      <c r="M23" s="34"/>
-      <c r="N23" s="34"/>
-      <c r="O23" s="34"/>
-      <c r="P23" s="34"/>
-      <c r="Q23" s="34"/>
-      <c r="R23" s="34"/>
-      <c r="S23" s="34"/>
-      <c r="T23" s="34"/>
-      <c r="U23" s="34"/>
-      <c r="V23" s="34"/>
-      <c r="W23" s="34"/>
-    </row>
-    <row r="24" ht="17" customHeight="1">
-      <c r="A24" t="s" s="35">
-        <v>47</v>
-      </c>
-      <c r="B24" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C24" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D24" s="34"/>
-      <c r="E24" t="s" s="35">
-        <v>49</v>
-      </c>
-      <c r="F24" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G24" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H24" s="36"/>
-      <c r="I24" t="s" s="35">
-        <v>51</v>
-      </c>
-      <c r="J24" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="K24" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="L24" s="34"/>
-      <c r="M24" t="s" s="37">
-        <v>139</v>
-      </c>
-      <c r="N24" t="s" s="37">
-        <v>105</v>
-      </c>
-      <c r="O24" t="s" s="37">
-        <v>106</v>
-      </c>
-      <c r="P24" s="34"/>
-      <c r="Q24" t="s" s="37">
-        <v>140</v>
-      </c>
-      <c r="R24" t="s" s="37">
-        <v>105</v>
-      </c>
-      <c r="S24" t="s" s="37">
-        <v>106</v>
-      </c>
-      <c r="T24" s="34"/>
-      <c r="U24" s="34"/>
-      <c r="V24" s="34"/>
-      <c r="W24" s="34"/>
-    </row>
-    <row r="25" ht="17" customHeight="1">
-      <c r="A25" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B25" t="s" s="38">
-        <v>118</v>
-      </c>
-      <c r="C25" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="D25" s="34"/>
-      <c r="E25" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F25" t="s" s="38">
-        <v>141</v>
-      </c>
-      <c r="G25" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H25" s="36"/>
-      <c r="I25" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="J25" t="s" s="38">
-        <v>142</v>
-      </c>
-      <c r="K25" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L25" s="34"/>
-      <c r="M25" t="s" s="39">
-        <v>112</v>
-      </c>
-      <c r="N25" t="s" s="39">
-        <v>118</v>
-      </c>
-      <c r="O25" t="s" s="39">
-        <v>119</v>
-      </c>
-      <c r="P25" s="34"/>
-      <c r="Q25" t="s" s="39">
-        <v>112</v>
-      </c>
-      <c r="R25" t="s" s="39">
-        <v>143</v>
-      </c>
-      <c r="S25" t="s" s="39">
-        <v>144</v>
-      </c>
-      <c r="T25" s="34"/>
-      <c r="U25" s="34"/>
-      <c r="V25" s="34"/>
-      <c r="W25" s="34"/>
-    </row>
-    <row r="26" ht="17" customHeight="1">
-      <c r="A26" s="36"/>
-      <c r="B26" t="s" s="40">
-        <v>141</v>
-      </c>
-      <c r="C26" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D26" s="34"/>
-      <c r="E26" s="36"/>
-      <c r="F26" t="s" s="40">
-        <v>145</v>
-      </c>
-      <c r="G26" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H26" s="36"/>
-      <c r="I26" s="36"/>
-      <c r="J26" t="s" s="40">
-        <v>146</v>
-      </c>
-      <c r="K26" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="L26" s="34"/>
-      <c r="M26" s="41"/>
-      <c r="N26" t="s" s="42">
-        <v>147</v>
-      </c>
-      <c r="O26" t="s" s="42">
-        <v>119</v>
-      </c>
-      <c r="P26" s="34"/>
-      <c r="Q26" s="41"/>
-      <c r="R26" t="s" s="42">
-        <v>148</v>
-      </c>
-      <c r="S26" t="s" s="42">
-        <v>149</v>
-      </c>
-      <c r="T26" s="34"/>
-      <c r="U26" s="34"/>
-      <c r="V26" s="34"/>
-      <c r="W26" s="34"/>
-    </row>
-    <row r="27" ht="17" customHeight="1">
-      <c r="A27" s="43"/>
-      <c r="B27" t="s" s="38">
-        <v>145</v>
-      </c>
-      <c r="C27" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="D27" s="34"/>
-      <c r="E27" s="43"/>
-      <c r="F27" t="s" s="38">
-        <v>143</v>
-      </c>
-      <c r="G27" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="H27" s="36"/>
-      <c r="I27" s="43"/>
-      <c r="J27" t="s" s="38">
+      <c r="B93" t="s" s="39">
+        <v>227</v>
+      </c>
+      <c r="C93" t="s" s="39">
+        <v>228</v>
+      </c>
+      <c r="D93" s="35"/>
+      <c r="E93" t="s" s="39">
+        <v>109</v>
+      </c>
+      <c r="F93" t="s" s="39">
+        <v>160</v>
+      </c>
+      <c r="G93" t="s" s="39">
+        <v>116</v>
+      </c>
+      <c r="H93" s="37"/>
+      <c r="I93" t="s" s="56">
+        <v>229</v>
+      </c>
+      <c r="J93" t="s" s="56">
+        <v>230</v>
+      </c>
+      <c r="K93" t="s" s="56">
         <v>150</v>
       </c>
-      <c r="K27" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="L27" s="34"/>
-      <c r="M27" s="44"/>
-      <c r="N27" t="s" s="39">
-        <v>151</v>
-      </c>
-      <c r="O27" t="s" s="39">
-        <v>152</v>
-      </c>
-      <c r="P27" s="34"/>
-      <c r="Q27" s="44"/>
-      <c r="R27" t="s" s="39">
-        <v>153</v>
-      </c>
-      <c r="S27" t="s" s="39">
-        <v>144</v>
-      </c>
-      <c r="T27" s="34"/>
-      <c r="U27" s="34"/>
-      <c r="V27" s="34"/>
-      <c r="W27" s="34"/>
-    </row>
-    <row r="28" ht="17" customHeight="1">
-      <c r="A28" s="36"/>
-      <c r="B28" t="s" s="40">
-        <v>143</v>
-      </c>
-      <c r="C28" t="s" s="40">
-        <v>144</v>
-      </c>
-      <c r="D28" s="34"/>
-      <c r="E28" s="36"/>
-      <c r="F28" t="s" s="40">
-        <v>148</v>
-      </c>
-      <c r="G28" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="H28" s="36"/>
-      <c r="I28" s="36"/>
-      <c r="J28" t="s" s="40">
-        <v>154</v>
-      </c>
-      <c r="K28" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="L28" s="34"/>
-      <c r="M28" s="41"/>
-      <c r="N28" t="s" s="42">
-        <v>155</v>
-      </c>
-      <c r="O28" t="s" s="42">
-        <v>140</v>
-      </c>
-      <c r="P28" s="34"/>
-      <c r="Q28" s="41"/>
-      <c r="R28" t="s" s="42">
-        <v>156</v>
-      </c>
-      <c r="S28" t="s" s="42">
-        <v>137</v>
-      </c>
-      <c r="T28" s="34"/>
-      <c r="U28" s="34"/>
-      <c r="V28" s="34"/>
-      <c r="W28" s="34"/>
-    </row>
-    <row r="29" ht="17" customHeight="1">
-      <c r="A29" s="43"/>
-      <c r="B29" t="s" s="38">
-        <v>148</v>
-      </c>
-      <c r="C29" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="D29" s="34"/>
-      <c r="E29" s="43"/>
-      <c r="F29" t="s" s="38">
-        <v>153</v>
-      </c>
-      <c r="G29" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="H29" s="36"/>
-      <c r="I29" s="43"/>
-      <c r="J29" t="s" s="38">
-        <v>157</v>
-      </c>
-      <c r="K29" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="L29" s="34"/>
-      <c r="M29" s="44"/>
-      <c r="N29" t="s" s="39">
-        <v>158</v>
-      </c>
-      <c r="O29" t="s" s="39">
-        <v>140</v>
-      </c>
-      <c r="P29" s="34"/>
-      <c r="Q29" s="44"/>
-      <c r="R29" s="44"/>
-      <c r="S29" s="44"/>
-      <c r="T29" s="34"/>
-      <c r="U29" s="34"/>
-      <c r="V29" s="34"/>
-      <c r="W29" s="34"/>
-    </row>
-    <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="36"/>
-      <c r="B30" t="s" s="40">
-        <v>153</v>
-      </c>
-      <c r="C30" t="s" s="40">
-        <v>144</v>
-      </c>
-      <c r="D30" s="34"/>
-      <c r="E30" s="34"/>
-      <c r="F30" s="34"/>
-      <c r="G30" s="34"/>
-      <c r="H30" s="34"/>
-      <c r="I30" s="34"/>
-      <c r="J30" s="34"/>
-      <c r="K30" s="34"/>
-      <c r="L30" s="34"/>
-      <c r="M30" s="41"/>
-      <c r="N30" t="s" s="42">
-        <v>159</v>
-      </c>
-      <c r="O30" t="s" s="42">
-        <v>115</v>
-      </c>
-      <c r="P30" s="34"/>
-      <c r="Q30" s="45"/>
-      <c r="R30" s="46"/>
-      <c r="S30" s="47"/>
-      <c r="T30" s="34"/>
-      <c r="U30" s="34"/>
-      <c r="V30" s="34"/>
-      <c r="W30" s="34"/>
-    </row>
-    <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="43"/>
-      <c r="B31" t="s" s="38">
-        <v>160</v>
-      </c>
-      <c r="C31" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="D31" s="34"/>
-      <c r="E31" s="34"/>
-      <c r="F31" s="34"/>
-      <c r="G31" s="34"/>
-      <c r="H31" s="34"/>
-      <c r="I31" s="34"/>
-      <c r="J31" s="34"/>
-      <c r="K31" s="34"/>
-      <c r="L31" s="34"/>
-      <c r="M31" s="44"/>
-      <c r="N31" s="44"/>
-      <c r="O31" s="44"/>
-      <c r="P31" s="34"/>
-      <c r="Q31" s="48"/>
-      <c r="R31" s="49"/>
-      <c r="S31" s="50"/>
-      <c r="T31" s="34"/>
-      <c r="U31" s="34"/>
-      <c r="V31" s="34"/>
-      <c r="W31" s="34"/>
-    </row>
-    <row r="32" ht="17" customHeight="1">
-      <c r="A32" s="36"/>
-      <c r="B32" t="s" s="40">
-        <v>161</v>
-      </c>
-      <c r="C32" t="s" s="40">
-        <v>162</v>
-      </c>
-      <c r="D32" s="34"/>
-      <c r="E32" s="34"/>
-      <c r="F32" s="34"/>
-      <c r="G32" s="34"/>
-      <c r="H32" s="34"/>
-      <c r="I32" s="34"/>
-      <c r="J32" s="34"/>
-      <c r="K32" s="34"/>
-      <c r="L32" s="34"/>
-      <c r="M32" s="34"/>
-      <c r="N32" s="34"/>
-      <c r="O32" s="34"/>
-      <c r="P32" s="34"/>
-      <c r="Q32" s="34"/>
-      <c r="R32" s="34"/>
-      <c r="S32" s="34"/>
-      <c r="T32" s="34"/>
-      <c r="U32" s="34"/>
-      <c r="V32" s="34"/>
-      <c r="W32" s="34"/>
-    </row>
-    <row r="33" ht="17" customHeight="1">
-      <c r="A33" s="43"/>
-      <c r="B33" t="s" s="38">
-        <v>163</v>
-      </c>
-      <c r="C33" t="s" s="38">
-        <v>137</v>
-      </c>
-      <c r="D33" s="34"/>
-      <c r="E33" s="34"/>
-      <c r="F33" s="34"/>
-      <c r="G33" s="34"/>
-      <c r="H33" s="34"/>
-      <c r="I33" s="34"/>
-      <c r="J33" s="34"/>
-      <c r="K33" s="34"/>
-      <c r="L33" s="34"/>
-      <c r="M33" s="34"/>
-      <c r="N33" s="34"/>
-      <c r="O33" s="34"/>
-      <c r="P33" s="34"/>
-      <c r="Q33" s="34"/>
-      <c r="R33" s="34"/>
-      <c r="S33" s="34"/>
-      <c r="T33" s="34"/>
-      <c r="U33" s="34"/>
-      <c r="V33" s="34"/>
-      <c r="W33" s="34"/>
-    </row>
-    <row r="34" ht="17" customHeight="1">
-      <c r="A34" t="s" s="40">
-        <v>164</v>
-      </c>
-      <c r="B34" t="s" s="40">
-        <v>165</v>
-      </c>
-      <c r="C34" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D34" s="34"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="34"/>
-      <c r="J34" s="34"/>
-      <c r="K34" s="34"/>
-      <c r="L34" s="34"/>
-      <c r="M34" s="34"/>
-      <c r="N34" s="34"/>
-      <c r="O34" s="34"/>
-      <c r="P34" s="34"/>
-      <c r="Q34" s="34"/>
-      <c r="R34" s="34"/>
-      <c r="S34" s="34"/>
-      <c r="T34" s="34"/>
-      <c r="U34" s="34"/>
-      <c r="V34" s="34"/>
-      <c r="W34" s="34"/>
-    </row>
-    <row r="35" ht="17" customHeight="1">
-      <c r="A35" s="43"/>
-      <c r="B35" t="s" s="38">
-        <v>166</v>
-      </c>
-      <c r="C35" t="s" s="38">
-        <v>115</v>
-      </c>
-      <c r="D35" s="34"/>
-      <c r="E35" s="34"/>
-      <c r="F35" s="34"/>
-      <c r="G35" s="34"/>
-      <c r="H35" s="34"/>
-      <c r="I35" s="34"/>
-      <c r="J35" s="34"/>
-      <c r="K35" s="34"/>
-      <c r="L35" s="34"/>
-      <c r="M35" s="34"/>
-      <c r="N35" s="34"/>
-      <c r="O35" s="34"/>
-      <c r="P35" s="34"/>
-      <c r="Q35" s="34"/>
-      <c r="R35" s="34"/>
-      <c r="S35" s="34"/>
-      <c r="T35" s="34"/>
-      <c r="U35" s="34"/>
-      <c r="V35" s="34"/>
-      <c r="W35" s="34"/>
-    </row>
-    <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="36"/>
-      <c r="B36" t="s" s="40">
-        <v>167</v>
-      </c>
-      <c r="C36" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D36" s="34"/>
-      <c r="E36" s="34"/>
-      <c r="F36" s="34"/>
-      <c r="G36" s="34"/>
-      <c r="H36" s="34"/>
-      <c r="I36" s="34"/>
-      <c r="J36" s="34"/>
-      <c r="K36" s="34"/>
-      <c r="L36" s="34"/>
-      <c r="M36" s="34"/>
-      <c r="N36" s="34"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="34"/>
-      <c r="Q36" s="34"/>
-      <c r="R36" s="34"/>
-      <c r="S36" s="34"/>
-      <c r="T36" s="34"/>
-      <c r="U36" s="34"/>
-      <c r="V36" s="34"/>
-      <c r="W36" s="34"/>
-    </row>
-    <row r="37" ht="17" customHeight="1">
-      <c r="A37" s="43"/>
-      <c r="B37" t="s" s="38">
-        <v>168</v>
-      </c>
-      <c r="C37" t="s" s="38">
-        <v>115</v>
-      </c>
-      <c r="D37" s="34"/>
-      <c r="E37" s="34"/>
-      <c r="F37" s="34"/>
-      <c r="G37" s="34"/>
-      <c r="H37" s="34"/>
-      <c r="I37" s="34"/>
-      <c r="J37" s="34"/>
-      <c r="K37" s="34"/>
-      <c r="L37" s="34"/>
-      <c r="M37" s="34"/>
-      <c r="N37" s="34"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="34"/>
-      <c r="Q37" s="34"/>
-      <c r="R37" s="34"/>
-      <c r="S37" s="34"/>
-      <c r="T37" s="34"/>
-      <c r="U37" s="34"/>
-      <c r="V37" s="34"/>
-      <c r="W37" s="34"/>
-    </row>
-    <row r="38" ht="70.95" customHeight="1">
-      <c r="A38" s="36"/>
-      <c r="B38" s="36"/>
-      <c r="C38" s="36"/>
-      <c r="D38" s="34"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="34"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="34"/>
-      <c r="M38" s="41"/>
-      <c r="N38" s="41"/>
-      <c r="O38" s="41"/>
-      <c r="P38" s="34"/>
-      <c r="Q38" s="41"/>
-      <c r="R38" s="41"/>
-      <c r="S38" s="41"/>
-      <c r="T38" s="34"/>
-      <c r="U38" s="34"/>
-      <c r="V38" s="34"/>
-      <c r="W38" s="34"/>
-    </row>
-    <row r="39" ht="34" customHeight="1">
-      <c r="A39" t="s" s="33">
-        <v>169</v>
-      </c>
-      <c r="B39" s="34"/>
-      <c r="C39" s="34"/>
-      <c r="D39" s="34"/>
-      <c r="E39" s="34"/>
-      <c r="F39" s="34"/>
-      <c r="G39" s="34"/>
-      <c r="H39" s="34"/>
-      <c r="I39" s="34"/>
-      <c r="J39" s="34"/>
-      <c r="K39" s="34"/>
-      <c r="L39" s="34"/>
-      <c r="M39" s="34"/>
-      <c r="N39" s="34"/>
-      <c r="O39" s="34"/>
-      <c r="P39" s="34"/>
-      <c r="Q39" s="34"/>
-      <c r="R39" s="34"/>
-      <c r="S39" s="34"/>
-      <c r="T39" s="34"/>
-      <c r="U39" s="34"/>
-      <c r="V39" s="34"/>
-      <c r="W39" s="34"/>
-    </row>
-    <row r="40" ht="17" customHeight="1">
-      <c r="A40" t="s" s="35">
-        <v>55</v>
-      </c>
-      <c r="B40" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C40" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D40" s="34"/>
-      <c r="E40" t="s" s="35">
-        <v>170</v>
-      </c>
-      <c r="F40" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G40" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H40" s="36"/>
-      <c r="I40" t="s" s="35">
-        <v>58</v>
-      </c>
-      <c r="J40" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="K40" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="L40" s="34"/>
-      <c r="M40" t="s" s="35">
-        <v>61</v>
-      </c>
-      <c r="N40" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="O40" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="P40" s="34"/>
-      <c r="Q40" s="34"/>
-      <c r="R40" s="34"/>
-      <c r="S40" s="34"/>
-      <c r="T40" s="34"/>
-      <c r="U40" s="34"/>
-      <c r="V40" s="34"/>
-      <c r="W40" s="34"/>
-    </row>
-    <row r="41" ht="17" customHeight="1">
-      <c r="A41" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B41" t="s" s="38">
-        <v>171</v>
-      </c>
-      <c r="C41" t="s" s="38">
-        <v>172</v>
-      </c>
-      <c r="D41" s="34"/>
-      <c r="E41" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F41" t="s" s="38">
-        <v>118</v>
-      </c>
-      <c r="G41" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="H41" s="36"/>
-      <c r="I41" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="J41" t="s" s="38">
-        <v>147</v>
-      </c>
-      <c r="K41" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="L41" s="34"/>
-      <c r="M41" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="N41" t="s" s="38">
-        <v>173</v>
-      </c>
-      <c r="O41" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="P41" s="34"/>
-      <c r="Q41" s="34"/>
-      <c r="R41" s="34"/>
-      <c r="S41" s="34"/>
-      <c r="T41" s="34"/>
-      <c r="U41" s="34"/>
-      <c r="V41" s="34"/>
-      <c r="W41" s="34"/>
-    </row>
-    <row r="42" ht="17" customHeight="1">
-      <c r="A42" s="34"/>
-      <c r="B42" s="34"/>
-      <c r="C42" s="34"/>
-      <c r="D42" s="34"/>
-      <c r="E42" s="36"/>
-      <c r="F42" t="s" s="40">
-        <v>147</v>
-      </c>
-      <c r="G42" t="s" s="40">
-        <v>119</v>
-      </c>
-      <c r="H42" s="36"/>
-      <c r="I42" s="36"/>
-      <c r="J42" t="s" s="40">
-        <v>174</v>
-      </c>
-      <c r="K42" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="L42" s="34"/>
-      <c r="M42" s="36"/>
-      <c r="N42" t="s" s="40">
-        <v>175</v>
-      </c>
-      <c r="O42" t="s" s="40">
-        <v>144</v>
-      </c>
-      <c r="P42" s="34"/>
-      <c r="Q42" s="34"/>
-      <c r="R42" s="34"/>
-      <c r="S42" s="34"/>
-      <c r="T42" s="34"/>
-      <c r="U42" s="34"/>
-      <c r="V42" s="34"/>
-      <c r="W42" s="34"/>
-    </row>
-    <row r="43" ht="17" customHeight="1">
-      <c r="A43" s="34"/>
-      <c r="B43" s="34"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="34"/>
-      <c r="E43" s="43"/>
-      <c r="F43" t="s" s="38">
-        <v>174</v>
-      </c>
-      <c r="G43" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="H43" s="36"/>
-      <c r="I43" s="43"/>
-      <c r="J43" t="s" s="38">
-        <v>176</v>
-      </c>
-      <c r="K43" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="L43" s="34"/>
-      <c r="M43" s="43"/>
-      <c r="N43" s="43"/>
-      <c r="O43" s="43"/>
-      <c r="P43" s="34"/>
-      <c r="Q43" s="34"/>
-      <c r="R43" s="34"/>
-      <c r="S43" s="34"/>
-      <c r="T43" s="34"/>
-      <c r="U43" s="34"/>
-      <c r="V43" s="34"/>
-      <c r="W43" s="34"/>
-    </row>
-    <row r="44" ht="17" customHeight="1">
-      <c r="A44" s="34"/>
-      <c r="B44" s="34"/>
-      <c r="C44" s="34"/>
-      <c r="D44" s="34"/>
-      <c r="E44" s="36"/>
-      <c r="F44" t="s" s="40">
-        <v>177</v>
-      </c>
-      <c r="G44" t="s" s="40">
-        <v>144</v>
-      </c>
-      <c r="H44" s="36"/>
-      <c r="I44" s="34"/>
-      <c r="J44" s="34"/>
-      <c r="K44" s="34"/>
-      <c r="L44" s="34"/>
-      <c r="M44" s="34"/>
-      <c r="N44" s="34"/>
-      <c r="O44" s="34"/>
-      <c r="P44" s="34"/>
-      <c r="Q44" s="34"/>
-      <c r="R44" s="34"/>
-      <c r="S44" s="34"/>
-      <c r="T44" s="34"/>
-      <c r="U44" s="34"/>
-      <c r="V44" s="34"/>
-      <c r="W44" s="34"/>
-    </row>
-    <row r="45" ht="17" customHeight="1">
-      <c r="A45" s="34"/>
-      <c r="B45" s="34"/>
-      <c r="C45" s="34"/>
-      <c r="D45" s="34"/>
-      <c r="E45" s="43"/>
-      <c r="F45" t="s" s="38">
-        <v>176</v>
-      </c>
-      <c r="G45" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="H45" s="36"/>
-      <c r="I45" s="34"/>
-      <c r="J45" s="34"/>
-      <c r="K45" s="34"/>
-      <c r="L45" s="34"/>
-      <c r="M45" s="34"/>
-      <c r="N45" s="34"/>
-      <c r="O45" s="34"/>
-      <c r="P45" s="34"/>
-      <c r="Q45" s="34"/>
-      <c r="R45" s="34"/>
-      <c r="S45" s="34"/>
-      <c r="T45" s="34"/>
-      <c r="U45" s="34"/>
-      <c r="V45" s="34"/>
-      <c r="W45" s="34"/>
-    </row>
-    <row r="46" ht="70.1" customHeight="1">
-      <c r="A46" s="34"/>
-      <c r="B46" s="34"/>
-      <c r="C46" s="34"/>
-      <c r="D46" s="34"/>
-      <c r="E46" s="34"/>
-      <c r="F46" s="34"/>
-      <c r="G46" s="34"/>
-      <c r="H46" s="34"/>
-      <c r="I46" s="34"/>
-      <c r="J46" s="34"/>
-      <c r="K46" s="34"/>
-      <c r="L46" s="34"/>
-      <c r="M46" s="34"/>
-      <c r="N46" s="34"/>
-      <c r="O46" s="34"/>
-      <c r="P46" s="34"/>
-      <c r="Q46" s="34"/>
-      <c r="R46" s="34"/>
-      <c r="S46" s="34"/>
-      <c r="T46" s="34"/>
-      <c r="U46" s="34"/>
-      <c r="V46" s="34"/>
-      <c r="W46" s="34"/>
-    </row>
-    <row r="47" ht="34" customHeight="1">
-      <c r="A47" t="s" s="33">
-        <v>178</v>
-      </c>
-      <c r="B47" s="34"/>
-      <c r="C47" s="34"/>
-      <c r="D47" s="34"/>
-      <c r="E47" s="34"/>
-      <c r="F47" s="34"/>
-      <c r="G47" s="34"/>
-      <c r="H47" s="34"/>
-      <c r="I47" s="34"/>
-      <c r="J47" s="34"/>
-      <c r="K47" s="34"/>
-      <c r="L47" s="34"/>
-      <c r="M47" s="34"/>
-      <c r="N47" s="34"/>
-      <c r="O47" s="34"/>
-      <c r="P47" s="34"/>
-      <c r="Q47" s="34"/>
-      <c r="R47" s="34"/>
-      <c r="S47" s="34"/>
-      <c r="T47" s="34"/>
-      <c r="U47" s="34"/>
-      <c r="V47" s="34"/>
-      <c r="W47" s="34"/>
-    </row>
-    <row r="48" ht="17" customHeight="1">
-      <c r="A48" t="s" s="35">
-        <v>69</v>
-      </c>
-      <c r="B48" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C48" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D48" s="34"/>
-      <c r="E48" t="s" s="35">
-        <v>71</v>
-      </c>
-      <c r="F48" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G48" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H48" s="36"/>
-      <c r="I48" t="s" s="35">
-        <v>179</v>
-      </c>
-      <c r="J48" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="K48" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="L48" s="36"/>
-      <c r="M48" s="51"/>
-      <c r="N48" s="51"/>
-      <c r="O48" s="51"/>
-      <c r="P48" s="34"/>
-      <c r="Q48" s="52"/>
-      <c r="R48" s="52"/>
-      <c r="S48" s="52"/>
-      <c r="T48" s="34"/>
-      <c r="U48" s="52"/>
-      <c r="V48" s="52"/>
-      <c r="W48" s="52"/>
-    </row>
-    <row r="49" ht="17" customHeight="1">
-      <c r="A49" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B49" t="s" s="38">
-        <v>180</v>
-      </c>
-      <c r="C49" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="D49" s="34"/>
-      <c r="E49" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F49" t="s" s="38">
-        <v>181</v>
-      </c>
-      <c r="G49" t="s" s="38">
-        <v>85</v>
-      </c>
-      <c r="H49" s="36"/>
-      <c r="I49" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="J49" t="s" s="38">
-        <v>147</v>
-      </c>
-      <c r="K49" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="L49" s="36"/>
-      <c r="M49" s="34"/>
-      <c r="N49" s="34"/>
-      <c r="O49" s="34"/>
-      <c r="P49" s="34"/>
-      <c r="Q49" s="34"/>
-      <c r="R49" s="34"/>
-      <c r="S49" s="34"/>
-      <c r="T49" s="34"/>
-      <c r="U49" s="34"/>
-      <c r="V49" s="34"/>
-      <c r="W49" s="34"/>
-    </row>
-    <row r="50" ht="17" customHeight="1">
-      <c r="A50" s="36"/>
-      <c r="B50" t="s" s="40">
-        <v>182</v>
-      </c>
-      <c r="C50" t="s" s="40">
+      <c r="L93" s="59">
+        <v>0</v>
+      </c>
+      <c r="M93" t="s" s="56">
+        <v>231</v>
+      </c>
+      <c r="N93" s="35"/>
+      <c r="O93" s="35"/>
+      <c r="P93" s="35"/>
+      <c r="Q93" s="35"/>
+      <c r="R93" s="35"/>
+      <c r="S93" s="35"/>
+      <c r="T93" s="35"/>
+      <c r="U93" s="35"/>
+      <c r="V93" s="35"/>
+      <c r="W93" s="35"/>
+    </row>
+    <row r="94" ht="17" customHeight="1">
+      <c r="A94" s="37"/>
+      <c r="B94" t="s" s="41">
+        <v>230</v>
+      </c>
+      <c r="C94" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="D94" s="35"/>
+      <c r="E94" s="37"/>
+      <c r="F94" t="s" s="41">
         <v>183</v>
       </c>
-      <c r="D50" s="34"/>
-      <c r="E50" s="36"/>
-      <c r="F50" t="s" s="40">
-        <v>184</v>
-      </c>
-      <c r="G50" t="s" s="40">
-        <v>85</v>
-      </c>
-      <c r="H50" s="36"/>
-      <c r="I50" s="36"/>
-      <c r="J50" t="s" s="40">
-        <v>174</v>
-      </c>
-      <c r="K50" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="L50" s="36"/>
-      <c r="M50" s="34"/>
-      <c r="N50" s="34"/>
-      <c r="O50" s="34"/>
-      <c r="P50" s="34"/>
-      <c r="Q50" s="34"/>
-      <c r="R50" s="34"/>
-      <c r="S50" s="34"/>
-      <c r="T50" s="34"/>
-      <c r="U50" s="34"/>
-      <c r="V50" s="34"/>
-      <c r="W50" s="34"/>
-    </row>
-    <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="43"/>
-      <c r="B51" t="s" s="38">
-        <v>185</v>
-      </c>
-      <c r="C51" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="D51" s="34"/>
-      <c r="E51" s="43"/>
-      <c r="F51" s="43"/>
-      <c r="G51" s="43"/>
-      <c r="H51" s="36"/>
-      <c r="I51" s="43"/>
-      <c r="J51" t="s" s="38">
-        <v>186</v>
-      </c>
-      <c r="K51" t="s" s="38">
-        <v>144</v>
-      </c>
-      <c r="L51" s="36"/>
-      <c r="M51" s="34"/>
-      <c r="N51" s="34"/>
-      <c r="O51" s="34"/>
-      <c r="P51" s="34"/>
-      <c r="Q51" s="34"/>
-      <c r="R51" s="34"/>
-      <c r="S51" s="34"/>
-      <c r="T51" s="34"/>
-      <c r="U51" s="34"/>
-      <c r="V51" s="34"/>
-      <c r="W51" s="34"/>
-    </row>
-    <row r="52" ht="17" customHeight="1">
-      <c r="A52" s="36"/>
-      <c r="B52" t="s" s="40">
-        <v>159</v>
-      </c>
-      <c r="C52" t="s" s="40">
-        <v>115</v>
-      </c>
-      <c r="D52" s="34"/>
-      <c r="E52" s="34"/>
-      <c r="F52" s="34"/>
-      <c r="G52" s="34"/>
-      <c r="H52" s="36"/>
-      <c r="I52" s="36"/>
-      <c r="J52" t="s" s="40">
-        <v>176</v>
-      </c>
-      <c r="K52" t="s" s="40">
-        <v>144</v>
-      </c>
-      <c r="L52" s="36"/>
-      <c r="M52" s="34"/>
-      <c r="N52" s="34"/>
-      <c r="O52" s="34"/>
-      <c r="P52" s="34"/>
-      <c r="Q52" s="34"/>
-      <c r="R52" s="34"/>
-      <c r="S52" s="34"/>
-      <c r="T52" s="34"/>
-      <c r="U52" s="34"/>
-      <c r="V52" s="34"/>
-      <c r="W52" s="34"/>
-    </row>
-    <row r="53" ht="17" customHeight="1">
-      <c r="A53" s="43"/>
-      <c r="B53" t="s" s="38">
-        <v>171</v>
-      </c>
-      <c r="C53" t="s" s="38">
-        <v>187</v>
-      </c>
-      <c r="D53" s="34"/>
-      <c r="E53" s="34"/>
-      <c r="F53" s="34"/>
-      <c r="G53" s="34"/>
-      <c r="H53" s="36"/>
-      <c r="I53" s="43"/>
-      <c r="J53" s="43"/>
-      <c r="K53" s="43"/>
-      <c r="L53" s="36"/>
-      <c r="M53" s="34"/>
-      <c r="N53" s="34"/>
-      <c r="O53" s="34"/>
-      <c r="P53" s="34"/>
-      <c r="Q53" s="34"/>
-      <c r="R53" s="34"/>
-      <c r="S53" s="34"/>
-      <c r="T53" s="34"/>
-      <c r="U53" s="34"/>
-      <c r="V53" s="34"/>
-      <c r="W53" s="34"/>
-    </row>
-    <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="36"/>
-      <c r="B54" t="s" s="40">
-        <v>188</v>
-      </c>
-      <c r="C54" t="s" s="40">
-        <v>119</v>
-      </c>
-      <c r="D54" s="34"/>
-      <c r="E54" s="34"/>
-      <c r="F54" s="34"/>
-      <c r="G54" s="34"/>
-      <c r="H54" s="34"/>
-      <c r="I54" s="34"/>
-      <c r="J54" s="34"/>
-      <c r="K54" s="34"/>
-      <c r="L54" s="36"/>
-      <c r="M54" s="34"/>
-      <c r="N54" s="34"/>
-      <c r="O54" s="34"/>
-      <c r="P54" s="34"/>
-      <c r="Q54" s="34"/>
-      <c r="R54" s="34"/>
-      <c r="S54" s="34"/>
-      <c r="T54" s="34"/>
-      <c r="U54" s="34"/>
-      <c r="V54" s="34"/>
-      <c r="W54" s="34"/>
-    </row>
-    <row r="55" ht="17" customHeight="1">
-      <c r="A55" s="43"/>
-      <c r="B55" t="s" s="38">
-        <v>189</v>
-      </c>
-      <c r="C55" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="D55" s="34"/>
-      <c r="E55" s="34"/>
-      <c r="F55" s="34"/>
-      <c r="G55" s="34"/>
-      <c r="H55" s="34"/>
-      <c r="I55" s="34"/>
-      <c r="J55" s="34"/>
-      <c r="K55" s="34"/>
-      <c r="L55" s="36"/>
-      <c r="M55" s="34"/>
-      <c r="N55" s="34"/>
-      <c r="O55" s="34"/>
-      <c r="P55" s="34"/>
-      <c r="Q55" s="34"/>
-      <c r="R55" s="34"/>
-      <c r="S55" s="34"/>
-      <c r="T55" s="34"/>
-      <c r="U55" s="34"/>
-      <c r="V55" s="34"/>
-      <c r="W55" s="34"/>
-    </row>
-    <row r="56" ht="70.3" customHeight="1">
-      <c r="A56" s="34"/>
-      <c r="B56" s="34"/>
-      <c r="C56" s="34"/>
-      <c r="D56" s="34"/>
-      <c r="E56" s="34"/>
-      <c r="F56" s="34"/>
-      <c r="G56" s="34"/>
-      <c r="H56" s="34"/>
-      <c r="I56" s="34"/>
-      <c r="J56" s="34"/>
-      <c r="K56" s="34"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="34"/>
-      <c r="N56" s="34"/>
-      <c r="O56" s="34"/>
-      <c r="P56" s="34"/>
-      <c r="Q56" s="34"/>
-      <c r="R56" s="34"/>
-      <c r="S56" s="34"/>
-      <c r="T56" s="34"/>
-      <c r="U56" s="34"/>
-      <c r="V56" s="34"/>
-      <c r="W56" s="34"/>
-    </row>
-    <row r="57" ht="34" customHeight="1">
-      <c r="A57" t="s" s="33">
-        <v>190</v>
-      </c>
-      <c r="B57" s="34"/>
-      <c r="C57" s="34"/>
-      <c r="D57" s="34"/>
-      <c r="E57" s="34"/>
-      <c r="F57" s="34"/>
-      <c r="G57" s="34"/>
-      <c r="H57" s="34"/>
-      <c r="I57" s="34"/>
-      <c r="J57" s="34"/>
-      <c r="K57" s="34"/>
-      <c r="L57" s="34"/>
-      <c r="M57" s="34"/>
-      <c r="N57" s="34"/>
-      <c r="O57" s="34"/>
-      <c r="P57" s="34"/>
-      <c r="Q57" s="34"/>
-      <c r="R57" s="34"/>
-      <c r="S57" s="34"/>
-      <c r="T57" s="34"/>
-      <c r="U57" s="34"/>
-      <c r="V57" s="34"/>
-      <c r="W57" s="34"/>
-    </row>
-    <row r="58" ht="17" customHeight="1">
-      <c r="A58" t="s" s="35">
-        <v>79</v>
-      </c>
-      <c r="B58" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C58" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D58" s="34"/>
-      <c r="E58" t="s" s="35">
-        <v>78</v>
-      </c>
-      <c r="F58" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G58" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H58" s="36"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="51"/>
-      <c r="K58" s="51"/>
-      <c r="L58" s="36"/>
-      <c r="M58" s="51"/>
-      <c r="N58" s="51"/>
-      <c r="O58" s="51"/>
-      <c r="P58" s="34"/>
-      <c r="Q58" s="52"/>
-      <c r="R58" s="52"/>
-      <c r="S58" s="52"/>
-      <c r="T58" s="34"/>
-      <c r="U58" s="52"/>
-      <c r="V58" s="52"/>
-      <c r="W58" s="52"/>
-    </row>
-    <row r="59" ht="17" customHeight="1">
-      <c r="A59" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B59" t="s" s="38">
-        <v>147</v>
-      </c>
-      <c r="C59" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="D59" s="34"/>
-      <c r="E59" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F59" t="s" s="38">
-        <v>147</v>
-      </c>
-      <c r="G59" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="H59" s="36"/>
-      <c r="I59" s="34"/>
-      <c r="J59" s="34"/>
-      <c r="K59" s="34"/>
-      <c r="L59" s="34"/>
-      <c r="M59" s="34"/>
-      <c r="N59" s="34"/>
-      <c r="O59" s="34"/>
-      <c r="P59" s="34"/>
-      <c r="Q59" s="34"/>
-      <c r="R59" s="34"/>
-      <c r="S59" s="34"/>
-      <c r="T59" s="34"/>
-      <c r="U59" s="34"/>
-      <c r="V59" s="34"/>
-      <c r="W59" s="34"/>
-    </row>
-    <row r="60" ht="17" customHeight="1">
-      <c r="A60" s="36"/>
-      <c r="B60" t="s" s="40">
-        <v>191</v>
-      </c>
-      <c r="C60" t="s" s="40">
-        <v>192</v>
-      </c>
-      <c r="D60" s="34"/>
-      <c r="E60" s="36"/>
-      <c r="F60" t="s" s="40">
-        <v>193</v>
-      </c>
-      <c r="G60" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="H60" s="36"/>
-      <c r="I60" s="34"/>
-      <c r="J60" s="34"/>
-      <c r="K60" s="34"/>
-      <c r="L60" s="34"/>
-      <c r="M60" s="34"/>
-      <c r="N60" s="34"/>
-      <c r="O60" s="34"/>
-      <c r="P60" s="34"/>
-      <c r="Q60" s="34"/>
-      <c r="R60" s="34"/>
-      <c r="S60" s="34"/>
-      <c r="T60" s="34"/>
-      <c r="U60" s="34"/>
-      <c r="V60" s="34"/>
-      <c r="W60" s="34"/>
-    </row>
-    <row r="61" ht="17" customHeight="1">
-      <c r="A61" s="43"/>
-      <c r="B61" t="s" s="38">
-        <v>193</v>
-      </c>
-      <c r="C61" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="D61" s="34"/>
-      <c r="E61" s="43"/>
-      <c r="F61" t="s" s="38">
-        <v>194</v>
-      </c>
-      <c r="G61" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H61" s="36"/>
-      <c r="I61" s="34"/>
-      <c r="J61" s="34"/>
-      <c r="K61" s="34"/>
-      <c r="L61" s="34"/>
-      <c r="M61" s="34"/>
-      <c r="N61" s="34"/>
-      <c r="O61" s="34"/>
-      <c r="P61" s="34"/>
-      <c r="Q61" s="34"/>
-      <c r="R61" s="34"/>
-      <c r="S61" s="34"/>
-      <c r="T61" s="34"/>
-      <c r="U61" s="34"/>
-      <c r="V61" s="34"/>
-      <c r="W61" s="34"/>
-    </row>
-    <row r="62" ht="17" customHeight="1">
-      <c r="A62" s="36"/>
-      <c r="B62" t="s" s="40">
-        <v>194</v>
-      </c>
-      <c r="C62" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D62" s="34"/>
-      <c r="E62" s="34"/>
-      <c r="F62" s="34"/>
-      <c r="G62" s="34"/>
-      <c r="H62" s="36"/>
-      <c r="I62" s="34"/>
-      <c r="J62" s="34"/>
-      <c r="K62" s="34"/>
-      <c r="L62" s="34"/>
-      <c r="M62" s="34"/>
-      <c r="N62" s="34"/>
-      <c r="O62" s="34"/>
-      <c r="P62" s="34"/>
-      <c r="Q62" s="34"/>
-      <c r="R62" s="34"/>
-      <c r="S62" s="34"/>
-      <c r="T62" s="34"/>
-      <c r="U62" s="34"/>
-      <c r="V62" s="34"/>
-      <c r="W62" s="34"/>
-    </row>
-    <row r="63" ht="17" customHeight="1">
-      <c r="A63" s="43"/>
-      <c r="B63" t="s" s="38">
-        <v>159</v>
-      </c>
-      <c r="C63" t="s" s="38">
-        <v>115</v>
-      </c>
-      <c r="D63" s="34"/>
-      <c r="E63" s="34"/>
-      <c r="F63" s="34"/>
-      <c r="G63" s="34"/>
-      <c r="H63" s="36"/>
-      <c r="I63" s="34"/>
-      <c r="J63" s="34"/>
-      <c r="K63" s="34"/>
-      <c r="L63" s="34"/>
-      <c r="M63" s="34"/>
-      <c r="N63" s="34"/>
-      <c r="O63" s="34"/>
-      <c r="P63" s="34"/>
-      <c r="Q63" s="34"/>
-      <c r="R63" s="34"/>
-      <c r="S63" s="34"/>
-      <c r="T63" s="34"/>
-      <c r="U63" s="34"/>
-      <c r="V63" s="34"/>
-      <c r="W63" s="34"/>
-    </row>
-    <row r="64" ht="70.7" customHeight="1">
-      <c r="A64" s="36"/>
-      <c r="B64" s="36"/>
-      <c r="C64" s="36"/>
-      <c r="D64" s="34"/>
-      <c r="E64" s="53"/>
-      <c r="F64" s="53"/>
-      <c r="G64" s="53"/>
-      <c r="H64" s="36"/>
-      <c r="I64" s="36"/>
-      <c r="J64" s="36"/>
-      <c r="K64" s="36"/>
-      <c r="L64" s="36"/>
-      <c r="M64" s="36"/>
-      <c r="N64" s="36"/>
-      <c r="O64" s="36"/>
-      <c r="P64" s="34"/>
-      <c r="Q64" s="41"/>
-      <c r="R64" s="41"/>
-      <c r="S64" s="41"/>
-      <c r="T64" s="34"/>
-      <c r="U64" s="41"/>
-      <c r="V64" s="41"/>
-      <c r="W64" s="41"/>
-    </row>
-    <row r="65" ht="34" customHeight="1">
-      <c r="A65" t="s" s="33">
-        <v>195</v>
-      </c>
-      <c r="B65" s="34"/>
-      <c r="C65" s="34"/>
-      <c r="D65" s="34"/>
-      <c r="E65" s="34"/>
-      <c r="F65" s="34"/>
-      <c r="G65" s="34"/>
-      <c r="H65" s="34"/>
-      <c r="I65" s="34"/>
-      <c r="J65" s="34"/>
-      <c r="K65" s="34"/>
-      <c r="L65" s="34"/>
-      <c r="M65" s="34"/>
-      <c r="N65" s="34"/>
-      <c r="O65" s="34"/>
-      <c r="P65" s="34"/>
-      <c r="Q65" s="34"/>
-      <c r="R65" s="34"/>
-      <c r="S65" s="34"/>
-      <c r="T65" s="34"/>
-      <c r="U65" s="34"/>
-      <c r="V65" s="34"/>
-      <c r="W65" s="34"/>
-    </row>
-    <row r="66" ht="17" customHeight="1">
-      <c r="A66" t="s" s="35">
-        <v>85</v>
-      </c>
-      <c r="B66" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C66" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D66" s="34"/>
-      <c r="E66" t="s" s="35">
-        <v>84</v>
-      </c>
-      <c r="F66" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G66" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H66" s="36"/>
-      <c r="I66" t="s" s="35">
-        <v>88</v>
-      </c>
-      <c r="J66" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="K66" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="L66" s="36"/>
-      <c r="M66" s="51"/>
-      <c r="N66" s="51"/>
-      <c r="O66" s="51"/>
-      <c r="P66" s="34"/>
-      <c r="Q66" s="52"/>
-      <c r="R66" s="52"/>
-      <c r="S66" s="52"/>
-      <c r="T66" s="34"/>
-      <c r="U66" s="52"/>
-      <c r="V66" s="52"/>
-      <c r="W66" s="52"/>
-    </row>
-    <row r="67" ht="17" customHeight="1">
-      <c r="A67" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B67" t="s" s="38">
-        <v>118</v>
-      </c>
-      <c r="C67" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="D67" s="34"/>
-      <c r="E67" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F67" t="s" s="38">
-        <v>196</v>
-      </c>
-      <c r="G67" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H67" s="36"/>
-      <c r="I67" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="J67" t="s" s="38">
-        <v>197</v>
-      </c>
-      <c r="K67" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L67" s="36"/>
-      <c r="M67" s="34"/>
-      <c r="N67" s="34"/>
-      <c r="O67" s="34"/>
-      <c r="P67" s="34"/>
-      <c r="Q67" s="34"/>
-      <c r="R67" s="34"/>
-      <c r="S67" s="34"/>
-      <c r="T67" s="34"/>
-      <c r="U67" s="34"/>
-      <c r="V67" s="34"/>
-      <c r="W67" s="34"/>
-    </row>
-    <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="36"/>
-      <c r="B68" t="s" s="40">
-        <v>196</v>
-      </c>
-      <c r="C68" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D68" s="34"/>
-      <c r="E68" s="36"/>
-      <c r="F68" t="s" s="40">
-        <v>198</v>
-      </c>
-      <c r="G68" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H68" s="36"/>
-      <c r="I68" s="36"/>
-      <c r="J68" t="s" s="40">
-        <v>199</v>
-      </c>
-      <c r="K68" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="L68" s="36"/>
-      <c r="M68" s="34"/>
-      <c r="N68" s="34"/>
-      <c r="O68" s="34"/>
-      <c r="P68" s="34"/>
-      <c r="Q68" s="34"/>
-      <c r="R68" s="34"/>
-      <c r="S68" s="34"/>
-      <c r="T68" s="34"/>
-      <c r="U68" s="34"/>
-      <c r="V68" s="34"/>
-      <c r="W68" s="34"/>
-    </row>
-    <row r="69" ht="17" customHeight="1">
-      <c r="A69" s="43"/>
-      <c r="B69" t="s" s="38">
-        <v>198</v>
-      </c>
-      <c r="C69" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="D69" s="34"/>
-      <c r="E69" s="43"/>
-      <c r="F69" t="s" s="38">
-        <v>200</v>
-      </c>
-      <c r="G69" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H69" s="36"/>
-      <c r="I69" s="43"/>
-      <c r="J69" t="s" s="38">
-        <v>201</v>
-      </c>
-      <c r="K69" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L69" s="36"/>
-      <c r="M69" s="34"/>
-      <c r="N69" s="34"/>
-      <c r="O69" s="34"/>
-      <c r="P69" s="34"/>
-      <c r="Q69" s="34"/>
-      <c r="R69" s="34"/>
-      <c r="S69" s="34"/>
-      <c r="T69" s="34"/>
-      <c r="U69" s="34"/>
-      <c r="V69" s="34"/>
-      <c r="W69" s="34"/>
-    </row>
-    <row r="70" ht="17" customHeight="1">
-      <c r="A70" s="36"/>
-      <c r="B70" t="s" s="40">
-        <v>200</v>
-      </c>
-      <c r="C70" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D70" s="34"/>
-      <c r="E70" s="36"/>
-      <c r="F70" t="s" s="40">
-        <v>202</v>
-      </c>
-      <c r="G70" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H70" s="36"/>
-      <c r="I70" s="36"/>
-      <c r="J70" t="s" s="40">
-        <v>203</v>
-      </c>
-      <c r="K70" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="L70" s="36"/>
-      <c r="M70" s="34"/>
-      <c r="N70" s="34"/>
-      <c r="O70" s="34"/>
-      <c r="P70" s="34"/>
-      <c r="Q70" s="34"/>
-      <c r="R70" s="34"/>
-      <c r="S70" s="34"/>
-      <c r="T70" s="34"/>
-      <c r="U70" s="34"/>
-      <c r="V70" s="34"/>
-      <c r="W70" s="34"/>
-    </row>
-    <row r="71" ht="17" customHeight="1">
-      <c r="A71" s="43"/>
-      <c r="B71" t="s" s="38">
-        <v>202</v>
-      </c>
-      <c r="C71" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="D71" s="34"/>
-      <c r="E71" s="43"/>
-      <c r="F71" t="s" s="38">
-        <v>204</v>
-      </c>
-      <c r="G71" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H71" s="36"/>
-      <c r="I71" s="43"/>
-      <c r="J71" t="s" s="38">
-        <v>205</v>
-      </c>
-      <c r="K71" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="L71" s="36"/>
-      <c r="M71" s="34"/>
-      <c r="N71" s="34"/>
-      <c r="O71" s="34"/>
-      <c r="P71" s="34"/>
-      <c r="Q71" s="34"/>
-      <c r="R71" s="34"/>
-      <c r="S71" s="34"/>
-      <c r="T71" s="34"/>
-      <c r="U71" s="34"/>
-      <c r="V71" s="34"/>
-      <c r="W71" s="34"/>
-    </row>
-    <row r="72" ht="17" customHeight="1">
-      <c r="A72" s="36"/>
-      <c r="B72" t="s" s="40">
-        <v>204</v>
-      </c>
-      <c r="C72" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="D72" s="34"/>
-      <c r="E72" s="36"/>
-      <c r="F72" t="s" s="40">
-        <v>206</v>
-      </c>
-      <c r="G72" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H72" s="36"/>
-      <c r="I72" s="36"/>
-      <c r="J72" t="s" s="40">
-        <v>207</v>
-      </c>
-      <c r="K72" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="L72" s="36"/>
-      <c r="M72" s="34"/>
-      <c r="N72" s="34"/>
-      <c r="O72" s="34"/>
-      <c r="P72" s="34"/>
-      <c r="Q72" s="34"/>
-      <c r="R72" s="34"/>
-      <c r="S72" s="34"/>
-      <c r="T72" s="34"/>
-      <c r="U72" s="34"/>
-      <c r="V72" s="34"/>
-      <c r="W72" s="34"/>
-    </row>
-    <row r="73" ht="17" customHeight="1">
-      <c r="A73" s="43"/>
-      <c r="B73" t="s" s="38">
-        <v>206</v>
-      </c>
-      <c r="C73" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="D73" s="34"/>
-      <c r="E73" s="43"/>
-      <c r="F73" s="43"/>
-      <c r="G73" s="43"/>
-      <c r="H73" s="36"/>
-      <c r="I73" s="43"/>
-      <c r="J73" s="43"/>
-      <c r="K73" s="43"/>
-      <c r="L73" s="36"/>
-      <c r="M73" s="34"/>
-      <c r="N73" s="34"/>
-      <c r="O73" s="34"/>
-      <c r="P73" s="34"/>
-      <c r="Q73" s="34"/>
-      <c r="R73" s="34"/>
-      <c r="S73" s="34"/>
-      <c r="T73" s="34"/>
-      <c r="U73" s="34"/>
-      <c r="V73" s="34"/>
-      <c r="W73" s="34"/>
-    </row>
-    <row r="74" ht="70.2" customHeight="1">
-      <c r="A74" s="36"/>
-      <c r="B74" s="36"/>
-      <c r="C74" s="36"/>
-      <c r="D74" s="34"/>
-      <c r="E74" s="36"/>
-      <c r="F74" s="36"/>
-      <c r="G74" s="36"/>
-      <c r="H74" s="36"/>
-      <c r="I74" s="36"/>
-      <c r="J74" s="36"/>
-      <c r="K74" s="36"/>
-      <c r="L74" s="36"/>
-      <c r="M74" s="36"/>
-      <c r="N74" s="36"/>
-      <c r="O74" s="36"/>
-      <c r="P74" s="34"/>
-      <c r="Q74" s="41"/>
-      <c r="R74" s="41"/>
-      <c r="S74" s="41"/>
-      <c r="T74" s="34"/>
-      <c r="U74" s="41"/>
-      <c r="V74" s="41"/>
-      <c r="W74" s="41"/>
-    </row>
-    <row r="75" ht="34" customHeight="1">
-      <c r="A75" t="s" s="33">
-        <v>208</v>
-      </c>
-      <c r="B75" s="34"/>
-      <c r="C75" s="34"/>
-      <c r="D75" s="34"/>
-      <c r="E75" s="34"/>
-      <c r="F75" s="34"/>
-      <c r="G75" s="34"/>
-      <c r="H75" s="34"/>
-      <c r="I75" s="34"/>
-      <c r="J75" s="34"/>
-      <c r="K75" s="34"/>
-      <c r="L75" s="34"/>
-      <c r="M75" s="34"/>
-      <c r="N75" s="34"/>
-      <c r="O75" s="34"/>
-      <c r="P75" s="34"/>
-      <c r="Q75" s="34"/>
-      <c r="R75" s="34"/>
-      <c r="S75" s="34"/>
-      <c r="T75" s="34"/>
-      <c r="U75" s="34"/>
-      <c r="V75" s="34"/>
-      <c r="W75" s="34"/>
-    </row>
-    <row r="76" ht="17" customHeight="1">
-      <c r="A76" t="s" s="35">
-        <v>95</v>
-      </c>
-      <c r="B76" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C76" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D76" s="34"/>
-      <c r="E76" t="s" s="35">
-        <v>94</v>
-      </c>
-      <c r="F76" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G76" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H76" s="36"/>
-      <c r="I76" t="s" s="35">
-        <v>98</v>
-      </c>
-      <c r="J76" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="K76" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="L76" s="36"/>
-      <c r="M76" s="51"/>
-      <c r="N76" s="51"/>
-      <c r="O76" s="51"/>
-      <c r="P76" s="34"/>
-      <c r="Q76" s="52"/>
-      <c r="R76" s="52"/>
-      <c r="S76" s="52"/>
-      <c r="T76" s="34"/>
-      <c r="U76" s="52"/>
-      <c r="V76" s="52"/>
-      <c r="W76" s="52"/>
-    </row>
-    <row r="77" ht="17" customHeight="1">
-      <c r="A77" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B77" t="s" s="38">
-        <v>118</v>
-      </c>
-      <c r="C77" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="D77" s="34"/>
-      <c r="E77" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F77" t="s" s="38">
-        <v>147</v>
-      </c>
-      <c r="G77" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="H77" s="36"/>
-      <c r="I77" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="J77" t="s" s="38">
-        <v>209</v>
-      </c>
-      <c r="K77" t="s" s="38">
-        <v>210</v>
-      </c>
-      <c r="L77" s="36"/>
-      <c r="M77" s="34"/>
-      <c r="N77" s="34"/>
-      <c r="O77" s="34"/>
-      <c r="P77" s="34"/>
-      <c r="Q77" s="34"/>
-      <c r="R77" s="34"/>
-      <c r="S77" s="34"/>
-      <c r="T77" s="34"/>
-      <c r="U77" s="34"/>
-      <c r="V77" s="34"/>
-      <c r="W77" s="34"/>
-    </row>
-    <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="36"/>
-      <c r="B78" t="s" s="40">
-        <v>211</v>
-      </c>
-      <c r="C78" t="s" s="40">
-        <v>119</v>
-      </c>
-      <c r="D78" s="34"/>
-      <c r="E78" s="36"/>
-      <c r="F78" t="s" s="40">
-        <v>209</v>
-      </c>
-      <c r="G78" t="s" s="40">
-        <v>210</v>
-      </c>
-      <c r="H78" s="36"/>
-      <c r="I78" s="34"/>
-      <c r="J78" s="34"/>
-      <c r="K78" s="34"/>
-      <c r="L78" s="36"/>
-      <c r="M78" s="34"/>
-      <c r="N78" s="34"/>
-      <c r="O78" s="34"/>
-      <c r="P78" s="34"/>
-      <c r="Q78" s="34"/>
-      <c r="R78" s="34"/>
-      <c r="S78" s="34"/>
-      <c r="T78" s="34"/>
-      <c r="U78" s="34"/>
-      <c r="V78" s="34"/>
-      <c r="W78" s="34"/>
-    </row>
-    <row r="79" ht="17" customHeight="1">
-      <c r="A79" s="43"/>
-      <c r="B79" t="s" s="38">
-        <v>147</v>
-      </c>
-      <c r="C79" t="s" s="38">
-        <v>119</v>
-      </c>
-      <c r="D79" s="34"/>
-      <c r="E79" s="43"/>
-      <c r="F79" s="43"/>
-      <c r="G79" s="43"/>
-      <c r="H79" s="36"/>
-      <c r="I79" s="34"/>
-      <c r="J79" s="34"/>
-      <c r="K79" s="34"/>
-      <c r="L79" s="36"/>
-      <c r="M79" s="34"/>
-      <c r="N79" s="34"/>
-      <c r="O79" s="34"/>
-      <c r="P79" s="34"/>
-      <c r="Q79" s="34"/>
-      <c r="R79" s="34"/>
-      <c r="S79" s="34"/>
-      <c r="T79" s="34"/>
-      <c r="U79" s="34"/>
-      <c r="V79" s="34"/>
-      <c r="W79" s="34"/>
-    </row>
-    <row r="80" ht="17" customHeight="1">
-      <c r="A80" s="36"/>
-      <c r="B80" t="s" s="40">
-        <v>209</v>
-      </c>
-      <c r="C80" t="s" s="40">
-        <v>210</v>
-      </c>
-      <c r="D80" s="34"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="36"/>
-      <c r="G80" s="36"/>
-      <c r="H80" s="36"/>
-      <c r="I80" s="36"/>
-      <c r="J80" s="36"/>
-      <c r="K80" s="36"/>
-      <c r="L80" s="36"/>
-      <c r="M80" s="36"/>
-      <c r="N80" s="36"/>
-      <c r="O80" s="36"/>
-      <c r="P80" s="34"/>
-      <c r="Q80" s="41"/>
-      <c r="R80" s="41"/>
-      <c r="S80" s="41"/>
-      <c r="T80" s="34"/>
-      <c r="U80" s="41"/>
-      <c r="V80" s="41"/>
-      <c r="W80" s="41"/>
-    </row>
-    <row r="81" ht="70.5" customHeight="1">
-      <c r="A81" s="36"/>
-      <c r="B81" s="36"/>
-      <c r="C81" s="36"/>
-      <c r="D81" s="34"/>
-      <c r="E81" s="53"/>
-      <c r="F81" s="53"/>
-      <c r="G81" s="53"/>
-      <c r="H81" s="36"/>
-      <c r="I81" s="36"/>
-      <c r="J81" s="36"/>
-      <c r="K81" s="36"/>
-      <c r="L81" s="36"/>
-      <c r="M81" s="36"/>
-      <c r="N81" s="36"/>
-      <c r="O81" s="36"/>
-      <c r="P81" s="34"/>
-      <c r="Q81" s="41"/>
-      <c r="R81" s="41"/>
-      <c r="S81" s="41"/>
-      <c r="T81" s="34"/>
-      <c r="U81" s="41"/>
-      <c r="V81" s="41"/>
-      <c r="W81" s="41"/>
-    </row>
-    <row r="82" ht="34" customHeight="1">
-      <c r="A82" t="s" s="33">
-        <v>212</v>
-      </c>
-      <c r="B82" s="34"/>
-      <c r="C82" s="34"/>
-      <c r="D82" s="34"/>
-      <c r="E82" s="34"/>
-      <c r="F82" s="34"/>
-      <c r="G82" s="34"/>
-      <c r="H82" s="34"/>
-      <c r="I82" s="34"/>
-      <c r="J82" s="34"/>
-      <c r="K82" s="34"/>
-      <c r="L82" s="34"/>
-      <c r="M82" s="34"/>
-      <c r="N82" s="34"/>
-      <c r="O82" s="34"/>
-      <c r="P82" s="34"/>
-      <c r="Q82" s="34"/>
-      <c r="R82" s="34"/>
-      <c r="S82" s="34"/>
-      <c r="T82" s="34"/>
-      <c r="U82" s="34"/>
-      <c r="V82" s="34"/>
-      <c r="W82" s="34"/>
-    </row>
-    <row r="83" ht="17" customHeight="1">
-      <c r="A83" t="s" s="37">
-        <v>213</v>
-      </c>
-      <c r="B83" t="s" s="37">
-        <v>105</v>
-      </c>
-      <c r="C83" t="s" s="37">
-        <v>106</v>
-      </c>
-      <c r="D83" s="34"/>
-      <c r="E83" t="s" s="54">
-        <v>214</v>
-      </c>
-      <c r="F83" t="s" s="54">
-        <v>105</v>
-      </c>
-      <c r="G83" t="s" s="54">
-        <v>106</v>
-      </c>
-      <c r="H83" s="36"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="51"/>
-      <c r="K83" s="51"/>
-      <c r="L83" s="36"/>
-      <c r="M83" s="51"/>
-      <c r="N83" s="51"/>
-      <c r="O83" s="51"/>
-      <c r="P83" s="34"/>
-      <c r="Q83" s="52"/>
-      <c r="R83" s="52"/>
-      <c r="S83" s="52"/>
-      <c r="T83" s="34"/>
-      <c r="U83" s="52"/>
-      <c r="V83" s="52"/>
-      <c r="W83" s="52"/>
-    </row>
-    <row r="84" ht="17" customHeight="1">
-      <c r="A84" t="s" s="39">
-        <v>112</v>
-      </c>
-      <c r="B84" t="s" s="39">
-        <v>118</v>
-      </c>
-      <c r="C84" t="s" s="39">
-        <v>119</v>
-      </c>
-      <c r="D84" s="34"/>
-      <c r="E84" t="s" s="55">
-        <v>215</v>
-      </c>
-      <c r="F84" t="s" s="55">
-        <v>216</v>
-      </c>
-      <c r="G84" t="s" s="55">
-        <v>110</v>
-      </c>
-      <c r="H84" s="34"/>
-      <c r="I84" s="34"/>
-      <c r="J84" s="34"/>
-      <c r="K84" s="34"/>
-      <c r="L84" s="34"/>
-      <c r="M84" s="34"/>
-      <c r="N84" s="34"/>
-      <c r="O84" s="34"/>
-      <c r="P84" s="34"/>
-      <c r="Q84" s="34"/>
-      <c r="R84" s="34"/>
-      <c r="S84" s="34"/>
-      <c r="T84" s="34"/>
-      <c r="U84" s="34"/>
-      <c r="V84" s="34"/>
-      <c r="W84" s="34"/>
-    </row>
-    <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="41"/>
-      <c r="B85" t="s" s="42">
-        <v>211</v>
-      </c>
-      <c r="C85" t="s" s="42">
-        <v>119</v>
-      </c>
-      <c r="D85" s="34"/>
-      <c r="E85" s="53"/>
-      <c r="F85" t="s" s="56">
+      <c r="G94" t="s" s="41">
+        <v>150</v>
+      </c>
+      <c r="H94" s="37"/>
+      <c r="I94" t="s" s="57">
+        <v>232</v>
+      </c>
+      <c r="J94" t="s" s="57">
+        <v>233</v>
+      </c>
+      <c r="K94" t="s" s="57">
+        <v>150</v>
+      </c>
+      <c r="L94" s="60">
+        <v>20</v>
+      </c>
+      <c r="M94" t="s" s="57">
+        <v>234</v>
+      </c>
+      <c r="N94" s="35"/>
+      <c r="O94" s="35"/>
+      <c r="P94" s="35"/>
+      <c r="Q94" s="35"/>
+      <c r="R94" s="35"/>
+      <c r="S94" s="35"/>
+      <c r="T94" s="35"/>
+      <c r="U94" s="35"/>
+      <c r="V94" s="35"/>
+      <c r="W94" s="35"/>
+    </row>
+    <row r="95" ht="17" customHeight="1">
+      <c r="A95" s="44"/>
+      <c r="B95" t="s" s="39">
+        <v>233</v>
+      </c>
+      <c r="C95" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="D95" s="35"/>
+      <c r="E95" s="44"/>
+      <c r="F95" t="s" s="39">
+        <v>235</v>
+      </c>
+      <c r="G95" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H95" s="37"/>
+      <c r="I95" s="58"/>
+      <c r="J95" t="s" s="56">
+        <v>236</v>
+      </c>
+      <c r="K95" t="s" s="56">
+        <v>111</v>
+      </c>
+      <c r="L95" t="s" s="56">
+        <v>237</v>
+      </c>
+      <c r="M95" t="s" s="56">
+        <v>238</v>
+      </c>
+      <c r="N95" s="35"/>
+      <c r="O95" s="35"/>
+      <c r="P95" s="35"/>
+      <c r="Q95" s="35"/>
+      <c r="R95" s="35"/>
+      <c r="S95" s="35"/>
+      <c r="T95" s="35"/>
+      <c r="U95" s="35"/>
+      <c r="V95" s="35"/>
+      <c r="W95" s="35"/>
+    </row>
+    <row r="96" ht="17" customHeight="1">
+      <c r="A96" s="37"/>
+      <c r="B96" t="s" s="41">
+        <v>239</v>
+      </c>
+      <c r="C96" t="s" s="41">
+        <v>240</v>
+      </c>
+      <c r="D96" s="35"/>
+      <c r="E96" s="37"/>
+      <c r="F96" t="s" s="41">
         <v>217</v>
       </c>
-      <c r="G85" t="s" s="56">
-        <v>218</v>
-      </c>
-      <c r="H85" s="34"/>
-      <c r="I85" s="34"/>
-      <c r="J85" s="34"/>
-      <c r="K85" s="34"/>
-      <c r="L85" s="34"/>
-      <c r="M85" s="34"/>
-      <c r="N85" s="34"/>
-      <c r="O85" s="34"/>
-      <c r="P85" s="34"/>
-      <c r="Q85" s="34"/>
-      <c r="R85" s="34"/>
-      <c r="S85" s="34"/>
-      <c r="T85" s="34"/>
-      <c r="U85" s="34"/>
-      <c r="V85" s="34"/>
-      <c r="W85" s="34"/>
-    </row>
-    <row r="86" ht="17" customHeight="1">
-      <c r="A86" s="44"/>
-      <c r="B86" t="s" s="39">
-        <v>216</v>
-      </c>
-      <c r="C86" t="s" s="39">
-        <v>110</v>
-      </c>
-      <c r="D86" s="34"/>
-      <c r="E86" s="57"/>
-      <c r="F86" t="s" s="55">
-        <v>182</v>
-      </c>
-      <c r="G86" t="s" s="55">
-        <v>219</v>
-      </c>
-      <c r="H86" s="34"/>
-      <c r="I86" s="34"/>
-      <c r="J86" s="34"/>
-      <c r="K86" s="34"/>
-      <c r="L86" s="34"/>
-      <c r="M86" s="34"/>
-      <c r="N86" s="34"/>
-      <c r="O86" s="34"/>
-      <c r="P86" s="34"/>
-      <c r="Q86" s="34"/>
-      <c r="R86" s="34"/>
-      <c r="S86" s="34"/>
-      <c r="T86" s="34"/>
-      <c r="U86" s="34"/>
-      <c r="V86" s="34"/>
-      <c r="W86" s="34"/>
-    </row>
-    <row r="87" ht="17" customHeight="1">
-      <c r="A87" s="41"/>
-      <c r="B87" t="s" s="42">
-        <v>217</v>
-      </c>
-      <c r="C87" t="s" s="42">
-        <v>218</v>
-      </c>
-      <c r="D87" s="34"/>
-      <c r="E87" s="53"/>
-      <c r="F87" t="s" s="56">
-        <v>159</v>
-      </c>
-      <c r="G87" t="s" s="56">
-        <v>115</v>
-      </c>
-      <c r="H87" s="34"/>
-      <c r="I87" s="34"/>
-      <c r="J87" s="34"/>
-      <c r="K87" s="34"/>
-      <c r="L87" s="34"/>
-      <c r="M87" s="34"/>
-      <c r="N87" s="34"/>
-      <c r="O87" s="34"/>
-      <c r="P87" s="34"/>
-      <c r="Q87" s="34"/>
-      <c r="R87" s="34"/>
-      <c r="S87" s="34"/>
-      <c r="T87" s="34"/>
-      <c r="U87" s="34"/>
-      <c r="V87" s="34"/>
-      <c r="W87" s="34"/>
-    </row>
-    <row r="88" ht="17" customHeight="1">
-      <c r="A88" s="44"/>
-      <c r="B88" t="s" s="39">
-        <v>182</v>
-      </c>
-      <c r="C88" t="s" s="39">
-        <v>219</v>
-      </c>
-      <c r="D88" s="34"/>
-      <c r="E88" s="57"/>
-      <c r="F88" s="57"/>
-      <c r="G88" s="57"/>
-      <c r="H88" s="34"/>
-      <c r="I88" s="34"/>
-      <c r="J88" s="34"/>
-      <c r="K88" s="34"/>
-      <c r="L88" s="34"/>
-      <c r="M88" s="34"/>
-      <c r="N88" s="34"/>
-      <c r="O88" s="34"/>
-      <c r="P88" s="34"/>
-      <c r="Q88" s="34"/>
-      <c r="R88" s="34"/>
-      <c r="S88" s="34"/>
-      <c r="T88" s="34"/>
-      <c r="U88" s="34"/>
-      <c r="V88" s="34"/>
-      <c r="W88" s="34"/>
-    </row>
-    <row r="89" ht="17" customHeight="1">
-      <c r="A89" s="41"/>
-      <c r="B89" t="s" s="42">
-        <v>159</v>
-      </c>
-      <c r="C89" t="s" s="42">
-        <v>115</v>
-      </c>
-      <c r="D89" s="34"/>
-      <c r="E89" s="53"/>
-      <c r="F89" s="53"/>
-      <c r="G89" s="53"/>
-      <c r="H89" s="36"/>
-      <c r="I89" s="36"/>
-      <c r="J89" s="36"/>
-      <c r="K89" s="36"/>
-      <c r="L89" s="36"/>
-      <c r="M89" s="36"/>
-      <c r="N89" s="36"/>
-      <c r="O89" s="36"/>
-      <c r="P89" s="34"/>
-      <c r="Q89" s="41"/>
-      <c r="R89" s="41"/>
-      <c r="S89" s="41"/>
-      <c r="T89" s="34"/>
-      <c r="U89" s="41"/>
-      <c r="V89" s="41"/>
-      <c r="W89" s="41"/>
-    </row>
-    <row r="90" ht="70.45" customHeight="1">
-      <c r="A90" s="34"/>
-      <c r="B90" s="34"/>
-      <c r="C90" s="34"/>
-      <c r="D90" s="34"/>
-      <c r="E90" s="34"/>
-      <c r="F90" s="34"/>
-      <c r="G90" s="34"/>
-      <c r="H90" s="34"/>
-      <c r="I90" s="34"/>
-      <c r="J90" s="34"/>
-      <c r="K90" s="34"/>
-      <c r="L90" s="34"/>
-      <c r="M90" s="34"/>
-      <c r="N90" s="34"/>
-      <c r="O90" s="34"/>
-      <c r="P90" s="34"/>
-      <c r="Q90" s="34"/>
-      <c r="R90" s="34"/>
-      <c r="S90" s="34"/>
-      <c r="T90" s="34"/>
-      <c r="U90" s="34"/>
-      <c r="V90" s="34"/>
-      <c r="W90" s="34"/>
-    </row>
-    <row r="91" ht="34" customHeight="1">
-      <c r="A91" t="s" s="33">
-        <v>220</v>
-      </c>
-      <c r="B91" s="34"/>
-      <c r="C91" s="34"/>
-      <c r="D91" s="34"/>
-      <c r="E91" s="34"/>
-      <c r="F91" s="34"/>
-      <c r="G91" s="34"/>
-      <c r="H91" s="34"/>
-      <c r="I91" s="34"/>
-      <c r="J91" s="34"/>
-      <c r="K91" s="34"/>
-      <c r="L91" s="34"/>
-      <c r="M91" s="34"/>
-      <c r="N91" s="34"/>
-      <c r="O91" s="34"/>
-      <c r="P91" s="34"/>
-      <c r="Q91" s="34"/>
-      <c r="R91" s="34"/>
-      <c r="S91" s="34"/>
-      <c r="T91" s="34"/>
-      <c r="U91" s="34"/>
-      <c r="V91" s="34"/>
-      <c r="W91" s="34"/>
-    </row>
-    <row r="92" ht="17" customHeight="1">
-      <c r="A92" t="s" s="35">
-        <v>221</v>
-      </c>
-      <c r="B92" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="C92" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="D92" s="34"/>
-      <c r="E92" t="s" s="35">
-        <v>222</v>
-      </c>
-      <c r="F92" t="s" s="35">
-        <v>105</v>
-      </c>
-      <c r="G92" t="s" s="35">
-        <v>106</v>
-      </c>
-      <c r="H92" s="36"/>
-      <c r="I92" t="s" s="54">
-        <v>223</v>
-      </c>
-      <c r="J92" t="s" s="54">
-        <v>224</v>
-      </c>
-      <c r="K92" t="s" s="54">
-        <v>106</v>
-      </c>
-      <c r="L92" t="s" s="54">
-        <v>225</v>
-      </c>
-      <c r="M92" t="s" s="54">
-        <v>1</v>
-      </c>
-      <c r="N92" s="51"/>
-      <c r="O92" s="51"/>
-      <c r="P92" s="34"/>
-      <c r="Q92" s="52"/>
-      <c r="R92" s="52"/>
-      <c r="S92" s="52"/>
-      <c r="T92" s="34"/>
-      <c r="U92" s="52"/>
-      <c r="V92" s="52"/>
-      <c r="W92" s="52"/>
-    </row>
-    <row r="93" ht="17" customHeight="1">
-      <c r="A93" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="B93" t="s" s="38">
-        <v>226</v>
-      </c>
-      <c r="C93" t="s" s="38">
-        <v>227</v>
-      </c>
-      <c r="D93" s="34"/>
-      <c r="E93" t="s" s="38">
-        <v>108</v>
-      </c>
-      <c r="F93" t="s" s="38">
-        <v>159</v>
-      </c>
-      <c r="G93" t="s" s="38">
-        <v>115</v>
-      </c>
-      <c r="H93" s="36"/>
-      <c r="I93" t="s" s="55">
-        <v>228</v>
-      </c>
-      <c r="J93" t="s" s="55">
-        <v>229</v>
-      </c>
-      <c r="K93" t="s" s="55">
-        <v>149</v>
-      </c>
-      <c r="L93" s="58">
-        <v>0</v>
-      </c>
-      <c r="M93" t="s" s="55">
-        <v>230</v>
-      </c>
-      <c r="N93" s="34"/>
-      <c r="O93" s="34"/>
-      <c r="P93" s="34"/>
-      <c r="Q93" s="34"/>
-      <c r="R93" s="34"/>
-      <c r="S93" s="34"/>
-      <c r="T93" s="34"/>
-      <c r="U93" s="34"/>
-      <c r="V93" s="34"/>
-      <c r="W93" s="34"/>
-    </row>
-    <row r="94" ht="17" customHeight="1">
-      <c r="A94" s="36"/>
-      <c r="B94" t="s" s="40">
-        <v>229</v>
-      </c>
-      <c r="C94" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="D94" s="34"/>
-      <c r="E94" s="36"/>
-      <c r="F94" t="s" s="40">
-        <v>182</v>
-      </c>
-      <c r="G94" t="s" s="40">
-        <v>149</v>
-      </c>
-      <c r="H94" s="36"/>
-      <c r="I94" t="s" s="56">
-        <v>231</v>
-      </c>
-      <c r="J94" t="s" s="56">
-        <v>232</v>
-      </c>
-      <c r="K94" t="s" s="56">
-        <v>149</v>
-      </c>
-      <c r="L94" s="59">
-        <v>20</v>
-      </c>
-      <c r="M94" t="s" s="56">
-        <v>233</v>
-      </c>
-      <c r="N94" s="34"/>
-      <c r="O94" s="34"/>
-      <c r="P94" s="34"/>
-      <c r="Q94" s="34"/>
-      <c r="R94" s="34"/>
-      <c r="S94" s="34"/>
-      <c r="T94" s="34"/>
-      <c r="U94" s="34"/>
-      <c r="V94" s="34"/>
-      <c r="W94" s="34"/>
-    </row>
-    <row r="95" ht="17" customHeight="1">
-      <c r="A95" s="43"/>
-      <c r="B95" t="s" s="38">
-        <v>232</v>
-      </c>
-      <c r="C95" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="D95" s="34"/>
-      <c r="E95" s="43"/>
-      <c r="F95" t="s" s="38">
-        <v>234</v>
-      </c>
-      <c r="G95" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H95" s="36"/>
-      <c r="I95" s="57"/>
-      <c r="J95" t="s" s="55">
-        <v>235</v>
-      </c>
-      <c r="K95" t="s" s="55">
-        <v>110</v>
-      </c>
-      <c r="L95" t="s" s="55">
+      <c r="G96" t="s" s="41">
+        <v>111</v>
+      </c>
+      <c r="H96" s="37"/>
+      <c r="I96" s="54"/>
+      <c r="J96" t="s" s="57">
+        <v>241</v>
+      </c>
+      <c r="K96" t="s" s="57">
+        <v>242</v>
+      </c>
+      <c r="L96" t="s" s="57">
+        <v>243</v>
+      </c>
+      <c r="M96" t="s" s="57">
+        <v>244</v>
+      </c>
+      <c r="N96" s="35"/>
+      <c r="O96" s="35"/>
+      <c r="P96" s="35"/>
+      <c r="Q96" s="35"/>
+      <c r="R96" s="35"/>
+      <c r="S96" s="35"/>
+      <c r="T96" s="35"/>
+      <c r="U96" s="35"/>
+      <c r="V96" s="35"/>
+      <c r="W96" s="35"/>
+    </row>
+    <row r="97" ht="17" customHeight="1">
+      <c r="A97" s="44"/>
+      <c r="B97" t="s" s="39">
+        <v>245</v>
+      </c>
+      <c r="C97" t="s" s="39">
+        <v>150</v>
+      </c>
+      <c r="D97" s="35"/>
+      <c r="E97" s="44"/>
+      <c r="F97" t="s" s="39">
+        <v>246</v>
+      </c>
+      <c r="G97" t="s" s="39">
+        <v>111</v>
+      </c>
+      <c r="H97" s="37"/>
+      <c r="I97" s="58"/>
+      <c r="J97" s="58"/>
+      <c r="K97" s="58"/>
+      <c r="L97" s="58"/>
+      <c r="M97" s="58"/>
+      <c r="N97" s="35"/>
+      <c r="O97" s="35"/>
+      <c r="P97" s="35"/>
+      <c r="Q97" s="35"/>
+      <c r="R97" s="35"/>
+      <c r="S97" s="35"/>
+      <c r="T97" s="35"/>
+      <c r="U97" s="35"/>
+      <c r="V97" s="35"/>
+      <c r="W97" s="35"/>
+    </row>
+    <row r="98" ht="17" customHeight="1">
+      <c r="A98" s="37"/>
+      <c r="B98" t="s" s="41">
         <v>236</v>
       </c>
-      <c r="M95" t="s" s="55">
-        <v>237</v>
-      </c>
-      <c r="N95" s="34"/>
-      <c r="O95" s="34"/>
-      <c r="P95" s="34"/>
-      <c r="Q95" s="34"/>
-      <c r="R95" s="34"/>
-      <c r="S95" s="34"/>
-      <c r="T95" s="34"/>
-      <c r="U95" s="34"/>
-      <c r="V95" s="34"/>
-      <c r="W95" s="34"/>
-    </row>
-    <row r="96" ht="17" customHeight="1">
-      <c r="A96" s="36"/>
-      <c r="B96" t="s" s="40">
-        <v>238</v>
-      </c>
-      <c r="C96" t="s" s="40">
-        <v>239</v>
-      </c>
-      <c r="D96" s="34"/>
-      <c r="E96" s="36"/>
-      <c r="F96" t="s" s="40">
-        <v>216</v>
-      </c>
-      <c r="G96" t="s" s="40">
-        <v>110</v>
-      </c>
-      <c r="H96" s="36"/>
-      <c r="I96" s="53"/>
-      <c r="J96" t="s" s="56">
-        <v>240</v>
-      </c>
-      <c r="K96" t="s" s="56">
-        <v>241</v>
-      </c>
-      <c r="L96" t="s" s="56">
-        <v>242</v>
-      </c>
-      <c r="M96" t="s" s="56">
-        <v>243</v>
-      </c>
-      <c r="N96" s="34"/>
-      <c r="O96" s="34"/>
-      <c r="P96" s="34"/>
-      <c r="Q96" s="34"/>
-      <c r="R96" s="34"/>
-      <c r="S96" s="34"/>
-      <c r="T96" s="34"/>
-      <c r="U96" s="34"/>
-      <c r="V96" s="34"/>
-      <c r="W96" s="34"/>
-    </row>
-    <row r="97" ht="17" customHeight="1">
-      <c r="A97" s="43"/>
-      <c r="B97" t="s" s="38">
-        <v>244</v>
-      </c>
-      <c r="C97" t="s" s="38">
-        <v>149</v>
-      </c>
-      <c r="D97" s="34"/>
-      <c r="E97" s="43"/>
-      <c r="F97" t="s" s="38">
-        <v>245</v>
-      </c>
-      <c r="G97" t="s" s="38">
-        <v>110</v>
-      </c>
-      <c r="H97" s="36"/>
-      <c r="I97" s="57"/>
-      <c r="J97" s="57"/>
-      <c r="K97" s="57"/>
-      <c r="L97" s="57"/>
-      <c r="M97" s="57"/>
-      <c r="N97" s="34"/>
-      <c r="O97" s="34"/>
-      <c r="P97" s="34"/>
-      <c r="Q97" s="34"/>
-      <c r="R97" s="34"/>
-      <c r="S97" s="34"/>
-      <c r="T97" s="34"/>
-      <c r="U97" s="34"/>
-      <c r="V97" s="34"/>
-      <c r="W97" s="34"/>
-    </row>
-    <row r="98" ht="17" customHeight="1">
-      <c r="A98" s="36"/>
-      <c r="B98" t="s" s="40">
-        <v>235</v>
-      </c>
-      <c r="C98" t="s" s="40">
-        <v>246</v>
-      </c>
-      <c r="D98" s="34"/>
-      <c r="E98" s="36"/>
-      <c r="F98" s="36"/>
-      <c r="G98" s="36"/>
-      <c r="H98" s="36"/>
-      <c r="I98" s="36"/>
-      <c r="J98" s="36"/>
-      <c r="K98" s="36"/>
-      <c r="L98" s="34"/>
-      <c r="M98" s="34"/>
-      <c r="N98" s="34"/>
-      <c r="O98" s="34"/>
-      <c r="P98" s="34"/>
-      <c r="Q98" s="34"/>
-      <c r="R98" s="34"/>
-      <c r="S98" s="34"/>
-      <c r="T98" s="34"/>
-      <c r="U98" s="34"/>
-      <c r="V98" s="34"/>
-      <c r="W98" s="34"/>
+      <c r="C98" t="s" s="41">
+        <v>247</v>
+      </c>
+      <c r="D98" s="35"/>
+      <c r="E98" s="37"/>
+      <c r="F98" s="37"/>
+      <c r="G98" s="37"/>
+      <c r="H98" s="37"/>
+      <c r="I98" s="37"/>
+      <c r="J98" s="37"/>
+      <c r="K98" s="37"/>
+      <c r="L98" s="35"/>
+      <c r="M98" s="35"/>
+      <c r="N98" s="35"/>
+      <c r="O98" s="35"/>
+      <c r="P98" s="35"/>
+      <c r="Q98" s="35"/>
+      <c r="R98" s="35"/>
+      <c r="S98" s="35"/>
+      <c r="T98" s="35"/>
+      <c r="U98" s="35"/>
+      <c r="V98" s="35"/>
+      <c r="W98" s="35"/>
     </row>
     <row r="99" ht="17" customHeight="1">
-      <c r="A99" s="43"/>
-      <c r="B99" t="s" s="38">
-        <v>247</v>
-      </c>
-      <c r="C99" t="s" s="38">
+      <c r="A99" s="44"/>
+      <c r="B99" t="s" s="39">
         <v>248</v>
       </c>
-      <c r="D99" s="34"/>
-      <c r="E99" s="45"/>
-      <c r="F99" s="46"/>
-      <c r="G99" s="46"/>
-      <c r="H99" s="46"/>
-      <c r="I99" s="46"/>
-      <c r="J99" s="46"/>
-      <c r="K99" s="47"/>
-      <c r="L99" s="34"/>
-      <c r="M99" s="34"/>
-      <c r="N99" s="34"/>
-      <c r="O99" s="34"/>
-      <c r="P99" s="34"/>
-      <c r="Q99" s="34"/>
-      <c r="R99" s="34"/>
-      <c r="S99" s="34"/>
-      <c r="T99" s="34"/>
-      <c r="U99" s="34"/>
-      <c r="V99" s="34"/>
-      <c r="W99" s="34"/>
+      <c r="C99" t="s" s="39">
+        <v>249</v>
+      </c>
+      <c r="D99" s="35"/>
+      <c r="E99" s="46"/>
+      <c r="F99" s="47"/>
+      <c r="G99" s="47"/>
+      <c r="H99" s="47"/>
+      <c r="I99" s="47"/>
+      <c r="J99" s="47"/>
+      <c r="K99" s="48"/>
+      <c r="L99" s="35"/>
+      <c r="M99" s="35"/>
+      <c r="N99" s="35"/>
+      <c r="O99" s="35"/>
+      <c r="P99" s="35"/>
+      <c r="Q99" s="35"/>
+      <c r="R99" s="35"/>
+      <c r="S99" s="35"/>
+      <c r="T99" s="35"/>
+      <c r="U99" s="35"/>
+      <c r="V99" s="35"/>
+      <c r="W99" s="35"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6778,15 +6797,31 @@
       <c r="I6" s="7"/>
     </row>
     <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="14"/>
+      <c r="A7" t="s" s="8">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s" s="8">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s" s="8">
+        <v>32</v>
+      </c>
+      <c r="D7" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="E7" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="G7" t="s" s="8">
+        <v>33</v>
+      </c>
+      <c r="H7" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="I7" s="24"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="15"/>
@@ -6835,16 +6870,16 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="24" customWidth="1"/>
-    <col min="2" max="2" width="35" style="24" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="24" customWidth="1"/>
-    <col min="4" max="4" width="36.8516" style="24" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="24" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="24" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="24" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="24" customWidth="1"/>
-    <col min="9" max="9" width="11" style="24" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="24" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="25" customWidth="1"/>
+    <col min="2" max="2" width="35" style="25" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="25" customWidth="1"/>
+    <col min="4" max="4" width="36.8516" style="25" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="25" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="25" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="25" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="25" customWidth="1"/>
+    <col min="9" max="9" width="11" style="25" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="25" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -6903,16 +6938,16 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" t="s" s="8">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C3" t="s" s="8">
         <v>15</v>
       </c>
       <c r="D3" t="s" s="8">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="E3" t="s" s="8">
         <v>17</v>
@@ -6924,16 +6959,16 @@
         <v>18</v>
       </c>
       <c r="H3" t="s" s="8">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="I3" s="3"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" t="s" s="9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C4" t="s" s="10">
         <v>15</v>
@@ -6951,16 +6986,16 @@
         <v>18</v>
       </c>
       <c r="H4" t="s" s="10">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I4" s="7"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" t="s" s="11">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="B5" t="s" s="11">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C5" t="s" s="11">
         <v>25</v>
@@ -6972,13 +7007,13 @@
         <v>17</v>
       </c>
       <c r="F5" t="s" s="11">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="G5" t="s" s="11">
         <v>27</v>
       </c>
       <c r="H5" t="s" s="11">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="I5" s="3"/>
     </row>
@@ -7051,210 +7086,10 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="25" customWidth="1"/>
-    <col min="2" max="2" width="35" style="25" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="25" customWidth="1"/>
-    <col min="4" max="4" width="44.5" style="25" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="25" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="25" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="25" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="25" customWidth="1"/>
-    <col min="9" max="9" width="11" style="25" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="25" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="17" customHeight="1">
-      <c r="A1" t="s" s="2">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="2">
-        <v>1</v>
-      </c>
-      <c r="C1" t="s" s="2">
-        <v>2</v>
-      </c>
-      <c r="D1" t="s" s="2">
-        <v>3</v>
-      </c>
-      <c r="E1" t="s" s="2">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s" s="2">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s" s="2">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s" s="2">
-        <v>7</v>
-      </c>
-      <c r="I1" s="3"/>
-    </row>
-    <row r="2" ht="28.25" customHeight="1">
-      <c r="A2" t="s" s="4">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s" s="5">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s" s="6">
-        <v>10</v>
-      </c>
-      <c r="D2" t="s" s="6">
-        <v>10</v>
-      </c>
-      <c r="E2" t="s" s="6">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s" s="6">
-        <v>10</v>
-      </c>
-      <c r="G2" t="s" s="6">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s" s="6">
-        <v>12</v>
-      </c>
-      <c r="I2" s="7"/>
-    </row>
-    <row r="3" ht="17" customHeight="1">
-      <c r="A3" t="s" s="8">
-        <v>72</v>
-      </c>
-      <c r="B3" t="s" s="8">
-        <v>73</v>
-      </c>
-      <c r="C3" t="s" s="8">
-        <v>15</v>
-      </c>
-      <c r="D3" t="s" s="8">
-        <v>74</v>
-      </c>
-      <c r="E3" t="s" s="8">
-        <v>75</v>
-      </c>
-      <c r="F3" t="s" s="8">
-        <v>17</v>
-      </c>
-      <c r="G3" t="s" s="8">
-        <v>18</v>
-      </c>
-      <c r="H3" t="s" s="8">
-        <v>76</v>
-      </c>
-      <c r="I3" s="3"/>
-    </row>
-    <row r="4" ht="17" customHeight="1">
-      <c r="A4" t="s" s="9">
-        <v>72</v>
-      </c>
-      <c r="B4" t="s" s="10">
-        <v>77</v>
-      </c>
-      <c r="C4" t="s" s="10">
-        <v>25</v>
-      </c>
-      <c r="D4" t="s" s="10">
-        <v>17</v>
-      </c>
-      <c r="E4" t="s" s="10">
-        <v>75</v>
-      </c>
-      <c r="F4" t="s" s="10">
-        <v>78</v>
-      </c>
-      <c r="G4" t="s" s="10">
-        <v>27</v>
-      </c>
-      <c r="H4" t="s" s="10">
-        <v>79</v>
-      </c>
-      <c r="I4" s="7"/>
-    </row>
-    <row r="5" ht="17" customHeight="1">
-      <c r="A5" s="15"/>
-      <c r="B5" s="16"/>
-      <c r="C5" s="16"/>
-      <c r="D5" s="16"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="16"/>
-      <c r="G5" s="16"/>
-      <c r="H5" s="16"/>
-      <c r="I5" s="14"/>
-    </row>
-    <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="15"/>
-      <c r="B6" s="16"/>
-      <c r="C6" s="16"/>
-      <c r="D6" s="16"/>
-      <c r="E6" s="16"/>
-      <c r="F6" s="16"/>
-      <c r="G6" s="16"/>
-      <c r="H6" s="16"/>
-      <c r="I6" s="17"/>
-    </row>
-    <row r="7" ht="17" customHeight="1">
-      <c r="A7" s="15"/>
-      <c r="B7" s="16"/>
-      <c r="C7" s="16"/>
-      <c r="D7" s="16"/>
-      <c r="E7" s="16"/>
-      <c r="F7" s="16"/>
-      <c r="G7" s="16"/>
-      <c r="H7" s="16"/>
-      <c r="I7" s="17"/>
-    </row>
-    <row r="8" ht="17" customHeight="1">
-      <c r="A8" s="15"/>
-      <c r="B8" s="16"/>
-      <c r="C8" s="16"/>
-      <c r="D8" s="16"/>
-      <c r="E8" s="16"/>
-      <c r="F8" s="16"/>
-      <c r="G8" s="16"/>
-      <c r="H8" s="16"/>
-      <c r="I8" s="17"/>
-    </row>
-    <row r="9" ht="17" customHeight="1">
-      <c r="A9" s="15"/>
-      <c r="B9" s="16"/>
-      <c r="C9" s="16"/>
-      <c r="D9" s="16"/>
-      <c r="E9" s="16"/>
-      <c r="F9" s="16"/>
-      <c r="G9" s="16"/>
-      <c r="H9" s="16"/>
-      <c r="I9" s="17"/>
-    </row>
-    <row r="10" ht="17" customHeight="1">
-      <c r="A10" s="18"/>
-      <c r="B10" s="19"/>
-      <c r="C10" s="19"/>
-      <c r="D10" s="19"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="19"/>
-      <c r="G10" s="19"/>
-      <c r="H10" s="19"/>
-      <c r="I10" s="20"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
-  <headerFooter>
-    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:I10"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
     <col min="1" max="1" width="30.6719" style="26" customWidth="1"/>
     <col min="2" max="2" width="35" style="26" customWidth="1"/>
     <col min="3" max="3" width="14.5" style="26" customWidth="1"/>
-    <col min="4" max="4" width="42" style="26" customWidth="1"/>
+    <col min="4" max="4" width="44.5" style="26" customWidth="1"/>
     <col min="5" max="5" width="25.8516" style="26" customWidth="1"/>
     <col min="6" max="6" width="34.1719" style="26" customWidth="1"/>
     <col min="7" max="7" width="24.1719" style="26" customWidth="1"/>
@@ -7319,19 +7154,19 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" t="s" s="8">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="C3" t="s" s="8">
         <v>15</v>
       </c>
       <c r="D3" t="s" s="8">
-        <v>17</v>
+        <v>75</v>
       </c>
       <c r="E3" t="s" s="8">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F3" t="s" s="8">
         <v>17</v>
@@ -7340,16 +7175,16 @@
         <v>18</v>
       </c>
       <c r="H3" t="s" s="8">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I3" s="3"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" t="s" s="9">
-        <v>80</v>
+        <v>73</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>83</v>
+        <v>78</v>
       </c>
       <c r="C4" t="s" s="10">
         <v>25</v>
@@ -7358,72 +7193,40 @@
         <v>17</v>
       </c>
       <c r="E4" t="s" s="10">
-        <v>17</v>
+        <v>76</v>
       </c>
       <c r="F4" t="s" s="10">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="G4" t="s" s="10">
         <v>27</v>
       </c>
       <c r="H4" t="s" s="10">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="I4" s="7"/>
     </row>
     <row r="5" ht="17" customHeight="1">
-      <c r="A5" t="s" s="8">
-        <v>86</v>
-      </c>
-      <c r="B5" t="s" s="8">
-        <v>87</v>
-      </c>
-      <c r="C5" t="s" s="8">
-        <v>29</v>
-      </c>
-      <c r="D5" t="s" s="8">
-        <v>17</v>
-      </c>
-      <c r="E5" t="s" s="8">
-        <v>22</v>
-      </c>
-      <c r="F5" t="s" s="8">
-        <v>88</v>
-      </c>
-      <c r="G5" t="s" s="8">
-        <v>18</v>
-      </c>
-      <c r="H5" t="s" s="8">
-        <v>85</v>
-      </c>
-      <c r="I5" s="3"/>
+      <c r="A5" s="15"/>
+      <c r="B5" s="16"/>
+      <c r="C5" s="16"/>
+      <c r="D5" s="16"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="16"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="14"/>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" t="s" s="9">
-        <v>86</v>
-      </c>
-      <c r="B6" t="s" s="10">
-        <v>89</v>
-      </c>
-      <c r="C6" t="s" s="10">
-        <v>32</v>
-      </c>
-      <c r="D6" t="s" s="10">
-        <v>17</v>
-      </c>
-      <c r="E6" t="s" s="10">
-        <v>22</v>
-      </c>
-      <c r="F6" t="s" s="10">
-        <v>17</v>
-      </c>
-      <c r="G6" t="s" s="10">
-        <v>33</v>
-      </c>
-      <c r="H6" t="s" s="10">
-        <v>17</v>
-      </c>
-      <c r="I6" s="7"/>
+      <c r="A6" s="15"/>
+      <c r="B6" s="16"/>
+      <c r="C6" s="16"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="16"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="17"/>
     </row>
     <row r="7" ht="17" customHeight="1">
       <c r="A7" s="15"/>
@@ -7434,7 +7237,7 @@
       <c r="F7" s="16"/>
       <c r="G7" s="16"/>
       <c r="H7" s="16"/>
-      <c r="I7" s="14"/>
+      <c r="I7" s="17"/>
     </row>
     <row r="8" ht="17" customHeight="1">
       <c r="A8" s="15"/>
@@ -7478,7 +7281,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
@@ -7551,10 +7354,10 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" t="s" s="8">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B3" t="s" s="8">
-        <v>91</v>
+        <v>82</v>
       </c>
       <c r="C3" t="s" s="8">
         <v>15</v>
@@ -7572,16 +7375,16 @@
         <v>18</v>
       </c>
       <c r="H3" t="s" s="8">
-        <v>92</v>
+        <v>83</v>
       </c>
       <c r="I3" s="3"/>
     </row>
     <row r="4" ht="17" customHeight="1">
       <c r="A4" t="s" s="9">
-        <v>90</v>
+        <v>81</v>
       </c>
       <c r="B4" t="s" s="10">
-        <v>93</v>
+        <v>84</v>
       </c>
       <c r="C4" t="s" s="10">
         <v>25</v>
@@ -7593,22 +7396,22 @@
         <v>17</v>
       </c>
       <c r="F4" t="s" s="10">
-        <v>94</v>
+        <v>85</v>
       </c>
       <c r="G4" t="s" s="10">
         <v>27</v>
       </c>
       <c r="H4" t="s" s="10">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I4" s="7"/>
     </row>
     <row r="5" ht="17" customHeight="1">
       <c r="A5" t="s" s="8">
-        <v>96</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="8">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="C5" t="s" s="8">
         <v>29</v>
@@ -7620,22 +7423,254 @@
         <v>22</v>
       </c>
       <c r="F5" t="s" s="8">
-        <v>98</v>
+        <v>89</v>
       </c>
       <c r="G5" t="s" s="8">
         <v>18</v>
       </c>
       <c r="H5" t="s" s="8">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" ht="17" customHeight="1">
       <c r="A6" t="s" s="9">
+        <v>87</v>
+      </c>
+      <c r="B6" t="s" s="10">
+        <v>90</v>
+      </c>
+      <c r="C6" t="s" s="10">
+        <v>32</v>
+      </c>
+      <c r="D6" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="E6" t="s" s="10">
+        <v>22</v>
+      </c>
+      <c r="F6" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="G6" t="s" s="10">
+        <v>33</v>
+      </c>
+      <c r="H6" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="I6" s="7"/>
+    </row>
+    <row r="7" ht="17" customHeight="1">
+      <c r="A7" s="15"/>
+      <c r="B7" s="16"/>
+      <c r="C7" s="16"/>
+      <c r="D7" s="16"/>
+      <c r="E7" s="16"/>
+      <c r="F7" s="16"/>
+      <c r="G7" s="16"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="14"/>
+    </row>
+    <row r="8" ht="17" customHeight="1">
+      <c r="A8" s="15"/>
+      <c r="B8" s="16"/>
+      <c r="C8" s="16"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="16"/>
+      <c r="F8" s="16"/>
+      <c r="G8" s="16"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="17"/>
+    </row>
+    <row r="9" ht="17" customHeight="1">
+      <c r="A9" s="15"/>
+      <c r="B9" s="16"/>
+      <c r="C9" s="16"/>
+      <c r="D9" s="16"/>
+      <c r="E9" s="16"/>
+      <c r="F9" s="16"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="16"/>
+      <c r="I9" s="17"/>
+    </row>
+    <row r="10" ht="17" customHeight="1">
+      <c r="A10" s="18"/>
+      <c r="B10" s="19"/>
+      <c r="C10" s="19"/>
+      <c r="D10" s="19"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="19"/>
+      <c r="G10" s="19"/>
+      <c r="H10" s="19"/>
+      <c r="I10" s="20"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup firstPageNumber="1" fitToHeight="1" fitToWidth="1" scale="100" useFirstPageNumber="0" orientation="portrait" pageOrder="downThenOver"/>
+  <headerFooter>
+    <oddFooter>&amp;C&amp;"Helvetica Neue,Regular"&amp;12&amp;K000000&amp;P</oddFooter>
+  </headerFooter>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:I10"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
+  <cols>
+    <col min="1" max="1" width="30.6719" style="28" customWidth="1"/>
+    <col min="2" max="2" width="35" style="28" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="28" customWidth="1"/>
+    <col min="4" max="4" width="42" style="28" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="28" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="28" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="28" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="28" customWidth="1"/>
+    <col min="9" max="9" width="11" style="28" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="28" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="17" customHeight="1">
+      <c r="A1" t="s" s="2">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s" s="2">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s" s="2">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s" s="2">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s" s="2">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s" s="2">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s" s="2">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s" s="2">
+        <v>7</v>
+      </c>
+      <c r="I1" s="3"/>
+    </row>
+    <row r="2" ht="28.25" customHeight="1">
+      <c r="A2" t="s" s="4">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s" s="5">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="E2" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="F2" t="s" s="6">
+        <v>10</v>
+      </c>
+      <c r="G2" t="s" s="6">
+        <v>11</v>
+      </c>
+      <c r="H2" t="s" s="6">
+        <v>12</v>
+      </c>
+      <c r="I2" s="7"/>
+    </row>
+    <row r="3" ht="17" customHeight="1">
+      <c r="A3" t="s" s="8">
+        <v>91</v>
+      </c>
+      <c r="B3" t="s" s="8">
+        <v>92</v>
+      </c>
+      <c r="C3" t="s" s="8">
+        <v>15</v>
+      </c>
+      <c r="D3" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="E3" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="G3" t="s" s="8">
+        <v>18</v>
+      </c>
+      <c r="H3" t="s" s="8">
+        <v>93</v>
+      </c>
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" ht="17" customHeight="1">
+      <c r="A4" t="s" s="9">
+        <v>91</v>
+      </c>
+      <c r="B4" t="s" s="10">
+        <v>94</v>
+      </c>
+      <c r="C4" t="s" s="10">
+        <v>25</v>
+      </c>
+      <c r="D4" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="E4" t="s" s="10">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s" s="10">
+        <v>95</v>
+      </c>
+      <c r="G4" t="s" s="10">
+        <v>27</v>
+      </c>
+      <c r="H4" t="s" s="10">
         <v>96</v>
       </c>
+      <c r="I4" s="7"/>
+    </row>
+    <row r="5" ht="17" customHeight="1">
+      <c r="A5" t="s" s="8">
+        <v>97</v>
+      </c>
+      <c r="B5" t="s" s="8">
+        <v>98</v>
+      </c>
+      <c r="C5" t="s" s="8">
+        <v>29</v>
+      </c>
+      <c r="D5" t="s" s="8">
+        <v>17</v>
+      </c>
+      <c r="E5" t="s" s="8">
+        <v>22</v>
+      </c>
+      <c r="F5" t="s" s="8">
+        <v>99</v>
+      </c>
+      <c r="G5" t="s" s="8">
+        <v>18</v>
+      </c>
+      <c r="H5" t="s" s="8">
+        <v>96</v>
+      </c>
+      <c r="I5" s="3"/>
+    </row>
+    <row r="6" ht="17" customHeight="1">
+      <c r="A6" t="s" s="9">
+        <v>97</v>
+      </c>
       <c r="B6" t="s" s="10">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C6" t="s" s="10">
         <v>32</v>
@@ -7715,16 +7750,16 @@
   <dimension ref="A1:I10"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.15" customHeight="1" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col min="1" max="1" width="30.6719" style="28" customWidth="1"/>
-    <col min="2" max="2" width="35" style="28" customWidth="1"/>
-    <col min="3" max="3" width="14.5" style="28" customWidth="1"/>
-    <col min="4" max="4" width="67.3516" style="28" customWidth="1"/>
-    <col min="5" max="5" width="25.8516" style="28" customWidth="1"/>
-    <col min="6" max="6" width="34.1719" style="28" customWidth="1"/>
-    <col min="7" max="7" width="24.1719" style="28" customWidth="1"/>
-    <col min="8" max="8" width="54.3516" style="28" customWidth="1"/>
-    <col min="9" max="9" width="11" style="28" customWidth="1"/>
-    <col min="10" max="16384" width="11" style="28" customWidth="1"/>
+    <col min="1" max="1" width="30.6719" style="29" customWidth="1"/>
+    <col min="2" max="2" width="35" style="29" customWidth="1"/>
+    <col min="3" max="3" width="14.5" style="29" customWidth="1"/>
+    <col min="4" max="4" width="67.3516" style="29" customWidth="1"/>
+    <col min="5" max="5" width="25.8516" style="29" customWidth="1"/>
+    <col min="6" max="6" width="34.1719" style="29" customWidth="1"/>
+    <col min="7" max="7" width="24.1719" style="29" customWidth="1"/>
+    <col min="8" max="8" width="54.3516" style="29" customWidth="1"/>
+    <col min="9" max="9" width="11" style="29" customWidth="1"/>
+    <col min="10" max="16384" width="11" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="17" customHeight="1">
@@ -7783,16 +7818,16 @@
     </row>
     <row r="3" ht="17" customHeight="1">
       <c r="A3" t="s" s="11">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="B3" t="s" s="11">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C3" t="s" s="11">
         <v>15</v>
       </c>
       <c r="D3" t="s" s="11">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="E3" t="s" s="11">
         <v>17</v>
@@ -7804,7 +7839,7 @@
         <v>18</v>
       </c>
       <c r="H3" t="s" s="11">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="I3" s="3"/>
     </row>

--- a/docs/rest-api.xlsx
+++ b/docs/rest-api.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="9"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="6"/>
   </bookViews>
   <sheets>
     <sheet name="UserController" sheetId="1" state="visible" r:id="rId3"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="854" uniqueCount="252">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="856" uniqueCount="253">
   <si>
     <t xml:space="preserve">URI-Template</t>
   </si>
@@ -442,6 +442,15 @@
     <t xml:space="preserve">Boolean</t>
   </si>
   <si>
+    <t xml:space="preserve">channels</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Set&lt;NotificationType&gt;</t>
+  </si>
+  <si>
+    <t xml:space="preserve">channels?</t>
+  </si>
+  <si>
     <t xml:space="preserve">enabled</t>
   </si>
   <si>
@@ -668,12 +677,6 @@
   </si>
   <si>
     <t xml:space="preserve">userId</t>
-  </si>
-  <si>
-    <t xml:space="preserve">channels</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Set&lt;NotificationType&gt;</t>
   </si>
   <si>
     <t xml:space="preserve">Notification</t>
@@ -831,7 +834,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -842,6 +845,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
         <bgColor rgb="FFFFFFCC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor rgb="FFFFFF00"/>
       </patternFill>
     </fill>
   </fills>
@@ -984,7 +993,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="39">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1073,6 +1082,38 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="5" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="6" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="7" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="14" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1090,6 +1131,18 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1327,7 +1380,7 @@
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="28.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="4" t="s">
         <v>8</v>
       </c>
@@ -1566,32 +1619,32 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="22"/>
-      <c r="B1" s="23"/>
-      <c r="C1" s="23"/>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
-      <c r="M1" s="23"/>
-      <c r="N1" s="23"/>
-      <c r="O1" s="23"/>
-      <c r="P1" s="23"/>
-      <c r="Q1" s="23"/>
-      <c r="R1" s="23"/>
-      <c r="S1" s="23"/>
-      <c r="T1" s="23"/>
-      <c r="U1" s="23"/>
-      <c r="V1" s="23"/>
+      <c r="A1" s="30"/>
+      <c r="B1" s="31"/>
+      <c r="C1" s="31"/>
+      <c r="D1" s="31"/>
+      <c r="E1" s="31"/>
+      <c r="F1" s="31"/>
+      <c r="G1" s="31"/>
+      <c r="H1" s="31"/>
+      <c r="I1" s="31"/>
+      <c r="J1" s="31"/>
+      <c r="K1" s="31"/>
+      <c r="L1" s="31"/>
+      <c r="M1" s="31"/>
+      <c r="N1" s="31"/>
+      <c r="O1" s="31"/>
+      <c r="P1" s="31"/>
+      <c r="Q1" s="31"/>
+      <c r="R1" s="31"/>
+      <c r="S1" s="31"/>
+      <c r="T1" s="31"/>
+      <c r="U1" s="31"/>
+      <c r="V1" s="31"/>
       <c r="W1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="29.55" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="32" t="s">
         <v>105</v>
       </c>
       <c r="B2" s="3"/>
@@ -1661,33 +1714,33 @@
       <c r="W3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="25" t="s">
+      <c r="A4" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B4" s="25" t="s">
+      <c r="B4" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="C4" s="25" t="s">
+      <c r="C4" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D4" s="3"/>
-      <c r="E4" s="25" t="s">
+      <c r="E4" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F4" s="25" t="s">
+      <c r="F4" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="25" t="s">
+      <c r="G4" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H4" s="3"/>
-      <c r="I4" s="25" t="s">
+      <c r="I4" s="33" t="s">
         <v>113</v>
       </c>
-      <c r="J4" s="25" t="s">
+      <c r="J4" s="33" t="s">
         <v>112</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L4" s="3"/>
@@ -1705,26 +1758,26 @@
     </row>
     <row r="5" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3"/>
-      <c r="B5" s="25" t="s">
+      <c r="B5" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C5" s="25" t="s">
+      <c r="C5" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-      <c r="F5" s="25" t="s">
+      <c r="F5" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="33" t="s">
         <v>116</v>
       </c>
       <c r="H5" s="3"/>
       <c r="I5" s="3"/>
-      <c r="J5" s="25" t="s">
+      <c r="J5" s="33" t="s">
         <v>115</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="K5" s="33" t="s">
         <v>116</v>
       </c>
       <c r="L5" s="3"/>
@@ -1746,10 +1799,10 @@
       <c r="C6" s="3"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-      <c r="F6" s="25" t="s">
+      <c r="F6" s="33" t="s">
         <v>117</v>
       </c>
-      <c r="G6" s="25" t="s">
+      <c r="G6" s="33" t="s">
         <v>40</v>
       </c>
       <c r="H6" s="3"/>
@@ -1795,7 +1848,7 @@
       <c r="W7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="24" t="s">
+      <c r="A8" s="32" t="s">
         <v>118</v>
       </c>
       <c r="B8" s="3"/>
@@ -1871,43 +1924,43 @@
       <c r="W9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B10" s="25" t="s">
+      <c r="B10" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="C10" s="25" t="s">
+      <c r="C10" s="33" t="s">
         <v>120</v>
       </c>
       <c r="D10" s="3"/>
-      <c r="E10" s="25" t="s">
+      <c r="E10" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F10" s="25" t="s">
+      <c r="F10" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="G10" s="25" t="s">
+      <c r="G10" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H10" s="3"/>
-      <c r="I10" s="25" t="s">
+      <c r="I10" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="J10" s="25" t="s">
+      <c r="J10" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="K10" s="25" t="s">
+      <c r="K10" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L10" s="3"/>
-      <c r="M10" s="25" t="s">
+      <c r="M10" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="N10" s="25" t="s">
+      <c r="N10" s="33" t="s">
         <v>121</v>
       </c>
-      <c r="O10" s="25" t="s">
+      <c r="O10" s="33" t="s">
         <v>111</v>
       </c>
       <c r="P10" s="3"/>
@@ -1921,34 +1974,34 @@
     </row>
     <row r="11" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="3"/>
-      <c r="B11" s="25" t="s">
+      <c r="B11" s="33" t="s">
         <v>122</v>
       </c>
-      <c r="C11" s="25" t="s">
+      <c r="C11" s="33" t="s">
         <v>120</v>
       </c>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-      <c r="F11" s="25" t="s">
+      <c r="F11" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="G11" s="25" t="s">
+      <c r="G11" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H11" s="3"/>
       <c r="I11" s="3"/>
-      <c r="J11" s="25" t="s">
+      <c r="J11" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="K11" s="25" t="s">
+      <c r="K11" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L11" s="3"/>
       <c r="M11" s="3"/>
-      <c r="N11" s="25" t="s">
+      <c r="N11" s="33" t="s">
         <v>124</v>
       </c>
-      <c r="O11" s="25" t="s">
+      <c r="O11" s="33" t="s">
         <v>111</v>
       </c>
       <c r="P11" s="3"/>
@@ -1962,34 +2015,34 @@
     </row>
     <row r="12" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="3"/>
-      <c r="B12" s="25" t="s">
+      <c r="B12" s="33" t="s">
         <v>125</v>
       </c>
-      <c r="C12" s="25" t="s">
+      <c r="C12" s="33" t="s">
         <v>116</v>
       </c>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-      <c r="F12" s="25" t="s">
+      <c r="F12" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G12" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H12" s="3"/>
       <c r="I12" s="3"/>
-      <c r="J12" s="25" t="s">
+      <c r="J12" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="K12" s="25" t="s">
+      <c r="K12" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L12" s="3"/>
       <c r="M12" s="3"/>
-      <c r="N12" s="25" t="s">
+      <c r="N12" s="33" t="s">
         <v>127</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="33" t="s">
         <v>111</v>
       </c>
       <c r="P12" s="3"/>
@@ -2003,34 +2056,34 @@
     </row>
     <row r="13" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="3"/>
-      <c r="B13" s="25" t="s">
+      <c r="B13" s="33" t="s">
         <v>128</v>
       </c>
-      <c r="C13" s="25" t="s">
+      <c r="C13" s="33" t="s">
         <v>120</v>
       </c>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-      <c r="F13" s="25" t="s">
+      <c r="F13" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="G13" s="25" t="s">
+      <c r="G13" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H13" s="3"/>
       <c r="I13" s="3"/>
-      <c r="J13" s="25" t="s">
+      <c r="J13" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="K13" s="25" t="s">
+      <c r="K13" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L13" s="3"/>
       <c r="M13" s="3"/>
-      <c r="N13" s="25" t="s">
+      <c r="N13" s="33" t="s">
         <v>130</v>
       </c>
-      <c r="O13" s="25" t="s">
+      <c r="O13" s="33" t="s">
         <v>111</v>
       </c>
       <c r="P13" s="3"/>
@@ -2044,34 +2097,34 @@
     </row>
     <row r="14" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="3"/>
-      <c r="B14" s="25" t="s">
+      <c r="B14" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="C14" s="25" t="s">
+      <c r="C14" s="33" t="s">
         <v>116</v>
       </c>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-      <c r="F14" s="25" t="s">
+      <c r="F14" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G14" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="J14" s="25" t="s">
+      <c r="J14" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="K14" s="25" t="s">
+      <c r="K14" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L14" s="3"/>
       <c r="M14" s="3"/>
-      <c r="N14" s="25" t="s">
+      <c r="N14" s="33" t="s">
         <v>132</v>
       </c>
-      <c r="O14" s="25" t="s">
+      <c r="O14" s="33" t="s">
         <v>133</v>
       </c>
       <c r="P14" s="3"/>
@@ -2085,34 +2138,34 @@
     </row>
     <row r="15" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="3"/>
-      <c r="B15" s="25" t="s">
+      <c r="B15" s="33" t="s">
         <v>110</v>
       </c>
-      <c r="C15" s="25" t="s">
+      <c r="C15" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-      <c r="F15" s="25" t="s">
+      <c r="F15" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G15" s="33" t="s">
         <v>133</v>
       </c>
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="J15" s="25" t="s">
+      <c r="J15" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="K15" s="25" t="s">
+      <c r="K15" s="33" t="s">
         <v>133</v>
       </c>
       <c r="L15" s="3"/>
       <c r="M15" s="3"/>
-      <c r="N15" s="25" t="s">
+      <c r="N15" s="33" t="s">
         <v>135</v>
       </c>
-      <c r="O15" s="25" t="s">
+      <c r="O15" s="33" t="s">
         <v>136</v>
       </c>
       <c r="P15" s="3"/>
@@ -2126,24 +2179,36 @@
     </row>
     <row r="16" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="3"/>
-      <c r="B16" s="25" t="s">
+      <c r="B16" s="33" t="s">
         <v>123</v>
       </c>
-      <c r="C16" s="25" t="s">
+      <c r="C16" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-      <c r="F16" s="3"/>
-      <c r="G16" s="3"/>
+      <c r="F16" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>138</v>
+      </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3"/>
+      <c r="J16" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="K16" s="33" t="s">
+        <v>138</v>
+      </c>
       <c r="L16" s="3"/>
       <c r="M16" s="3"/>
-      <c r="N16" s="3"/>
-      <c r="O16" s="3"/>
+      <c r="N16" s="33" t="s">
+        <v>139</v>
+      </c>
+      <c r="O16" s="33" t="s">
+        <v>138</v>
+      </c>
       <c r="P16" s="3"/>
       <c r="Q16" s="3"/>
       <c r="R16" s="3"/>
@@ -2155,10 +2220,10 @@
     </row>
     <row r="17" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="3"/>
-      <c r="B17" s="25" t="s">
+      <c r="B17" s="33" t="s">
         <v>126</v>
       </c>
-      <c r="C17" s="25" t="s">
+      <c r="C17" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D17" s="3"/>
@@ -2184,10 +2249,10 @@
     </row>
     <row r="18" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="3"/>
-      <c r="B18" s="25" t="s">
+      <c r="B18" s="33" t="s">
         <v>129</v>
       </c>
-      <c r="C18" s="25" t="s">
+      <c r="C18" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D18" s="3"/>
@@ -2213,10 +2278,10 @@
     </row>
     <row r="19" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="3"/>
-      <c r="B19" s="25" t="s">
+      <c r="B19" s="33" t="s">
         <v>114</v>
       </c>
-      <c r="C19" s="25" t="s">
+      <c r="C19" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D19" s="3"/>
@@ -2242,11 +2307,11 @@
     </row>
     <row r="20" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="3"/>
-      <c r="B20" s="25" t="s">
-        <v>137</v>
-      </c>
-      <c r="C20" s="25" t="s">
-        <v>138</v>
+      <c r="B20" s="33" t="s">
+        <v>140</v>
+      </c>
+      <c r="C20" s="33" t="s">
+        <v>141</v>
       </c>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
@@ -2271,10 +2336,10 @@
     </row>
     <row r="21" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="3"/>
-      <c r="B21" s="25" t="s">
+      <c r="B21" s="33" t="s">
         <v>134</v>
       </c>
-      <c r="C21" s="25" t="s">
+      <c r="C21" s="33" t="s">
         <v>133</v>
       </c>
       <c r="D21" s="3"/>
@@ -2298,10 +2363,14 @@
       <c r="V21" s="3"/>
       <c r="W21" s="3"/>
     </row>
-    <row r="22" customFormat="false" ht="70.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="22" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="3"/>
-      <c r="B22" s="3"/>
-      <c r="C22" s="3"/>
+      <c r="B22" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="C22" s="33" t="s">
+        <v>138</v>
+      </c>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
       <c r="F22" s="3"/>
@@ -2323,10 +2392,8 @@
       <c r="V22" s="3"/>
       <c r="W22" s="3"/>
     </row>
-    <row r="23" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="24" t="s">
-        <v>139</v>
-      </c>
+    <row r="23" customFormat="false" ht="70.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="3"/>
@@ -2350,110 +2417,82 @@
       <c r="V23" s="3"/>
       <c r="W23" s="3"/>
     </row>
-    <row r="24" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>107</v>
-      </c>
+    <row r="24" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A24" s="32" t="s">
+        <v>142</v>
+      </c>
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
       <c r="D24" s="3"/>
-      <c r="E24" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="F24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G24" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="E24" s="3"/>
+      <c r="F24" s="3"/>
+      <c r="G24" s="3"/>
       <c r="H24" s="3"/>
-      <c r="I24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="J24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K24" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="I24" s="3"/>
+      <c r="J24" s="3"/>
+      <c r="K24" s="3"/>
       <c r="L24" s="3"/>
-      <c r="M24" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="N24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O24" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="M24" s="3"/>
+      <c r="N24" s="3"/>
+      <c r="O24" s="3"/>
       <c r="P24" s="3"/>
-      <c r="Q24" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="R24" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="S24" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="Q24" s="3"/>
+      <c r="R24" s="3"/>
+      <c r="S24" s="3"/>
       <c r="T24" s="3"/>
       <c r="U24" s="3"/>
       <c r="V24" s="3"/>
       <c r="W24" s="3"/>
     </row>
     <row r="25" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B25" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="C25" s="25" t="s">
-        <v>120</v>
+      <c r="A25" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C25" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="D25" s="3"/>
-      <c r="E25" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="F25" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="G25" s="25" t="s">
-        <v>111</v>
+      <c r="E25" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="F25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G25" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="H25" s="3"/>
-      <c r="I25" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="J25" s="25" t="s">
+      <c r="I25" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="J25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K25" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="L25" s="3"/>
+      <c r="M25" s="2" t="s">
         <v>143</v>
       </c>
-      <c r="K25" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="L25" s="3"/>
-      <c r="M25" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="N25" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="O25" s="25" t="s">
-        <v>120</v>
+      <c r="N25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O25" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="P25" s="3"/>
-      <c r="Q25" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="R25" s="25" t="s">
+      <c r="Q25" s="2" t="s">
         <v>144</v>
       </c>
-      <c r="S25" s="25" t="s">
-        <v>145</v>
+      <c r="R25" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="S25" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="T25" s="3"/>
       <c r="U25" s="3"/>
@@ -2461,44 +2500,54 @@
       <c r="W25" s="3"/>
     </row>
     <row r="26" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="3"/>
-      <c r="B26" s="25" t="s">
-        <v>142</v>
-      </c>
-      <c r="C26" s="25" t="s">
+      <c r="A26" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B26" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="C26" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="D26" s="3"/>
+      <c r="E26" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F26" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="G26" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="D26" s="3"/>
-      <c r="E26" s="3"/>
-      <c r="F26" s="25" t="s">
+      <c r="H26" s="3"/>
+      <c r="I26" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="J26" s="33" t="s">
         <v>146</v>
       </c>
-      <c r="G26" s="25" t="s">
+      <c r="K26" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-      <c r="J26" s="25" t="s">
+      <c r="L26" s="3"/>
+      <c r="M26" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="N26" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="O26" s="33" t="s">
+        <v>120</v>
+      </c>
+      <c r="P26" s="3"/>
+      <c r="Q26" s="33" t="s">
+        <v>113</v>
+      </c>
+      <c r="R26" s="33" t="s">
         <v>147</v>
       </c>
-      <c r="K26" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="L26" s="3"/>
-      <c r="M26" s="3"/>
-      <c r="N26" s="25" t="s">
+      <c r="S26" s="33" t="s">
         <v>148</v>
-      </c>
-      <c r="O26" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="P26" s="3"/>
-      <c r="Q26" s="3"/>
-      <c r="R26" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="S26" s="25" t="s">
-        <v>150</v>
       </c>
       <c r="T26" s="3"/>
       <c r="U26" s="3"/>
@@ -2507,43 +2556,43 @@
     </row>
     <row r="27" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="3"/>
-      <c r="B27" s="25" t="s">
-        <v>146</v>
-      </c>
-      <c r="C27" s="25" t="s">
+      <c r="B27" s="33" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-      <c r="F27" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="G27" s="25" t="s">
-        <v>145</v>
+      <c r="F27" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="G27" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
-      <c r="J27" s="25" t="s">
-        <v>151</v>
-      </c>
-      <c r="K27" s="25" t="s">
-        <v>145</v>
+      <c r="J27" s="33" t="s">
+        <v>150</v>
+      </c>
+      <c r="K27" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="L27" s="3"/>
       <c r="M27" s="3"/>
-      <c r="N27" s="25" t="s">
-        <v>152</v>
-      </c>
-      <c r="O27" s="25" t="s">
-        <v>153</v>
+      <c r="N27" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="O27" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="P27" s="3"/>
       <c r="Q27" s="3"/>
-      <c r="R27" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="S27" s="25" t="s">
-        <v>145</v>
+      <c r="R27" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="S27" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="T27" s="3"/>
       <c r="U27" s="3"/>
@@ -2552,43 +2601,43 @@
     </row>
     <row r="28" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="3"/>
-      <c r="B28" s="25" t="s">
-        <v>144</v>
-      </c>
-      <c r="C28" s="25" t="s">
-        <v>145</v>
+      <c r="B28" s="33" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-      <c r="F28" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="G28" s="25" t="s">
-        <v>150</v>
+      <c r="F28" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="G28" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="J28" s="25" t="s">
-        <v>155</v>
-      </c>
-      <c r="K28" s="25" t="s">
-        <v>150</v>
+      <c r="J28" s="33" t="s">
+        <v>154</v>
+      </c>
+      <c r="K28" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="L28" s="3"/>
       <c r="M28" s="3"/>
-      <c r="N28" s="25" t="s">
+      <c r="N28" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="O28" s="33" t="s">
         <v>156</v>
-      </c>
-      <c r="O28" s="25" t="s">
-        <v>141</v>
       </c>
       <c r="P28" s="3"/>
       <c r="Q28" s="3"/>
-      <c r="R28" s="25" t="s">
+      <c r="R28" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="S28" s="25" t="s">
-        <v>138</v>
+      <c r="S28" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="T28" s="3"/>
       <c r="U28" s="3"/>
@@ -2597,40 +2646,44 @@
     </row>
     <row r="29" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="3"/>
-      <c r="B29" s="25" t="s">
-        <v>149</v>
-      </c>
-      <c r="C29" s="25" t="s">
-        <v>150</v>
+      <c r="B29" s="33" t="s">
+        <v>147</v>
+      </c>
+      <c r="C29" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-      <c r="F29" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="G29" s="25" t="s">
-        <v>145</v>
+      <c r="F29" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="G29" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="J29" s="25" t="s">
+      <c r="J29" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="K29" s="25" t="s">
-        <v>145</v>
+      <c r="K29" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="L29" s="3"/>
       <c r="M29" s="3"/>
-      <c r="N29" s="25" t="s">
+      <c r="N29" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="O29" s="25" t="s">
-        <v>141</v>
+      <c r="O29" s="33" t="s">
+        <v>144</v>
       </c>
       <c r="P29" s="3"/>
       <c r="Q29" s="3"/>
-      <c r="R29" s="3"/>
-      <c r="S29" s="3"/>
+      <c r="R29" s="33" t="s">
+        <v>160</v>
+      </c>
+      <c r="S29" s="33" t="s">
+        <v>141</v>
+      </c>
       <c r="T29" s="3"/>
       <c r="U29" s="3"/>
       <c r="V29" s="3"/>
@@ -2638,27 +2691,35 @@
     </row>
     <row r="30" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="3"/>
-      <c r="B30" s="25" t="s">
-        <v>154</v>
-      </c>
-      <c r="C30" s="25" t="s">
-        <v>145</v>
+      <c r="B30" s="33" t="s">
+        <v>152</v>
+      </c>
+      <c r="C30" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-      <c r="F30" s="3"/>
-      <c r="G30" s="3"/>
+      <c r="F30" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="G30" s="33" t="s">
+        <v>148</v>
+      </c>
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
-      <c r="J30" s="3"/>
-      <c r="K30" s="3"/>
+      <c r="J30" s="33" t="s">
+        <v>161</v>
+      </c>
+      <c r="K30" s="33" t="s">
+        <v>148</v>
+      </c>
       <c r="L30" s="3"/>
       <c r="M30" s="3"/>
-      <c r="N30" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="O30" s="25" t="s">
-        <v>116</v>
+      <c r="N30" s="33" t="s">
+        <v>162</v>
+      </c>
+      <c r="O30" s="33" t="s">
+        <v>144</v>
       </c>
       <c r="P30" s="3"/>
       <c r="Q30" s="3"/>
@@ -2671,11 +2732,11 @@
     </row>
     <row r="31" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="3"/>
-      <c r="B31" s="25" t="s">
-        <v>161</v>
-      </c>
-      <c r="C31" s="25" t="s">
-        <v>145</v>
+      <c r="B31" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="C31" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
@@ -2687,8 +2748,12 @@
       <c r="K31" s="3"/>
       <c r="L31" s="3"/>
       <c r="M31" s="3"/>
-      <c r="N31" s="3"/>
-      <c r="O31" s="3"/>
+      <c r="N31" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="O31" s="33" t="s">
+        <v>116</v>
+      </c>
       <c r="P31" s="3"/>
       <c r="Q31" s="3"/>
       <c r="R31" s="3"/>
@@ -2700,11 +2765,11 @@
     </row>
     <row r="32" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3"/>
-      <c r="B32" s="25" t="s">
-        <v>162</v>
-      </c>
-      <c r="C32" s="25" t="s">
-        <v>163</v>
+      <c r="B32" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="C32" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
@@ -2729,11 +2794,11 @@
     </row>
     <row r="33" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3"/>
-      <c r="B33" s="25" t="s">
-        <v>164</v>
-      </c>
-      <c r="C33" s="25" t="s">
-        <v>138</v>
+      <c r="B33" s="33" t="s">
+        <v>165</v>
+      </c>
+      <c r="C33" s="33" t="s">
+        <v>166</v>
       </c>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
@@ -2757,14 +2822,12 @@
       <c r="W33" s="3"/>
     </row>
     <row r="34" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="25" t="s">
-        <v>165</v>
-      </c>
-      <c r="B34" s="25" t="s">
-        <v>166</v>
-      </c>
-      <c r="C34" s="25" t="s">
-        <v>111</v>
+      <c r="A34" s="3"/>
+      <c r="B34" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="C34" s="33" t="s">
+        <v>141</v>
       </c>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
@@ -2788,12 +2851,14 @@
       <c r="W34" s="3"/>
     </row>
     <row r="35" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="3"/>
-      <c r="B35" s="25" t="s">
-        <v>167</v>
-      </c>
-      <c r="C35" s="25" t="s">
-        <v>116</v>
+      <c r="A35" s="33" t="s">
+        <v>168</v>
+      </c>
+      <c r="B35" s="33" t="s">
+        <v>169</v>
+      </c>
+      <c r="C35" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
@@ -2818,11 +2883,11 @@
     </row>
     <row r="36" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="3"/>
-      <c r="B36" s="25" t="s">
-        <v>168</v>
-      </c>
-      <c r="C36" s="25" t="s">
-        <v>111</v>
+      <c r="B36" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="C36" s="33" t="s">
+        <v>116</v>
       </c>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
@@ -2847,11 +2912,11 @@
     </row>
     <row r="37" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="3"/>
-      <c r="B37" s="25" t="s">
-        <v>169</v>
-      </c>
-      <c r="C37" s="25" t="s">
-        <v>116</v>
+      <c r="B37" s="33" t="s">
+        <v>171</v>
+      </c>
+      <c r="C37" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
@@ -2874,10 +2939,14 @@
       <c r="V37" s="3"/>
       <c r="W37" s="3"/>
     </row>
-    <row r="38" customFormat="false" ht="70.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="38" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3"/>
-      <c r="B38" s="3"/>
-      <c r="C38" s="3"/>
+      <c r="B38" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="C38" s="33" t="s">
+        <v>116</v>
+      </c>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
       <c r="F38" s="3"/>
@@ -2899,10 +2968,8 @@
       <c r="V38" s="3"/>
       <c r="W38" s="3"/>
     </row>
-    <row r="39" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="24" t="s">
-        <v>170</v>
-      </c>
+    <row r="39" customFormat="false" ht="70.95" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
       <c r="D39" s="3"/>
@@ -2926,46 +2993,24 @@
       <c r="V39" s="3"/>
       <c r="W39" s="3"/>
     </row>
-    <row r="40" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="2" t="s">
-        <v>55</v>
-      </c>
-      <c r="B40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>107</v>
-      </c>
+    <row r="40" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A40" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
       <c r="D40" s="3"/>
-      <c r="E40" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="F40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="G40" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="E40" s="3"/>
+      <c r="F40" s="3"/>
+      <c r="G40" s="3"/>
       <c r="H40" s="3"/>
-      <c r="I40" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="J40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="K40" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="I40" s="3"/>
+      <c r="J40" s="3"/>
+      <c r="K40" s="3"/>
       <c r="L40" s="3"/>
-      <c r="M40" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="N40" s="2" t="s">
-        <v>106</v>
-      </c>
-      <c r="O40" s="2" t="s">
-        <v>107</v>
-      </c>
+      <c r="M40" s="3"/>
+      <c r="N40" s="3"/>
+      <c r="O40" s="3"/>
       <c r="P40" s="3"/>
       <c r="Q40" s="3"/>
       <c r="R40" s="3"/>
@@ -2976,44 +3021,44 @@
       <c r="W40" s="3"/>
     </row>
     <row r="41" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="B41" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C41" s="25" t="s">
-        <v>173</v>
+      <c r="A41" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="D41" s="3"/>
-      <c r="E41" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="F41" s="25" t="s">
-        <v>119</v>
-      </c>
-      <c r="G41" s="25" t="s">
-        <v>120</v>
+      <c r="E41" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="F41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="G41" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="H41" s="3"/>
-      <c r="I41" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="J41" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="K41" s="25" t="s">
-        <v>120</v>
+      <c r="I41" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="J41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="L41" s="3"/>
-      <c r="M41" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="N41" s="25" t="s">
-        <v>174</v>
-      </c>
-      <c r="O41" s="25" t="s">
-        <v>150</v>
+      <c r="M41" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="N41" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="O41" s="2" t="s">
+        <v>107</v>
       </c>
       <c r="P41" s="3"/>
       <c r="Q41" s="3"/>
@@ -3025,32 +3070,44 @@
       <c r="W41" s="3"/>
     </row>
     <row r="42" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="3"/>
-      <c r="B42" s="3"/>
-      <c r="C42" s="3"/>
+      <c r="A42" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="B42" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C42" s="33" t="s">
+        <v>176</v>
+      </c>
       <c r="D42" s="3"/>
-      <c r="E42" s="3"/>
-      <c r="F42" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="G42" s="25" t="s">
+      <c r="E42" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="F42" s="33" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="33" t="s">
         <v>120</v>
       </c>
       <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-      <c r="J42" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="K42" s="25" t="s">
-        <v>150</v>
+      <c r="I42" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="J42" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="K42" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="L42" s="3"/>
-      <c r="M42" s="3"/>
-      <c r="N42" s="25" t="s">
-        <v>176</v>
-      </c>
-      <c r="O42" s="25" t="s">
-        <v>145</v>
+      <c r="M42" s="33" t="s">
+        <v>109</v>
+      </c>
+      <c r="N42" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="O42" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="P42" s="3"/>
       <c r="Q42" s="3"/>
@@ -3067,24 +3124,28 @@
       <c r="C43" s="3"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-      <c r="F43" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="G43" s="25" t="s">
-        <v>150</v>
+      <c r="F43" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="G43" s="33" t="s">
+        <v>120</v>
       </c>
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="J43" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="K43" s="25" t="s">
-        <v>145</v>
+      <c r="J43" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="K43" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="L43" s="3"/>
       <c r="M43" s="3"/>
-      <c r="N43" s="3"/>
-      <c r="O43" s="3"/>
+      <c r="N43" s="33" t="s">
+        <v>179</v>
+      </c>
+      <c r="O43" s="33" t="s">
+        <v>148</v>
+      </c>
       <c r="P43" s="3"/>
       <c r="Q43" s="3"/>
       <c r="R43" s="3"/>
@@ -3100,16 +3161,20 @@
       <c r="C44" s="3"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-      <c r="F44" s="25" t="s">
+      <c r="F44" s="33" t="s">
         <v>178</v>
       </c>
-      <c r="G44" s="25" t="s">
-        <v>145</v>
+      <c r="G44" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="J44" s="3"/>
-      <c r="K44" s="3"/>
+      <c r="J44" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="K44" s="33" t="s">
+        <v>148</v>
+      </c>
       <c r="L44" s="3"/>
       <c r="M44" s="3"/>
       <c r="N44" s="3"/>
@@ -3129,11 +3194,11 @@
       <c r="C45" s="3"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-      <c r="F45" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="G45" s="25" t="s">
-        <v>145</v>
+      <c r="F45" s="33" t="s">
+        <v>181</v>
+      </c>
+      <c r="G45" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
@@ -3152,14 +3217,18 @@
       <c r="V45" s="3"/>
       <c r="W45" s="3"/>
     </row>
-    <row r="46" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="46" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="3"/>
+      <c r="F46" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="G46" s="33" t="s">
+        <v>148</v>
+      </c>
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
       <c r="J46" s="3"/>
@@ -3177,10 +3246,8 @@
       <c r="V46" s="3"/>
       <c r="W46" s="3"/>
     </row>
-    <row r="47" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="24" t="s">
-        <v>179</v>
-      </c>
+    <row r="47" customFormat="false" ht="70.1" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
       <c r="D47" s="3"/>
@@ -3204,115 +3271,105 @@
       <c r="V47" s="3"/>
       <c r="W47" s="3"/>
     </row>
-    <row r="48" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="2" t="s">
+    <row r="48" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A48" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="3"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="3"/>
+      <c r="H48" s="3"/>
+      <c r="I48" s="3"/>
+      <c r="J48" s="3"/>
+      <c r="K48" s="3"/>
+      <c r="L48" s="3"/>
+      <c r="M48" s="3"/>
+      <c r="N48" s="3"/>
+      <c r="O48" s="3"/>
+      <c r="P48" s="3"/>
+      <c r="Q48" s="3"/>
+      <c r="R48" s="3"/>
+      <c r="S48" s="3"/>
+      <c r="T48" s="3"/>
+      <c r="U48" s="3"/>
+      <c r="V48" s="3"/>
+      <c r="W48" s="3"/>
+    </row>
+    <row r="49" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A49" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="B48" s="2" t="s">
+      <c r="B49" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C48" s="2" t="s">
+      <c r="C49" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D48" s="3"/>
-      <c r="E48" s="2" t="s">
+      <c r="D49" s="3"/>
+      <c r="E49" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="F48" s="2" t="s">
+      <c r="F49" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G48" s="2" t="s">
+      <c r="G49" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H48" s="3"/>
-      <c r="I48" s="2" t="s">
-        <v>180</v>
-      </c>
-      <c r="J48" s="2" t="s">
+      <c r="H49" s="3"/>
+      <c r="I49" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="J49" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K48" s="2" t="s">
+      <c r="K49" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="L48" s="3"/>
-      <c r="M48" s="26"/>
-      <c r="N48" s="26"/>
-      <c r="O48" s="26"/>
-      <c r="P48" s="3"/>
-      <c r="Q48" s="26"/>
-      <c r="R48" s="26"/>
-      <c r="S48" s="26"/>
-      <c r="T48" s="3"/>
-      <c r="U48" s="26"/>
-      <c r="V48" s="26"/>
-      <c r="W48" s="26"/>
-    </row>
-    <row r="49" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="25" t="s">
+      <c r="L49" s="3"/>
+      <c r="M49" s="34"/>
+      <c r="N49" s="34"/>
+      <c r="O49" s="34"/>
+      <c r="P49" s="3"/>
+      <c r="Q49" s="34"/>
+      <c r="R49" s="34"/>
+      <c r="S49" s="34"/>
+      <c r="T49" s="3"/>
+      <c r="U49" s="34"/>
+      <c r="V49" s="34"/>
+      <c r="W49" s="34"/>
+    </row>
+    <row r="50" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A50" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B49" s="25" t="s">
-        <v>181</v>
-      </c>
-      <c r="C49" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="D49" s="3"/>
-      <c r="E49" s="25" t="s">
+      <c r="B50" s="33" t="s">
+        <v>184</v>
+      </c>
+      <c r="C50" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="D50" s="3"/>
+      <c r="E50" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F49" s="25" t="s">
-        <v>182</v>
-      </c>
-      <c r="G49" s="25" t="s">
+      <c r="F50" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="G50" s="33" t="s">
         <v>86</v>
       </c>
-      <c r="H49" s="3"/>
-      <c r="I49" s="25" t="s">
+      <c r="H50" s="3"/>
+      <c r="I50" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="J49" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="K49" s="25" t="s">
+      <c r="J50" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="K50" s="33" t="s">
         <v>120</v>
-      </c>
-      <c r="L49" s="3"/>
-      <c r="M49" s="3"/>
-      <c r="N49" s="3"/>
-      <c r="O49" s="3"/>
-      <c r="P49" s="3"/>
-      <c r="Q49" s="3"/>
-      <c r="R49" s="3"/>
-      <c r="S49" s="3"/>
-      <c r="T49" s="3"/>
-      <c r="U49" s="3"/>
-      <c r="V49" s="3"/>
-      <c r="W49" s="3"/>
-    </row>
-    <row r="50" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="3"/>
-      <c r="B50" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C50" s="25" t="s">
-        <v>184</v>
-      </c>
-      <c r="D50" s="3"/>
-      <c r="E50" s="3"/>
-      <c r="F50" s="25" t="s">
-        <v>185</v>
-      </c>
-      <c r="G50" s="25" t="s">
-        <v>86</v>
-      </c>
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-      <c r="J50" s="25" t="s">
-        <v>175</v>
-      </c>
-      <c r="K50" s="25" t="s">
-        <v>150</v>
       </c>
       <c r="L50" s="3"/>
       <c r="M50" s="3"/>
@@ -3329,23 +3386,27 @@
     </row>
     <row r="51" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="3"/>
-      <c r="B51" s="25" t="s">
+      <c r="B51" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="C51" s="25" t="s">
-        <v>145</v>
+      <c r="C51" s="33" t="s">
+        <v>187</v>
       </c>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="3"/>
+      <c r="F51" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="G51" s="33" t="s">
+        <v>86</v>
+      </c>
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="J51" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="K51" s="25" t="s">
-        <v>145</v>
+      <c r="J51" s="33" t="s">
+        <v>178</v>
+      </c>
+      <c r="K51" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="L51" s="3"/>
       <c r="M51" s="3"/>
@@ -3362,11 +3423,11 @@
     </row>
     <row r="52" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="3"/>
-      <c r="B52" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C52" s="25" t="s">
-        <v>116</v>
+      <c r="B52" s="33" t="s">
+        <v>189</v>
+      </c>
+      <c r="C52" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
@@ -3374,11 +3435,11 @@
       <c r="G52" s="3"/>
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="J52" s="25" t="s">
-        <v>177</v>
-      </c>
-      <c r="K52" s="25" t="s">
-        <v>145</v>
+      <c r="J52" s="33" t="s">
+        <v>190</v>
+      </c>
+      <c r="K52" s="33" t="s">
+        <v>148</v>
       </c>
       <c r="L52" s="3"/>
       <c r="M52" s="3"/>
@@ -3395,11 +3456,11 @@
     </row>
     <row r="53" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="3"/>
-      <c r="B53" s="25" t="s">
-        <v>172</v>
-      </c>
-      <c r="C53" s="25" t="s">
-        <v>188</v>
+      <c r="B53" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C53" s="33" t="s">
+        <v>116</v>
       </c>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
@@ -3407,8 +3468,12 @@
       <c r="G53" s="3"/>
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="J53" s="3"/>
-      <c r="K53" s="3"/>
+      <c r="J53" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="K53" s="33" t="s">
+        <v>148</v>
+      </c>
       <c r="L53" s="3"/>
       <c r="M53" s="3"/>
       <c r="N53" s="3"/>
@@ -3424,11 +3489,11 @@
     </row>
     <row r="54" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="3"/>
-      <c r="B54" s="25" t="s">
-        <v>189</v>
-      </c>
-      <c r="C54" s="25" t="s">
-        <v>120</v>
+      <c r="B54" s="33" t="s">
+        <v>175</v>
+      </c>
+      <c r="C54" s="33" t="s">
+        <v>191</v>
       </c>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
@@ -3453,10 +3518,10 @@
     </row>
     <row r="55" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="3"/>
-      <c r="B55" s="25" t="s">
-        <v>190</v>
-      </c>
-      <c r="C55" s="25" t="s">
+      <c r="B55" s="33" t="s">
+        <v>192</v>
+      </c>
+      <c r="C55" s="33" t="s">
         <v>120</v>
       </c>
       <c r="D55" s="3"/>
@@ -3480,10 +3545,14 @@
       <c r="V55" s="3"/>
       <c r="W55" s="3"/>
     </row>
-    <row r="56" customFormat="false" ht="70.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="56" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="3"/>
-      <c r="B56" s="3"/>
-      <c r="C56" s="3"/>
+      <c r="B56" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="C56" s="33" t="s">
+        <v>120</v>
+      </c>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
       <c r="F56" s="3"/>
@@ -3505,10 +3574,8 @@
       <c r="V56" s="3"/>
       <c r="W56" s="3"/>
     </row>
-    <row r="57" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="24" t="s">
-        <v>191</v>
-      </c>
+    <row r="57" customFormat="false" ht="70.3" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
       <c r="D57" s="3"/>
@@ -3532,95 +3599,89 @@
       <c r="V57" s="3"/>
       <c r="W57" s="3"/>
     </row>
-    <row r="58" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="2" t="s">
+    <row r="58" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="32" t="s">
+        <v>194</v>
+      </c>
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+      <c r="D58" s="3"/>
+      <c r="E58" s="3"/>
+      <c r="F58" s="3"/>
+      <c r="G58" s="3"/>
+      <c r="H58" s="3"/>
+      <c r="I58" s="3"/>
+      <c r="J58" s="3"/>
+      <c r="K58" s="3"/>
+      <c r="L58" s="3"/>
+      <c r="M58" s="3"/>
+      <c r="N58" s="3"/>
+      <c r="O58" s="3"/>
+      <c r="P58" s="3"/>
+      <c r="Q58" s="3"/>
+      <c r="R58" s="3"/>
+      <c r="S58" s="3"/>
+      <c r="T58" s="3"/>
+      <c r="U58" s="3"/>
+      <c r="V58" s="3"/>
+      <c r="W58" s="3"/>
+    </row>
+    <row r="59" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A59" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B58" s="2" t="s">
+      <c r="B59" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C58" s="2" t="s">
+      <c r="C59" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D58" s="3"/>
-      <c r="E58" s="2" t="s">
+      <c r="D59" s="3"/>
+      <c r="E59" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="F58" s="2" t="s">
+      <c r="F59" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G58" s="2" t="s">
+      <c r="G59" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H58" s="3"/>
-      <c r="I58" s="26"/>
-      <c r="J58" s="26"/>
-      <c r="K58" s="26"/>
-      <c r="L58" s="3"/>
-      <c r="M58" s="26"/>
-      <c r="N58" s="26"/>
-      <c r="O58" s="26"/>
-      <c r="P58" s="3"/>
-      <c r="Q58" s="26"/>
-      <c r="R58" s="26"/>
-      <c r="S58" s="26"/>
-      <c r="T58" s="3"/>
-      <c r="U58" s="26"/>
-      <c r="V58" s="26"/>
-      <c r="W58" s="26"/>
-    </row>
-    <row r="59" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="25" t="s">
+      <c r="H59" s="3"/>
+      <c r="I59" s="34"/>
+      <c r="J59" s="34"/>
+      <c r="K59" s="34"/>
+      <c r="L59" s="3"/>
+      <c r="M59" s="34"/>
+      <c r="N59" s="34"/>
+      <c r="O59" s="34"/>
+      <c r="P59" s="3"/>
+      <c r="Q59" s="34"/>
+      <c r="R59" s="34"/>
+      <c r="S59" s="34"/>
+      <c r="T59" s="3"/>
+      <c r="U59" s="34"/>
+      <c r="V59" s="34"/>
+      <c r="W59" s="34"/>
+    </row>
+    <row r="60" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A60" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B59" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="C59" s="25" t="s">
+      <c r="B60" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="C60" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="D59" s="3"/>
-      <c r="E59" s="25" t="s">
+      <c r="D60" s="3"/>
+      <c r="E60" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F59" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="G59" s="25" t="s">
+      <c r="F60" s="33" t="s">
+        <v>151</v>
+      </c>
+      <c r="G60" s="33" t="s">
         <v>120</v>
-      </c>
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-      <c r="J59" s="3"/>
-      <c r="K59" s="3"/>
-      <c r="L59" s="3"/>
-      <c r="M59" s="3"/>
-      <c r="N59" s="3"/>
-      <c r="O59" s="3"/>
-      <c r="P59" s="3"/>
-      <c r="Q59" s="3"/>
-      <c r="R59" s="3"/>
-      <c r="S59" s="3"/>
-      <c r="T59" s="3"/>
-      <c r="U59" s="3"/>
-      <c r="V59" s="3"/>
-      <c r="W59" s="3"/>
-    </row>
-    <row r="60" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="3"/>
-      <c r="B60" s="25" t="s">
-        <v>192</v>
-      </c>
-      <c r="C60" s="25" t="s">
-        <v>193</v>
-      </c>
-      <c r="D60" s="3"/>
-      <c r="E60" s="3"/>
-      <c r="F60" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="G60" s="25" t="s">
-        <v>150</v>
       </c>
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
@@ -3641,19 +3702,19 @@
     </row>
     <row r="61" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="3"/>
-      <c r="B61" s="25" t="s">
-        <v>194</v>
-      </c>
-      <c r="C61" s="25" t="s">
-        <v>150</v>
+      <c r="B61" s="33" t="s">
+        <v>195</v>
+      </c>
+      <c r="C61" s="33" t="s">
+        <v>196</v>
       </c>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-      <c r="F61" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="G61" s="25" t="s">
-        <v>111</v>
+      <c r="F61" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="G61" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
@@ -3674,16 +3735,20 @@
     </row>
     <row r="62" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="3"/>
-      <c r="B62" s="25" t="s">
-        <v>195</v>
-      </c>
-      <c r="C62" s="25" t="s">
-        <v>111</v>
+      <c r="B62" s="33" t="s">
+        <v>197</v>
+      </c>
+      <c r="C62" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-      <c r="F62" s="3"/>
-      <c r="G62" s="3"/>
+      <c r="F62" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="G62" s="33" t="s">
+        <v>111</v>
+      </c>
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
       <c r="J62" s="3"/>
@@ -3703,11 +3768,11 @@
     </row>
     <row r="63" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="3"/>
-      <c r="B63" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C63" s="25" t="s">
-        <v>116</v>
+      <c r="B63" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="C63" s="33" t="s">
+        <v>111</v>
       </c>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
@@ -3730,10 +3795,14 @@
       <c r="V63" s="3"/>
       <c r="W63" s="3"/>
     </row>
-    <row r="64" customFormat="false" ht="70.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="64" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="3"/>
-      <c r="B64" s="3"/>
-      <c r="C64" s="3"/>
+      <c r="B64" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="C64" s="33" t="s">
+        <v>116</v>
+      </c>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
       <c r="F64" s="3"/>
@@ -3755,10 +3824,8 @@
       <c r="V64" s="3"/>
       <c r="W64" s="3"/>
     </row>
-    <row r="65" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A65" s="24" t="s">
-        <v>196</v>
-      </c>
+    <row r="65" customFormat="false" ht="70.7" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
       <c r="D65" s="3"/>
@@ -3782,114 +3849,104 @@
       <c r="V65" s="3"/>
       <c r="W65" s="3"/>
     </row>
-    <row r="66" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A66" s="2" t="s">
+    <row r="66" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A66" s="32" t="s">
+        <v>199</v>
+      </c>
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+      <c r="D66" s="3"/>
+      <c r="E66" s="3"/>
+      <c r="F66" s="3"/>
+      <c r="G66" s="3"/>
+      <c r="H66" s="3"/>
+      <c r="I66" s="3"/>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3"/>
+      <c r="L66" s="3"/>
+      <c r="M66" s="3"/>
+      <c r="N66" s="3"/>
+      <c r="O66" s="3"/>
+      <c r="P66" s="3"/>
+      <c r="Q66" s="3"/>
+      <c r="R66" s="3"/>
+      <c r="S66" s="3"/>
+      <c r="T66" s="3"/>
+      <c r="U66" s="3"/>
+      <c r="V66" s="3"/>
+      <c r="W66" s="3"/>
+    </row>
+    <row r="67" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A67" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B66" s="2" t="s">
+      <c r="B67" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C66" s="2" t="s">
+      <c r="C67" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="D66" s="3"/>
-      <c r="E66" s="2" t="s">
+      <c r="D67" s="3"/>
+      <c r="E67" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F66" s="2" t="s">
+      <c r="F67" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="G66" s="2" t="s">
+      <c r="G67" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="H66" s="3"/>
-      <c r="I66" s="2" t="s">
+      <c r="H67" s="3"/>
+      <c r="I67" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="J66" s="2" t="s">
+      <c r="J67" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="K66" s="2" t="s">
+      <c r="K67" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="L66" s="3"/>
-      <c r="M66" s="26"/>
-      <c r="N66" s="26"/>
-      <c r="O66" s="26"/>
-      <c r="P66" s="3"/>
-      <c r="Q66" s="26"/>
-      <c r="R66" s="26"/>
-      <c r="S66" s="26"/>
-      <c r="T66" s="3"/>
-      <c r="U66" s="26"/>
-      <c r="V66" s="26"/>
-      <c r="W66" s="26"/>
-    </row>
-    <row r="67" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A67" s="25" t="s">
+      <c r="L67" s="3"/>
+      <c r="M67" s="34"/>
+      <c r="N67" s="34"/>
+      <c r="O67" s="34"/>
+      <c r="P67" s="3"/>
+      <c r="Q67" s="34"/>
+      <c r="R67" s="34"/>
+      <c r="S67" s="34"/>
+      <c r="T67" s="3"/>
+      <c r="U67" s="34"/>
+      <c r="V67" s="34"/>
+      <c r="W67" s="34"/>
+    </row>
+    <row r="68" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A68" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B67" s="25" t="s">
+      <c r="B68" s="33" t="s">
         <v>119</v>
       </c>
-      <c r="C67" s="25" t="s">
+      <c r="C68" s="33" t="s">
         <v>120</v>
       </c>
-      <c r="D67" s="3"/>
-      <c r="E67" s="25" t="s">
+      <c r="D68" s="3"/>
+      <c r="E68" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F67" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="G67" s="25" t="s">
+      <c r="F68" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="G68" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="H67" s="3"/>
-      <c r="I67" s="25" t="s">
+      <c r="H68" s="3"/>
+      <c r="I68" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="J67" s="25" t="s">
-        <v>198</v>
-      </c>
-      <c r="K67" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="L67" s="3"/>
-      <c r="M67" s="3"/>
-      <c r="N67" s="3"/>
-      <c r="O67" s="3"/>
-      <c r="P67" s="3"/>
-      <c r="Q67" s="3"/>
-      <c r="R67" s="3"/>
-      <c r="S67" s="3"/>
-      <c r="T67" s="3"/>
-      <c r="U67" s="3"/>
-      <c r="V67" s="3"/>
-      <c r="W67" s="3"/>
-    </row>
-    <row r="68" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A68" s="3"/>
-      <c r="B68" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="C68" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="D68" s="3"/>
-      <c r="E68" s="3"/>
-      <c r="F68" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="G68" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-      <c r="J68" s="25" t="s">
-        <v>200</v>
-      </c>
-      <c r="K68" s="25" t="s">
+      <c r="J68" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="K68" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L68" s="3"/>
@@ -3907,26 +3964,26 @@
     </row>
     <row r="69" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="3"/>
-      <c r="B69" s="25" t="s">
-        <v>199</v>
-      </c>
-      <c r="C69" s="25" t="s">
+      <c r="B69" s="33" t="s">
+        <v>200</v>
+      </c>
+      <c r="C69" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-      <c r="F69" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="G69" s="25" t="s">
+      <c r="F69" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="G69" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
-      <c r="J69" s="25" t="s">
-        <v>202</v>
-      </c>
-      <c r="K69" s="25" t="s">
+      <c r="J69" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="K69" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L69" s="3"/>
@@ -3944,26 +4001,26 @@
     </row>
     <row r="70" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="3"/>
-      <c r="B70" s="25" t="s">
-        <v>201</v>
-      </c>
-      <c r="C70" s="25" t="s">
+      <c r="B70" s="33" t="s">
+        <v>202</v>
+      </c>
+      <c r="C70" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-      <c r="F70" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="G70" s="25" t="s">
+      <c r="F70" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="G70" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
-      <c r="J70" s="25" t="s">
-        <v>204</v>
-      </c>
-      <c r="K70" s="25" t="s">
+      <c r="J70" s="33" t="s">
+        <v>205</v>
+      </c>
+      <c r="K70" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L70" s="3"/>
@@ -3981,26 +4038,26 @@
     </row>
     <row r="71" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="3"/>
-      <c r="B71" s="25" t="s">
-        <v>203</v>
-      </c>
-      <c r="C71" s="25" t="s">
+      <c r="B71" s="33" t="s">
+        <v>204</v>
+      </c>
+      <c r="C71" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-      <c r="F71" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="G71" s="25" t="s">
+      <c r="F71" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="G71" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
-      <c r="J71" s="25" t="s">
-        <v>206</v>
-      </c>
-      <c r="K71" s="25" t="s">
+      <c r="J71" s="33" t="s">
+        <v>207</v>
+      </c>
+      <c r="K71" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L71" s="3"/>
@@ -4018,26 +4075,26 @@
     </row>
     <row r="72" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="3"/>
-      <c r="B72" s="25" t="s">
-        <v>205</v>
-      </c>
-      <c r="C72" s="25" t="s">
+      <c r="B72" s="33" t="s">
+        <v>206</v>
+      </c>
+      <c r="C72" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-      <c r="F72" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="G72" s="25" t="s">
+      <c r="F72" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="G72" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
-      <c r="J72" s="25" t="s">
-        <v>208</v>
-      </c>
-      <c r="K72" s="25" t="s">
+      <c r="J72" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="K72" s="33" t="s">
         <v>111</v>
       </c>
       <c r="L72" s="3"/>
@@ -4055,20 +4112,28 @@
     </row>
     <row r="73" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="3"/>
-      <c r="B73" s="25" t="s">
-        <v>207</v>
-      </c>
-      <c r="C73" s="25" t="s">
+      <c r="B73" s="33" t="s">
+        <v>208</v>
+      </c>
+      <c r="C73" s="33" t="s">
         <v>111</v>
       </c>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-      <c r="F73" s="3"/>
-      <c r="G73" s="3"/>
+      <c r="F73" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="G73" s="33" t="s">
+        <v>111</v>
+      </c>
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3"/>
+      <c r="J73" s="33" t="s">
+        <v>211</v>
+      </c>
+      <c r="K73" s="33" t="s">
+        <v>111</v>
+      </c>
       <c r="L73" s="3"/>
       <c r="M73" s="3"/>
       <c r="N73" s="3"/>
@@ -4082,10 +4147,14 @@
       <c r="V73" s="3"/>
       <c r="W73" s="3"/>
     </row>
-    <row r="74" customFormat="false" ht="70.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="74" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="3"/>
-      <c r="B74" s="3"/>
-      <c r="C74" s="3"/>
+      <c r="B74" s="33" t="s">
+        <v>210</v>
+      </c>
+      <c r="C74" s="33" t="s">
+        <v>111</v>
+      </c>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
       <c r="F74" s="3"/>
@@ -4107,10 +4176,8 @@
       <c r="V74" s="3"/>
       <c r="W74" s="3"/>
     </row>
-    <row r="75" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A75" s="24" t="s">
-        <v>209</v>
-      </c>
+    <row r="75" customFormat="false" ht="70.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
       <c r="D75" s="3"/>
@@ -4134,114 +4201,104 @@
       <c r="V75" s="3"/>
       <c r="W75" s="3"/>
     </row>
-    <row r="76" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A76" s="2" t="s">
+    <row r="76" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A76" s="35" t="s">
+        <v>212</v>
+      </c>
+      <c r="B76" s="36"/>
+      <c r="C76" s="36"/>
+      <c r="D76" s="36"/>
+      <c r="E76" s="36"/>
+      <c r="F76" s="36"/>
+      <c r="G76" s="36"/>
+      <c r="H76" s="36"/>
+      <c r="I76" s="36"/>
+      <c r="J76" s="36"/>
+      <c r="K76" s="36"/>
+      <c r="L76" s="3"/>
+      <c r="M76" s="3"/>
+      <c r="N76" s="3"/>
+      <c r="O76" s="3"/>
+      <c r="P76" s="3"/>
+      <c r="Q76" s="3"/>
+      <c r="R76" s="3"/>
+      <c r="S76" s="3"/>
+      <c r="T76" s="3"/>
+      <c r="U76" s="3"/>
+      <c r="V76" s="3"/>
+      <c r="W76" s="3"/>
+    </row>
+    <row r="77" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A77" s="22" t="s">
         <v>96</v>
       </c>
-      <c r="B76" s="2" t="s">
+      <c r="B77" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C76" s="2" t="s">
+      <c r="C77" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D76" s="3"/>
-      <c r="E76" s="2" t="s">
+      <c r="D77" s="36"/>
+      <c r="E77" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="F76" s="2" t="s">
+      <c r="F77" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G76" s="2" t="s">
+      <c r="G77" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="H76" s="3"/>
-      <c r="I76" s="2" t="s">
+      <c r="H77" s="36"/>
+      <c r="I77" s="22" t="s">
         <v>99</v>
       </c>
-      <c r="J76" s="2" t="s">
+      <c r="J77" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="K76" s="2" t="s">
+      <c r="K77" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="L76" s="3"/>
-      <c r="M76" s="26"/>
-      <c r="N76" s="26"/>
-      <c r="O76" s="26"/>
-      <c r="P76" s="3"/>
-      <c r="Q76" s="26"/>
-      <c r="R76" s="26"/>
-      <c r="S76" s="26"/>
-      <c r="T76" s="3"/>
-      <c r="U76" s="26"/>
-      <c r="V76" s="26"/>
-      <c r="W76" s="26"/>
-    </row>
-    <row r="77" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A77" s="25" t="s">
+      <c r="L77" s="3"/>
+      <c r="M77" s="34"/>
+      <c r="N77" s="34"/>
+      <c r="O77" s="34"/>
+      <c r="P77" s="3"/>
+      <c r="Q77" s="34"/>
+      <c r="R77" s="34"/>
+      <c r="S77" s="34"/>
+      <c r="T77" s="3"/>
+      <c r="U77" s="34"/>
+      <c r="V77" s="34"/>
+      <c r="W77" s="34"/>
+    </row>
+    <row r="78" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A78" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="B77" s="25" t="s">
+      <c r="B78" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="C77" s="25" t="s">
+      <c r="C78" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="D77" s="3"/>
-      <c r="E77" s="25" t="s">
+      <c r="D78" s="36"/>
+      <c r="E78" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="F77" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="G77" s="25" t="s">
+      <c r="F78" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="G78" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="25" t="s">
+      <c r="H78" s="36"/>
+      <c r="I78" s="37" t="s">
         <v>109</v>
       </c>
-      <c r="J77" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="K77" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="L77" s="3"/>
-      <c r="M77" s="3"/>
-      <c r="N77" s="3"/>
-      <c r="O77" s="3"/>
-      <c r="P77" s="3"/>
-      <c r="Q77" s="3"/>
-      <c r="R77" s="3"/>
-      <c r="S77" s="3"/>
-      <c r="T77" s="3"/>
-      <c r="U77" s="3"/>
-      <c r="V77" s="3"/>
-      <c r="W77" s="3"/>
-    </row>
-    <row r="78" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A78" s="3"/>
-      <c r="B78" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C78" s="25" t="s">
-        <v>120</v>
-      </c>
-      <c r="D78" s="3"/>
-      <c r="E78" s="3"/>
-      <c r="F78" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="G78" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-      <c r="J78" s="25" t="s">
+      <c r="J78" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="K78" s="25" t="s">
+      <c r="K78" s="37" t="s">
         <v>214</v>
       </c>
       <c r="L78" s="3"/>
@@ -4258,25 +4315,25 @@
       <c r="W78" s="3"/>
     </row>
     <row r="79" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A79" s="3"/>
-      <c r="B79" s="25" t="s">
-        <v>148</v>
-      </c>
-      <c r="C79" s="25" t="s">
+      <c r="A79" s="36"/>
+      <c r="B79" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="C79" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="D79" s="3"/>
-      <c r="E79" s="3"/>
-      <c r="F79" s="25" t="s">
+      <c r="D79" s="36"/>
+      <c r="E79" s="36"/>
+      <c r="F79" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="G79" s="25" t="s">
+      <c r="G79" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-      <c r="J79" s="3"/>
-      <c r="K79" s="3"/>
+      <c r="H79" s="36"/>
+      <c r="I79" s="36"/>
+      <c r="J79" s="36"/>
+      <c r="K79" s="36"/>
       <c r="L79" s="3"/>
       <c r="M79" s="3"/>
       <c r="N79" s="3"/>
@@ -4291,21 +4348,21 @@
       <c r="W79" s="3"/>
     </row>
     <row r="80" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A80" s="3"/>
-      <c r="B80" s="25" t="s">
-        <v>210</v>
-      </c>
-      <c r="C80" s="25" t="s">
-        <v>211</v>
-      </c>
-      <c r="D80" s="3"/>
-      <c r="E80" s="3"/>
-      <c r="F80" s="3"/>
-      <c r="G80" s="3"/>
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-      <c r="J80" s="3"/>
-      <c r="K80" s="3"/>
+      <c r="A80" s="36"/>
+      <c r="B80" s="37" t="s">
+        <v>151</v>
+      </c>
+      <c r="C80" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="D80" s="36"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="36"/>
+      <c r="G80" s="36"/>
+      <c r="H80" s="36"/>
+      <c r="I80" s="36"/>
+      <c r="J80" s="36"/>
+      <c r="K80" s="36"/>
       <c r="L80" s="3"/>
       <c r="M80" s="3"/>
       <c r="N80" s="3"/>
@@ -4320,21 +4377,21 @@
       <c r="W80" s="3"/>
     </row>
     <row r="81" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A81" s="3"/>
-      <c r="B81" s="25" t="s">
+      <c r="A81" s="36"/>
+      <c r="B81" s="37" t="s">
         <v>213</v>
       </c>
-      <c r="C81" s="25" t="s">
+      <c r="C81" s="37" t="s">
         <v>214</v>
       </c>
-      <c r="D81" s="3"/>
-      <c r="E81" s="3"/>
-      <c r="F81" s="3"/>
-      <c r="G81" s="3"/>
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-      <c r="J81" s="3"/>
-      <c r="K81" s="3"/>
+      <c r="D81" s="36"/>
+      <c r="E81" s="36"/>
+      <c r="F81" s="36"/>
+      <c r="G81" s="36"/>
+      <c r="H81" s="36"/>
+      <c r="I81" s="36"/>
+      <c r="J81" s="36"/>
+      <c r="K81" s="36"/>
       <c r="L81" s="3"/>
       <c r="M81" s="3"/>
       <c r="N81" s="3"/>
@@ -4374,15 +4431,15 @@
       <c r="W82" s="3"/>
     </row>
     <row r="83" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A83" s="24" t="s">
-        <v>215</v>
-      </c>
-      <c r="B83" s="3"/>
-      <c r="C83" s="3"/>
-      <c r="D83" s="3"/>
-      <c r="E83" s="3"/>
-      <c r="F83" s="3"/>
-      <c r="G83" s="3"/>
+      <c r="A83" s="35" t="s">
+        <v>216</v>
+      </c>
+      <c r="B83" s="36"/>
+      <c r="C83" s="36"/>
+      <c r="D83" s="36"/>
+      <c r="E83" s="36"/>
+      <c r="F83" s="36"/>
+      <c r="G83" s="36"/>
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
       <c r="J83" s="3"/>
@@ -4401,60 +4458,60 @@
       <c r="W83" s="3"/>
     </row>
     <row r="84" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A84" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="B84" s="2" t="s">
+      <c r="A84" s="22" t="s">
+        <v>217</v>
+      </c>
+      <c r="B84" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="C84" s="2" t="s">
+      <c r="C84" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="D84" s="3"/>
-      <c r="E84" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="F84" s="2" t="s">
+      <c r="D84" s="36"/>
+      <c r="E84" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="F84" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="G84" s="2" t="s">
+      <c r="G84" s="22" t="s">
         <v>107</v>
       </c>
       <c r="H84" s="3"/>
-      <c r="I84" s="26"/>
-      <c r="J84" s="26"/>
-      <c r="K84" s="26"/>
+      <c r="I84" s="34"/>
+      <c r="J84" s="34"/>
+      <c r="K84" s="34"/>
       <c r="L84" s="3"/>
-      <c r="M84" s="26"/>
-      <c r="N84" s="26"/>
-      <c r="O84" s="26"/>
+      <c r="M84" s="34"/>
+      <c r="N84" s="34"/>
+      <c r="O84" s="34"/>
       <c r="P84" s="3"/>
-      <c r="Q84" s="26"/>
-      <c r="R84" s="26"/>
-      <c r="S84" s="26"/>
+      <c r="Q84" s="34"/>
+      <c r="R84" s="34"/>
+      <c r="S84" s="34"/>
       <c r="T84" s="3"/>
-      <c r="U84" s="26"/>
-      <c r="V84" s="26"/>
-      <c r="W84" s="26"/>
+      <c r="U84" s="34"/>
+      <c r="V84" s="34"/>
+      <c r="W84" s="34"/>
     </row>
     <row r="85" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A85" s="25" t="s">
+      <c r="A85" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="B85" s="25" t="s">
+      <c r="B85" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="C85" s="25" t="s">
+      <c r="C85" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="D85" s="3"/>
-      <c r="E85" s="25" t="s">
-        <v>218</v>
-      </c>
-      <c r="F85" s="25" t="s">
+      <c r="D85" s="36"/>
+      <c r="E85" s="37" t="s">
         <v>219</v>
       </c>
-      <c r="G85" s="25" t="s">
+      <c r="F85" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="G85" s="37" t="s">
         <v>111</v>
       </c>
       <c r="H85" s="3"/>
@@ -4475,20 +4532,20 @@
       <c r="W85" s="3"/>
     </row>
     <row r="86" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A86" s="3"/>
-      <c r="B86" s="25" t="s">
-        <v>212</v>
-      </c>
-      <c r="C86" s="25" t="s">
+      <c r="A86" s="36"/>
+      <c r="B86" s="37" t="s">
+        <v>215</v>
+      </c>
+      <c r="C86" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="D86" s="3"/>
-      <c r="E86" s="3"/>
-      <c r="F86" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="G86" s="25" t="s">
+      <c r="D86" s="36"/>
+      <c r="E86" s="36"/>
+      <c r="F86" s="37" t="s">
         <v>221</v>
+      </c>
+      <c r="G86" s="37" t="s">
+        <v>222</v>
       </c>
       <c r="H86" s="3"/>
       <c r="I86" s="3"/>
@@ -4508,20 +4565,20 @@
       <c r="W86" s="3"/>
     </row>
     <row r="87" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A87" s="3"/>
-      <c r="B87" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="C87" s="25" t="s">
+      <c r="A87" s="36"/>
+      <c r="B87" s="37" t="s">
+        <v>220</v>
+      </c>
+      <c r="C87" s="37" t="s">
         <v>111</v>
       </c>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="F87" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="G87" s="25" t="s">
-        <v>222</v>
+      <c r="D87" s="36"/>
+      <c r="E87" s="36"/>
+      <c r="F87" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="G87" s="37" t="s">
+        <v>223</v>
       </c>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
@@ -4541,19 +4598,19 @@
       <c r="W87" s="3"/>
     </row>
     <row r="88" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A88" s="3"/>
-      <c r="B88" s="25" t="s">
-        <v>220</v>
-      </c>
-      <c r="C88" s="25" t="s">
+      <c r="A88" s="36"/>
+      <c r="B88" s="37" t="s">
         <v>221</v>
       </c>
-      <c r="D88" s="3"/>
-      <c r="E88" s="3"/>
-      <c r="F88" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="G88" s="25" t="s">
+      <c r="C88" s="37" t="s">
+        <v>222</v>
+      </c>
+      <c r="D88" s="36"/>
+      <c r="E88" s="36"/>
+      <c r="F88" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="G88" s="37" t="s">
         <v>116</v>
       </c>
       <c r="H88" s="3"/>
@@ -4574,17 +4631,17 @@
       <c r="W88" s="3"/>
     </row>
     <row r="89" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A89" s="3"/>
-      <c r="B89" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="C89" s="25" t="s">
-        <v>222</v>
-      </c>
-      <c r="D89" s="3"/>
-      <c r="E89" s="3"/>
-      <c r="F89" s="3"/>
-      <c r="G89" s="3"/>
+      <c r="A89" s="36"/>
+      <c r="B89" s="37" t="s">
+        <v>186</v>
+      </c>
+      <c r="C89" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="D89" s="36"/>
+      <c r="E89" s="36"/>
+      <c r="F89" s="36"/>
+      <c r="G89" s="36"/>
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
       <c r="J89" s="3"/>
@@ -4603,17 +4660,17 @@
       <c r="W89" s="3"/>
     </row>
     <row r="90" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A90" s="3"/>
-      <c r="B90" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="C90" s="25" t="s">
+      <c r="A90" s="36"/>
+      <c r="B90" s="37" t="s">
+        <v>163</v>
+      </c>
+      <c r="C90" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="D90" s="3"/>
-      <c r="E90" s="3"/>
-      <c r="F90" s="3"/>
-      <c r="G90" s="3"/>
+      <c r="D90" s="36"/>
+      <c r="E90" s="36"/>
+      <c r="F90" s="36"/>
+      <c r="G90" s="36"/>
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
       <c r="J90" s="3"/>
@@ -4657,8 +4714,8 @@
       <c r="W91" s="3"/>
     </row>
     <row r="92" customFormat="false" ht="34" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A92" s="24" t="s">
-        <v>223</v>
+      <c r="A92" s="32" t="s">
+        <v>224</v>
       </c>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -4685,7 +4742,7 @@
     </row>
     <row r="93" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="2" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="B93" s="2" t="s">
         <v>106</v>
@@ -4695,7 +4752,7 @@
       </c>
       <c r="D93" s="3"/>
       <c r="E93" s="2" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>106</v>
@@ -4705,66 +4762,66 @@
       </c>
       <c r="H93" s="3"/>
       <c r="I93" s="2" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="J93" s="2" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="K93" s="2" t="s">
         <v>107</v>
       </c>
       <c r="L93" s="2" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="M93" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="N93" s="26"/>
-      <c r="O93" s="26"/>
+      <c r="N93" s="34"/>
+      <c r="O93" s="34"/>
       <c r="P93" s="3"/>
-      <c r="Q93" s="26"/>
-      <c r="R93" s="26"/>
-      <c r="S93" s="26"/>
+      <c r="Q93" s="34"/>
+      <c r="R93" s="34"/>
+      <c r="S93" s="34"/>
       <c r="T93" s="3"/>
-      <c r="U93" s="26"/>
-      <c r="V93" s="26"/>
-      <c r="W93" s="26"/>
+      <c r="U93" s="34"/>
+      <c r="V93" s="34"/>
+      <c r="W93" s="34"/>
     </row>
     <row r="94" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A94" s="25" t="s">
+      <c r="A94" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="B94" s="25" t="s">
-        <v>229</v>
-      </c>
-      <c r="C94" s="25" t="s">
+      <c r="B94" s="33" t="s">
         <v>230</v>
       </c>
+      <c r="C94" s="33" t="s">
+        <v>231</v>
+      </c>
       <c r="D94" s="3"/>
-      <c r="E94" s="25" t="s">
+      <c r="E94" s="33" t="s">
         <v>109</v>
       </c>
-      <c r="F94" s="25" t="s">
-        <v>160</v>
-      </c>
-      <c r="G94" s="25" t="s">
+      <c r="F94" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="G94" s="33" t="s">
         <v>116</v>
       </c>
       <c r="H94" s="3"/>
-      <c r="I94" s="25" t="s">
-        <v>231</v>
-      </c>
-      <c r="J94" s="25" t="s">
+      <c r="I94" s="33" t="s">
         <v>232</v>
       </c>
-      <c r="K94" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="L94" s="27" t="n">
+      <c r="J94" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="K94" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="L94" s="38" t="n">
         <v>0</v>
       </c>
-      <c r="M94" s="25" t="s">
-        <v>233</v>
+      <c r="M94" s="33" t="s">
+        <v>234</v>
       </c>
       <c r="N94" s="3"/>
       <c r="O94" s="3"/>
@@ -4779,35 +4836,35 @@
     </row>
     <row r="95" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="3"/>
-      <c r="B95" s="25" t="s">
-        <v>232</v>
-      </c>
-      <c r="C95" s="25" t="s">
-        <v>150</v>
+      <c r="B95" s="33" t="s">
+        <v>233</v>
+      </c>
+      <c r="C95" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
-      <c r="F95" s="25" t="s">
-        <v>183</v>
-      </c>
-      <c r="G95" s="25" t="s">
-        <v>150</v>
+      <c r="F95" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="G95" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="H95" s="3"/>
-      <c r="I95" s="25" t="s">
-        <v>234</v>
-      </c>
-      <c r="J95" s="25" t="s">
+      <c r="I95" s="33" t="s">
         <v>235</v>
       </c>
-      <c r="K95" s="25" t="s">
-        <v>150</v>
-      </c>
-      <c r="L95" s="27" t="n">
+      <c r="J95" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="K95" s="33" t="s">
+        <v>153</v>
+      </c>
+      <c r="L95" s="38" t="n">
         <v>20</v>
       </c>
-      <c r="M95" s="25" t="s">
-        <v>236</v>
+      <c r="M95" s="33" t="s">
+        <v>237</v>
       </c>
       <c r="N95" s="3"/>
       <c r="O95" s="3"/>
@@ -4822,33 +4879,33 @@
     </row>
     <row r="96" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="3"/>
-      <c r="B96" s="25" t="s">
-        <v>235</v>
-      </c>
-      <c r="C96" s="25" t="s">
-        <v>150</v>
+      <c r="B96" s="33" t="s">
+        <v>236</v>
+      </c>
+      <c r="C96" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
-      <c r="F96" s="25" t="s">
-        <v>237</v>
-      </c>
-      <c r="G96" s="25" t="s">
+      <c r="F96" s="33" t="s">
+        <v>238</v>
+      </c>
+      <c r="G96" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H96" s="3"/>
       <c r="I96" s="3"/>
-      <c r="J96" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="K96" s="25" t="s">
+      <c r="J96" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="K96" s="33" t="s">
         <v>111</v>
       </c>
-      <c r="L96" s="25" t="s">
-        <v>239</v>
-      </c>
-      <c r="M96" s="25" t="s">
+      <c r="L96" s="33" t="s">
         <v>240</v>
+      </c>
+      <c r="M96" s="33" t="s">
+        <v>241</v>
       </c>
       <c r="N96" s="3"/>
       <c r="O96" s="3"/>
@@ -4863,33 +4920,33 @@
     </row>
     <row r="97" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="3"/>
-      <c r="B97" s="25" t="s">
-        <v>241</v>
-      </c>
-      <c r="C97" s="25" t="s">
+      <c r="B97" s="33" t="s">
         <v>242</v>
+      </c>
+      <c r="C97" s="33" t="s">
+        <v>243</v>
       </c>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
-      <c r="F97" s="25" t="s">
-        <v>219</v>
-      </c>
-      <c r="G97" s="25" t="s">
+      <c r="F97" s="33" t="s">
+        <v>220</v>
+      </c>
+      <c r="G97" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H97" s="3"/>
       <c r="I97" s="3"/>
-      <c r="J97" s="25" t="s">
-        <v>243</v>
-      </c>
-      <c r="K97" s="25" t="s">
+      <c r="J97" s="33" t="s">
         <v>244</v>
       </c>
-      <c r="L97" s="25" t="s">
+      <c r="K97" s="33" t="s">
         <v>245</v>
       </c>
-      <c r="M97" s="25" t="s">
+      <c r="L97" s="33" t="s">
         <v>246</v>
+      </c>
+      <c r="M97" s="33" t="s">
+        <v>247</v>
       </c>
       <c r="N97" s="3"/>
       <c r="O97" s="3"/>
@@ -4904,18 +4961,18 @@
     </row>
     <row r="98" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="3"/>
-      <c r="B98" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="C98" s="25" t="s">
-        <v>150</v>
+      <c r="B98" s="33" t="s">
+        <v>248</v>
+      </c>
+      <c r="C98" s="33" t="s">
+        <v>153</v>
       </c>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-      <c r="F98" s="25" t="s">
-        <v>248</v>
-      </c>
-      <c r="G98" s="25" t="s">
+      <c r="F98" s="33" t="s">
+        <v>249</v>
+      </c>
+      <c r="G98" s="33" t="s">
         <v>111</v>
       </c>
       <c r="H98" s="3"/>
@@ -4937,11 +4994,11 @@
     </row>
     <row r="99" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="3"/>
-      <c r="B99" s="25" t="s">
-        <v>238</v>
-      </c>
-      <c r="C99" s="25" t="s">
-        <v>249</v>
+      <c r="B99" s="33" t="s">
+        <v>239</v>
+      </c>
+      <c r="C99" s="33" t="s">
+        <v>250</v>
       </c>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
@@ -4966,11 +5023,11 @@
     </row>
     <row r="100" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="3"/>
-      <c r="B100" s="25" t="s">
-        <v>250</v>
-      </c>
-      <c r="C100" s="25" t="s">
+      <c r="B100" s="33" t="s">
         <v>251</v>
+      </c>
+      <c r="C100" s="33" t="s">
+        <v>252</v>
       </c>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
@@ -6392,163 +6449,163 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="28.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="34.3" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="25" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="8" t="s">
+      <c r="A3" s="26" t="s">
         <v>91</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="26" t="s">
         <v>92</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="8" t="s">
+      <c r="D3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E3" s="8" t="s">
+      <c r="E3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="8" t="s">
+      <c r="F3" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="8" t="s">
+      <c r="G3" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="8" t="s">
+      <c r="H3" s="26" t="s">
         <v>93</v>
       </c>
       <c r="I3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="27" t="s">
         <v>91</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="28" t="s">
         <v>94</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="28" t="s">
         <v>25</v>
       </c>
-      <c r="D4" s="10" t="s">
+      <c r="D4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E4" s="10" t="s">
+      <c r="E4" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="F4" s="10" t="s">
+      <c r="F4" s="28" t="s">
         <v>95</v>
       </c>
-      <c r="G4" s="10" t="s">
+      <c r="G4" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="H4" s="10" t="s">
+      <c r="H4" s="28" t="s">
         <v>96</v>
       </c>
       <c r="I4" s="7"/>
     </row>
     <row r="5" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="26" t="s">
         <v>97</v>
       </c>
-      <c r="B5" s="8" t="s">
+      <c r="B5" s="26" t="s">
         <v>98</v>
       </c>
-      <c r="C5" s="8" t="s">
+      <c r="C5" s="26" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="8" t="s">
+      <c r="D5" s="26" t="s">
         <v>17</v>
       </c>
-      <c r="E5" s="8" t="s">
+      <c r="E5" s="26" t="s">
         <v>22</v>
       </c>
-      <c r="F5" s="8" t="s">
+      <c r="F5" s="26" t="s">
         <v>99</v>
       </c>
-      <c r="G5" s="8" t="s">
+      <c r="G5" s="26" t="s">
         <v>18</v>
       </c>
-      <c r="H5" s="8" t="s">
+      <c r="H5" s="26" t="s">
         <v>96</v>
       </c>
       <c r="I5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="9" t="s">
+      <c r="A6" s="27" t="s">
         <v>97</v>
       </c>
-      <c r="B6" s="10" t="s">
+      <c r="B6" s="28" t="s">
         <v>100</v>
       </c>
-      <c r="C6" s="10" t="s">
+      <c r="C6" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="D6" s="10" t="s">
+      <c r="D6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="E6" s="10" t="s">
+      <c r="E6" s="28" t="s">
         <v>22</v>
       </c>
-      <c r="F6" s="10" t="s">
+      <c r="F6" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="10" t="s">
+      <c r="G6" s="28" t="s">
         <v>33</v>
       </c>
-      <c r="H6" s="10" t="s">
+      <c r="H6" s="28" t="s">
         <v>17</v>
       </c>
       <c r="I6" s="7"/>
@@ -6628,82 +6685,82 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="22" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
       <c r="I1" s="3"/>
     </row>
-    <row r="2" customFormat="false" ht="28.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="4" t="s">
+    <row r="2" customFormat="false" ht="35.1" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="23" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="24" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="6" t="s">
+      <c r="E2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="F2" s="6" t="s">
+      <c r="F2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="6" t="s">
+      <c r="G2" s="25" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="6" t="s">
+      <c r="H2" s="25" t="s">
         <v>12</v>
       </c>
       <c r="I2" s="7"/>
     </row>
     <row r="3" customFormat="false" ht="17" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="11" t="s">
+      <c r="A3" s="29" t="s">
         <v>101</v>
       </c>
-      <c r="B3" s="11" t="s">
+      <c r="B3" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="C3" s="11" t="s">
+      <c r="C3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="D3" s="11" t="s">
+      <c r="D3" s="29" t="s">
         <v>103</v>
       </c>
-      <c r="E3" s="11" t="s">
+      <c r="E3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="F3" s="11" t="s">
+      <c r="F3" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="G3" s="11" t="s">
+      <c r="G3" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="H3" s="11" t="s">
+      <c r="H3" s="29" t="s">
         <v>104</v>
       </c>
       <c r="I3" s="3"/>
